--- a/Plan_8sem_vol_definitivo_con_cardio.xlsx
+++ b/Plan_8sem_vol_definitivo_con_cardio.xlsx
@@ -9215,35 +9215,35 @@
         <v/>
       </c>
       <c r="C73" s="77">
-        <f t="array" ref="C73:C73">SUM(($B$3:$B$63="Espalda")*IFERROR(VALUE(LEFT(C$3:C$63,FIND(" ",C$3:C$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(C25,FIND(" ",C25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C26,FIND(" ",C26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C28,FIND(" ",C28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C51,FIND(" ",C51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C52,FIND(" ",C52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C53,FIND(" ",C53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D73" s="77">
-        <f t="array" ref="D73:D73">SUM(($B$3:$B$63="Espalda")*IFERROR(VALUE(LEFT(D$3:D$63,FIND(" ",D$3:D$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(D25,FIND(" ",D25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D26,FIND(" ",D26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D28,FIND(" ",D28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D51,FIND(" ",D51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D52,FIND(" ",D52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D53,FIND(" ",D53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E73" s="77">
-        <f t="array" ref="E73:E73">SUM(($B$3:$B$63="Espalda")*IFERROR(VALUE(LEFT(E$3:E$63,FIND(" ",E$3:E$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(E25,FIND(" ",E25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E26,FIND(" ",E26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E28,FIND(" ",E28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E51,FIND(" ",E51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E52,FIND(" ",E52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E53,FIND(" ",E53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F73" s="77">
-        <f t="array" ref="F73:F73">SUM(($B$3:$B$63="Espalda")*IFERROR(VALUE(LEFT(F$3:F$63,FIND(" ",F$3:F$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(F25,FIND(" ",F25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F26,FIND(" ",F26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F28,FIND(" ",F28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F51,FIND(" ",F51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F52,FIND(" ",F52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F53,FIND(" ",F53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G73" s="77">
-        <f t="array" ref="G73:G73">SUM(($B$3:$B$63="Espalda")*IFERROR(VALUE(LEFT(G$3:G$63,FIND(" ",G$3:G$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(G25,FIND(" ",G25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G26,FIND(" ",G26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G28,FIND(" ",G28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G51,FIND(" ",G51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G52,FIND(" ",G52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G53,FIND(" ",G53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H73" s="77">
-        <f t="array" ref="H73:H73">SUM(($B$3:$B$63="Espalda")*IFERROR(VALUE(LEFT(H$3:H$63,FIND(" ",H$3:H$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(H25,FIND(" ",H25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H26,FIND(" ",H26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H28,FIND(" ",H28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H51,FIND(" ",H51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H52,FIND(" ",H52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H53,FIND(" ",H53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I73" s="77">
-        <f t="array" ref="I73:I73">SUM(($B$3:$B$63="Espalda")*IFERROR(VALUE(LEFT(I$3:I$63,FIND(" ",I$3:I$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(I25,FIND(" ",I25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I26,FIND(" ",I26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I28,FIND(" ",I28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I51,FIND(" ",I51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I52,FIND(" ",I52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I53,FIND(" ",I53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J73" s="77">
-        <f t="array" ref="J73:J73">SUM(($B$3:$B$63="Espalda")*IFERROR(VALUE(LEFT(J$3:J$63,FIND(" ",J$3:J$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(J25,FIND(" ",J25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J26,FIND(" ",J26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J28,FIND(" ",J28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J51,FIND(" ",J51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J52,FIND(" ",J52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J53,FIND(" ",J53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K73" s="77" t="n"/>
@@ -9259,35 +9259,35 @@
         <v/>
       </c>
       <c r="C74" s="77">
-        <f t="array" ref="C74:C74">SUM(($B$3:$B$63="Pecho")*IFERROR(VALUE(LEFT(C$3:C$63,FIND(" ",C$3:C$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(C16,FIND(" ",C16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C18,FIND(" ",C18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C50,FIND(" ",C50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D74" s="77">
-        <f t="array" ref="D74:D74">SUM(($B$3:$B$63="Pecho")*IFERROR(VALUE(LEFT(D$3:D$63,FIND(" ",D$3:D$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(D16,FIND(" ",D16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D18,FIND(" ",D18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D50,FIND(" ",D50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E74" s="77">
-        <f t="array" ref="E74:E74">SUM(($B$3:$B$63="Pecho")*IFERROR(VALUE(LEFT(E$3:E$63,FIND(" ",E$3:E$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(E16,FIND(" ",E16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E18,FIND(" ",E18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E50,FIND(" ",E50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F74" s="77">
-        <f t="array" ref="F74:F74">SUM(($B$3:$B$63="Pecho")*IFERROR(VALUE(LEFT(F$3:F$63,FIND(" ",F$3:F$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(F16,FIND(" ",F16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F18,FIND(" ",F18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F50,FIND(" ",F50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G74" s="77">
-        <f t="array" ref="G74:G74">SUM(($B$3:$B$63="Pecho")*IFERROR(VALUE(LEFT(G$3:G$63,FIND(" ",G$3:G$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(G16,FIND(" ",G16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G18,FIND(" ",G18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G50,FIND(" ",G50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H74" s="77">
-        <f t="array" ref="H74:H74">SUM(($B$3:$B$63="Pecho")*IFERROR(VALUE(LEFT(H$3:H$63,FIND(" ",H$3:H$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(H16,FIND(" ",H16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H18,FIND(" ",H18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H50,FIND(" ",H50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I74" s="77">
-        <f t="array" ref="I74:I74">SUM(($B$3:$B$63="Pecho")*IFERROR(VALUE(LEFT(I$3:I$63,FIND(" ",I$3:I$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(I16,FIND(" ",I16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I18,FIND(" ",I18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I50,FIND(" ",I50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J74" s="77">
-        <f t="array" ref="J74:J74">SUM(($B$3:$B$63="Pecho")*IFERROR(VALUE(LEFT(J$3:J$63,FIND(" ",J$3:J$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(J16,FIND(" ",J16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J18,FIND(" ",J18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J50,FIND(" ",J50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K74" s="77" t="n"/>
@@ -9303,35 +9303,35 @@
         <v/>
       </c>
       <c r="C75" s="77">
-        <f t="array" ref="C75:C75">SUM(($B$3:$B$63="Hombro lat.")*IFERROR(VALUE(LEFT(C$3:C$63,FIND(" ",C$3:C$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(C6,FIND(" ",C6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C8,FIND(" ",C8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C27,FIND(" ",C27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C47,FIND(" ",C47&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D75" s="77">
-        <f t="array" ref="D75:D75">SUM(($B$3:$B$63="Hombro lat.")*IFERROR(VALUE(LEFT(D$3:D$63,FIND(" ",D$3:D$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(D6,FIND(" ",D6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D8,FIND(" ",D8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D27,FIND(" ",D27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D47,FIND(" ",D47&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E75" s="77">
-        <f t="array" ref="E75:E75">SUM(($B$3:$B$63="Hombro lat.")*IFERROR(VALUE(LEFT(E$3:E$63,FIND(" ",E$3:E$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(E6,FIND(" ",E6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E8,FIND(" ",E8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E27,FIND(" ",E27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E47,FIND(" ",E47&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F75" s="77">
-        <f t="array" ref="F75:F75">SUM(($B$3:$B$63="Hombro lat.")*IFERROR(VALUE(LEFT(F$3:F$63,FIND(" ",F$3:F$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(F6,FIND(" ",F6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F8,FIND(" ",F8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F27,FIND(" ",F27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F47,FIND(" ",F47&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G75" s="77">
-        <f t="array" ref="G75:G75">SUM(($B$3:$B$63="Hombro lat.")*IFERROR(VALUE(LEFT(G$3:G$63,FIND(" ",G$3:G$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(G6,FIND(" ",G6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G8,FIND(" ",G8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G27,FIND(" ",G27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G47,FIND(" ",G47&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H75" s="77">
-        <f t="array" ref="H75:H75">SUM(($B$3:$B$63="Hombro lat.")*IFERROR(VALUE(LEFT(H$3:H$63,FIND(" ",H$3:H$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(H6,FIND(" ",H6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H8,FIND(" ",H8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H27,FIND(" ",H27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H47,FIND(" ",H47&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I75" s="77">
-        <f t="array" ref="I75:I75">SUM(($B$3:$B$63="Hombro lat.")*IFERROR(VALUE(LEFT(I$3:I$63,FIND(" ",I$3:I$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(I6,FIND(" ",I6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I8,FIND(" ",I8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I27,FIND(" ",I27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I47,FIND(" ",I47&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J75" s="77">
-        <f t="array" ref="J75:J75">SUM(($B$3:$B$63="Hombro lat.")*IFERROR(VALUE(LEFT(J$3:J$63,FIND(" ",J$3:J$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(J6,FIND(" ",J6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J8,FIND(" ",J8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J27,FIND(" ",J27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J47,FIND(" ",J47&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K75" s="77" t="n"/>
@@ -9347,35 +9347,35 @@
         <v/>
       </c>
       <c r="C76" s="77">
-        <f t="array" ref="C76:C76">SUM(($B$3:$B$63="Hombro post.")*IFERROR(VALUE(LEFT(C$3:C$63,FIND(" ",C$3:C$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(C30,FIND(" ",C30&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D76" s="77">
-        <f t="array" ref="D76:D76">SUM(($B$3:$B$63="Hombro post.")*IFERROR(VALUE(LEFT(D$3:D$63,FIND(" ",D$3:D$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(D30,FIND(" ",D30&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E76" s="77">
-        <f t="array" ref="E76:E76">SUM(($B$3:$B$63="Hombro post.")*IFERROR(VALUE(LEFT(E$3:E$63,FIND(" ",E$3:E$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(E30,FIND(" ",E30&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F76" s="77">
-        <f t="array" ref="F76:F76">SUM(($B$3:$B$63="Hombro post.")*IFERROR(VALUE(LEFT(F$3:F$63,FIND(" ",F$3:F$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(F30,FIND(" ",F30&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G76" s="77">
-        <f t="array" ref="G76:G76">SUM(($B$3:$B$63="Hombro post.")*IFERROR(VALUE(LEFT(G$3:G$63,FIND(" ",G$3:G$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(G30,FIND(" ",G30&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H76" s="77">
-        <f t="array" ref="H76:H76">SUM(($B$3:$B$63="Hombro post.")*IFERROR(VALUE(LEFT(H$3:H$63,FIND(" ",H$3:H$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(H30,FIND(" ",H30&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I76" s="77">
-        <f t="array" ref="I76:I76">SUM(($B$3:$B$63="Hombro post.")*IFERROR(VALUE(LEFT(I$3:I$63,FIND(" ",I$3:I$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(I30,FIND(" ",I30&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J76" s="77">
-        <f t="array" ref="J76:J76">SUM(($B$3:$B$63="Hombro post.")*IFERROR(VALUE(LEFT(J$3:J$63,FIND(" ",J$3:J$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(J30,FIND(" ",J30&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K76" s="77" t="n"/>
@@ -9391,35 +9391,35 @@
         <v/>
       </c>
       <c r="C77" s="77">
-        <f t="array" ref="C77:C77">SUM(($B$3:$B$63="Bíceps")*IFERROR(VALUE(LEFT(C$3:C$63,FIND(" ",C$3:C$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(C29,FIND(" ",C29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C31,FIND(" ",C31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C49,FIND(" ",C49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D77" s="77">
-        <f t="array" ref="D77:D77">SUM(($B$3:$B$63="Bíceps")*IFERROR(VALUE(LEFT(D$3:D$63,FIND(" ",D$3:D$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(D29,FIND(" ",D29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D31,FIND(" ",D31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D49,FIND(" ",D49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E77" s="77">
-        <f t="array" ref="E77:E77">SUM(($B$3:$B$63="Bíceps")*IFERROR(VALUE(LEFT(E$3:E$63,FIND(" ",E$3:E$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(E29,FIND(" ",E29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E31,FIND(" ",E31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E49,FIND(" ",E49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F77" s="77">
-        <f t="array" ref="F77:F77">SUM(($B$3:$B$63="Bíceps")*IFERROR(VALUE(LEFT(F$3:F$63,FIND(" ",F$3:F$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(F29,FIND(" ",F29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F31,FIND(" ",F31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F49,FIND(" ",F49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G77" s="77">
-        <f t="array" ref="G77:G77">SUM(($B$3:$B$63="Bíceps")*IFERROR(VALUE(LEFT(G$3:G$63,FIND(" ",G$3:G$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(G29,FIND(" ",G29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G31,FIND(" ",G31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G49,FIND(" ",G49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H77" s="77">
-        <f t="array" ref="H77:H77">SUM(($B$3:$B$63="Bíceps")*IFERROR(VALUE(LEFT(H$3:H$63,FIND(" ",H$3:H$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(H29,FIND(" ",H29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H31,FIND(" ",H31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H49,FIND(" ",H49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I77" s="77">
-        <f t="array" ref="I77:I77">SUM(($B$3:$B$63="Bíceps")*IFERROR(VALUE(LEFT(I$3:I$63,FIND(" ",I$3:I$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(I29,FIND(" ",I29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I31,FIND(" ",I31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I49,FIND(" ",I49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J77" s="77">
-        <f t="array" ref="J77:J77">SUM(($B$3:$B$63="Bíceps")*IFERROR(VALUE(LEFT(J$3:J$63,FIND(" ",J$3:J$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(J29,FIND(" ",J29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J31,FIND(" ",J31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J49,FIND(" ",J49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K77" s="77" t="n"/>
@@ -9435,35 +9435,35 @@
         <v/>
       </c>
       <c r="C78" s="77">
-        <f t="array" ref="C78:C78">SUM(($B$3:$B$63="Tríceps")*IFERROR(VALUE(LEFT(C$3:C$63,FIND(" ",C$3:C$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(C17,FIND(" ",C17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C19,FIND(" ",C19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C46,FIND(" ",C46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C48,FIND(" ",C48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D78" s="77">
-        <f t="array" ref="D78:D78">SUM(($B$3:$B$63="Tríceps")*IFERROR(VALUE(LEFT(D$3:D$63,FIND(" ",D$3:D$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(D17,FIND(" ",D17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D19,FIND(" ",D19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D46,FIND(" ",D46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D48,FIND(" ",D48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E78" s="77">
-        <f t="array" ref="E78:E78">SUM(($B$3:$B$63="Tríceps")*IFERROR(VALUE(LEFT(E$3:E$63,FIND(" ",E$3:E$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(E17,FIND(" ",E17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E19,FIND(" ",E19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E46,FIND(" ",E46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E48,FIND(" ",E48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F78" s="77">
-        <f t="array" ref="F78:F78">SUM(($B$3:$B$63="Tríceps")*IFERROR(VALUE(LEFT(F$3:F$63,FIND(" ",F$3:F$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(F17,FIND(" ",F17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F19,FIND(" ",F19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F46,FIND(" ",F46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F48,FIND(" ",F48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G78" s="77">
-        <f t="array" ref="G78:G78">SUM(($B$3:$B$63="Tríceps")*IFERROR(VALUE(LEFT(G$3:G$63,FIND(" ",G$3:G$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(G17,FIND(" ",G17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G19,FIND(" ",G19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G46,FIND(" ",G46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G48,FIND(" ",G48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H78" s="77">
-        <f t="array" ref="H78:H78">SUM(($B$3:$B$63="Tríceps")*IFERROR(VALUE(LEFT(H$3:H$63,FIND(" ",H$3:H$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(H17,FIND(" ",H17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H19,FIND(" ",H19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H46,FIND(" ",H46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H48,FIND(" ",H48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I78" s="77">
-        <f t="array" ref="I78:I78">SUM(($B$3:$B$63="Tríceps")*IFERROR(VALUE(LEFT(I$3:I$63,FIND(" ",I$3:I$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(I17,FIND(" ",I17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I19,FIND(" ",I19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I46,FIND(" ",I46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I48,FIND(" ",I48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J78" s="77">
-        <f t="array" ref="J78:J78">SUM(($B$3:$B$63="Tríceps")*IFERROR(VALUE(LEFT(J$3:J$63,FIND(" ",J$3:J$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(J17,FIND(" ",J17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J19,FIND(" ",J19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J46,FIND(" ",J46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J48,FIND(" ",J48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K78" s="77" t="n"/>
@@ -9479,35 +9479,35 @@
         <v/>
       </c>
       <c r="C79" s="77">
-        <f t="array" ref="C79:C79">SUM(($B$3:$B$63="Isquios")*IFERROR(VALUE(LEFT(C$3:C$63,FIND(" ",C$3:C$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(C12,FIND(" ",C12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C40,FIND(" ",C40&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D79" s="77">
-        <f t="array" ref="D79:D79">SUM(($B$3:$B$63="Isquios")*IFERROR(VALUE(LEFT(D$3:D$63,FIND(" ",D$3:D$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(D12,FIND(" ",D12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D40,FIND(" ",D40&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E79" s="77">
-        <f t="array" ref="E79:E79">SUM(($B$3:$B$63="Isquios")*IFERROR(VALUE(LEFT(E$3:E$63,FIND(" ",E$3:E$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(E12,FIND(" ",E12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E40,FIND(" ",E40&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F79" s="77">
-        <f t="array" ref="F79:F79">SUM(($B$3:$B$63="Isquios")*IFERROR(VALUE(LEFT(F$3:F$63,FIND(" ",F$3:F$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(F12,FIND(" ",F12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F40,FIND(" ",F40&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G79" s="77">
-        <f t="array" ref="G79:G79">SUM(($B$3:$B$63="Isquios")*IFERROR(VALUE(LEFT(G$3:G$63,FIND(" ",G$3:G$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(G12,FIND(" ",G12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G40,FIND(" ",G40&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H79" s="77">
-        <f t="array" ref="H79:H79">SUM(($B$3:$B$63="Isquios")*IFERROR(VALUE(LEFT(H$3:H$63,FIND(" ",H$3:H$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(H12,FIND(" ",H12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H40,FIND(" ",H40&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I79" s="77">
-        <f t="array" ref="I79:I79">SUM(($B$3:$B$63="Isquios")*IFERROR(VALUE(LEFT(I$3:I$63,FIND(" ",I$3:I$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(I12,FIND(" ",I12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I40,FIND(" ",I40&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J79" s="77">
-        <f t="array" ref="J79:J79">SUM(($B$3:$B$63="Isquios")*IFERROR(VALUE(LEFT(J$3:J$63,FIND(" ",J$3:J$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(J12,FIND(" ",J12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J40,FIND(" ",J40&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K79" s="77" t="n"/>
@@ -9523,35 +9523,35 @@
         <v/>
       </c>
       <c r="C80" s="77">
-        <f t="array" ref="C80:C80">SUM(($B$3:$B$63="Abs")*IFERROR(VALUE(LEFT(C$3:C$63,FIND(" ",C$3:C$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(C20,FIND(" ",C20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C60,FIND(" ",C60&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D80" s="77">
-        <f t="array" ref="D80:D80">SUM(($B$3:$B$63="Abs")*IFERROR(VALUE(LEFT(D$3:D$63,FIND(" ",D$3:D$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(D20,FIND(" ",D20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D60,FIND(" ",D60&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E80" s="77">
-        <f t="array" ref="E80:E80">SUM(($B$3:$B$63="Abs")*IFERROR(VALUE(LEFT(E$3:E$63,FIND(" ",E$3:E$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(E20,FIND(" ",E20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E60,FIND(" ",E60&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F80" s="77">
-        <f t="array" ref="F80:F80">SUM(($B$3:$B$63="Abs")*IFERROR(VALUE(LEFT(F$3:F$63,FIND(" ",F$3:F$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(F20,FIND(" ",F20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F60,FIND(" ",F60&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G80" s="77">
-        <f t="array" ref="G80:G80">SUM(($B$3:$B$63="Abs")*IFERROR(VALUE(LEFT(G$3:G$63,FIND(" ",G$3:G$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(G20,FIND(" ",G20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G60,FIND(" ",G60&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H80" s="77">
-        <f t="array" ref="H80:H80">SUM(($B$3:$B$63="Abs")*IFERROR(VALUE(LEFT(H$3:H$63,FIND(" ",H$3:H$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(H20,FIND(" ",H20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H60,FIND(" ",H60&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I80" s="77">
-        <f t="array" ref="I80:I80">SUM(($B$3:$B$63="Abs")*IFERROR(VALUE(LEFT(I$3:I$63,FIND(" ",I$3:I$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(I20,FIND(" ",I20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I60,FIND(" ",I60&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J80" s="77">
-        <f t="array" ref="J80:J80">SUM(($B$3:$B$63="Abs")*IFERROR(VALUE(LEFT(J$3:J$63,FIND(" ",J$3:J$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(J20,FIND(" ",J20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J60,FIND(" ",J60&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K80" s="77" t="n"/>
@@ -9567,35 +9567,35 @@
         <v/>
       </c>
       <c r="C81" s="77">
-        <f t="array" ref="C81:C81">SUM(($B$3:$B$63="Gemelos")*IFERROR(VALUE(LEFT(C$3:C$63,FIND(" ",C$3:C$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(C11,FIND(" ",C11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C42,FIND(" ",C42&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D81" s="77">
-        <f t="array" ref="D81:D81">SUM(($B$3:$B$63="Gemelos")*IFERROR(VALUE(LEFT(D$3:D$63,FIND(" ",D$3:D$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(D11,FIND(" ",D11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D42,FIND(" ",D42&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E81" s="77">
-        <f t="array" ref="E81:E81">SUM(($B$3:$B$63="Gemelos")*IFERROR(VALUE(LEFT(E$3:E$63,FIND(" ",E$3:E$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(E11,FIND(" ",E11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E42,FIND(" ",E42&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F81" s="77">
-        <f t="array" ref="F81:F81">SUM(($B$3:$B$63="Gemelos")*IFERROR(VALUE(LEFT(F$3:F$63,FIND(" ",F$3:F$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(F11,FIND(" ",F11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F42,FIND(" ",F42&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G81" s="77">
-        <f t="array" ref="G81:G81">SUM(($B$3:$B$63="Gemelos")*IFERROR(VALUE(LEFT(G$3:G$63,FIND(" ",G$3:G$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(G11,FIND(" ",G11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G42,FIND(" ",G42&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H81" s="77">
-        <f t="array" ref="H81:H81">SUM(($B$3:$B$63="Gemelos")*IFERROR(VALUE(LEFT(H$3:H$63,FIND(" ",H$3:H$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(H11,FIND(" ",H11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H42,FIND(" ",H42&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I81" s="77">
-        <f t="array" ref="I81:I81">SUM(($B$3:$B$63="Gemelos")*IFERROR(VALUE(LEFT(I$3:I$63,FIND(" ",I$3:I$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(I11,FIND(" ",I11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I42,FIND(" ",I42&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J81" s="77">
-        <f t="array" ref="J81:J81">SUM(($B$3:$B$63="Gemelos")*IFERROR(VALUE(LEFT(J$3:J$63,FIND(" ",J$3:J$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(J11,FIND(" ",J11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J42,FIND(" ",J42&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K81" s="77" t="n"/>
@@ -9611,35 +9611,35 @@
         <v/>
       </c>
       <c r="C82" s="77">
-        <f t="array" ref="C82:C82">SUM(($B$3:$B$63="Aductores")*IFERROR(VALUE(LEFT(C$3:C$63,FIND(" ",C$3:C$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(C41,FIND(" ",C41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D82" s="77">
-        <f t="array" ref="D82:D82">SUM(($B$3:$B$63="Aductores")*IFERROR(VALUE(LEFT(D$3:D$63,FIND(" ",D$3:D$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(D41,FIND(" ",D41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E82" s="77">
-        <f t="array" ref="E82:E82">SUM(($B$3:$B$63="Aductores")*IFERROR(VALUE(LEFT(E$3:E$63,FIND(" ",E$3:E$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(E41,FIND(" ",E41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F82" s="77">
-        <f t="array" ref="F82:F82">SUM(($B$3:$B$63="Aductores")*IFERROR(VALUE(LEFT(F$3:F$63,FIND(" ",F$3:F$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(F41,FIND(" ",F41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G82" s="77">
-        <f t="array" ref="G82:G82">SUM(($B$3:$B$63="Aductores")*IFERROR(VALUE(LEFT(G$3:G$63,FIND(" ",G$3:G$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(G41,FIND(" ",G41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H82" s="77">
-        <f t="array" ref="H82:H82">SUM(($B$3:$B$63="Aductores")*IFERROR(VALUE(LEFT(H$3:H$63,FIND(" ",H$3:H$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(H41,FIND(" ",H41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I82" s="77">
-        <f t="array" ref="I82:I82">SUM(($B$3:$B$63="Aductores")*IFERROR(VALUE(LEFT(I$3:I$63,FIND(" ",I$3:I$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(I41,FIND(" ",I41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J82" s="77">
-        <f t="array" ref="J82:J82">SUM(($B$3:$B$63="Aductores")*IFERROR(VALUE(LEFT(J$3:J$63,FIND(" ",J$3:J$63&amp;" ")-1)),0))</f>
+        <f>IFERROR(VALUE(LEFT(J41,FIND(" ",J41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K82" s="77" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="K95" s="62" t="inlineStr">
         <is>
-          <t>No se hizo en S1: estímulo NUEVO [LÓGICA]. Entra en S4 (el viernes) solo si S2 y S3 cumplieron la regla; desde S5, martes y viernes. Sin Z3 en este bloque. En la regla de 48-72 h se mantiene si ya estaba introducida. Sillín alto (rodilla a 20-25° abajo), 85-90 rpm, sentado. 10 min fijos en el bloque; subir a 15 después del viaje, como novedad única.</t>
+          <t>No se hizo en S1: estímulo NUEVO [LÓGICA]. Entra en S4 (el viernes) solo si S2 y S3 cumplieron la regla; desde S5, martes y viernes. Sin Z3 en este bloque. Lo primero que se quita si hay brote. Sillín alto (rodilla a 20-25° abajo), 85-90 rpm, sentado. 10 min fijos en el bloque; subir a 15 después del viaje, como novedad única.</t>
         </is>
       </c>
     </row>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="K97" s="62" t="inlineStr">
         <is>
-          <t>Formato: minutos trotando / minutos andando. Niveles: N1 8×(1'/2') · N2 6×(2'/1') · N3 4×(4'/1') · N4 4×(5'/1') · N5 3×(8'/1') · N6 2×(12'/1') · N7 30' seguidos (después del viaje). N5 es un nivel intermedio para que el tramo continuo más largo no crezca más de un 50 % por nivel (5 → 8 → 12 min) [LÓGICA]. El calendario marca el máximo de cada semana; el nivel real sale del semáforo: Avanzar = +1, Mantener = el mismo, Retroceder = −1. Nivel nuevo solo si esa mañana estás igual o mejor. 5 min andando antes; llano y firme. Regla de carrera: Retroceder si pasas de 2/10 durante, no vuelves al nivel previo en ≤60 min o la mañana siguiente estás peor; Mantener si cumple pero el peor valor 24-48 h supera la referencia; Avanzar si cumple y el peor 24-48 h ≤ referencia [EVIDENCIA de uso: TREK Education, basada en Esculier; no comparada con otros umbrales]. Cadencia +5-10% opcional [EVIDENCIA mixta: Bramah 2019, serie de 12 corredores con mejora de dolor y función mantenida a 3 meses; Esculier 2018, sin beneficio extra sobre la educación].</t>
+          <t>Formato: minutos trotando / minutos andando. Niveles: N1 8×(1'/2') · N2 6×(2'/1') · N3 4×(4'/1') · N4 4×(5'/1') · N5 3×(8'/1') · N6 2×(12'/1'); después del viaje, N7 18' · N8 25' · N9 30' seguidos. Desde N4 el tramo continuo más largo crece como mucho un 50 % por nivel (5 → 8 → 12 → 18 → 25 → 30 min); de N1 a N3 se dobla porque los tramos son muy cortos [LÓGICA]. El calendario marca el máximo de cada semana; el nivel real sale del semáforo: Avanzar = +1, Mantener = el mismo, Retroceder = −1. Nivel nuevo solo si esa mañana estás igual o mejor. 5 min andando antes; llano y firme. Regla de carrera: Retroceder si pasas de 2/10 durante, no vuelves al nivel previo en ≤60 min o la mañana siguiente estás peor; Mantener si cumple pero el peor valor 24-48 h supera la referencia; Avanzar si cumple y el peor 24-48 h ≤ referencia [EVIDENCIA de uso: TREK Education, basada en Esculier; no comparada con otros umbrales]. Cadencia +5-10% opcional [EVIDENCIA mixta: Bramah 2019, serie de 12 corredores con mejora de dolor y función mantenida a 3 meses; Esculier 2018, sin beneficio extra sobre la educación].</t>
         </is>
       </c>
     </row>
@@ -10421,7 +10421,7 @@
     <row r="106" ht="30.75" customHeight="1" s="52">
       <c r="A106" s="67" t="inlineStr">
         <is>
-          <t>Novedades [LÓGICA]: una por día y validada a las 24 y 48 h antes de repetirla. Lunes: escalón o reps (prensa) · miércoles: nivel de carrera · viernes de S4: bici. Solo si esa mañana estás igual o mejor. El calendario marca el máximo de cada semana; el nivel real sale del semáforo: Avanzar = nivel +1 (sin pasar del calendario), Mantener = el mismo, Retroceder = nivel −1. Lo validado se repite: el jueves usa la profundidad del lunes y el domingo repite el nivel del miércoles.</t>
+          <t>Novedades [LÓGICA]: una por día y validada a las 24 y 48 h antes de repetirla. Lunes: escalón o reps (prensa) · miércoles: nivel de carrera · viernes de S4: bici. Solo si esa mañana estás igual o mejor que la referencia (la mañana del mismo día de la semana anterior; en S3, la primera medición de S2), no que el día anterior: así un empeoramiento lento también salta. El calendario marca el máximo de cada semana; el nivel real sale del semáforo: Avanzar = nivel +1 (sin pasar del calendario), Mantener = el mismo, Retroceder = nivel −1. Lo validado se repite: el jueves usa la profundidad del lunes y el domingo repite el nivel del miércoles.</t>
         </is>
       </c>
       <c r="B106" s="56" t="n"/>
@@ -10489,7 +10489,7 @@
     <row r="110" ht="18" customHeight="1" s="52">
       <c r="A110" s="67" t="inlineStr">
         <is>
-          <t>Retroceso y brote [LÓGICA]: si una medición falla, se retrocede solo la última novedad anterior a ella (p. ej., jueves bien y viernes peor → se retrocede la carrera del miércoles y el escalón se mantiene); si tras el retroceso la siguiente medición vuelve a fallar, se retrocede la novedad anterior, y así hacia atrás. Si falla sin ninguna novedad reciente, o fallan dos sesiones seguidas: 48-72 h solo isométricos (sentadilla española 5×45 s diaria), y la bici si ya estaba introducida; luego se retoma un escalón por debajo en todo.</t>
+          <t>Retroceso y brote [LÓGICA]: un dolor durante la sesión retrocede la escalera de esa sesión. Si una mañana sale peor, se retrocede la última novedad aún no validada (la que todavía no tiene en verde sus dos mañanas, 24 y 48 h; p. ej., jueves bien y viernes peor → se retrocede la carrera del miércoles y el escalón se mantiene); una novedad ya validada no se culpa. Si tras el retroceso vuelve a fallar, se retrocede la novedad anterior sin validar. Brote = un fallo sin ninguna novedad sin validar, o dos sesiones seguidas en Retroceder: lo primero que se quita es la bici; 48-72 h solo isométricos (sentadilla española 5×45 s diaria) y caminar, sin bici; luego se retoma un escalón por debajo en todo. La bici vuelve al nivel del calendario cuando lleves una semana entera en verde.</t>
         </is>
       </c>
       <c r="B110" s="56" t="n"/>
@@ -15290,7 +15290,7 @@
       <c r="C72" s="56" t="n"/>
       <c r="D72" s="57" t="n"/>
       <c r="E72" s="92">
-        <f t="array" ref="E72:E72">IF(COUNTIFS($C$5:$C$67,$A72,$I$5:$I$67,"&gt;=0")=0,"",MAX(IF(($C$5:$C$67=$A72)*ISNUMBER($I$5:$I$67),$I$5:$I$67)))</f>
+        <f>IF(COUNT(I5:I11)=0,"",MAX(I5:I11))</f>
         <v/>
       </c>
       <c r="F72" s="92">
@@ -15325,7 +15325,7 @@
       <c r="C73" s="56" t="n"/>
       <c r="D73" s="57" t="n"/>
       <c r="E73" s="92">
-        <f t="array" ref="E73:E73">IF(COUNTIFS($C$5:$C$67,$A73,$I$5:$I$67,"&gt;=0")=0,"",MAX(IF(($C$5:$C$67=$A73)*ISNUMBER($I$5:$I$67),$I$5:$I$67)))</f>
+        <f>IF(COUNT(I12:I18)=0,"",MAX(I12:I18))</f>
         <v/>
       </c>
       <c r="F73" s="92">
@@ -15360,7 +15360,7 @@
       <c r="C74" s="56" t="n"/>
       <c r="D74" s="57" t="n"/>
       <c r="E74" s="92">
-        <f t="array" ref="E74:E74">IF(COUNTIFS($C$5:$C$67,$A74,$I$5:$I$67,"&gt;=0")=0,"",MAX(IF(($C$5:$C$67=$A74)*ISNUMBER($I$5:$I$67),$I$5:$I$67)))</f>
+        <f>IF(COUNT(I19:I25)=0,"",MAX(I19:I25))</f>
         <v/>
       </c>
       <c r="F74" s="92">
@@ -15395,7 +15395,7 @@
       <c r="C75" s="56" t="n"/>
       <c r="D75" s="57" t="n"/>
       <c r="E75" s="92">
-        <f t="array" ref="E75:E75">IF(COUNTIFS($C$5:$C$67,$A75,$I$5:$I$67,"&gt;=0")=0,"",MAX(IF(($C$5:$C$67=$A75)*ISNUMBER($I$5:$I$67),$I$5:$I$67)))</f>
+        <f>IF(COUNT(I26:I32)=0,"",MAX(I26:I32))</f>
         <v/>
       </c>
       <c r="F75" s="92">
@@ -15430,7 +15430,7 @@
       <c r="C76" s="56" t="n"/>
       <c r="D76" s="57" t="n"/>
       <c r="E76" s="92">
-        <f t="array" ref="E76:E76">IF(COUNTIFS($C$5:$C$67,$A76,$I$5:$I$67,"&gt;=0")=0,"",MAX(IF(($C$5:$C$67=$A76)*ISNUMBER($I$5:$I$67),$I$5:$I$67)))</f>
+        <f>IF(COUNT(I33:I39)=0,"",MAX(I33:I39))</f>
         <v/>
       </c>
       <c r="F76" s="92">
@@ -15465,7 +15465,7 @@
       <c r="C77" s="56" t="n"/>
       <c r="D77" s="57" t="n"/>
       <c r="E77" s="92">
-        <f t="array" ref="E77:E77">IF(COUNTIFS($C$5:$C$67,$A77,$I$5:$I$67,"&gt;=0")=0,"",MAX(IF(($C$5:$C$67=$A77)*ISNUMBER($I$5:$I$67),$I$5:$I$67)))</f>
+        <f>IF(COUNT(I40:I46)=0,"",MAX(I40:I46))</f>
         <v/>
       </c>
       <c r="F77" s="92">
@@ -15500,7 +15500,7 @@
       <c r="C78" s="56" t="n"/>
       <c r="D78" s="57" t="n"/>
       <c r="E78" s="92">
-        <f t="array" ref="E78:E78">IF(COUNTIFS($C$5:$C$67,$A78,$I$5:$I$67,"&gt;=0")=0,"",MAX(IF(($C$5:$C$67=$A78)*ISNUMBER($I$5:$I$67),$I$5:$I$67)))</f>
+        <f>IF(COUNT(I47:I53)=0,"",MAX(I47:I53))</f>
         <v/>
       </c>
       <c r="F78" s="92">
@@ -15535,7 +15535,7 @@
       <c r="C79" s="56" t="n"/>
       <c r="D79" s="57" t="n"/>
       <c r="E79" s="92">
-        <f t="array" ref="E79:E79">IF(COUNTIFS($C$5:$C$67,$A79,$I$5:$I$67,"&gt;=0")=0,"",MAX(IF(($C$5:$C$67=$A79)*ISNUMBER($I$5:$I$67),$I$5:$I$67)))</f>
+        <f>IF(COUNT(I54:I60)=0,"",MAX(I54:I60))</f>
         <v/>
       </c>
       <c r="F79" s="92">
@@ -15570,7 +15570,7 @@
       <c r="C80" s="56" t="n"/>
       <c r="D80" s="57" t="n"/>
       <c r="E80" s="92">
-        <f t="array" ref="E80:E80">IF(COUNTIFS($C$5:$C$67,$A80,$I$5:$I$67,"&gt;=0")=0,"",MAX(IF(($C$5:$C$67=$A80)*ISNUMBER($I$5:$I$67),$I$5:$I$67)))</f>
+        <f>IF(COUNT(I61:I67)=0,"",MAX(I61:I67))</f>
         <v/>
       </c>
       <c r="F80" s="92">

--- a/Plan_8sem_vol_definitivo_con_cardio.xlsx
+++ b/Plan_8sem_vol_definitivo_con_cardio.xlsx
@@ -20,11 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -147,6 +146,11 @@
       <family val="0"/>
       <color rgb="FF222222"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF8A939C"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="10">
@@ -283,7 +287,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -596,6 +600,7 @@
     <xf numFmtId="9" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6092,13 +6097,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="36.05" customWidth="1" style="51" min="1" max="1"/>
     <col width="16.01" customWidth="1" style="51" min="2" max="2"/>
     <col width="13.04" customWidth="1" style="51" min="3" max="10"/>
     <col width="94.97" customWidth="1" style="51" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" style="52" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" s="52">
@@ -6112,6 +6118,11 @@
       <c r="A2" s="64" t="inlineStr">
         <is>
           <t>RIR1/0 = todas las series a RIR1 y la ÚLTIMA a RIR0 (si solo hay 1 serie, RIR0).  REHAB RODILLA S2-S8 en 2 días: lunes (touchdown + prensa) y jueves (sentadilla + búlgara), pesado y lento, tempo 3-1-3; D a RIR 2 y en su escalón de profundidad, I a RIR 1-2 y rango completo. Reps: ×12 S1 → ×10 S2-4 → ×8 S5-8 → ×6 tras el viaje. Una novedad por día (lunes profundidad/reps · miércoles carrera), solo si esa mañana estás igual o mejor. El calendario marca el máximo de cada semana: se progresa según el semáforo (Avanzar / Mantener / Retroceder) y la app prescribe con el nivel real. Reglas al final de la hoja; registro diario en «Seguimiento rodilla».</t>
+        </is>
+      </c>
+      <c r="L2" s="106" t="inlineStr">
+        <is>
+          <t>regla</t>
         </is>
       </c>
     </row>
@@ -6144,6 +6155,11 @@
       <c r="I4" s="56" t="n"/>
       <c r="J4" s="56" t="n"/>
       <c r="K4" s="57" t="n"/>
+      <c r="L4" s="106" t="inlineStr">
+        <is>
+          <t>sesion</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="27" customHeight="1" s="52">
       <c r="A5" s="66" t="inlineStr">
@@ -6201,6 +6217,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="L5" s="106" t="inlineStr">
+        <is>
+          <t>App (no tocar)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="52">
       <c r="A6" s="59" t="inlineStr">
@@ -6258,6 +6279,11 @@
           <t>Prioridad 1 · Polea altura muñeca/muslo en plano escapular (~30° adelante). Intercalar en superserie alterna con la abducción (máquina) para dar 3-4 min de descanso al deltoides antes de las mancuernas.</t>
         </is>
       </c>
+      <c r="L6" s="106" t="inlineStr">
+        <is>
+          <t>id=elev-laterales-polea</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="43.5" customHeight="1" s="52">
       <c r="A7" s="62" t="inlineStr">
@@ -6322,6 +6348,11 @@
           <t>Cadera: de pie, unilateral, en máquina; empieza por la D y sube carga cuando llegues a 15 con RIR 1-2. Cadera + rodilla combinadas = primera línea en los consensos de 2016 y 2018 [EVIDENCIA]. No cuenta como novedad: apenas carga la rodilla [LÓGICA]. Antes del rehab: sentadilla española 2-3×45 s.</t>
         </is>
       </c>
+      <c r="L7" s="106" t="inlineStr">
+        <is>
+          <t>id=abduccion-de-pie-unilateral-maquina</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="52">
       <c r="A8" s="59" t="inlineStr">
@@ -6379,6 +6410,11 @@
           <t>Prioridad 1 · Hacer tras el 1er bloque de la abducción (máquina) · Perfil en acortamiento, controlar bajada sin rebotar.</t>
         </is>
       </c>
+      <c r="L8" s="106" t="inlineStr">
+        <is>
+          <t>id=elev-laterales-mancuerna</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="43.5" customHeight="1" s="52">
       <c r="A9" s="62" t="inlineStr">
@@ -6437,6 +6473,11 @@
           <t>Control antes de la prensa. D a la profundidad YA validada (la de la semana anterior), I completa; tempo 2-0-2, RIR 3; pelvis nivelada y rodilla hacia el 2.º-4.º dedo. Hace de filtro: si la D pasa de 3/10 aquí, ese lunes no se sube escalón en la prensa [LÓGICA].</t>
         </is>
       </c>
+      <c r="L9" s="106" t="inlineStr">
+        <is>
+          <t>id=touchdown-squat;escalera=prensa:anterior</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="68.25" customHeight="1" s="52">
       <c r="A10" s="62" t="inlineStr">
@@ -6501,6 +6542,11 @@
           <t>Pesado y lento para el tendón [EVIDENCIA: Kongsgaard 2009; 1-2 veces/semana para mantenerlo: LÓGICA]. Tempo 3-1-3. D primero: RIR 2 y profundidad de su escalón. I: RIR 1-2, rango completo y mismas reps. Lunes = día de novedad (escalón o reps): solo si esa mañana estás igual o mejor y la touchdown no pasa de 3/10; si no, repite la semana anterior. En la sesión con novedad no cambies nada más (con escalón nuevo, mismo peso).</t>
         </is>
       </c>
+      <c r="L10" s="106" t="inlineStr">
+        <is>
+          <t>id=prensa-unil-pesado-y-lento-n-1;escalera=prensa</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="52">
       <c r="A11" s="59" t="inlineStr">
@@ -6558,6 +6604,11 @@
           <t>Prensa con pies abajo · Pausa estricta de 2 s en máximo estiramiento abajo (sin rebotar en el tendón de Aquiles) + rodilla semirrígida.</t>
         </is>
       </c>
+      <c r="L11" s="106" t="inlineStr">
+        <is>
+          <t>id=gemelos-prensa</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="52">
       <c r="A12" s="59" t="inlineStr">
@@ -6613,6 +6664,11 @@
       <c r="K12" s="62" t="inlineStr">
         <is>
           <t>Extensión de cadera · Rodillas con ligera flexión fija (~10-15°), subir empujando talones sin hiperextender zona lumbar.</t>
+        </is>
+      </c>
+      <c r="L12" s="106" t="inlineStr">
+        <is>
+          <t>id=hiperextensiones</t>
         </is>
       </c>
     </row>
@@ -6633,6 +6689,11 @@
       <c r="I14" s="56" t="n"/>
       <c r="J14" s="56" t="n"/>
       <c r="K14" s="57" t="n"/>
+      <c r="L14" s="106" t="inlineStr">
+        <is>
+          <t>sesion</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="27" customHeight="1" s="52">
       <c r="A15" s="66" t="inlineStr">
@@ -6690,6 +6751,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="L15" s="106" t="inlineStr">
+        <is>
+          <t>App (no tocar)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="52">
       <c r="A16" s="59" t="inlineStr">
@@ -6747,6 +6813,11 @@
           <t>Prioridad 4 (Haz clavicular) · Agarre ~1.3x ancho hombros y codos a 45–60° (plano escapular) para proteger hombro y codo.</t>
         </is>
       </c>
+      <c r="L16" s="106" t="inlineStr">
+        <is>
+          <t>id=press-inclinado-barra-30-40</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="52">
       <c r="A17" s="59" t="inlineStr">
@@ -6804,6 +6875,11 @@
           <t>Prioridad 2 (Tríceps) · Hombro a 0° pegado al costado (máxima palanca de cabeza larga sin estrés articular en codo).</t>
         </is>
       </c>
+      <c r="L17" s="106" t="inlineStr">
+        <is>
+          <t>id=extension-triceps-unil-polea</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="52">
       <c r="A18" s="59" t="inlineStr">
@@ -6861,6 +6937,11 @@
           <t>Prioridad 4 (Haz clavicular/esternal) · Asiento medio-bajo (manos altura clavícula/esternón sup.) · NO hiperextender húmeros detrás del torso al abrir para no irritar cápsula anterior del hombro.</t>
         </is>
       </c>
+      <c r="L18" s="106" t="inlineStr">
+        <is>
+          <t>id=contractora-pec-deck</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="52">
       <c r="A19" s="59" t="inlineStr">
@@ -6918,6 +6999,11 @@
           <t>Prioridad 2 (Tríceps en estiramiento) · Dejar que el codo apunte ligeramente hacia fuera (~20-30° plano escapular) para no forzar cápsula del hombro ni tendón olecraniano.</t>
         </is>
       </c>
+      <c r="L19" s="106" t="inlineStr">
+        <is>
+          <t>id=triceps-tras-nuca-unil-polea</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="52">
       <c r="A20" s="59" t="inlineStr">
@@ -6973,6 +7059,11 @@
       <c r="K20" s="62" t="inlineStr">
         <is>
           <t>Colgado con depresión escapular (activa dorsal) · Enrollar pelvis hacia costillas (retroversión). Usar straps si el agarre molesta al codo.</t>
+        </is>
+      </c>
+      <c r="L20" s="106" t="inlineStr">
+        <is>
+          <t>id=abs-colgado-retroversion</t>
         </is>
       </c>
     </row>
@@ -7018,6 +7109,11 @@
       <c r="I23" s="56" t="n"/>
       <c r="J23" s="56" t="n"/>
       <c r="K23" s="57" t="n"/>
+      <c r="L23" s="106" t="inlineStr">
+        <is>
+          <t>sesion</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="27" customHeight="1" s="52">
       <c r="A24" s="66" t="inlineStr">
@@ -7075,6 +7171,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="L24" s="106" t="inlineStr">
+        <is>
+          <t>App (no tocar)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="52">
       <c r="A25" s="59" t="inlineStr">
@@ -7132,6 +7233,11 @@
           <t>Prioridad 3 (Dorsal Bajo) · 1º fresco · Torso vertical, codos abiertos en plano frontal hasta ~90° · No encoger hombros.</t>
         </is>
       </c>
+      <c r="L25" s="106" t="inlineStr">
+        <is>
+          <t>id=jalon-ancho-plano-frontal</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="52">
       <c r="A26" s="59" t="inlineStr">
@@ -7189,6 +7295,11 @@
           <t>Plano transversal (Espalda Alta) · Codos abiertos y retracción escapular completa.</t>
         </is>
       </c>
+      <c r="L26" s="106" t="inlineStr">
+        <is>
+          <t>id=remo-gironda-abierto</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="52">
       <c r="A27" s="59" t="inlineStr">
@@ -7246,6 +7357,11 @@
           <t>Prioridad 1 (Hombro Lat.) · Sentado en banco a 75–80°, abducir en plano escapular (~30° adelante) sin rotar internamente el hombro.</t>
         </is>
       </c>
+      <c r="L27" s="106" t="inlineStr">
+        <is>
+          <t>id=laterales-sentado</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="52">
       <c r="A28" s="59" t="inlineStr">
@@ -7303,6 +7419,11 @@
           <t>Plano sagital (Dorsal Sup.) · Agarre neutro ancho hombros, llevar codos a los bolsillos cortando a 90° (protege codo/bíceps).</t>
         </is>
       </c>
+      <c r="L28" s="106" t="inlineStr">
+        <is>
+          <t>id=jalon-neutro</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="52">
       <c r="A29" s="59" t="inlineStr">
@@ -7360,6 +7481,11 @@
           <t>Prioridad 2 (Bíceps/Braquiorradial) · Agarre neutro (muy amigable para el codo). Bajar en 2-3 s y parar a ~15° de la extensión total para no sobrecargar tendón distal.</t>
         </is>
       </c>
+      <c r="L29" s="106" t="inlineStr">
+        <is>
+          <t>id=curl-martillo-scott</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="52">
       <c r="A30" s="59" t="inlineStr">
@@ -7417,6 +7543,11 @@
           <t>Salud Hombro / Transversal · Clave para centrar cabeza humeral y compensar presses.</t>
         </is>
       </c>
+      <c r="L30" s="106" t="inlineStr">
+        <is>
+          <t>id=posterior-polea</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="52">
       <c r="A31" s="59" t="inlineStr">
@@ -7472,6 +7603,11 @@
       <c r="K31" s="62" t="inlineStr">
         <is>
           <t>Prioridad 2 (Bíceps en estiramiento) · Hombro en extensión detrás del torso; no dejar que el hombro rote hacia delante al subir.</t>
+        </is>
+      </c>
+      <c r="L31" s="106" t="inlineStr">
+        <is>
+          <t>id=curl-bayesian</t>
         </is>
       </c>
     </row>
@@ -7492,6 +7628,11 @@
       <c r="I33" s="56" t="n"/>
       <c r="J33" s="56" t="n"/>
       <c r="K33" s="57" t="n"/>
+      <c r="L33" s="106" t="inlineStr">
+        <is>
+          <t>sesion</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="27" customHeight="1" s="52">
       <c r="A34" s="66" t="inlineStr">
@@ -7547,6 +7688,11 @@
       <c r="K34" s="66" t="inlineStr">
         <is>
           <t>Notas</t>
+        </is>
+      </c>
+      <c r="L34" s="106" t="inlineStr">
+        <is>
+          <t>App (no tocar)</t>
         </is>
       </c>
     </row>
@@ -7613,6 +7759,11 @@
           <t>Al empezar la sesión, tras la española 2-3×45 s y 2 series de aproximación. Mismo asiento y SIEMPRE rango fijo 90→45° (si el rango cambia, la comparación entre semanas no vale). Misma carga en las dos piernas (la que la I haga unas 10-15 reps), tempo 2-0-2, D primero, 3 min de descanso y luego la I; para si pasa de 3/10. Apunta carga y reps en «Seguimiento rodilla», que calcula la simetría. Objetivo ≥90% antes del balón [LÓGICA; el 90% viene de la vuelta al deporte tras LCA, no está validado en dolor femoropatelar: INCERTIDUMBRE]. Test en rango completo opcional en S8 y no en S7, para que sea la única novedad de su semana.</t>
         </is>
       </c>
+      <c r="L35" s="106" t="inlineStr">
+        <is>
+          <t>id=test-fuerza-extension-unilateral-en-maquina-90-45</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="43.5" customHeight="1" s="52">
       <c r="A36" s="62" t="inlineStr">
@@ -7675,6 +7826,11 @@
           <t>Tras el test (S2/S5/S7), carga por RIR. Tempo 3-1-3, RIR 2. Profundidad = la validada el lunes en la prensa. Postura habitual: un chasquido sin dolor no cambia nada; el apoyo ancho solo si te reduce el DOLOR [LÓGICA]. Antes del rehab (si no hay test): sentadilla española 2-3×45 s.</t>
         </is>
       </c>
+      <c r="L36" s="106" t="inlineStr">
+        <is>
+          <t>id=sentadilla-al-cajon-o-desde-pines-pesado-y-lento-n-2;escalera=prensa:sigue</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30.75" customHeight="1" s="52">
       <c r="A37" s="62" t="inlineStr">
@@ -7733,6 +7889,11 @@
           <t>D primero: RIR 2 y profundidad validada el lunes. I: RIR 1-2 y rango completo. Tempo 3-1-3. Alterna piernas, 60-90 s entre una y otra.</t>
         </is>
       </c>
+      <c r="L37" s="106" t="inlineStr">
+        <is>
+          <t>id=bulgarian-split-squat;escalera=prensa:sigue</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30.75" customHeight="1" s="52">
       <c r="A38" s="62" t="inlineStr">
@@ -7797,6 +7958,11 @@
           <t>Misma máquina que el lunes; empieza por la D. Va DESPUÉS de la búlgara, para no fatigar el glúteo medio antes del trabajo a una pierna [LÓGICA]. Lunes + jueves = 72-96 h entre sesiones de cadera.</t>
         </is>
       </c>
+      <c r="L38" s="106" t="inlineStr">
+        <is>
+          <t>id=abduccion-de-pie-unilateral-maquina</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="52">
       <c r="A39" s="62" t="inlineStr">
@@ -7854,6 +8020,11 @@
           <t>Sale del jueves desde S2: va el lunes, antes de la prensa [LÓGICA].</t>
         </is>
       </c>
+      <c r="L39" s="106" t="inlineStr">
+        <is>
+          <t>id=touchdown-squat</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="52">
       <c r="A40" s="59" t="inlineStr">
@@ -7911,6 +8082,11 @@
           <t>Isquios en estiramiento máximo (cadera a 90°) · Controlar fase excéntrica.</t>
         </is>
       </c>
+      <c r="L40" s="106" t="inlineStr">
+        <is>
+          <t>id=isquios-sentado</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="52">
       <c r="A41" s="59" t="inlineStr">
@@ -7968,6 +8144,11 @@
           <t>Plano transversal/frontal · Pausa de 1 s en apertura máxima sin dolor inguinal/rodilla.</t>
         </is>
       </c>
+      <c r="L41" s="106" t="inlineStr">
+        <is>
+          <t>id=aductores</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="52">
       <c r="A42" s="59" t="inlineStr">
@@ -8023,6 +8204,11 @@
       <c r="K42" s="62" t="inlineStr">
         <is>
           <t>Prensa con pies abajo · Pausa estricta de 2 s en máximo estiramiento abajo (sin rebote elástico).</t>
+        </is>
+      </c>
+      <c r="L42" s="106" t="inlineStr">
+        <is>
+          <t>id=gemelos-prensa</t>
         </is>
       </c>
     </row>
@@ -8043,6 +8229,11 @@
       <c r="I44" s="56" t="n"/>
       <c r="J44" s="56" t="n"/>
       <c r="K44" s="57" t="n"/>
+      <c r="L44" s="106" t="inlineStr">
+        <is>
+          <t>sesion</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="27" customHeight="1" s="52">
       <c r="A45" s="66" t="inlineStr">
@@ -8100,6 +8291,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="L45" s="106" t="inlineStr">
+        <is>
+          <t>App (no tocar)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="52">
       <c r="A46" s="59" t="inlineStr">
@@ -8157,6 +8353,11 @@
           <t>Prioridad 2 + Potenciación de codo · Hombro a -15° (extensión): máximo acortamiento de cabeza larga con torque nulo en flexión máxima de codo (calienta tendón para el francés).</t>
         </is>
       </c>
+      <c r="L46" s="106" t="inlineStr">
+        <is>
+          <t>id=triceps-conc-polea-15</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="52">
       <c r="A47" s="59" t="inlineStr">
@@ -8214,6 +8415,11 @@
           <t>Prioridad 1 (Hombro Lat.) · Polea a altura de muñeca/muslo, abducción en plano escapular.</t>
         </is>
       </c>
+      <c r="L47" s="106" t="inlineStr">
+        <is>
+          <t>id=laterales-polea</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="52">
       <c r="A48" s="59" t="inlineStr">
@@ -8271,6 +8477,11 @@
           <t>Prioridad 2 (Tríceps) · Agarre neutro (martillo) y brazos inclinados a ~100° hacia la cabeza: quita cizalla en epitróclea/olécranon y mantiene tensión constante.</t>
         </is>
       </c>
+      <c r="L48" s="106" t="inlineStr">
+        <is>
+          <t>id=press-frances-manc-banco-plano</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="52">
       <c r="A49" s="59" t="inlineStr">
@@ -8328,6 +8539,11 @@
           <t>Prioridad 2 (Bíceps rango medio) · Usar el agarre de la barra Z (ancho o estrecho) que resulte 100% libre de molestia en muñeca y codo.</t>
         </is>
       </c>
+      <c r="L49" s="106" t="inlineStr">
+        <is>
+          <t>id=curl-biceps-barra-z</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="52">
       <c r="A50" s="59" t="inlineStr">
@@ -8385,6 +8601,11 @@
           <t>Prioridad 4 (Haz clavicular) · 10/10 tras brazos: el agarre neutro y la trayectoria convergente ascendente aíslan el haz clavicular sin estrés en hombro ni codo.</t>
         </is>
       </c>
+      <c r="L50" s="106" t="inlineStr">
+        <is>
+          <t>id=press-maquina-neutro-ascendente</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="52">
       <c r="A51" s="59" t="inlineStr">
@@ -8442,6 +8663,11 @@
           <t>Plano sagital (Dorsal Sup.) · Usar STRAPS obligatoriamente para anular fatiga previa de bíceps y proteger codos.</t>
         </is>
       </c>
+      <c r="L51" s="106" t="inlineStr">
+        <is>
+          <t>id=dominada-neutra-dorsal</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="52">
       <c r="A52" s="59" t="inlineStr">
@@ -8499,6 +8725,11 @@
           <t>Plano sagital/híbrido (Dorsal Sup.) · Usar STRAPS, codos a ~30° hasta línea del torso.</t>
         </is>
       </c>
+      <c r="L52" s="106" t="inlineStr">
+        <is>
+          <t>id=remo-maquina-pecho-apoyado-30</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="52">
       <c r="A53" s="59" t="inlineStr">
@@ -8554,6 +8785,11 @@
       <c r="K53" s="62" t="inlineStr">
         <is>
           <t>Prioridad 3 (Dorsal Bajo) · De lado a la polea (con tobillera en muñeca o codo semirrígido) para aislar haz inferior sin usar bíceps ni codo · Sem 1-2 a RIR 1-2.</t>
+        </is>
+      </c>
+      <c r="L53" s="106" t="inlineStr">
+        <is>
+          <t>id=aduccion-unil-polea-alta-pull-in</t>
         </is>
       </c>
     </row>
@@ -8574,6 +8810,11 @@
       <c r="I55" s="56" t="n"/>
       <c r="J55" s="56" t="n"/>
       <c r="K55" s="57" t="n"/>
+      <c r="L55" s="106" t="inlineStr">
+        <is>
+          <t>sesion;nombreS1=Sábado/Domingo</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="27" customHeight="1" s="52">
       <c r="A56" s="66" t="inlineStr">
@@ -8631,6 +8872,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="L56" s="106" t="inlineStr">
+        <is>
+          <t>App (no tocar)</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="30.75" customHeight="1" s="52">
       <c r="A57" s="62" t="inlineStr">
@@ -8688,6 +8934,11 @@
           <t>Sale del sábado desde S2: la abducción va el lunes y el jueves en máquina; la pierna se concentra en 2 días [LÓGICA].</t>
         </is>
       </c>
+      <c r="L57" s="106" t="inlineStr">
+        <is>
+          <t>id=abduccion-unilateral</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="52">
       <c r="A58" s="62" t="inlineStr">
@@ -8745,6 +8996,11 @@
           <t>Sale del sábado desde S2: va el lunes, antes de la prensa [LÓGICA].</t>
         </is>
       </c>
+      <c r="L58" s="106" t="inlineStr">
+        <is>
+          <t>id=touchdown-squat</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="52">
       <c r="A59" s="62" t="inlineStr">
@@ -8802,6 +9058,11 @@
           <t>Sale del sábado desde S2: la pierna se concentra en el lunes y el jueves [LÓGICA].</t>
         </is>
       </c>
+      <c r="L59" s="106" t="inlineStr">
+        <is>
+          <t>id=bulgarian-split-squat</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="52">
       <c r="A60" s="59" t="inlineStr">
@@ -8855,6 +9116,11 @@
         </is>
       </c>
       <c r="K60" s="61" t="n"/>
+      <c r="L60" s="106" t="inlineStr">
+        <is>
+          <t>id=abs-wesley-banco</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30.75" customHeight="1" s="52">
       <c r="A61" s="59" t="inlineStr">
@@ -8919,6 +9185,11 @@
           <t>Postura: trapecio medio e inferior y deltoides posterior. Boca abajo en el banco, pulgar arriba, muy poco peso. RIR 3-4; no cuenta como serie de hipertrofia. Libro, p. 290.</t>
         </is>
       </c>
+      <c r="L61" s="106" t="inlineStr">
+        <is>
+          <t>id=elevacion-lateral-en-prono-t-mancuernas-banco</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30.75" customHeight="1" s="52">
       <c r="A62" s="59" t="inlineStr">
@@ -8983,6 +9254,11 @@
           <t>Codos pegados al cuerpo a 90°. RIR 3-4. Libro, p. 288.</t>
         </is>
       </c>
+      <c r="L62" s="106" t="inlineStr">
+        <is>
+          <t>id=rotacion-externa-con-banda-w</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="43.5" customHeight="1" s="52">
       <c r="A63" s="59" t="inlineStr">
@@ -9045,6 +9321,11 @@
       <c r="K63" s="61" t="inlineStr">
         <is>
           <t>Codo (cara externa). Antebrazo apoyado, palma abajo. Si ahora agarrar te duele: isométrico 4-5×30-45 s las 1-2 primeras semanas. Antes, test del nervio radial (libro, p. 323): si es positivo, se cambia por deslizamientos del nervio (p. 338). Dolor ≤3/10 y no peor al día siguiente. Libro, pp. 332-333.</t>
+        </is>
+      </c>
+      <c r="L63" s="106" t="inlineStr">
+        <is>
+          <t>id=curl-de-muneca-en-extension-mancuerna</t>
         </is>
       </c>
     </row>
@@ -9064,6 +9345,11 @@
       <c r="I64" s="56" t="n"/>
       <c r="J64" s="56" t="n"/>
       <c r="K64" s="57" t="n"/>
+      <c r="L64" s="106" t="inlineStr">
+        <is>
+          <t>regla</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="52"/>
     <row r="66" ht="19.5" customHeight="1" s="52">
@@ -9082,6 +9368,11 @@
       <c r="I66" s="56" t="n"/>
       <c r="J66" s="56" t="n"/>
       <c r="K66" s="57" t="n"/>
+      <c r="L66" s="106" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="30" customHeight="1" s="52">
       <c r="A67" s="73" t="inlineStr">
@@ -9099,6 +9390,11 @@
       <c r="I67" s="56" t="n"/>
       <c r="J67" s="56" t="n"/>
       <c r="K67" s="57" t="n"/>
+      <c r="L67" s="106" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="42" customHeight="1" s="52">
       <c r="A68" s="73" t="inlineStr">
@@ -9116,6 +9412,11 @@
       <c r="I68" s="56" t="n"/>
       <c r="J68" s="56" t="n"/>
       <c r="K68" s="57" t="n"/>
+      <c r="L68" s="106" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="42" customHeight="1" s="52">
       <c r="A69" s="73" t="inlineStr">
@@ -9133,6 +9434,11 @@
       <c r="I69" s="56" t="n"/>
       <c r="J69" s="56" t="n"/>
       <c r="K69" s="57" t="n"/>
+      <c r="L69" s="106" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="52"/>
     <row r="71" ht="19.5" customHeight="1" s="52">
@@ -9203,6 +9509,11 @@
           <t>Sem 8</t>
         </is>
       </c>
+      <c r="L72" s="106" t="inlineStr">
+        <is>
+          <t>grupos</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="52">
       <c r="A73" s="76" t="inlineStr">
@@ -9810,6 +10121,11 @@
           <t>Jalón ancho plano frontal (X) + Aducción unil. polea alta (V)</t>
         </is>
       </c>
+      <c r="L87" s="106" t="inlineStr">
+        <is>
+          <t>desglose=jalon-ancho-plano-frontal,aduccion-unil-polea-alta-pull-in</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="52">
       <c r="A88" s="76" t="inlineStr">
@@ -9858,6 +10174,11 @@
           <t>Jalón neutro bolsillos (X) + Dominada neutra (V) + Remo máq. 30° (V)</t>
         </is>
       </c>
+      <c r="L88" s="106" t="inlineStr">
+        <is>
+          <t>desglose=jalon-neutro,dominada-neutra-dorsal,remo-maquina-pecho-apoyado-30</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="52">
       <c r="A89" s="76" t="inlineStr">
@@ -9906,6 +10227,11 @@
           <t>Remo gironda abierto (X)</t>
         </is>
       </c>
+      <c r="L89" s="106" t="inlineStr">
+        <is>
+          <t>desglose=remo-gironda-abierto</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="52">
       <c r="A90" s="78" t="inlineStr">
@@ -9952,6 +10278,11 @@
       <c r="K90" s="80" t="inlineStr">
         <is>
           <t>Remo gironda abierto (X) + Posterior polea (X)</t>
+        </is>
+      </c>
+      <c r="L90" s="106" t="inlineStr">
+        <is>
+          <t>desglose=remo-gironda-abierto,posterior-polea</t>
         </is>
       </c>
     </row>
@@ -9973,6 +10304,11 @@
       <c r="I93" s="56" t="n"/>
       <c r="J93" s="56" t="n"/>
       <c r="K93" s="57" t="n"/>
+      <c r="L93" s="106" t="inlineStr">
+        <is>
+          <t>cardio</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="52">
       <c r="A94" s="75" t="inlineStr">
@@ -10030,6 +10366,11 @@
           <t>Pautas Biomecánicas Rodilla &amp; Intensidad</t>
         </is>
       </c>
+      <c r="L94" s="106" t="inlineStr">
+        <is>
+          <t>App (no tocar)</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="55.5" customHeight="1" s="52">
       <c r="A95" s="81" t="inlineStr">
@@ -10087,6 +10428,11 @@
           <t>No se hizo en S1: estímulo NUEVO [LÓGICA]. Entra en S4 (el viernes) solo si S2 y S3 cumplieron la regla; desde S5, martes y viernes. Sin Z3 en este bloque. Lo primero que se quita si hay brote. Sillín alto (rodilla a 20-25° abajo), 85-90 rpm, sentado. 10 min fijos en el bloque; subir a 15 después del viaje, como novedad única.</t>
         </is>
       </c>
+      <c r="L95" s="106" t="inlineStr">
+        <is>
+          <t>id=bici-z2-65-75-fc;sesion=M;bici</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="30.75" customHeight="1" s="52">
       <c r="A96" s="81" t="inlineStr">
@@ -10145,6 +10491,11 @@
           <t>S4: primera vez, solo si esa mañana estás igual o mejor; se valida con las mediciones del sábado y del domingo (el sábado no hay pierna). Ver la nota del martes.</t>
         </is>
       </c>
+      <c r="L96" s="106" t="inlineStr">
+        <is>
+          <t>id=bici-z2-sin-z3-en-este-bloque;sesion=V;bici</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="81" customHeight="1" s="52">
       <c r="A97" s="81" t="inlineStr">
@@ -10202,6 +10553,11 @@
           <t>Formato: minutos trotando / minutos andando. Niveles: N1 8×(1'/2') · N2 6×(2'/1') · N3 4×(4'/1') · N4 4×(5'/1') · N5 3×(8'/1') · N6 2×(12'/1'); después del viaje, N7 18' · N8 25' · N9 30' seguidos. Desde N4 el tramo continuo más largo crece como mucho un 50 % por nivel (5 → 8 → 12 → 18 → 25 → 30 min); de N1 a N3 se dobla porque los tramos son muy cortos [LÓGICA]. El calendario marca el máximo de cada semana; el nivel real sale del semáforo: Avanzar = +1, Mantener = el mismo, Retroceder = −1. Nivel nuevo solo si esa mañana estás igual o mejor. 5 min andando antes; llano y firme. Regla de carrera: Retroceder si pasas de 2/10 durante, no vuelves al nivel previo en ≤60 min o la mañana siguiente estás peor; Mantener si cumple pero el peor valor 24-48 h supera la referencia; Avanzar si cumple y el peor 24-48 h ≤ referencia [EVIDENCIA de uso: TREK Education, basada en Esculier; no comparada con otros umbrales]. Cadencia +5-10% opcional [EVIDENCIA mixta: Bramah 2019, serie de 12 corredores con mejora de dolor y función mantenida a 3 meses; Esculier 2018, sin beneficio extra sobre la educación].</t>
         </is>
       </c>
+      <c r="L97" s="106" t="inlineStr">
+        <is>
+          <t>id=andar-correr-en-llano;sesion=X;escalera=carrera</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="30.75" customHeight="1" s="52">
       <c r="A98" s="81" t="inlineStr">
@@ -10264,6 +10620,11 @@
       <c r="K98" s="62" t="inlineStr">
         <is>
           <t>Repite el nivel validado el miércoles. Si el miércoles no se cumplieron los criterios de entrada, esa semana no hay carrera: el domingo no se corre (como mucho, un paseo). Nunca dos días seguidos corriendo [LÓGICA]. El sábado no hay pierna: llegas descansado.</t>
+        </is>
+      </c>
+      <c r="L98" s="106" t="inlineStr">
+        <is>
+          <t>id=andar-correr-en-llano;sesion=D;titulo=Carrera;escalera=carrera:domingo</t>
         </is>
       </c>
     </row>
@@ -10329,6 +10690,11 @@
       <c r="K99" s="62" t="inlineStr">
         <is>
           <t>Entrada a la carrera (S2), con la regla de carrera: martes, paseo de 30 min a paso rápido (≤2/10, nivel previo en ≤60 min y el miércoles por la mañana no peor: el criterio 1 se evalúa solo con esa mañana, sin esperar a las 48 h); miércoles antes de correr, 10 touchdown con cada pierna y 20 saltitos a dos piernas (≤2/10). Si se cumplen los tres, 1.ª carrera ese miércoles (N1). Si no, esa semana no hay carrera (el domingo, como mucho, un paseo) y los criterios se repiten el miércoles siguiente [LÓGICA].</t>
+        </is>
+      </c>
+      <c r="L99" s="106" t="inlineStr">
+        <is>
+          <t>hitos</t>
         </is>
       </c>
     </row>
@@ -10349,6 +10715,11 @@
       <c r="I101" s="56" t="n"/>
       <c r="J101" s="56" t="n"/>
       <c r="K101" s="57" t="n"/>
+      <c r="L101" s="106" t="inlineStr">
+        <is>
+          <t>reglas-bloque</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="30.75" customHeight="1" s="52">
       <c r="A102" s="67" t="inlineStr">
@@ -11499,7 +11870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q110"/>
+  <dimension ref="A1:R110"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="51" min="1" max="1"/>
@@ -11517,6 +11888,7 @@
     <col width="10" customWidth="1" style="51" min="15" max="15"/>
     <col width="13" customWidth="1" style="51" min="16" max="16"/>
     <col width="42" customWidth="1" style="51" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" style="52" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1" s="52">
@@ -11674,6 +12046,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="R4" s="106" t="inlineStr">
+        <is>
+          <t>dias</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="27" customHeight="1" s="52">
       <c r="A5" s="85" t="n">
@@ -15134,7 +15511,7 @@
         <v/>
       </c>
       <c r="N66" s="92">
-        <f>IF(I68="","",I68)</f>
+        <f>""</f>
         <v/>
       </c>
       <c r="O66" s="92">
@@ -15186,11 +15563,11 @@
       <c r="K67" s="91" t="n"/>
       <c r="L67" s="91" t="n"/>
       <c r="M67" s="92">
-        <f>IF(I68="","",I68)</f>
+        <f>""</f>
         <v/>
       </c>
       <c r="N67" s="92">
-        <f>IF(I69="","",I69)</f>
+        <f>""</f>
         <v/>
       </c>
       <c r="O67" s="92">
@@ -15203,6 +15580,8 @@
       </c>
       <c r="Q67" s="94" t="n"/>
     </row>
+    <row r="68"/>
+    <row r="69"/>
     <row r="70" ht="19.5" customHeight="1" s="52">
       <c r="A70" s="65" t="inlineStr">
         <is>
@@ -15276,6 +15655,11 @@
       <c r="O71" s="56" t="n"/>
       <c r="P71" s="56" t="n"/>
       <c r="Q71" s="57" t="n"/>
+      <c r="R71" s="106" t="inlineStr">
+        <is>
+          <t>semanas</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="52">
       <c r="A72" s="86" t="inlineStr">
@@ -15617,6 +16001,11 @@
       <c r="O81" s="56" t="n"/>
       <c r="P81" s="56" t="n"/>
       <c r="Q81" s="57" t="n"/>
+      <c r="R81" s="106" t="inlineStr">
+        <is>
+          <t>aviso=s2</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="52">
       <c r="A82" s="101" t="inlineStr">
@@ -15643,6 +16032,11 @@
       <c r="O82" s="56" t="n"/>
       <c r="P82" s="56" t="n"/>
       <c r="Q82" s="57" t="n"/>
+      <c r="R82" s="106" t="inlineStr">
+        <is>
+          <t>aviso=s4</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="52">
       <c r="A83" s="101" t="inlineStr">
@@ -15669,6 +16063,11 @@
       <c r="O83" s="56" t="n"/>
       <c r="P83" s="56" t="n"/>
       <c r="Q83" s="57" t="n"/>
+      <c r="R83" s="106" t="inlineStr">
+        <is>
+          <t>aviso=chasquido</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="27.75" customHeight="1" s="52">
       <c r="A84" s="73" t="inlineStr">
@@ -15692,7 +16091,14 @@
       <c r="O84" s="56" t="n"/>
       <c r="P84" s="56" t="n"/>
       <c r="Q84" s="57" t="n"/>
-    </row>
+      <c r="R84" s="106" t="inlineStr">
+        <is>
+          <t>texto=resumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="85"/>
+    <row r="86"/>
     <row r="87" ht="19.5" customHeight="1" s="52">
       <c r="A87" s="65" t="inlineStr">
         <is>
@@ -15715,6 +16121,11 @@
       <c r="O87" s="56" t="n"/>
       <c r="P87" s="56" t="n"/>
       <c r="Q87" s="57" t="n"/>
+      <c r="R87" s="106" t="inlineStr">
+        <is>
+          <t>titulo=entrada</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="52">
       <c r="A88" s="84" t="inlineStr">
@@ -15793,6 +16204,11 @@
       <c r="O89" s="56" t="n"/>
       <c r="P89" s="56" t="n"/>
       <c r="Q89" s="57" t="n"/>
+      <c r="R89" s="106" t="inlineStr">
+        <is>
+          <t>entrada=walk;dia=martes</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="27" customHeight="1" s="52">
       <c r="A90" s="88" t="inlineStr">
@@ -15830,6 +16246,11 @@
       <c r="O90" s="56" t="n"/>
       <c r="P90" s="56" t="n"/>
       <c r="Q90" s="57" t="n"/>
+      <c r="R90" s="106" t="inlineStr">
+        <is>
+          <t>entrada=touchdown;dia=miércoles</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="27" customHeight="1" s="52">
       <c r="A91" s="88" t="inlineStr">
@@ -15867,6 +16288,11 @@
       <c r="O91" s="56" t="n"/>
       <c r="P91" s="56" t="n"/>
       <c r="Q91" s="57" t="n"/>
+      <c r="R91" s="106" t="inlineStr">
+        <is>
+          <t>entrada=hops;dia=miércoles</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="52">
       <c r="A92" s="101" t="inlineStr">
@@ -15893,7 +16319,14 @@
       <c r="O92" s="56" t="n"/>
       <c r="P92" s="56" t="n"/>
       <c r="Q92" s="57" t="n"/>
-    </row>
+      <c r="R92" s="106" t="inlineStr">
+        <is>
+          <t>entrada-resultado</t>
+        </is>
+      </c>
+    </row>
+    <row r="93"/>
+    <row r="94"/>
     <row r="95" ht="19.5" customHeight="1" s="52">
       <c r="A95" s="65" t="inlineStr">
         <is>
@@ -15916,6 +16349,11 @@
       <c r="O95" s="56" t="n"/>
       <c r="P95" s="56" t="n"/>
       <c r="Q95" s="57" t="n"/>
+      <c r="R95" s="106" t="inlineStr">
+        <is>
+          <t>titulo=fuerza</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="30" customHeight="1" s="52">
       <c r="A96" s="84" t="inlineStr">
@@ -16020,6 +16458,11 @@
       <c r="O97" s="56" t="n"/>
       <c r="P97" s="56" t="n"/>
       <c r="Q97" s="57" t="n"/>
+      <c r="R97" s="106" t="inlineStr">
+        <is>
+          <t>test=t1</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="52">
       <c r="A98" s="101" t="inlineStr">
@@ -16061,6 +16504,11 @@
       <c r="O98" s="56" t="n"/>
       <c r="P98" s="56" t="n"/>
       <c r="Q98" s="57" t="n"/>
+      <c r="R98" s="106" t="inlineStr">
+        <is>
+          <t>test=t2</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="52">
       <c r="A99" s="101" t="inlineStr">
@@ -16102,6 +16550,11 @@
       <c r="O99" s="56" t="n"/>
       <c r="P99" s="56" t="n"/>
       <c r="Q99" s="57" t="n"/>
+      <c r="R99" s="106" t="inlineStr">
+        <is>
+          <t>test=t3</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="52">
       <c r="A100" s="101" t="inlineStr">
@@ -16143,6 +16596,11 @@
       <c r="O100" s="56" t="n"/>
       <c r="P100" s="56" t="n"/>
       <c r="Q100" s="57" t="n"/>
+      <c r="R100" s="106" t="inlineStr">
+        <is>
+          <t>test=t4</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="39.75" customHeight="1" s="52">
       <c r="A101" s="73" t="inlineStr">
@@ -16166,7 +16624,13 @@
       <c r="O101" s="56" t="n"/>
       <c r="P101" s="56" t="n"/>
       <c r="Q101" s="57" t="n"/>
-    </row>
+      <c r="R101" s="106" t="inlineStr">
+        <is>
+          <t>texto=fuerza</t>
+        </is>
+      </c>
+    </row>
+    <row r="102"/>
     <row r="103" ht="19.5" customHeight="1" s="52">
       <c r="A103" s="65" t="inlineStr">
         <is>
@@ -16189,6 +16653,11 @@
       <c r="O103" s="56" t="n"/>
       <c r="P103" s="56" t="n"/>
       <c r="Q103" s="57" t="n"/>
+      <c r="R103" s="106" t="inlineStr">
+        <is>
+          <t>titulo=escalones</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="30" customHeight="1" s="52">
       <c r="A104" s="84" t="inlineStr">
@@ -16263,6 +16732,11 @@
       <c r="O105" s="56" t="n"/>
       <c r="P105" s="56" t="n"/>
       <c r="Q105" s="57" t="n"/>
+      <c r="R105" s="106" t="inlineStr">
+        <is>
+          <t>escalon=0</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="52">
       <c r="A106" s="86" t="inlineStr">
@@ -16286,6 +16760,11 @@
       <c r="O106" s="56" t="n"/>
       <c r="P106" s="56" t="n"/>
       <c r="Q106" s="57" t="n"/>
+      <c r="R106" s="106" t="inlineStr">
+        <is>
+          <t>escalon=1</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="52">
       <c r="A107" s="86" t="inlineStr">
@@ -16309,6 +16788,11 @@
       <c r="O107" s="56" t="n"/>
       <c r="P107" s="56" t="n"/>
       <c r="Q107" s="57" t="n"/>
+      <c r="R107" s="106" t="inlineStr">
+        <is>
+          <t>escalon=2</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="52">
       <c r="A108" s="86" t="inlineStr">
@@ -16332,6 +16816,11 @@
       <c r="O108" s="56" t="n"/>
       <c r="P108" s="56" t="n"/>
       <c r="Q108" s="57" t="n"/>
+      <c r="R108" s="106" t="inlineStr">
+        <is>
+          <t>escalon=3</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="52">
       <c r="A109" s="86" t="inlineStr">
@@ -16355,6 +16844,11 @@
       <c r="O109" s="56" t="n"/>
       <c r="P109" s="56" t="n"/>
       <c r="Q109" s="57" t="n"/>
+      <c r="R109" s="106" t="inlineStr">
+        <is>
+          <t>escalon=4</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="39.75" customHeight="1" s="52">
       <c r="A110" s="73" t="inlineStr">
@@ -16378,6 +16872,11 @@
       <c r="O110" s="56" t="n"/>
       <c r="P110" s="56" t="n"/>
       <c r="Q110" s="57" t="n"/>
+      <c r="R110" s="106" t="inlineStr">
+        <is>
+          <t>texto=escalones</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="116">
@@ -16498,16 +16997,6 @@
     <mergeCell ref="B71:D71"/>
     <mergeCell ref="G72:H72"/>
   </mergeCells>
-  <conditionalFormatting sqref="L5:L67">
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>L5="Sí"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J67">
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>AND($J5&lt;&gt;"",OR($J5&gt;3,AND($E5="Carrera (≤2/10)",$J5&gt;2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E82">
     <cfRule type="expression" rank="0" priority="6" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
       <formula>ISNUMBER(SEARCH("PEOR",E82))</formula>
@@ -16576,17 +17065,6 @@
       <formula>L100="Sí"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P67">
-    <cfRule type="expression" priority="23" dxfId="0">
-      <formula>P5="Retroceder"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="24" dxfId="3">
-      <formula>P5="Mantener"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="25" dxfId="1">
-      <formula>P5="Avanzar"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E81">
     <cfRule type="expression" priority="26" dxfId="2">
       <formula>ISNUMBER(SEARCH("REPITE",E81))</formula>
@@ -16595,12 +17073,33 @@
       <formula>ISNUMBER(SEARCH("estable",E81))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L5:L67">
+    <cfRule type="expression" priority="26" dxfId="2">
+      <formula>L5="Sí"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J67">
+    <cfRule type="expression" priority="27" dxfId="2">
+      <formula>AND($J5&lt;&gt;"",OR($J5&gt;3,AND($E5="Carrera (≤2/10)",$J5&gt;2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P5:P67">
+    <cfRule type="expression" priority="28" dxfId="0">
+      <formula>P5="Retroceder"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="29" dxfId="3">
+      <formula>P5="Mantener"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" dxfId="1">
+      <formula>P5="Avanzar"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="G5:H67 J5:J67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Escala 0-10" error="Pon un número entero de 0 a 10." type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="G5:G67 H5:H67 J5:J67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Escala 0-10" error="Pon un número entero de 0 a 10." type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
-    <dataValidation sqref="K5:L67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="K5:K67 L5:L67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Sí,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Plan_8sem_vol_definitivo_con_cardio.xlsx
+++ b/Plan_8sem_vol_definitivo_con_cardio.xlsx
@@ -6097,7 +6097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="36.05" customWidth="1" style="51" min="1" max="1"/>
@@ -7023,226 +7023,226 @@
       </c>
       <c r="D20" s="61" t="inlineStr">
         <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="E20" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="F20" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="G20" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="H20" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="I20" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="J20" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="K20" s="62" t="inlineStr">
+        <is>
+          <t>Colgado con depresión escapular (activa dorsal) · Enrollar pelvis hacia costillas (retroversión). Usar straps si el agarre molesta al codo.</t>
+        </is>
+      </c>
+      <c r="L20" s="106" t="inlineStr">
+        <is>
+          <t>id=abs-colgado-retroversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="52">
+      <c r="A21" s="59" t="inlineStr">
+        <is>
+          <t>Abs en máquina (crunch)</t>
+        </is>
+      </c>
+      <c r="B21" s="59" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E21" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F21" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G21" s="61" t="inlineStr">
+        <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="E20" s="61" t="inlineStr">
+      <c r="H21" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F20" s="61" t="inlineStr">
+      <c r="I21" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G20" s="61" t="inlineStr">
+      <c r="J21" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H20" s="61" t="inlineStr">
-        <is>
-          <t>4 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I20" s="61" t="inlineStr">
-        <is>
-          <t>4 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J20" s="61" t="inlineStr">
-        <is>
-          <t>5 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K20" s="62" t="inlineStr">
-        <is>
-          <t>Colgado con depresión escapular (activa dorsal) · Enrollar pelvis hacia costillas (retroversión). Usar straps si el agarre molesta al codo.</t>
-        </is>
-      </c>
-      <c r="L20" s="106" t="inlineStr">
-        <is>
-          <t>id=abs-colgado-retroversion</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="52">
-      <c r="A21" s="59" t="n"/>
-      <c r="B21" s="59" t="n"/>
-      <c r="C21" s="61" t="n"/>
-      <c r="D21" s="61" t="n"/>
-      <c r="E21" s="61" t="n"/>
-      <c r="F21" s="61" t="n"/>
-      <c r="G21" s="61" t="n"/>
-      <c r="H21" s="61" t="n"/>
-      <c r="I21" s="61" t="n"/>
-      <c r="J21" s="61" t="n"/>
-      <c r="K21" s="61" t="n"/>
+      <c r="K21" s="62" t="inlineStr">
+        <is>
+          <t>Desde S2 recoge las series del colgado (que se queda en 1) · Pies enganchados y cadera fija: enrollar el tronco llevando costillas hacia pelvis, sin tirar con los brazos ni flexionar la cadera. Bajar controlado, 2 s.</t>
+        </is>
+      </c>
+      <c r="L21" s="106" t="inlineStr">
+        <is>
+          <t>id=abs-maquina-crunch</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="52">
-      <c r="A22" s="69" t="n"/>
-      <c r="B22" s="69" t="n"/>
-      <c r="C22" s="70" t="n"/>
-      <c r="D22" s="70" t="n"/>
-      <c r="E22" s="70" t="n"/>
-      <c r="F22" s="70" t="n"/>
-      <c r="G22" s="70" t="n"/>
-      <c r="H22" s="70" t="n"/>
-      <c r="I22" s="70" t="n"/>
-      <c r="J22" s="70" t="n"/>
-      <c r="K22" s="70" t="n"/>
+      <c r="A22" s="59" t="n"/>
+      <c r="B22" s="59" t="n"/>
+      <c r="C22" s="61" t="n"/>
+      <c r="D22" s="61" t="n"/>
+      <c r="E22" s="61" t="n"/>
+      <c r="F22" s="61" t="n"/>
+      <c r="G22" s="61" t="n"/>
+      <c r="H22" s="61" t="n"/>
+      <c r="I22" s="61" t="n"/>
+      <c r="J22" s="61" t="n"/>
+      <c r="K22" s="61" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="52">
-      <c r="A23" s="65" t="inlineStr">
+      <c r="A23" s="69" t="n"/>
+      <c r="B23" s="69" t="n"/>
+      <c r="C23" s="70" t="n"/>
+      <c r="D23" s="70" t="n"/>
+      <c r="E23" s="70" t="n"/>
+      <c r="F23" s="70" t="n"/>
+      <c r="G23" s="70" t="n"/>
+      <c r="H23" s="70" t="n"/>
+      <c r="I23" s="70" t="n"/>
+      <c r="J23" s="70" t="n"/>
+      <c r="K23" s="70" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="52">
+      <c r="A24" s="65" t="inlineStr">
         <is>
           <t>(X) Miércoles  ·  Pull  ·  + carrera (ver bloque de carrera)</t>
         </is>
       </c>
-      <c r="B23" s="56" t="n"/>
-      <c r="C23" s="56" t="n"/>
-      <c r="D23" s="56" t="n"/>
-      <c r="E23" s="56" t="n"/>
-      <c r="F23" s="56" t="n"/>
-      <c r="G23" s="56" t="n"/>
-      <c r="H23" s="56" t="n"/>
-      <c r="I23" s="56" t="n"/>
-      <c r="J23" s="56" t="n"/>
-      <c r="K23" s="57" t="n"/>
-      <c r="L23" s="106" t="inlineStr">
+      <c r="B24" s="56" t="n"/>
+      <c r="C24" s="56" t="n"/>
+      <c r="D24" s="56" t="n"/>
+      <c r="E24" s="56" t="n"/>
+      <c r="F24" s="56" t="n"/>
+      <c r="G24" s="56" t="n"/>
+      <c r="H24" s="56" t="n"/>
+      <c r="I24" s="56" t="n"/>
+      <c r="J24" s="56" t="n"/>
+      <c r="K24" s="57" t="n"/>
+      <c r="L24" s="106" t="inlineStr">
         <is>
           <t>sesion</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="27" customHeight="1" s="52">
-      <c r="A24" s="66" t="inlineStr">
+    <row r="25" ht="27" customHeight="1" s="52">
+      <c r="A25" s="66" t="inlineStr">
         <is>
           <t>Ejercicio</t>
         </is>
       </c>
-      <c r="B24" s="66" t="inlineStr">
+      <c r="B25" s="66" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="C24" s="66" t="inlineStr">
+      <c r="C25" s="66" t="inlineStr">
         <is>
           <t>Sem 1 (series@RIR)</t>
         </is>
       </c>
-      <c r="D24" s="66" t="inlineStr">
+      <c r="D25" s="66" t="inlineStr">
         <is>
           <t>Sem 2 (series@RIR)</t>
         </is>
       </c>
-      <c r="E24" s="66" t="inlineStr">
+      <c r="E25" s="66" t="inlineStr">
         <is>
           <t>Sem 3 (series@RIR)</t>
         </is>
       </c>
-      <c r="F24" s="66" t="inlineStr">
+      <c r="F25" s="66" t="inlineStr">
         <is>
           <t>Sem 4 (series@RIR)</t>
         </is>
       </c>
-      <c r="G24" s="66" t="inlineStr">
+      <c r="G25" s="66" t="inlineStr">
         <is>
           <t>Sem 5 (series@RIR)</t>
         </is>
       </c>
-      <c r="H24" s="66" t="inlineStr">
+      <c r="H25" s="66" t="inlineStr">
         <is>
           <t>Sem 6 (series@RIR)</t>
         </is>
       </c>
-      <c r="I24" s="66" t="inlineStr">
+      <c r="I25" s="66" t="inlineStr">
         <is>
           <t>Sem 7 (series@RIR)</t>
         </is>
       </c>
-      <c r="J24" s="66" t="inlineStr">
+      <c r="J25" s="66" t="inlineStr">
         <is>
           <t>Sem 8 (series@RIR)</t>
         </is>
       </c>
-      <c r="K24" s="66" t="inlineStr">
+      <c r="K25" s="66" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="L24" s="106" t="inlineStr">
+      <c r="L25" s="106" t="inlineStr">
         <is>
           <t>App (no tocar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" s="52">
-      <c r="A25" s="59" t="inlineStr">
-        <is>
-          <t>Jalón ancho plano frontal</t>
-        </is>
-      </c>
-      <c r="B25" s="59" t="inlineStr">
-        <is>
-          <t>Espalda</t>
-        </is>
-      </c>
-      <c r="C25" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D25" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E25" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F25" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G25" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H25" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I25" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J25" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K25" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 3 (Dorsal Bajo) · 1º fresco · Torso vertical, codos abiertos en plano frontal hasta ~90° · No encoger hombros.</t>
-        </is>
-      </c>
-      <c r="L25" s="106" t="inlineStr">
-        <is>
-          <t>id=jalon-ancho-plano-frontal</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="52">
       <c r="A26" s="59" t="inlineStr">
         <is>
-          <t>Remo gironda abierto</t>
+          <t>Jalón ancho plano frontal</t>
         </is>
       </c>
       <c r="B26" s="59" t="inlineStr">
@@ -7267,22 +7267,22 @@
       </c>
       <c r="F26" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="G26" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="H26" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="I26" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="J26" s="61" t="inlineStr">
@@ -7292,34 +7292,34 @@
       </c>
       <c r="K26" s="62" t="inlineStr">
         <is>
-          <t>Plano transversal (Espalda Alta) · Codos abiertos y retracción escapular completa.</t>
+          <t>Prioridad 3 (Dorsal Bajo) · 1º fresco · Torso vertical, codos abiertos en plano frontal hasta ~90° · No encoger hombros.</t>
         </is>
       </c>
       <c r="L26" s="106" t="inlineStr">
         <is>
-          <t>id=remo-gironda-abierto</t>
+          <t>id=jalon-ancho-plano-frontal</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="52">
       <c r="A27" s="59" t="inlineStr">
         <is>
-          <t>Laterales sentado</t>
+          <t>Remo gironda abierto</t>
         </is>
       </c>
       <c r="B27" s="59" t="inlineStr">
         <is>
-          <t>Hombro lat.</t>
+          <t>Espalda</t>
         </is>
       </c>
       <c r="C27" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="D27" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="E27" s="61" t="inlineStr">
@@ -7344,34 +7344,34 @@
       </c>
       <c r="I27" s="61" t="inlineStr">
         <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J27" s="61" t="inlineStr">
+        <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J27" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
       <c r="K27" s="62" t="inlineStr">
         <is>
-          <t>Prioridad 1 (Hombro Lat.) · Sentado en banco a 75–80°, abducir en plano escapular (~30° adelante) sin rotar internamente el hombro.</t>
+          <t>Plano transversal (Espalda Alta) · Codos abiertos y retracción escapular completa.</t>
         </is>
       </c>
       <c r="L27" s="106" t="inlineStr">
         <is>
-          <t>id=laterales-sentado</t>
+          <t>id=remo-gironda-abierto</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="52">
       <c r="A28" s="59" t="inlineStr">
         <is>
-          <t>Jalón neutro</t>
+          <t>Laterales sentado</t>
         </is>
       </c>
       <c r="B28" s="59" t="inlineStr">
         <is>
-          <t>Espalda</t>
+          <t>Hombro lat.</t>
         </is>
       </c>
       <c r="C28" s="61" t="inlineStr">
@@ -7381,1055 +7381,1055 @@
       </c>
       <c r="D28" s="61" t="inlineStr">
         <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="E28" s="61" t="inlineStr">
+        <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="E28" s="61" t="inlineStr">
+      <c r="F28" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F28" s="61" t="inlineStr">
+      <c r="G28" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G28" s="61" t="inlineStr">
+      <c r="H28" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H28" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
       <c r="I28" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="J28" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="K28" s="62" t="inlineStr">
         <is>
-          <t>Plano sagital (Dorsal Sup.) · Agarre neutro ancho hombros, llevar codos a los bolsillos cortando a 90° (protege codo/bíceps).</t>
+          <t>Prioridad 1 (Hombro Lat.) · Sentado en banco a 75–80°, abducir en plano escapular (~30° adelante) sin rotar internamente el hombro.</t>
         </is>
       </c>
       <c r="L28" s="106" t="inlineStr">
         <is>
-          <t>id=jalon-neutro</t>
+          <t>id=laterales-sentado</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="52">
       <c r="A29" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curl martillo scott </t>
+          <t>Jalón neutro</t>
         </is>
       </c>
       <c r="B29" s="59" t="inlineStr">
         <is>
-          <t>Bíceps</t>
+          <t>Espalda</t>
         </is>
       </c>
       <c r="C29" s="61" t="inlineStr">
         <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="D29" s="61" t="inlineStr">
+        <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="D29" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
       <c r="E29" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="F29" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="G29" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="H29" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="I29" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="J29" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="K29" s="62" t="inlineStr">
         <is>
-          <t>Prioridad 2 (Bíceps/Braquiorradial) · Agarre neutro (muy amigable para el codo). Bajar en 2-3 s y parar a ~15° de la extensión total para no sobrecargar tendón distal.</t>
+          <t>Plano sagital (Dorsal Sup.) · Agarre neutro ancho hombros, llevar codos a los bolsillos cortando a 90° (protege codo/bíceps).</t>
         </is>
       </c>
       <c r="L29" s="106" t="inlineStr">
         <is>
-          <t>id=curl-martillo-scott</t>
+          <t>id=jalon-neutro</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="52">
       <c r="A30" s="59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Curl martillo scott </t>
+        </is>
+      </c>
+      <c r="B30" s="59" t="inlineStr">
+        <is>
+          <t>Bíceps</t>
+        </is>
+      </c>
+      <c r="C30" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D30" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E30" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F30" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G30" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H30" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I30" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J30" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K30" s="62" t="inlineStr">
+        <is>
+          <t>Prioridad 2 (Bíceps/Braquiorradial) · Agarre neutro (muy amigable para el codo). Bajar en 2-3 s y parar a ~15° de la extensión total para no sobrecargar tendón distal.</t>
+        </is>
+      </c>
+      <c r="L30" s="106" t="inlineStr">
+        <is>
+          <t>id=curl-martillo-scott</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="52">
+      <c r="A31" s="59" t="inlineStr">
+        <is>
           <t>Posterior polea</t>
         </is>
       </c>
-      <c r="B30" s="59" t="inlineStr">
+      <c r="B31" s="59" t="inlineStr">
         <is>
           <t>Hombro post.</t>
         </is>
       </c>
-      <c r="C30" s="61" t="inlineStr">
+      <c r="C31" s="61" t="inlineStr">
         <is>
           <t>1 @ RIR0</t>
         </is>
       </c>
-      <c r="D30" s="61" t="inlineStr">
+      <c r="D31" s="61" t="inlineStr">
         <is>
           <t>1 @ RIR0</t>
         </is>
       </c>
-      <c r="E30" s="61" t="inlineStr">
+      <c r="E31" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F30" s="61" t="inlineStr">
+      <c r="F31" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G30" s="61" t="inlineStr">
+      <c r="G31" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H30" s="61" t="inlineStr">
+      <c r="H31" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I30" s="61" t="inlineStr">
+      <c r="I31" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J30" s="61" t="inlineStr">
+      <c r="J31" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K30" s="62" t="inlineStr">
+      <c r="K31" s="62" t="inlineStr">
         <is>
           <t>Salud Hombro / Transversal · Clave para centrar cabeza humeral y compensar presses.</t>
         </is>
       </c>
-      <c r="L30" s="106" t="inlineStr">
+      <c r="L31" s="106" t="inlineStr">
         <is>
           <t>id=posterior-polea</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="52">
-      <c r="A31" s="59" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="52">
+      <c r="A32" s="59" t="inlineStr">
         <is>
           <t>Curl bayesian</t>
         </is>
       </c>
-      <c r="B31" s="59" t="inlineStr">
+      <c r="B32" s="59" t="inlineStr">
         <is>
           <t>Bíceps</t>
         </is>
       </c>
-      <c r="C31" s="61" t="inlineStr">
+      <c r="C32" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="D31" s="61" t="inlineStr">
+      <c r="D32" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="E31" s="61" t="inlineStr">
+      <c r="E32" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F31" s="61" t="inlineStr">
+      <c r="F32" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G31" s="61" t="inlineStr">
+      <c r="G32" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H31" s="61" t="inlineStr">
+      <c r="H32" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I31" s="61" t="inlineStr">
+      <c r="I32" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J31" s="61" t="inlineStr">
+      <c r="J32" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K31" s="62" t="inlineStr">
+      <c r="K32" s="62" t="inlineStr">
         <is>
           <t>Prioridad 2 (Bíceps en estiramiento) · Hombro en extensión detrás del torso; no dejar que el hombro rote hacia delante al subir.</t>
         </is>
       </c>
-      <c r="L31" s="106" t="inlineStr">
+      <c r="L32" s="106" t="inlineStr">
         <is>
           <t>id=curl-bayesian</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="52"/>
-    <row r="33" ht="19.5" customHeight="1" s="52">
-      <c r="A33" s="65" t="inlineStr">
+    <row r="33" ht="15.75" customHeight="1" s="52"/>
+    <row r="34" ht="19.5" customHeight="1" s="52">
+      <c r="A34" s="65" t="inlineStr">
         <is>
           <t>(J) Jueves  ·  Rehab + Isquios + Aductores  ·  test de fuerza S2 / S5 / S7</t>
         </is>
       </c>
-      <c r="B33" s="56" t="n"/>
-      <c r="C33" s="56" t="n"/>
-      <c r="D33" s="56" t="n"/>
-      <c r="E33" s="56" t="n"/>
-      <c r="F33" s="56" t="n"/>
-      <c r="G33" s="56" t="n"/>
-      <c r="H33" s="56" t="n"/>
-      <c r="I33" s="56" t="n"/>
-      <c r="J33" s="56" t="n"/>
-      <c r="K33" s="57" t="n"/>
-      <c r="L33" s="106" t="inlineStr">
+      <c r="B34" s="56" t="n"/>
+      <c r="C34" s="56" t="n"/>
+      <c r="D34" s="56" t="n"/>
+      <c r="E34" s="56" t="n"/>
+      <c r="F34" s="56" t="n"/>
+      <c r="G34" s="56" t="n"/>
+      <c r="H34" s="56" t="n"/>
+      <c r="I34" s="56" t="n"/>
+      <c r="J34" s="56" t="n"/>
+      <c r="K34" s="57" t="n"/>
+      <c r="L34" s="106" t="inlineStr">
         <is>
           <t>sesion</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="27" customHeight="1" s="52">
-      <c r="A34" s="66" t="inlineStr">
+    <row r="35" ht="27" customHeight="1" s="52">
+      <c r="A35" s="66" t="inlineStr">
         <is>
           <t>Ejercicio</t>
         </is>
       </c>
-      <c r="B34" s="66" t="inlineStr">
+      <c r="B35" s="66" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="C34" s="66" t="inlineStr">
+      <c r="C35" s="66" t="inlineStr">
         <is>
           <t>Sem 1 (series@RIR)</t>
         </is>
       </c>
-      <c r="D34" s="66" t="inlineStr">
+      <c r="D35" s="66" t="inlineStr">
         <is>
           <t>Sem 2 (series@RIR)</t>
         </is>
       </c>
-      <c r="E34" s="66" t="inlineStr">
+      <c r="E35" s="66" t="inlineStr">
         <is>
           <t>Sem 3 (series@RIR)</t>
         </is>
       </c>
-      <c r="F34" s="66" t="inlineStr">
+      <c r="F35" s="66" t="inlineStr">
         <is>
           <t>Sem 4 (series@RIR)</t>
         </is>
       </c>
-      <c r="G34" s="66" t="inlineStr">
+      <c r="G35" s="66" t="inlineStr">
         <is>
           <t>Sem 5 (series@RIR)</t>
         </is>
       </c>
-      <c r="H34" s="66" t="inlineStr">
+      <c r="H35" s="66" t="inlineStr">
         <is>
           <t>Sem 6 (series@RIR)</t>
         </is>
       </c>
-      <c r="I34" s="66" t="inlineStr">
+      <c r="I35" s="66" t="inlineStr">
         <is>
           <t>Sem 7 (series@RIR)</t>
         </is>
       </c>
-      <c r="J34" s="66" t="inlineStr">
+      <c r="J35" s="66" t="inlineStr">
         <is>
           <t>Sem 8 (series@RIR)</t>
         </is>
       </c>
-      <c r="K34" s="66" t="inlineStr">
+      <c r="K35" s="66" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="L34" s="106" t="inlineStr">
+      <c r="L35" s="106" t="inlineStr">
         <is>
           <t>App (no tocar)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="81" customHeight="1" s="52">
-      <c r="A35" s="71" t="inlineStr">
+    <row r="36" ht="81" customHeight="1" s="52">
+      <c r="A36" s="71" t="inlineStr">
         <is>
           <t>TEST fuerza · extensión unilateral en máquina 90→45°</t>
         </is>
       </c>
-      <c r="B35" s="71" t="inlineStr">
+      <c r="B36" s="71" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C35" s="72" t="inlineStr">
+      <c r="C36" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D35" s="72" t="inlineStr">
+      <c r="D36" s="72" t="inlineStr">
         <is>
           <t>2 aprox. +
 1 al fallo
 por pierna</t>
         </is>
       </c>
-      <c r="E35" s="72" t="inlineStr">
+      <c r="E36" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="72" t="inlineStr">
+      <c r="F36" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="72" t="inlineStr">
+      <c r="G36" s="72" t="inlineStr">
         <is>
           <t>2 aprox. +
 1 al fallo
 por pierna</t>
         </is>
       </c>
-      <c r="H35" s="72" t="inlineStr">
+      <c r="H36" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I35" s="72" t="inlineStr">
+      <c r="I36" s="72" t="inlineStr">
         <is>
           <t>2 aprox. +
 1 al fallo
 por pierna</t>
         </is>
       </c>
-      <c r="J35" s="72" t="inlineStr">
+      <c r="J36" s="72" t="inlineStr">
         <is>
           <t>Opcional:
 rango completo</t>
         </is>
       </c>
-      <c r="K35" s="71" t="inlineStr">
+      <c r="K36" s="71" t="inlineStr">
         <is>
           <t>Al empezar la sesión, tras la española 2-3×45 s y 2 series de aproximación. Mismo asiento y SIEMPRE rango fijo 90→45° (si el rango cambia, la comparación entre semanas no vale). Misma carga en las dos piernas (la que la I haga unas 10-15 reps), tempo 2-0-2, D primero, 3 min de descanso y luego la I; para si pasa de 3/10. Apunta carga y reps en «Seguimiento rodilla», que calcula la simetría. Objetivo ≥90% antes del balón [LÓGICA; el 90% viene de la vuelta al deporte tras LCA, no está validado en dolor femoropatelar: INCERTIDUMBRE]. Test en rango completo opcional en S8 y no en S7, para que sea la única novedad de su semana.</t>
         </is>
       </c>
-      <c r="L35" s="106" t="inlineStr">
+      <c r="L36" s="106" t="inlineStr">
         <is>
           <t>id=test-fuerza-extension-unilateral-en-maquina-90-45</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="43.5" customHeight="1" s="52">
-      <c r="A36" s="62" t="inlineStr">
+    <row r="37" ht="43.5" customHeight="1" s="52">
+      <c r="A37" s="62" t="inlineStr">
         <is>
           <t>Sentadilla al cajón o desde pines · pesado y lento n.º 2</t>
         </is>
       </c>
-      <c r="B36" s="62" t="inlineStr">
+      <c r="B37" s="62" t="inlineStr">
         <is>
           <t>Rehab</t>
         </is>
       </c>
-      <c r="C36" s="63" t="inlineStr">
+      <c r="C37" s="63" t="inlineStr">
         <is>
           <t>3 x12</t>
         </is>
       </c>
-      <c r="D36" s="63" t="inlineStr">
+      <c r="D37" s="63" t="inlineStr">
         <is>
           <t>3 x10</t>
         </is>
       </c>
-      <c r="E36" s="63" t="inlineStr">
+      <c r="E37" s="63" t="inlineStr">
         <is>
           <t>3 x10
 prof. del lunes</t>
         </is>
       </c>
-      <c r="F36" s="63" t="inlineStr">
+      <c r="F37" s="63" t="inlineStr">
         <is>
           <t>3 x10
 prof. del lunes</t>
         </is>
       </c>
-      <c r="G36" s="63" t="inlineStr">
+      <c r="G37" s="63" t="inlineStr">
         <is>
           <t>3 x8</t>
         </is>
       </c>
-      <c r="H36" s="63" t="inlineStr">
+      <c r="H37" s="63" t="inlineStr">
         <is>
           <t>3 x8
 prof. del lunes</t>
         </is>
       </c>
-      <c r="I36" s="63" t="inlineStr">
+      <c r="I37" s="63" t="inlineStr">
         <is>
           <t>3 x8
 prof. del lunes</t>
         </is>
       </c>
-      <c r="J36" s="63" t="inlineStr">
+      <c r="J37" s="63" t="inlineStr">
         <is>
           <t>3 x8
 repite S7</t>
         </is>
       </c>
-      <c r="K36" s="62" t="inlineStr">
+      <c r="K37" s="62" t="inlineStr">
         <is>
           <t>Tras el test (S2/S5/S7), carga por RIR. Tempo 3-1-3, RIR 2. Profundidad = la validada el lunes en la prensa. Postura habitual: un chasquido sin dolor no cambia nada; el apoyo ancho solo si te reduce el DOLOR [LÓGICA]. Antes del rehab (si no hay test): sentadilla española 2-3×45 s.</t>
         </is>
       </c>
-      <c r="L36" s="106" t="inlineStr">
+      <c r="L37" s="106" t="inlineStr">
         <is>
           <t>id=sentadilla-al-cajon-o-desde-pines-pesado-y-lento-n-2;escalera=prensa:sigue</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30.75" customHeight="1" s="52">
-      <c r="A37" s="62" t="inlineStr">
+    <row r="38" ht="30.75" customHeight="1" s="52">
+      <c r="A38" s="62" t="inlineStr">
         <is>
           <t>Bulgarian split squat</t>
         </is>
       </c>
-      <c r="B37" s="62" t="inlineStr">
+      <c r="B38" s="62" t="inlineStr">
         <is>
           <t>Rehab</t>
         </is>
       </c>
-      <c r="C37" s="63" t="inlineStr">
+      <c r="C38" s="63" t="inlineStr">
         <is>
           <t>2 x12</t>
         </is>
       </c>
-      <c r="D37" s="63" t="inlineStr">
+      <c r="D38" s="63" t="inlineStr">
         <is>
           <t>2 x10/pierna</t>
         </is>
       </c>
-      <c r="E37" s="63" t="inlineStr">
+      <c r="E38" s="63" t="inlineStr">
         <is>
           <t>2 x10/pierna</t>
         </is>
       </c>
-      <c r="F37" s="63" t="inlineStr">
+      <c r="F38" s="63" t="inlineStr">
         <is>
           <t>2 x10/pierna</t>
         </is>
       </c>
-      <c r="G37" s="63" t="inlineStr">
+      <c r="G38" s="63" t="inlineStr">
         <is>
           <t>2 x8/pierna</t>
         </is>
       </c>
-      <c r="H37" s="63" t="inlineStr">
+      <c r="H38" s="63" t="inlineStr">
         <is>
           <t>2 x8/pierna</t>
         </is>
       </c>
-      <c r="I37" s="63" t="inlineStr">
+      <c r="I38" s="63" t="inlineStr">
         <is>
           <t>2 x8/pierna</t>
         </is>
       </c>
-      <c r="J37" s="63" t="inlineStr">
+      <c r="J38" s="63" t="inlineStr">
         <is>
           <t>2 x8/pierna
 repite S7</t>
         </is>
       </c>
-      <c r="K37" s="62" t="inlineStr">
+      <c r="K38" s="62" t="inlineStr">
         <is>
           <t>D primero: RIR 2 y profundidad validada el lunes. I: RIR 1-2 y rango completo. Tempo 3-1-3. Alterna piernas, 60-90 s entre una y otra.</t>
         </is>
       </c>
-      <c r="L37" s="106" t="inlineStr">
+      <c r="L38" s="106" t="inlineStr">
         <is>
           <t>id=bulgarian-split-squat;escalera=prensa:sigue</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30.75" customHeight="1" s="52">
-      <c r="A38" s="62" t="inlineStr">
+    <row r="39" ht="30.75" customHeight="1" s="52">
+      <c r="A39" s="62" t="inlineStr">
         <is>
           <t>Abducción de pie unilateral (máquina)</t>
         </is>
       </c>
-      <c r="B38" s="62" t="inlineStr">
+      <c r="B39" s="62" t="inlineStr">
         <is>
           <t>Rehab (cadera)</t>
         </is>
       </c>
-      <c r="C38" s="63" t="inlineStr">
+      <c r="C39" s="63" t="inlineStr">
         <is>
           <t>2 x15–20</t>
         </is>
       </c>
-      <c r="D38" s="63" t="inlineStr">
+      <c r="D39" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="E38" s="63" t="inlineStr">
+      <c r="E39" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="F38" s="63" t="inlineStr">
+      <c r="F39" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="G38" s="63" t="inlineStr">
+      <c r="G39" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="H38" s="63" t="inlineStr">
+      <c r="H39" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="I38" s="63" t="inlineStr">
+      <c r="I39" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="J38" s="63" t="inlineStr">
+      <c r="J39" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="K38" s="62" t="inlineStr">
+      <c r="K39" s="62" t="inlineStr">
         <is>
           <t>Misma máquina que el lunes; empieza por la D. Va DESPUÉS de la búlgara, para no fatigar el glúteo medio antes del trabajo a una pierna [LÓGICA]. Lunes + jueves = 72-96 h entre sesiones de cadera.</t>
         </is>
       </c>
-      <c r="L38" s="106" t="inlineStr">
+      <c r="L39" s="106" t="inlineStr">
         <is>
           <t>id=abduccion-de-pie-unilateral-maquina</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1" s="52">
-      <c r="A39" s="62" t="inlineStr">
+    <row r="40" ht="18" customHeight="1" s="52">
+      <c r="A40" s="62" t="inlineStr">
         <is>
           <t>Touchdown squat</t>
         </is>
       </c>
-      <c r="B39" s="62" t="inlineStr">
+      <c r="B40" s="62" t="inlineStr">
         <is>
           <t>Rehab</t>
         </is>
       </c>
-      <c r="C39" s="63" t="inlineStr">
+      <c r="C40" s="63" t="inlineStr">
         <is>
           <t>2 x15–20</t>
         </is>
       </c>
-      <c r="D39" s="63" t="inlineStr">
+      <c r="D40" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E39" s="63" t="inlineStr">
+      <c r="E40" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F39" s="63" t="inlineStr">
+      <c r="F40" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="63" t="inlineStr">
+      <c r="G40" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H39" s="63" t="inlineStr">
+      <c r="H40" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I39" s="63" t="inlineStr">
+      <c r="I40" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J39" s="63" t="inlineStr">
+      <c r="J40" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K39" s="63" t="inlineStr">
+      <c r="K40" s="63" t="inlineStr">
         <is>
           <t>Sale del jueves desde S2: va el lunes, antes de la prensa [LÓGICA].</t>
         </is>
       </c>
-      <c r="L39" s="106" t="inlineStr">
+      <c r="L40" s="106" t="inlineStr">
         <is>
           <t>id=touchdown-squat</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1" s="52">
-      <c r="A40" s="59" t="inlineStr">
-        <is>
-          <t>Isquios sentado</t>
-        </is>
-      </c>
-      <c r="B40" s="59" t="inlineStr">
-        <is>
-          <t>Isquios</t>
-        </is>
-      </c>
-      <c r="C40" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D40" s="61" t="inlineStr">
-        <is>
-          <t>4 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E40" s="61" t="inlineStr">
-        <is>
-          <t>4 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F40" s="61" t="inlineStr">
-        <is>
-          <t>4 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G40" s="61" t="inlineStr">
-        <is>
-          <t>4 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H40" s="61" t="inlineStr">
-        <is>
-          <t>5 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I40" s="61" t="inlineStr">
-        <is>
-          <t>5 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J40" s="61" t="inlineStr">
-        <is>
-          <t>5 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K40" s="62" t="inlineStr">
-        <is>
-          <t>Isquios en estiramiento máximo (cadera a 90°) · Controlar fase excéntrica.</t>
-        </is>
-      </c>
-      <c r="L40" s="106" t="inlineStr">
-        <is>
-          <t>id=isquios-sentado</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="52">
       <c r="A41" s="59" t="inlineStr">
         <is>
-          <t>Aductores</t>
+          <t>Isquios sentado</t>
         </is>
       </c>
       <c r="B41" s="59" t="inlineStr">
         <is>
-          <t>Aductores</t>
+          <t>Isquios</t>
         </is>
       </c>
       <c r="C41" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="D41" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>4 @ RIR1/0</t>
         </is>
       </c>
       <c r="E41" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>4 @ RIR1/0</t>
         </is>
       </c>
       <c r="F41" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>4 @ RIR1/0</t>
         </is>
       </c>
       <c r="G41" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>4 @ RIR1/0</t>
         </is>
       </c>
       <c r="H41" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>5 @ RIR1/0</t>
         </is>
       </c>
       <c r="I41" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>5 @ RIR1/0</t>
         </is>
       </c>
       <c r="J41" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>5 @ RIR1/0</t>
         </is>
       </c>
       <c r="K41" s="62" t="inlineStr">
         <is>
-          <t>Plano transversal/frontal · Pausa de 1 s en apertura máxima sin dolor inguinal/rodilla.</t>
+          <t>Isquios en estiramiento máximo (cadera a 90°) · Controlar fase excéntrica.</t>
         </is>
       </c>
       <c r="L41" s="106" t="inlineStr">
         <is>
-          <t>id=aductores</t>
+          <t>id=isquios-sentado</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="52">
       <c r="A42" s="59" t="inlineStr">
         <is>
+          <t>Aductores</t>
+        </is>
+      </c>
+      <c r="B42" s="59" t="inlineStr">
+        <is>
+          <t>Aductores</t>
+        </is>
+      </c>
+      <c r="C42" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D42" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E42" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F42" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G42" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H42" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I42" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J42" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K42" s="62" t="inlineStr">
+        <is>
+          <t>Plano transversal/frontal · Pausa de 1 s en apertura máxima sin dolor inguinal/rodilla.</t>
+        </is>
+      </c>
+      <c r="L42" s="106" t="inlineStr">
+        <is>
+          <t>id=aductores</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="52">
+      <c r="A43" s="59" t="inlineStr">
+        <is>
           <t>Gemelos prensa</t>
         </is>
       </c>
-      <c r="B42" s="59" t="inlineStr">
+      <c r="B43" s="59" t="inlineStr">
         <is>
           <t>Gemelos</t>
         </is>
       </c>
-      <c r="C42" s="61" t="inlineStr">
+      <c r="C43" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="D42" s="61" t="inlineStr">
+      <c r="D43" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="E42" s="61" t="inlineStr">
+      <c r="E43" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F42" s="61" t="inlineStr">
+      <c r="F43" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G42" s="61" t="inlineStr">
+      <c r="G43" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H42" s="61" t="inlineStr">
+      <c r="H43" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I42" s="61" t="inlineStr">
+      <c r="I43" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J42" s="61" t="inlineStr">
+      <c r="J43" s="61" t="inlineStr">
         <is>
           <t>5 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K42" s="62" t="inlineStr">
+      <c r="K43" s="62" t="inlineStr">
         <is>
           <t>Prensa con pies abajo · Pausa estricta de 2 s en máximo estiramiento abajo (sin rebote elástico).</t>
         </is>
       </c>
-      <c r="L42" s="106" t="inlineStr">
+      <c r="L43" s="106" t="inlineStr">
         <is>
           <t>id=gemelos-prensa</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="52"/>
-    <row r="44" ht="19.5" customHeight="1" s="52">
-      <c r="A44" s="65" t="inlineStr">
+    <row r="44" ht="15.75" customHeight="1" s="52"/>
+    <row r="45" ht="19.5" customHeight="1" s="52">
+      <c r="A45" s="65" t="inlineStr">
         <is>
           <t>(V) Viernes  ·  Torso</t>
         </is>
       </c>
-      <c r="B44" s="56" t="n"/>
-      <c r="C44" s="56" t="n"/>
-      <c r="D44" s="56" t="n"/>
-      <c r="E44" s="56" t="n"/>
-      <c r="F44" s="56" t="n"/>
-      <c r="G44" s="56" t="n"/>
-      <c r="H44" s="56" t="n"/>
-      <c r="I44" s="56" t="n"/>
-      <c r="J44" s="56" t="n"/>
-      <c r="K44" s="57" t="n"/>
-      <c r="L44" s="106" t="inlineStr">
+      <c r="B45" s="56" t="n"/>
+      <c r="C45" s="56" t="n"/>
+      <c r="D45" s="56" t="n"/>
+      <c r="E45" s="56" t="n"/>
+      <c r="F45" s="56" t="n"/>
+      <c r="G45" s="56" t="n"/>
+      <c r="H45" s="56" t="n"/>
+      <c r="I45" s="56" t="n"/>
+      <c r="J45" s="56" t="n"/>
+      <c r="K45" s="57" t="n"/>
+      <c r="L45" s="106" t="inlineStr">
         <is>
           <t>sesion</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="27" customHeight="1" s="52">
-      <c r="A45" s="66" t="inlineStr">
+    <row r="46" ht="27" customHeight="1" s="52">
+      <c r="A46" s="66" t="inlineStr">
         <is>
           <t>Ejercicio</t>
         </is>
       </c>
-      <c r="B45" s="66" t="inlineStr">
+      <c r="B46" s="66" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="C45" s="66" t="inlineStr">
+      <c r="C46" s="66" t="inlineStr">
         <is>
           <t>Sem 1 (series@RIR)</t>
         </is>
       </c>
-      <c r="D45" s="66" t="inlineStr">
+      <c r="D46" s="66" t="inlineStr">
         <is>
           <t>Sem 2 (series@RIR)</t>
         </is>
       </c>
-      <c r="E45" s="66" t="inlineStr">
+      <c r="E46" s="66" t="inlineStr">
         <is>
           <t>Sem 3 (series@RIR)</t>
         </is>
       </c>
-      <c r="F45" s="66" t="inlineStr">
+      <c r="F46" s="66" t="inlineStr">
         <is>
           <t>Sem 4 (series@RIR)</t>
         </is>
       </c>
-      <c r="G45" s="66" t="inlineStr">
+      <c r="G46" s="66" t="inlineStr">
         <is>
           <t>Sem 5 (series@RIR)</t>
         </is>
       </c>
-      <c r="H45" s="66" t="inlineStr">
+      <c r="H46" s="66" t="inlineStr">
         <is>
           <t>Sem 6 (series@RIR)</t>
         </is>
       </c>
-      <c r="I45" s="66" t="inlineStr">
+      <c r="I46" s="66" t="inlineStr">
         <is>
           <t>Sem 7 (series@RIR)</t>
         </is>
       </c>
-      <c r="J45" s="66" t="inlineStr">
+      <c r="J46" s="66" t="inlineStr">
         <is>
           <t>Sem 8 (series@RIR)</t>
         </is>
       </c>
-      <c r="K45" s="66" t="inlineStr">
+      <c r="K46" s="66" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="L45" s="106" t="inlineStr">
+      <c r="L46" s="106" t="inlineStr">
         <is>
           <t>App (no tocar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1" s="52">
-      <c r="A46" s="59" t="inlineStr">
-        <is>
-          <t>Triceps conc polea (-15°)</t>
-        </is>
-      </c>
-      <c r="B46" s="59" t="inlineStr">
-        <is>
-          <t>Tríceps</t>
-        </is>
-      </c>
-      <c r="C46" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="D46" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="E46" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="F46" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="G46" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="H46" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="I46" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="J46" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="K46" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 2 + Potenciación de codo · Hombro a -15° (extensión): máximo acortamiento de cabeza larga con torque nulo en flexión máxima de codo (calienta tendón para el francés).</t>
-        </is>
-      </c>
-      <c r="L46" s="106" t="inlineStr">
-        <is>
-          <t>id=triceps-conc-polea-15</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="52">
       <c r="A47" s="59" t="inlineStr">
         <is>
-          <t>Laterales polea</t>
+          <t>Triceps conc polea (-15°)</t>
         </is>
       </c>
       <c r="B47" s="59" t="inlineStr">
         <is>
-          <t>Hombro lat.</t>
+          <t>Tríceps</t>
         </is>
       </c>
       <c r="C47" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>1 @ RIR0</t>
         </is>
       </c>
       <c r="D47" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>1 @ RIR0</t>
         </is>
       </c>
       <c r="E47" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>1 @ RIR0</t>
         </is>
       </c>
       <c r="F47" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>1 @ RIR0</t>
         </is>
       </c>
       <c r="G47" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>1 @ RIR0</t>
         </is>
       </c>
       <c r="H47" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>1 @ RIR0</t>
         </is>
       </c>
       <c r="I47" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>1 @ RIR0</t>
         </is>
       </c>
       <c r="J47" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>1 @ RIR0</t>
         </is>
       </c>
       <c r="K47" s="62" t="inlineStr">
         <is>
-          <t>Prioridad 1 (Hombro Lat.) · Polea a altura de muñeca/muslo, abducción en plano escapular.</t>
+          <t>Prioridad 2 + Potenciación de codo · Hombro a -15° (extensión): máximo acortamiento de cabeza larga con torque nulo en flexión máxima de codo (calienta tendón para el francés).</t>
         </is>
       </c>
       <c r="L47" s="106" t="inlineStr">
         <is>
-          <t>id=laterales-polea</t>
+          <t>id=triceps-conc-polea-15</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="52">
       <c r="A48" s="59" t="inlineStr">
         <is>
-          <t>Press francés manc (banco plano)</t>
+          <t>Laterales polea</t>
         </is>
       </c>
       <c r="B48" s="59" t="inlineStr">
         <is>
-          <t>Tríceps</t>
+          <t>Hombro lat.</t>
         </is>
       </c>
       <c r="C48" s="61" t="inlineStr">
@@ -8464,34 +8464,34 @@
       </c>
       <c r="I48" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="J48" s="61" t="inlineStr">
         <is>
-          <t>3 @ RIR1/0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="K48" s="62" t="inlineStr">
         <is>
-          <t>Prioridad 2 (Tríceps) · Agarre neutro (martillo) y brazos inclinados a ~100° hacia la cabeza: quita cizalla en epitróclea/olécranon y mantiene tensión constante.</t>
+          <t>Prioridad 1 (Hombro Lat.) · Polea a altura de muñeca/muslo, abducción en plano escapular.</t>
         </is>
       </c>
       <c r="L48" s="106" t="inlineStr">
         <is>
-          <t>id=press-frances-manc-banco-plano</t>
+          <t>id=laterales-polea</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="52">
       <c r="A49" s="59" t="inlineStr">
         <is>
-          <t>Curl biceps barra z</t>
+          <t>Press francés manc (banco plano)</t>
         </is>
       </c>
       <c r="B49" s="59" t="inlineStr">
         <is>
-          <t>Bíceps</t>
+          <t>Tríceps</t>
         </is>
       </c>
       <c r="C49" s="61" t="inlineStr">
@@ -8511,49 +8511,49 @@
       </c>
       <c r="F49" s="61" t="inlineStr">
         <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G49" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H49" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I49" s="61" t="inlineStr">
+        <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G49" s="61" t="inlineStr">
+      <c r="J49" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H49" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I49" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J49" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
       <c r="K49" s="62" t="inlineStr">
         <is>
-          <t>Prioridad 2 (Bíceps rango medio) · Usar el agarre de la barra Z (ancho o estrecho) que resulte 100% libre de molestia en muñeca y codo.</t>
+          <t>Prioridad 2 (Tríceps) · Agarre neutro (martillo) y brazos inclinados a ~100° hacia la cabeza: quita cizalla en epitróclea/olécranon y mantiene tensión constante.</t>
         </is>
       </c>
       <c r="L49" s="106" t="inlineStr">
         <is>
-          <t>id=curl-biceps-barra-z</t>
+          <t>id=press-frances-manc-banco-plano</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="52">
       <c r="A50" s="59" t="inlineStr">
         <is>
-          <t>Press máquina neutro ascendente</t>
+          <t>Curl biceps barra z</t>
         </is>
       </c>
       <c r="B50" s="59" t="inlineStr">
         <is>
-          <t>Pecho</t>
+          <t>Bíceps</t>
         </is>
       </c>
       <c r="C50" s="61" t="inlineStr">
@@ -8573,12 +8573,12 @@
       </c>
       <c r="F50" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="G50" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="H50" s="61" t="inlineStr">
@@ -8598,786 +8598,826 @@
       </c>
       <c r="K50" s="62" t="inlineStr">
         <is>
-          <t>Prioridad 4 (Haz clavicular) · 10/10 tras brazos: el agarre neutro y la trayectoria convergente ascendente aíslan el haz clavicular sin estrés en hombro ni codo.</t>
+          <t>Prioridad 2 (Bíceps rango medio) · Usar el agarre de la barra Z (ancho o estrecho) que resulte 100% libre de molestia en muñeca y codo.</t>
         </is>
       </c>
       <c r="L50" s="106" t="inlineStr">
         <is>
-          <t>id=press-maquina-neutro-ascendente</t>
+          <t>id=curl-biceps-barra-z</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="52">
       <c r="A51" s="59" t="inlineStr">
         <is>
-          <t>Dominada neutra dorsal</t>
+          <t>Press máquina neutro ascendente</t>
         </is>
       </c>
       <c r="B51" s="59" t="inlineStr">
         <is>
-          <t>Espalda</t>
+          <t>Pecho</t>
         </is>
       </c>
       <c r="C51" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="D51" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="E51" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="F51" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="G51" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="H51" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="I51" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="J51" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="K51" s="62" t="inlineStr">
         <is>
-          <t>Plano sagital (Dorsal Sup.) · Usar STRAPS obligatoriamente para anular fatiga previa de bíceps y proteger codos.</t>
+          <t>Prioridad 4 (Haz clavicular) · 10/10 tras brazos: el agarre neutro y la trayectoria convergente ascendente aíslan el haz clavicular sin estrés en hombro ni codo.</t>
         </is>
       </c>
       <c r="L51" s="106" t="inlineStr">
         <is>
-          <t>id=dominada-neutra-dorsal</t>
+          <t>id=press-maquina-neutro-ascendente</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="52">
       <c r="A52" s="59" t="inlineStr">
         <is>
+          <t>Dominada neutra dorsal</t>
+        </is>
+      </c>
+      <c r="B52" s="59" t="inlineStr">
+        <is>
+          <t>Espalda</t>
+        </is>
+      </c>
+      <c r="C52" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="D52" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="E52" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="F52" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="G52" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="H52" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I52" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J52" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K52" s="62" t="inlineStr">
+        <is>
+          <t>Plano sagital (Dorsal Sup.) · Usar STRAPS obligatoriamente para anular fatiga previa de bíceps y proteger codos.</t>
+        </is>
+      </c>
+      <c r="L52" s="106" t="inlineStr">
+        <is>
+          <t>id=dominada-neutra-dorsal</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1" s="52">
+      <c r="A53" s="59" t="inlineStr">
+        <is>
           <t>Remo máquina (pecho apoyado 30°)</t>
         </is>
       </c>
-      <c r="B52" s="59" t="inlineStr">
+      <c r="B53" s="59" t="inlineStr">
         <is>
           <t>Espalda</t>
         </is>
       </c>
-      <c r="C52" s="61" t="inlineStr">
+      <c r="C53" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="D52" s="61" t="inlineStr">
+      <c r="D53" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="E52" s="61" t="inlineStr">
+      <c r="E53" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F52" s="61" t="inlineStr">
+      <c r="F53" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G52" s="61" t="inlineStr">
+      <c r="G53" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H52" s="61" t="inlineStr">
+      <c r="H53" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I52" s="61" t="inlineStr">
+      <c r="I53" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J52" s="61" t="inlineStr">
+      <c r="J53" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K52" s="62" t="inlineStr">
+      <c r="K53" s="62" t="inlineStr">
         <is>
           <t>Plano sagital/híbrido (Dorsal Sup.) · Usar STRAPS, codos a ~30° hasta línea del torso.</t>
         </is>
       </c>
-      <c r="L52" s="106" t="inlineStr">
+      <c r="L53" s="106" t="inlineStr">
         <is>
           <t>id=remo-maquina-pecho-apoyado-30</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="52">
-      <c r="A53" s="59" t="inlineStr">
+    <row r="54" ht="15" customHeight="1" s="52">
+      <c r="A54" s="59" t="inlineStr">
         <is>
           <t>Aducción unil. polea alta (Pull-in)</t>
         </is>
       </c>
-      <c r="B53" s="59" t="inlineStr">
+      <c r="B54" s="59" t="inlineStr">
         <is>
           <t>Espalda</t>
         </is>
       </c>
-      <c r="C53" s="61" t="inlineStr">
+      <c r="C54" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="D53" s="61" t="inlineStr">
+      <c r="D54" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="E53" s="61" t="inlineStr">
+      <c r="E54" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F53" s="61" t="inlineStr">
+      <c r="F54" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G53" s="61" t="inlineStr">
+      <c r="G54" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H53" s="61" t="inlineStr">
+      <c r="H54" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I53" s="61" t="inlineStr">
+      <c r="I54" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J53" s="61" t="inlineStr">
+      <c r="J54" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K53" s="62" t="inlineStr">
+      <c r="K54" s="62" t="inlineStr">
         <is>
           <t>Prioridad 3 (Dorsal Bajo) · De lado a la polea (con tobillera en muñeca o codo semirrígido) para aislar haz inferior sin usar bíceps ni codo · Sem 1-2 a RIR 1-2.</t>
         </is>
       </c>
-      <c r="L53" s="106" t="inlineStr">
+      <c r="L54" s="106" t="inlineStr">
         <is>
           <t>id=aduccion-unil-polea-alta-pull-in</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1" s="52"/>
-    <row r="55" ht="19.5" customHeight="1" s="52">
-      <c r="A55" s="65" t="inlineStr">
+    <row r="55" ht="15.75" customHeight="1" s="52"/>
+    <row r="56" ht="19.5" customHeight="1" s="52">
+      <c r="A56" s="65" t="inlineStr">
         <is>
           <t>(S) Sábado  ·  casa, sin máquinas ni poleas  ·  desde S2, sin pierna (el domingo: carrera)</t>
         </is>
       </c>
-      <c r="B55" s="56" t="n"/>
-      <c r="C55" s="56" t="n"/>
-      <c r="D55" s="56" t="n"/>
-      <c r="E55" s="56" t="n"/>
-      <c r="F55" s="56" t="n"/>
-      <c r="G55" s="56" t="n"/>
-      <c r="H55" s="56" t="n"/>
-      <c r="I55" s="56" t="n"/>
-      <c r="J55" s="56" t="n"/>
-      <c r="K55" s="57" t="n"/>
-      <c r="L55" s="106" t="inlineStr">
+      <c r="B56" s="56" t="n"/>
+      <c r="C56" s="56" t="n"/>
+      <c r="D56" s="56" t="n"/>
+      <c r="E56" s="56" t="n"/>
+      <c r="F56" s="56" t="n"/>
+      <c r="G56" s="56" t="n"/>
+      <c r="H56" s="56" t="n"/>
+      <c r="I56" s="56" t="n"/>
+      <c r="J56" s="56" t="n"/>
+      <c r="K56" s="57" t="n"/>
+      <c r="L56" s="106" t="inlineStr">
         <is>
           <t>sesion;nombreS1=Sábado/Domingo</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="27" customHeight="1" s="52">
-      <c r="A56" s="66" t="inlineStr">
+    <row r="57" ht="27" customHeight="1" s="52">
+      <c r="A57" s="66" t="inlineStr">
         <is>
           <t>Ejercicio</t>
         </is>
       </c>
-      <c r="B56" s="66" t="inlineStr">
+      <c r="B57" s="66" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="C56" s="66" t="inlineStr">
+      <c r="C57" s="66" t="inlineStr">
         <is>
           <t>Sem 1 (series@RIR)</t>
         </is>
       </c>
-      <c r="D56" s="66" t="inlineStr">
+      <c r="D57" s="66" t="inlineStr">
         <is>
           <t>Sem 2 (series@RIR)</t>
         </is>
       </c>
-      <c r="E56" s="66" t="inlineStr">
+      <c r="E57" s="66" t="inlineStr">
         <is>
           <t>Sem 3 (series@RIR)</t>
         </is>
       </c>
-      <c r="F56" s="66" t="inlineStr">
+      <c r="F57" s="66" t="inlineStr">
         <is>
           <t>Sem 4 (series@RIR)</t>
         </is>
       </c>
-      <c r="G56" s="66" t="inlineStr">
+      <c r="G57" s="66" t="inlineStr">
         <is>
           <t>Sem 5 (series@RIR)</t>
         </is>
       </c>
-      <c r="H56" s="66" t="inlineStr">
+      <c r="H57" s="66" t="inlineStr">
         <is>
           <t>Sem 6 (series@RIR)</t>
         </is>
       </c>
-      <c r="I56" s="66" t="inlineStr">
+      <c r="I57" s="66" t="inlineStr">
         <is>
           <t>Sem 7 (series@RIR)</t>
         </is>
       </c>
-      <c r="J56" s="66" t="inlineStr">
+      <c r="J57" s="66" t="inlineStr">
         <is>
           <t>Sem 8 (series@RIR)</t>
         </is>
       </c>
-      <c r="K56" s="66" t="inlineStr">
+      <c r="K57" s="66" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="L56" s="106" t="inlineStr">
+      <c r="L57" s="106" t="inlineStr">
         <is>
           <t>App (no tocar)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="30.75" customHeight="1" s="52">
-      <c r="A57" s="62" t="inlineStr">
+    <row r="58" ht="30.75" customHeight="1" s="52">
+      <c r="A58" s="62" t="inlineStr">
         <is>
           <t>Abducción unilateral</t>
         </is>
       </c>
-      <c r="B57" s="62" t="inlineStr">
+      <c r="B58" s="62" t="inlineStr">
         <is>
           <t>Rehab (cadera)</t>
         </is>
       </c>
-      <c r="C57" s="63" t="inlineStr">
+      <c r="C58" s="63" t="inlineStr">
         <is>
           <t>2 x15–20</t>
         </is>
       </c>
-      <c r="D57" s="63" t="inlineStr">
+      <c r="D58" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E57" s="63" t="inlineStr">
+      <c r="E58" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F57" s="63" t="inlineStr">
+      <c r="F58" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G57" s="63" t="inlineStr">
+      <c r="G58" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H57" s="63" t="inlineStr">
+      <c r="H58" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I57" s="63" t="inlineStr">
+      <c r="I58" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J57" s="63" t="inlineStr">
+      <c r="J58" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K57" s="62" t="inlineStr">
+      <c r="K58" s="62" t="inlineStr">
         <is>
           <t>Sale del sábado desde S2: la abducción va el lunes y el jueves en máquina; la pierna se concentra en 2 días [LÓGICA].</t>
         </is>
       </c>
-      <c r="L57" s="106" t="inlineStr">
+      <c r="L58" s="106" t="inlineStr">
         <is>
           <t>id=abduccion-unilateral</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1" s="52">
-      <c r="A58" s="62" t="inlineStr">
-        <is>
-          <t>Touchdown squat</t>
-        </is>
-      </c>
-      <c r="B58" s="62" t="inlineStr">
-        <is>
-          <t>Rehab</t>
-        </is>
-      </c>
-      <c r="C58" s="63" t="inlineStr">
-        <is>
-          <t>2 x15–20</t>
-        </is>
-      </c>
-      <c r="D58" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J58" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K58" s="63" t="inlineStr">
-        <is>
-          <t>Sale del sábado desde S2: va el lunes, antes de la prensa [LÓGICA].</t>
-        </is>
-      </c>
-      <c r="L58" s="106" t="inlineStr">
-        <is>
-          <t>id=touchdown-squat</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="52">
       <c r="A59" s="62" t="inlineStr">
         <is>
+          <t>Touchdown squat</t>
+        </is>
+      </c>
+      <c r="B59" s="62" t="inlineStr">
+        <is>
+          <t>Rehab</t>
+        </is>
+      </c>
+      <c r="C59" s="63" t="inlineStr">
+        <is>
+          <t>2 x15–20</t>
+        </is>
+      </c>
+      <c r="D59" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K59" s="63" t="inlineStr">
+        <is>
+          <t>Sale del sábado desde S2: va el lunes, antes de la prensa [LÓGICA].</t>
+        </is>
+      </c>
+      <c r="L59" s="106" t="inlineStr">
+        <is>
+          <t>id=touchdown-squat</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1" s="52">
+      <c r="A60" s="62" t="inlineStr">
+        <is>
           <t>Bulgarian split squat</t>
         </is>
       </c>
-      <c r="B59" s="62" t="inlineStr">
+      <c r="B60" s="62" t="inlineStr">
         <is>
           <t>Rehab</t>
         </is>
       </c>
-      <c r="C59" s="63" t="inlineStr">
+      <c r="C60" s="63" t="inlineStr">
         <is>
           <t>2 x12</t>
         </is>
       </c>
-      <c r="D59" s="63" t="inlineStr">
+      <c r="D60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E59" s="63" t="inlineStr">
+      <c r="E60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F59" s="63" t="inlineStr">
+      <c r="F60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G59" s="63" t="inlineStr">
+      <c r="G60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H59" s="63" t="inlineStr">
+      <c r="H60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I59" s="63" t="inlineStr">
+      <c r="I60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J59" s="63" t="inlineStr">
+      <c r="J60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K59" s="62" t="inlineStr">
+      <c r="K60" s="62" t="inlineStr">
         <is>
           <t>Sale del sábado desde S2: la pierna se concentra en el lunes y el jueves [LÓGICA].</t>
         </is>
       </c>
-      <c r="L59" s="106" t="inlineStr">
+      <c r="L60" s="106" t="inlineStr">
         <is>
           <t>id=bulgarian-split-squat</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1" s="52">
-      <c r="A60" s="59" t="inlineStr">
+    <row r="61" ht="15.75" customHeight="1" s="52">
+      <c r="A61" s="59" t="inlineStr">
         <is>
           <t>Abs wesley banco</t>
         </is>
       </c>
-      <c r="B60" s="59" t="inlineStr">
+      <c r="B61" s="59" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="C60" s="61" t="inlineStr">
+      <c r="C61" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="D60" s="61" t="inlineStr">
+      <c r="D61" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="E60" s="61" t="inlineStr">
+      <c r="E61" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F60" s="61" t="inlineStr">
+      <c r="F61" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G60" s="61" t="inlineStr">
+      <c r="G61" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H60" s="61" t="inlineStr">
+      <c r="H61" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I60" s="61" t="inlineStr">
+      <c r="I61" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J60" s="61" t="inlineStr">
+      <c r="J61" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K60" s="61" t="n"/>
-      <c r="L60" s="106" t="inlineStr">
+      <c r="K61" s="61" t="n"/>
+      <c r="L61" s="106" t="inlineStr">
         <is>
           <t>id=abs-wesley-banco</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="30.75" customHeight="1" s="52">
-      <c r="A61" s="59" t="inlineStr">
+    <row r="62" ht="30.75" customHeight="1" s="52">
+      <c r="A62" s="59" t="inlineStr">
         <is>
           <t>Elevación lateral en prono «T» (mancuernas, banco)</t>
         </is>
       </c>
-      <c r="B61" s="59" t="inlineStr">
+      <c r="B62" s="59" t="inlineStr">
         <is>
           <t>Hombro (correctivo)</t>
         </is>
       </c>
-      <c r="C61" s="61" t="inlineStr">
+      <c r="C62" s="61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D61" s="61" t="inlineStr">
+      <c r="D62" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="E61" s="61" t="inlineStr">
+      <c r="E62" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="F61" s="61" t="inlineStr">
+      <c r="F62" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="G61" s="61" t="inlineStr">
+      <c r="G62" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="H61" s="61" t="inlineStr">
+      <c r="H62" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="I61" s="61" t="inlineStr">
+      <c r="I62" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="J61" s="61" t="inlineStr">
+      <c r="J62" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="K61" s="61" t="inlineStr">
+      <c r="K62" s="61" t="inlineStr">
         <is>
           <t>Postura: trapecio medio e inferior y deltoides posterior. Boca abajo en el banco, pulgar arriba, muy poco peso. RIR 3-4; no cuenta como serie de hipertrofia. Libro, p. 290.</t>
         </is>
       </c>
-      <c r="L61" s="106" t="inlineStr">
+      <c r="L62" s="106" t="inlineStr">
         <is>
           <t>id=elevacion-lateral-en-prono-t-mancuernas-banco</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="30.75" customHeight="1" s="52">
-      <c r="A62" s="59" t="inlineStr">
+    <row r="63" ht="30.75" customHeight="1" s="52">
+      <c r="A63" s="59" t="inlineStr">
         <is>
           <t>Rotación externa con banda «W»</t>
         </is>
       </c>
-      <c r="B62" s="59" t="inlineStr">
+      <c r="B63" s="59" t="inlineStr">
         <is>
           <t>Hombro (correctivo)</t>
         </is>
       </c>
-      <c r="C62" s="61" t="inlineStr">
+      <c r="C63" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D62" s="61" t="inlineStr">
+      <c r="D63" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="E62" s="61" t="inlineStr">
+      <c r="E63" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="F62" s="61" t="inlineStr">
+      <c r="F63" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="G62" s="61" t="inlineStr">
+      <c r="G63" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="H62" s="61" t="inlineStr">
+      <c r="H63" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="I62" s="61" t="inlineStr">
+      <c r="I63" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="J62" s="61" t="inlineStr">
+      <c r="J63" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="K62" s="61" t="inlineStr">
+      <c r="K63" s="61" t="inlineStr">
         <is>
           <t>Codos pegados al cuerpo a 90°. RIR 3-4. Libro, p. 288.</t>
         </is>
       </c>
-      <c r="L62" s="106" t="inlineStr">
+      <c r="L63" s="106" t="inlineStr">
         <is>
           <t>id=rotacion-externa-con-banda-w</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="43.5" customHeight="1" s="52">
-      <c r="A63" s="59" t="inlineStr">
+    <row r="64" ht="43.5" customHeight="1" s="52">
+      <c r="A64" s="59" t="inlineStr">
         <is>
           <t>Curl de muñeca en extensión (mancuerna)</t>
         </is>
       </c>
-      <c r="B63" s="59" t="inlineStr">
+      <c r="B64" s="59" t="inlineStr">
         <is>
           <t>Codo (correctivo)</t>
         </is>
       </c>
-      <c r="C63" s="61" t="inlineStr">
+      <c r="C64" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D63" s="61" t="inlineStr">
+      <c r="D64" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="E63" s="61" t="inlineStr">
+      <c r="E64" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="F63" s="61" t="inlineStr">
+      <c r="F64" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="G63" s="61" t="inlineStr">
+      <c r="G64" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="H63" s="61" t="inlineStr">
+      <c r="H64" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="I63" s="61" t="inlineStr">
+      <c r="I64" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="J63" s="61" t="inlineStr">
+      <c r="J64" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="K63" s="61" t="inlineStr">
+      <c r="K64" s="61" t="inlineStr">
         <is>
           <t>Codo (cara externa). Antebrazo apoyado, palma abajo. Si ahora agarrar te duele: isométrico 4-5×30-45 s las 1-2 primeras semanas. Antes, test del nervio radial (libro, p. 323): si es positivo, se cambia por deslizamientos del nervio (p. 338). Dolor ≤3/10 y no peor al día siguiente. Libro, pp. 332-333.</t>
         </is>
       </c>
-      <c r="L63" s="106" t="inlineStr">
+      <c r="L64" s="106" t="inlineStr">
         <is>
           <t>id=curl-de-muneca-en-extension-mancuerna</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="30" customHeight="1" s="52">
-      <c r="A64" s="67" t="inlineStr">
+    <row r="65" ht="30" customHeight="1" s="52">
+      <c r="A65" s="67" t="inlineStr">
         <is>
           <t>Autorregulación: si un músculo pierde reps 2 sesiones seguidas, esa semana NO le subas series. Si se estancan varios a la vez o la rodilla empeora en el test, repite la semana anterior.</t>
         </is>
       </c>
-      <c r="B64" s="56" t="n"/>
-      <c r="C64" s="56" t="n"/>
-      <c r="D64" s="56" t="n"/>
-      <c r="E64" s="56" t="n"/>
-      <c r="F64" s="56" t="n"/>
-      <c r="G64" s="56" t="n"/>
-      <c r="H64" s="56" t="n"/>
-      <c r="I64" s="56" t="n"/>
-      <c r="J64" s="56" t="n"/>
-      <c r="K64" s="57" t="n"/>
-      <c r="L64" s="106" t="inlineStr">
+      <c r="B65" s="56" t="n"/>
+      <c r="C65" s="56" t="n"/>
+      <c r="D65" s="56" t="n"/>
+      <c r="E65" s="56" t="n"/>
+      <c r="F65" s="56" t="n"/>
+      <c r="G65" s="56" t="n"/>
+      <c r="H65" s="56" t="n"/>
+      <c r="I65" s="56" t="n"/>
+      <c r="J65" s="56" t="n"/>
+      <c r="K65" s="57" t="n"/>
+      <c r="L65" s="106" t="inlineStr">
         <is>
           <t>regla</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15.75" customHeight="1" s="52"/>
-    <row r="66" ht="19.5" customHeight="1" s="52">
-      <c r="A66" s="65" t="inlineStr">
+    <row r="66" ht="15.75" customHeight="1" s="52"/>
+    <row r="67" ht="19.5" customHeight="1" s="52">
+      <c r="A67" s="65" t="inlineStr">
         <is>
           <t>Semana 9 (14-20/12) · Viaje = descarga  ·  Semana 10 · Vuelta progresiva</t>
-        </is>
-      </c>
-      <c r="B66" s="56" t="n"/>
-      <c r="C66" s="56" t="n"/>
-      <c r="D66" s="56" t="n"/>
-      <c r="E66" s="56" t="n"/>
-      <c r="F66" s="56" t="n"/>
-      <c r="G66" s="56" t="n"/>
-      <c r="H66" s="56" t="n"/>
-      <c r="I66" s="56" t="n"/>
-      <c r="J66" s="56" t="n"/>
-      <c r="K66" s="57" t="n"/>
-      <c r="L66" s="106" t="inlineStr">
-        <is>
-          <t>nota</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1" s="52">
-      <c r="A67" s="73" t="inlineStr">
-        <is>
-          <t>Hipertrofia: la semana sin entrenar hace de descarga justo después del pico de volumen de la semana 8.</t>
         </is>
       </c>
       <c r="B67" s="56" t="n"/>
@@ -9396,10 +9436,10 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="42" customHeight="1" s="52">
+    <row r="68" ht="30" customHeight="1" s="52">
       <c r="A68" s="73" t="inlineStr">
         <is>
-          <t>Rodilla en el viaje: nunca reposo total del tendón. Sentadilla española 5×45 s cada día (sin anclaje → wall sit a 1 pierna) y las dos pruebas de la mañana (declive + 10 subidas). Carrera: si puedes, 2 rodajes suaves sin pasar del nivel de S8 y nunca dos días seguidos, con la regla de carrera (≤2/10, nivel previo en ≤60 min, mañana siguiente no peor).</t>
+          <t>Hipertrofia: la semana sin entrenar hace de descarga justo después del pico de volumen de la semana 8.</t>
         </is>
       </c>
       <c r="B68" s="56" t="n"/>
@@ -9421,7 +9461,7 @@
     <row r="69" ht="42" customHeight="1" s="52">
       <c r="A69" s="73" t="inlineStr">
         <is>
-          <t>Semana 10 (vuelta): hipertrofia con las series de la sem 3-4 y a RIR2. Rehab ×8 al ~80% del peso de la sem 8; si se cumple la regla de 24-48 h, semana 11 a peso completo y siguiente escalón del libro (×6). Carrera: retomas el nivel de S8, o uno por debajo si no pudiste correr en el viaje.</t>
+          <t>Rodilla en el viaje: nunca reposo total del tendón. Sentadilla española 5×45 s cada día (sin anclaje → wall sit a 1 pierna) y las dos pruebas de la mañana (declive + 10 subidas). Carrera: si puedes, 2 rodajes suaves sin pasar del nivel de S8 y nunca dos días seguidos, con la regla de carrera (≤2/10, nivel previo en ≤60 min, mañana siguiente no peor).</t>
         </is>
       </c>
       <c r="B69" s="56" t="n"/>
@@ -9440,129 +9480,107 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1" s="52"/>
-    <row r="71" ht="19.5" customHeight="1" s="52">
-      <c r="A71" s="74" t="inlineStr">
+    <row r="70" ht="42" customHeight="1" s="52">
+      <c r="A70" s="73" t="inlineStr">
+        <is>
+          <t>Semana 10 (vuelta): hipertrofia con las series de la sem 3-4 y a RIR2. Rehab ×8 al ~80% del peso de la sem 8; si se cumple la regla de 24-48 h, semana 11 a peso completo y siguiente escalón del libro (×6). Carrera: retomas el nivel de S8, o uno por debajo si no pudiste correr en el viaje.</t>
+        </is>
+      </c>
+      <c r="B70" s="56" t="n"/>
+      <c r="C70" s="56" t="n"/>
+      <c r="D70" s="56" t="n"/>
+      <c r="E70" s="56" t="n"/>
+      <c r="F70" s="56" t="n"/>
+      <c r="G70" s="56" t="n"/>
+      <c r="H70" s="56" t="n"/>
+      <c r="I70" s="56" t="n"/>
+      <c r="J70" s="56" t="n"/>
+      <c r="K70" s="57" t="n"/>
+      <c r="L70" s="106" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1" s="52"/>
+    <row r="72" ht="19.5" customHeight="1" s="52">
+      <c r="A72" s="74" t="inlineStr">
         <is>
           <t>Series semanales por grupo muscular (se recalculan solas al cambiar la tabla)</t>
         </is>
       </c>
-      <c r="B71" s="56" t="n"/>
-      <c r="C71" s="56" t="n"/>
-      <c r="D71" s="56" t="n"/>
-      <c r="E71" s="56" t="n"/>
-      <c r="F71" s="56" t="n"/>
-      <c r="G71" s="56" t="n"/>
-      <c r="H71" s="56" t="n"/>
-      <c r="I71" s="56" t="n"/>
-      <c r="J71" s="56" t="n"/>
-      <c r="K71" s="57" t="n"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1" s="52">
-      <c r="A72" s="75" t="inlineStr">
+      <c r="B72" s="56" t="n"/>
+      <c r="C72" s="56" t="n"/>
+      <c r="D72" s="56" t="n"/>
+      <c r="E72" s="56" t="n"/>
+      <c r="F72" s="56" t="n"/>
+      <c r="G72" s="56" t="n"/>
+      <c r="H72" s="56" t="n"/>
+      <c r="I72" s="56" t="n"/>
+      <c r="J72" s="56" t="n"/>
+      <c r="K72" s="57" t="n"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" s="52">
+      <c r="A73" s="75" t="inlineStr">
         <is>
           <t>Grupo muscular</t>
         </is>
       </c>
-      <c r="B72" s="75" t="inlineStr">
+      <c r="B73" s="75" t="inlineStr">
         <is>
           <t>Sem 1 → Sem 8</t>
         </is>
       </c>
-      <c r="C72" s="75" t="inlineStr">
+      <c r="C73" s="75" t="inlineStr">
         <is>
           <t>Sem 1</t>
         </is>
       </c>
-      <c r="D72" s="75" t="inlineStr">
+      <c r="D73" s="75" t="inlineStr">
         <is>
           <t>Sem 2</t>
         </is>
       </c>
-      <c r="E72" s="75" t="inlineStr">
+      <c r="E73" s="75" t="inlineStr">
         <is>
           <t>Sem 3</t>
         </is>
       </c>
-      <c r="F72" s="75" t="inlineStr">
+      <c r="F73" s="75" t="inlineStr">
         <is>
           <t>Sem 4</t>
         </is>
       </c>
-      <c r="G72" s="75" t="inlineStr">
+      <c r="G73" s="75" t="inlineStr">
         <is>
           <t>Sem 5</t>
         </is>
       </c>
-      <c r="H72" s="75" t="inlineStr">
+      <c r="H73" s="75" t="inlineStr">
         <is>
           <t>Sem 6</t>
         </is>
       </c>
-      <c r="I72" s="75" t="inlineStr">
+      <c r="I73" s="75" t="inlineStr">
         <is>
           <t>Sem 7</t>
         </is>
       </c>
-      <c r="J72" s="75" t="inlineStr">
+      <c r="J73" s="75" t="inlineStr">
         <is>
           <t>Sem 8</t>
         </is>
       </c>
-      <c r="L72" s="106" t="inlineStr">
+      <c r="L73" s="106" t="inlineStr">
         <is>
           <t>grupos</t>
         </is>
       </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1" s="52">
-      <c r="A73" s="76" t="inlineStr">
-        <is>
-          <t>Espalda</t>
-        </is>
-      </c>
-      <c r="B73" s="77">
-        <f>C73&amp;" → "&amp;J73</f>
-        <v/>
-      </c>
-      <c r="C73" s="77">
-        <f>IFERROR(VALUE(LEFT(C25,FIND(" ",C25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C26,FIND(" ",C26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C28,FIND(" ",C28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C51,FIND(" ",C51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C52,FIND(" ",C52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C53,FIND(" ",C53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="D73" s="77">
-        <f>IFERROR(VALUE(LEFT(D25,FIND(" ",D25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D26,FIND(" ",D26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D28,FIND(" ",D28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D51,FIND(" ",D51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D52,FIND(" ",D52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D53,FIND(" ",D53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="E73" s="77">
-        <f>IFERROR(VALUE(LEFT(E25,FIND(" ",E25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E26,FIND(" ",E26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E28,FIND(" ",E28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E51,FIND(" ",E51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E52,FIND(" ",E52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E53,FIND(" ",E53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="F73" s="77">
-        <f>IFERROR(VALUE(LEFT(F25,FIND(" ",F25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F26,FIND(" ",F26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F28,FIND(" ",F28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F51,FIND(" ",F51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F52,FIND(" ",F52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F53,FIND(" ",F53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="G73" s="77">
-        <f>IFERROR(VALUE(LEFT(G25,FIND(" ",G25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G26,FIND(" ",G26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G28,FIND(" ",G28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G51,FIND(" ",G51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G52,FIND(" ",G52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G53,FIND(" ",G53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="H73" s="77">
-        <f>IFERROR(VALUE(LEFT(H25,FIND(" ",H25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H26,FIND(" ",H26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H28,FIND(" ",H28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H51,FIND(" ",H51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H52,FIND(" ",H52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H53,FIND(" ",H53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="I73" s="77">
-        <f>IFERROR(VALUE(LEFT(I25,FIND(" ",I25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I26,FIND(" ",I26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I28,FIND(" ",I28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I51,FIND(" ",I51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I52,FIND(" ",I52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I53,FIND(" ",I53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="J73" s="77">
-        <f>IFERROR(VALUE(LEFT(J25,FIND(" ",J25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J26,FIND(" ",J26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J28,FIND(" ",J28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J51,FIND(" ",J51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J52,FIND(" ",J52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J53,FIND(" ",J53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="K73" s="77" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="52">
       <c r="A74" s="76" t="inlineStr">
         <is>
-          <t>Pecho</t>
+          <t>Espalda</t>
         </is>
       </c>
       <c r="B74" s="77">
@@ -9570,35 +9588,35 @@
         <v/>
       </c>
       <c r="C74" s="77">
-        <f>IFERROR(VALUE(LEFT(C16,FIND(" ",C16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C18,FIND(" ",C18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C50,FIND(" ",C50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C26,FIND(" ",C26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C27,FIND(" ",C27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C29,FIND(" ",C29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C52,FIND(" ",C52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C53,FIND(" ",C53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C54,FIND(" ",C54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D74" s="77">
-        <f>IFERROR(VALUE(LEFT(D16,FIND(" ",D16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D18,FIND(" ",D18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D50,FIND(" ",D50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D26,FIND(" ",D26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D27,FIND(" ",D27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D29,FIND(" ",D29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D52,FIND(" ",D52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D53,FIND(" ",D53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D54,FIND(" ",D54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E74" s="77">
-        <f>IFERROR(VALUE(LEFT(E16,FIND(" ",E16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E18,FIND(" ",E18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E50,FIND(" ",E50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E26,FIND(" ",E26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E27,FIND(" ",E27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E29,FIND(" ",E29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E52,FIND(" ",E52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E53,FIND(" ",E53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E54,FIND(" ",E54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F74" s="77">
-        <f>IFERROR(VALUE(LEFT(F16,FIND(" ",F16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F18,FIND(" ",F18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F50,FIND(" ",F50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F26,FIND(" ",F26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F27,FIND(" ",F27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F29,FIND(" ",F29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F52,FIND(" ",F52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F53,FIND(" ",F53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F54,FIND(" ",F54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G74" s="77">
-        <f>IFERROR(VALUE(LEFT(G16,FIND(" ",G16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G18,FIND(" ",G18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G50,FIND(" ",G50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G26,FIND(" ",G26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G27,FIND(" ",G27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G29,FIND(" ",G29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G52,FIND(" ",G52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G53,FIND(" ",G53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G54,FIND(" ",G54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H74" s="77">
-        <f>IFERROR(VALUE(LEFT(H16,FIND(" ",H16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H18,FIND(" ",H18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H50,FIND(" ",H50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H26,FIND(" ",H26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H27,FIND(" ",H27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H29,FIND(" ",H29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H52,FIND(" ",H52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H53,FIND(" ",H53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H54,FIND(" ",H54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I74" s="77">
-        <f>IFERROR(VALUE(LEFT(I16,FIND(" ",I16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I18,FIND(" ",I18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I50,FIND(" ",I50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I26,FIND(" ",I26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I27,FIND(" ",I27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I29,FIND(" ",I29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I52,FIND(" ",I52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I53,FIND(" ",I53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I54,FIND(" ",I54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J74" s="77">
-        <f>IFERROR(VALUE(LEFT(J16,FIND(" ",J16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J18,FIND(" ",J18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J50,FIND(" ",J50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J26,FIND(" ",J26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J27,FIND(" ",J27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J29,FIND(" ",J29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J52,FIND(" ",J52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J53,FIND(" ",J53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J54,FIND(" ",J54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K74" s="77" t="n"/>
@@ -9606,7 +9624,7 @@
     <row r="75" ht="15.75" customHeight="1" s="52">
       <c r="A75" s="76" t="inlineStr">
         <is>
-          <t>Hombro lat.</t>
+          <t>Pecho</t>
         </is>
       </c>
       <c r="B75" s="77">
@@ -9614,35 +9632,35 @@
         <v/>
       </c>
       <c r="C75" s="77">
-        <f>IFERROR(VALUE(LEFT(C6,FIND(" ",C6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C8,FIND(" ",C8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C27,FIND(" ",C27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C47,FIND(" ",C47&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C16,FIND(" ",C16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C18,FIND(" ",C18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C51,FIND(" ",C51&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D75" s="77">
-        <f>IFERROR(VALUE(LEFT(D6,FIND(" ",D6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D8,FIND(" ",D8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D27,FIND(" ",D27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D47,FIND(" ",D47&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D16,FIND(" ",D16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D18,FIND(" ",D18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D51,FIND(" ",D51&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E75" s="77">
-        <f>IFERROR(VALUE(LEFT(E6,FIND(" ",E6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E8,FIND(" ",E8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E27,FIND(" ",E27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E47,FIND(" ",E47&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E16,FIND(" ",E16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E18,FIND(" ",E18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E51,FIND(" ",E51&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F75" s="77">
-        <f>IFERROR(VALUE(LEFT(F6,FIND(" ",F6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F8,FIND(" ",F8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F27,FIND(" ",F27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F47,FIND(" ",F47&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F16,FIND(" ",F16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F18,FIND(" ",F18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F51,FIND(" ",F51&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G75" s="77">
-        <f>IFERROR(VALUE(LEFT(G6,FIND(" ",G6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G8,FIND(" ",G8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G27,FIND(" ",G27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G47,FIND(" ",G47&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G16,FIND(" ",G16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G18,FIND(" ",G18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G51,FIND(" ",G51&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H75" s="77">
-        <f>IFERROR(VALUE(LEFT(H6,FIND(" ",H6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H8,FIND(" ",H8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H27,FIND(" ",H27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H47,FIND(" ",H47&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H16,FIND(" ",H16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H18,FIND(" ",H18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H51,FIND(" ",H51&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I75" s="77">
-        <f>IFERROR(VALUE(LEFT(I6,FIND(" ",I6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I8,FIND(" ",I8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I27,FIND(" ",I27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I47,FIND(" ",I47&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I16,FIND(" ",I16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I18,FIND(" ",I18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I51,FIND(" ",I51&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J75" s="77">
-        <f>IFERROR(VALUE(LEFT(J6,FIND(" ",J6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J8,FIND(" ",J8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J27,FIND(" ",J27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J47,FIND(" ",J47&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J16,FIND(" ",J16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J18,FIND(" ",J18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J51,FIND(" ",J51&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K75" s="77" t="n"/>
@@ -9650,7 +9668,7 @@
     <row r="76" ht="15.75" customHeight="1" s="52">
       <c r="A76" s="76" t="inlineStr">
         <is>
-          <t>Hombro post.</t>
+          <t>Hombro lat.</t>
         </is>
       </c>
       <c r="B76" s="77">
@@ -9658,35 +9676,35 @@
         <v/>
       </c>
       <c r="C76" s="77">
-        <f>IFERROR(VALUE(LEFT(C30,FIND(" ",C30&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C6,FIND(" ",C6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C8,FIND(" ",C8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C28,FIND(" ",C28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C48,FIND(" ",C48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D76" s="77">
-        <f>IFERROR(VALUE(LEFT(D30,FIND(" ",D30&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D6,FIND(" ",D6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D8,FIND(" ",D8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D28,FIND(" ",D28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D48,FIND(" ",D48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E76" s="77">
-        <f>IFERROR(VALUE(LEFT(E30,FIND(" ",E30&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E6,FIND(" ",E6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E8,FIND(" ",E8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E28,FIND(" ",E28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E48,FIND(" ",E48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F76" s="77">
-        <f>IFERROR(VALUE(LEFT(F30,FIND(" ",F30&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F6,FIND(" ",F6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F8,FIND(" ",F8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F28,FIND(" ",F28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F48,FIND(" ",F48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G76" s="77">
-        <f>IFERROR(VALUE(LEFT(G30,FIND(" ",G30&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G6,FIND(" ",G6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G8,FIND(" ",G8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G28,FIND(" ",G28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G48,FIND(" ",G48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H76" s="77">
-        <f>IFERROR(VALUE(LEFT(H30,FIND(" ",H30&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H6,FIND(" ",H6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H8,FIND(" ",H8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H28,FIND(" ",H28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H48,FIND(" ",H48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I76" s="77">
-        <f>IFERROR(VALUE(LEFT(I30,FIND(" ",I30&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I6,FIND(" ",I6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I8,FIND(" ",I8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I28,FIND(" ",I28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I48,FIND(" ",I48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J76" s="77">
-        <f>IFERROR(VALUE(LEFT(J30,FIND(" ",J30&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J6,FIND(" ",J6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J8,FIND(" ",J8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J28,FIND(" ",J28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J48,FIND(" ",J48&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K76" s="77" t="n"/>
@@ -9694,7 +9712,7 @@
     <row r="77" ht="15.75" customHeight="1" s="52">
       <c r="A77" s="76" t="inlineStr">
         <is>
-          <t>Bíceps</t>
+          <t>Hombro post.</t>
         </is>
       </c>
       <c r="B77" s="77">
@@ -9702,35 +9720,35 @@
         <v/>
       </c>
       <c r="C77" s="77">
-        <f>IFERROR(VALUE(LEFT(C29,FIND(" ",C29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C31,FIND(" ",C31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C49,FIND(" ",C49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C31,FIND(" ",C31&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D77" s="77">
-        <f>IFERROR(VALUE(LEFT(D29,FIND(" ",D29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D31,FIND(" ",D31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D49,FIND(" ",D49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D31,FIND(" ",D31&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E77" s="77">
-        <f>IFERROR(VALUE(LEFT(E29,FIND(" ",E29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E31,FIND(" ",E31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E49,FIND(" ",E49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E31,FIND(" ",E31&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F77" s="77">
-        <f>IFERROR(VALUE(LEFT(F29,FIND(" ",F29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F31,FIND(" ",F31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F49,FIND(" ",F49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F31,FIND(" ",F31&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G77" s="77">
-        <f>IFERROR(VALUE(LEFT(G29,FIND(" ",G29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G31,FIND(" ",G31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G49,FIND(" ",G49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G31,FIND(" ",G31&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H77" s="77">
-        <f>IFERROR(VALUE(LEFT(H29,FIND(" ",H29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H31,FIND(" ",H31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H49,FIND(" ",H49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H31,FIND(" ",H31&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I77" s="77">
-        <f>IFERROR(VALUE(LEFT(I29,FIND(" ",I29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I31,FIND(" ",I31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I49,FIND(" ",I49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I31,FIND(" ",I31&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J77" s="77">
-        <f>IFERROR(VALUE(LEFT(J29,FIND(" ",J29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J31,FIND(" ",J31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J49,FIND(" ",J49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J31,FIND(" ",J31&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K77" s="77" t="n"/>
@@ -9738,7 +9756,7 @@
     <row r="78" ht="15.75" customHeight="1" s="52">
       <c r="A78" s="76" t="inlineStr">
         <is>
-          <t>Tríceps</t>
+          <t>Bíceps</t>
         </is>
       </c>
       <c r="B78" s="77">
@@ -9746,35 +9764,35 @@
         <v/>
       </c>
       <c r="C78" s="77">
-        <f>IFERROR(VALUE(LEFT(C17,FIND(" ",C17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C19,FIND(" ",C19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C46,FIND(" ",C46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C48,FIND(" ",C48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C30,FIND(" ",C30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C32,FIND(" ",C32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C50,FIND(" ",C50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D78" s="77">
-        <f>IFERROR(VALUE(LEFT(D17,FIND(" ",D17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D19,FIND(" ",D19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D46,FIND(" ",D46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D48,FIND(" ",D48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D30,FIND(" ",D30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D32,FIND(" ",D32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D50,FIND(" ",D50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E78" s="77">
-        <f>IFERROR(VALUE(LEFT(E17,FIND(" ",E17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E19,FIND(" ",E19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E46,FIND(" ",E46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E48,FIND(" ",E48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E30,FIND(" ",E30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E32,FIND(" ",E32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E50,FIND(" ",E50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F78" s="77">
-        <f>IFERROR(VALUE(LEFT(F17,FIND(" ",F17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F19,FIND(" ",F19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F46,FIND(" ",F46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F48,FIND(" ",F48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F30,FIND(" ",F30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F32,FIND(" ",F32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F50,FIND(" ",F50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G78" s="77">
-        <f>IFERROR(VALUE(LEFT(G17,FIND(" ",G17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G19,FIND(" ",G19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G46,FIND(" ",G46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G48,FIND(" ",G48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G30,FIND(" ",G30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G32,FIND(" ",G32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G50,FIND(" ",G50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H78" s="77">
-        <f>IFERROR(VALUE(LEFT(H17,FIND(" ",H17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H19,FIND(" ",H19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H46,FIND(" ",H46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H48,FIND(" ",H48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H30,FIND(" ",H30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H32,FIND(" ",H32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H50,FIND(" ",H50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I78" s="77">
-        <f>IFERROR(VALUE(LEFT(I17,FIND(" ",I17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I19,FIND(" ",I19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I46,FIND(" ",I46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I48,FIND(" ",I48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I30,FIND(" ",I30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I32,FIND(" ",I32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I50,FIND(" ",I50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J78" s="77">
-        <f>IFERROR(VALUE(LEFT(J17,FIND(" ",J17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J19,FIND(" ",J19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J46,FIND(" ",J46&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J48,FIND(" ",J48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J30,FIND(" ",J30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J32,FIND(" ",J32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J50,FIND(" ",J50&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K78" s="77" t="n"/>
@@ -9782,7 +9800,7 @@
     <row r="79" ht="15.75" customHeight="1" s="52">
       <c r="A79" s="76" t="inlineStr">
         <is>
-          <t>Isquios</t>
+          <t>Tríceps</t>
         </is>
       </c>
       <c r="B79" s="77">
@@ -9790,35 +9808,35 @@
         <v/>
       </c>
       <c r="C79" s="77">
-        <f>IFERROR(VALUE(LEFT(C12,FIND(" ",C12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C40,FIND(" ",C40&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C17,FIND(" ",C17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C19,FIND(" ",C19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C47,FIND(" ",C47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C49,FIND(" ",C49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D79" s="77">
-        <f>IFERROR(VALUE(LEFT(D12,FIND(" ",D12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D40,FIND(" ",D40&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D17,FIND(" ",D17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D19,FIND(" ",D19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D47,FIND(" ",D47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D49,FIND(" ",D49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E79" s="77">
-        <f>IFERROR(VALUE(LEFT(E12,FIND(" ",E12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E40,FIND(" ",E40&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E17,FIND(" ",E17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E19,FIND(" ",E19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E47,FIND(" ",E47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E49,FIND(" ",E49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F79" s="77">
-        <f>IFERROR(VALUE(LEFT(F12,FIND(" ",F12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F40,FIND(" ",F40&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F17,FIND(" ",F17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F19,FIND(" ",F19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F47,FIND(" ",F47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F49,FIND(" ",F49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G79" s="77">
-        <f>IFERROR(VALUE(LEFT(G12,FIND(" ",G12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G40,FIND(" ",G40&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G17,FIND(" ",G17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G19,FIND(" ",G19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G47,FIND(" ",G47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G49,FIND(" ",G49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H79" s="77">
-        <f>IFERROR(VALUE(LEFT(H12,FIND(" ",H12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H40,FIND(" ",H40&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H17,FIND(" ",H17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H19,FIND(" ",H19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H47,FIND(" ",H47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H49,FIND(" ",H49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I79" s="77">
-        <f>IFERROR(VALUE(LEFT(I12,FIND(" ",I12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I40,FIND(" ",I40&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I17,FIND(" ",I17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I19,FIND(" ",I19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I47,FIND(" ",I47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I49,FIND(" ",I49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J79" s="77">
-        <f>IFERROR(VALUE(LEFT(J12,FIND(" ",J12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J40,FIND(" ",J40&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J17,FIND(" ",J17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J19,FIND(" ",J19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J47,FIND(" ",J47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J49,FIND(" ",J49&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K79" s="77" t="n"/>
@@ -9826,7 +9844,7 @@
     <row r="80" ht="15.75" customHeight="1" s="52">
       <c r="A80" s="76" t="inlineStr">
         <is>
-          <t>Abs</t>
+          <t>Isquios</t>
         </is>
       </c>
       <c r="B80" s="77">
@@ -9834,35 +9852,35 @@
         <v/>
       </c>
       <c r="C80" s="77">
-        <f>IFERROR(VALUE(LEFT(C20,FIND(" ",C20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C60,FIND(" ",C60&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C12,FIND(" ",C12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C41,FIND(" ",C41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D80" s="77">
-        <f>IFERROR(VALUE(LEFT(D20,FIND(" ",D20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D60,FIND(" ",D60&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D12,FIND(" ",D12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D41,FIND(" ",D41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E80" s="77">
-        <f>IFERROR(VALUE(LEFT(E20,FIND(" ",E20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E60,FIND(" ",E60&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E12,FIND(" ",E12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E41,FIND(" ",E41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F80" s="77">
-        <f>IFERROR(VALUE(LEFT(F20,FIND(" ",F20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F60,FIND(" ",F60&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F12,FIND(" ",F12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F41,FIND(" ",F41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G80" s="77">
-        <f>IFERROR(VALUE(LEFT(G20,FIND(" ",G20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G60,FIND(" ",G60&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G12,FIND(" ",G12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G41,FIND(" ",G41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H80" s="77">
-        <f>IFERROR(VALUE(LEFT(H20,FIND(" ",H20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H60,FIND(" ",H60&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H12,FIND(" ",H12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H41,FIND(" ",H41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I80" s="77">
-        <f>IFERROR(VALUE(LEFT(I20,FIND(" ",I20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I60,FIND(" ",I60&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I12,FIND(" ",I12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I41,FIND(" ",I41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J80" s="77">
-        <f>IFERROR(VALUE(LEFT(J20,FIND(" ",J20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J60,FIND(" ",J60&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J12,FIND(" ",J12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J41,FIND(" ",J41&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K80" s="77" t="n"/>
@@ -9870,7 +9888,7 @@
     <row r="81" ht="15.75" customHeight="1" s="52">
       <c r="A81" s="76" t="inlineStr">
         <is>
-          <t>Gemelos</t>
+          <t>Abs</t>
         </is>
       </c>
       <c r="B81" s="77">
@@ -9878,35 +9896,35 @@
         <v/>
       </c>
       <c r="C81" s="77">
-        <f>IFERROR(VALUE(LEFT(C11,FIND(" ",C11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C42,FIND(" ",C42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C20,FIND(" ",C20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C21,FIND(" ",C21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C61,FIND(" ",C61&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D81" s="77">
-        <f>IFERROR(VALUE(LEFT(D11,FIND(" ",D11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D42,FIND(" ",D42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D20,FIND(" ",D20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D21,FIND(" ",D21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D61,FIND(" ",D61&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E81" s="77">
-        <f>IFERROR(VALUE(LEFT(E11,FIND(" ",E11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E42,FIND(" ",E42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E20,FIND(" ",E20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E21,FIND(" ",E21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E61,FIND(" ",E61&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F81" s="77">
-        <f>IFERROR(VALUE(LEFT(F11,FIND(" ",F11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F42,FIND(" ",F42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F20,FIND(" ",F20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F21,FIND(" ",F21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F61,FIND(" ",F61&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G81" s="77">
-        <f>IFERROR(VALUE(LEFT(G11,FIND(" ",G11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G42,FIND(" ",G42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G20,FIND(" ",G20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G21,FIND(" ",G21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G61,FIND(" ",G61&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H81" s="77">
-        <f>IFERROR(VALUE(LEFT(H11,FIND(" ",H11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H42,FIND(" ",H42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H20,FIND(" ",H20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H21,FIND(" ",H21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H61,FIND(" ",H61&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I81" s="77">
-        <f>IFERROR(VALUE(LEFT(I11,FIND(" ",I11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I42,FIND(" ",I42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I20,FIND(" ",I20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I21,FIND(" ",I21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I61,FIND(" ",I61&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J81" s="77">
-        <f>IFERROR(VALUE(LEFT(J11,FIND(" ",J11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J42,FIND(" ",J42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J20,FIND(" ",J20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J21,FIND(" ",J21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J61,FIND(" ",J61&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K81" s="77" t="n"/>
@@ -9914,7 +9932,7 @@
     <row r="82" ht="15.75" customHeight="1" s="52">
       <c r="A82" s="76" t="inlineStr">
         <is>
-          <t>Aductores</t>
+          <t>Gemelos</t>
         </is>
       </c>
       <c r="B82" s="77">
@@ -9922,215 +9940,206 @@
         <v/>
       </c>
       <c r="C82" s="77">
-        <f>IFERROR(VALUE(LEFT(C41,FIND(" ",C41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C11,FIND(" ",C11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C43,FIND(" ",C43&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D82" s="77">
-        <f>IFERROR(VALUE(LEFT(D41,FIND(" ",D41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D11,FIND(" ",D11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D43,FIND(" ",D43&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E82" s="77">
-        <f>IFERROR(VALUE(LEFT(E41,FIND(" ",E41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E11,FIND(" ",E11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E43,FIND(" ",E43&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F82" s="77">
-        <f>IFERROR(VALUE(LEFT(F41,FIND(" ",F41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F11,FIND(" ",F11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F43,FIND(" ",F43&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G82" s="77">
-        <f>IFERROR(VALUE(LEFT(G41,FIND(" ",G41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G11,FIND(" ",G11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G43,FIND(" ",G43&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H82" s="77">
-        <f>IFERROR(VALUE(LEFT(H41,FIND(" ",H41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H11,FIND(" ",H11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H43,FIND(" ",H43&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I82" s="77">
-        <f>IFERROR(VALUE(LEFT(I41,FIND(" ",I41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I11,FIND(" ",I11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I43,FIND(" ",I43&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J82" s="77">
-        <f>IFERROR(VALUE(LEFT(J41,FIND(" ",J41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J11,FIND(" ",J11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J43,FIND(" ",J43&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K82" s="77" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="52">
-      <c r="A83" s="78" t="inlineStr">
+      <c r="A83" s="76" t="inlineStr">
+        <is>
+          <t>Aductores</t>
+        </is>
+      </c>
+      <c r="B83" s="77">
+        <f>C83&amp;" → "&amp;J83</f>
+        <v/>
+      </c>
+      <c r="C83" s="77">
+        <f>IFERROR(VALUE(LEFT(C42,FIND(" ",C42&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="D83" s="77">
+        <f>IFERROR(VALUE(LEFT(D42,FIND(" ",D42&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="E83" s="77">
+        <f>IFERROR(VALUE(LEFT(E42,FIND(" ",E42&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="F83" s="77">
+        <f>IFERROR(VALUE(LEFT(F42,FIND(" ",F42&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="G83" s="77">
+        <f>IFERROR(VALUE(LEFT(G42,FIND(" ",G42&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="H83" s="77">
+        <f>IFERROR(VALUE(LEFT(H42,FIND(" ",H42&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="I83" s="77">
+        <f>IFERROR(VALUE(LEFT(I42,FIND(" ",I42&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="J83" s="77">
+        <f>IFERROR(VALUE(LEFT(J42,FIND(" ",J42&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="K83" s="77" t="n"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1" s="52">
+      <c r="A84" s="78" t="inlineStr">
         <is>
           <t>TOTAL hipertrofia</t>
         </is>
       </c>
-      <c r="B83" s="75">
-        <f>C83&amp;" → "&amp;J83</f>
-        <v/>
-      </c>
-      <c r="C83" s="75">
-        <f>SUM(C73:C82)</f>
-        <v/>
-      </c>
-      <c r="D83" s="75">
-        <f>SUM(D73:D82)</f>
-        <v/>
-      </c>
-      <c r="E83" s="75">
-        <f>SUM(E73:E82)</f>
-        <v/>
-      </c>
-      <c r="F83" s="75">
-        <f>SUM(F73:F82)</f>
-        <v/>
-      </c>
-      <c r="G83" s="75">
-        <f>SUM(G73:G82)</f>
-        <v/>
-      </c>
-      <c r="H83" s="75">
-        <f>SUM(H73:H82)</f>
-        <v/>
-      </c>
-      <c r="I83" s="75">
-        <f>SUM(I73:I82)</f>
-        <v/>
-      </c>
-      <c r="J83" s="75">
-        <f>SUM(J73:J82)</f>
-        <v/>
-      </c>
-      <c r="K83" s="75" t="n"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1" s="52"/>
-    <row r="85" ht="19.5" customHeight="1" s="52">
-      <c r="A85" s="74" t="inlineStr">
+      <c r="B84" s="75">
+        <f>C84&amp;" → "&amp;J84</f>
+        <v/>
+      </c>
+      <c r="C84" s="75">
+        <f>SUM(C74:C83)</f>
+        <v/>
+      </c>
+      <c r="D84" s="75">
+        <f>SUM(D74:D83)</f>
+        <v/>
+      </c>
+      <c r="E84" s="75">
+        <f>SUM(E74:E83)</f>
+        <v/>
+      </c>
+      <c r="F84" s="75">
+        <f>SUM(F74:F83)</f>
+        <v/>
+      </c>
+      <c r="G84" s="75">
+        <f>SUM(G74:G83)</f>
+        <v/>
+      </c>
+      <c r="H84" s="75">
+        <f>SUM(H74:H83)</f>
+        <v/>
+      </c>
+      <c r="I84" s="75">
+        <f>SUM(I74:I83)</f>
+        <v/>
+      </c>
+      <c r="J84" s="75">
+        <f>SUM(J74:J83)</f>
+        <v/>
+      </c>
+      <c r="K84" s="75" t="n"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" s="52"/>
+    <row r="86" ht="19.5" customHeight="1" s="52">
+      <c r="A86" s="74" t="inlineStr">
         <is>
           <t>Desglose biomecánico de Espalda por planos (se recalcula solo al cambiar la tabla)</t>
         </is>
       </c>
-      <c r="B85" s="56" t="n"/>
-      <c r="C85" s="56" t="n"/>
-      <c r="D85" s="56" t="n"/>
-      <c r="E85" s="56" t="n"/>
-      <c r="F85" s="56" t="n"/>
-      <c r="G85" s="56" t="n"/>
-      <c r="H85" s="56" t="n"/>
-      <c r="I85" s="56" t="n"/>
-      <c r="J85" s="56" t="n"/>
-      <c r="K85" s="57" t="n"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1" s="52">
-      <c r="A86" s="75" t="inlineStr">
+      <c r="B86" s="56" t="n"/>
+      <c r="C86" s="56" t="n"/>
+      <c r="D86" s="56" t="n"/>
+      <c r="E86" s="56" t="n"/>
+      <c r="F86" s="56" t="n"/>
+      <c r="G86" s="56" t="n"/>
+      <c r="H86" s="56" t="n"/>
+      <c r="I86" s="56" t="n"/>
+      <c r="J86" s="56" t="n"/>
+      <c r="K86" s="57" t="n"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1" s="52">
+      <c r="A87" s="75" t="inlineStr">
         <is>
           <t>Plano / Región de Espalda</t>
         </is>
       </c>
-      <c r="B86" s="75" t="inlineStr">
+      <c r="B87" s="75" t="inlineStr">
         <is>
           <t>Sem 1 → Sem 8</t>
         </is>
       </c>
-      <c r="C86" s="75" t="inlineStr">
+      <c r="C87" s="75" t="inlineStr">
         <is>
           <t>Sem 1</t>
         </is>
       </c>
-      <c r="D86" s="75" t="inlineStr">
+      <c r="D87" s="75" t="inlineStr">
         <is>
           <t>Sem 2</t>
         </is>
       </c>
-      <c r="E86" s="75" t="inlineStr">
+      <c r="E87" s="75" t="inlineStr">
         <is>
           <t>Sem 3</t>
         </is>
       </c>
-      <c r="F86" s="75" t="inlineStr">
+      <c r="F87" s="75" t="inlineStr">
         <is>
           <t>Sem 4</t>
         </is>
       </c>
-      <c r="G86" s="75" t="inlineStr">
+      <c r="G87" s="75" t="inlineStr">
         <is>
           <t>Sem 5</t>
         </is>
       </c>
-      <c r="H86" s="75" t="inlineStr">
+      <c r="H87" s="75" t="inlineStr">
         <is>
           <t>Sem 6</t>
         </is>
       </c>
-      <c r="I86" s="75" t="inlineStr">
+      <c r="I87" s="75" t="inlineStr">
         <is>
           <t>Sem 7</t>
         </is>
       </c>
-      <c r="J86" s="75" t="inlineStr">
+      <c r="J87" s="75" t="inlineStr">
         <is>
           <t>Sem 8</t>
         </is>
       </c>
-      <c r="K86" s="51" t="inlineStr">
+      <c r="K87" s="51" t="inlineStr">
         <is>
           <t>Ejercicios incluidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" s="52">
-      <c r="A87" s="76" t="inlineStr">
-        <is>
-          <t>Dorsal Bajo (Plano Frontal)</t>
-        </is>
-      </c>
-      <c r="B87" s="77">
-        <f>C87&amp;" → "&amp;J87</f>
-        <v/>
-      </c>
-      <c r="C87" s="77">
-        <f>IFERROR(VALUE(LEFT(C25,FIND(" ",C25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C53,FIND(" ",C53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="D87" s="77">
-        <f>IFERROR(VALUE(LEFT(D25,FIND(" ",D25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D53,FIND(" ",D53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="E87" s="77">
-        <f>IFERROR(VALUE(LEFT(E25,FIND(" ",E25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E53,FIND(" ",E53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="F87" s="77">
-        <f>IFERROR(VALUE(LEFT(F25,FIND(" ",F25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F53,FIND(" ",F53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="G87" s="77">
-        <f>IFERROR(VALUE(LEFT(G25,FIND(" ",G25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G53,FIND(" ",G53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="H87" s="77">
-        <f>IFERROR(VALUE(LEFT(H25,FIND(" ",H25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H53,FIND(" ",H53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="I87" s="77">
-        <f>IFERROR(VALUE(LEFT(I25,FIND(" ",I25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I53,FIND(" ",I53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="J87" s="77">
-        <f>IFERROR(VALUE(LEFT(J25,FIND(" ",J25&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J53,FIND(" ",J53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="K87" s="79" t="inlineStr">
-        <is>
-          <t>Jalón ancho plano frontal (X) + Aducción unil. polea alta (V)</t>
-        </is>
-      </c>
-      <c r="L87" s="106" t="inlineStr">
-        <is>
-          <t>desglose=jalon-ancho-plano-frontal,aduccion-unil-polea-alta-pull-in</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="52">
       <c r="A88" s="76" t="inlineStr">
         <is>
-          <t>Dorsal Superior (Plano Sagital)</t>
+          <t>Dorsal Bajo (Plano Frontal)</t>
         </is>
       </c>
       <c r="B88" s="77">
@@ -10138,52 +10147,52 @@
         <v/>
       </c>
       <c r="C88" s="77">
-        <f>IFERROR(VALUE(LEFT(C28,FIND(" ",C28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C51,FIND(" ",C51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C52,FIND(" ",C52&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C26,FIND(" ",C26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C54,FIND(" ",C54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D88" s="77">
-        <f>IFERROR(VALUE(LEFT(D28,FIND(" ",D28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D51,FIND(" ",D51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D52,FIND(" ",D52&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D26,FIND(" ",D26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D54,FIND(" ",D54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E88" s="77">
-        <f>IFERROR(VALUE(LEFT(E28,FIND(" ",E28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E51,FIND(" ",E51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E52,FIND(" ",E52&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E26,FIND(" ",E26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E54,FIND(" ",E54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F88" s="77">
-        <f>IFERROR(VALUE(LEFT(F28,FIND(" ",F28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F51,FIND(" ",F51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F52,FIND(" ",F52&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F26,FIND(" ",F26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F54,FIND(" ",F54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G88" s="77">
-        <f>IFERROR(VALUE(LEFT(G28,FIND(" ",G28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G51,FIND(" ",G51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G52,FIND(" ",G52&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G26,FIND(" ",G26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G54,FIND(" ",G54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H88" s="77">
-        <f>IFERROR(VALUE(LEFT(H28,FIND(" ",H28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H51,FIND(" ",H51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H52,FIND(" ",H52&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H26,FIND(" ",H26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H54,FIND(" ",H54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I88" s="77">
-        <f>IFERROR(VALUE(LEFT(I28,FIND(" ",I28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I51,FIND(" ",I51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I52,FIND(" ",I52&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I26,FIND(" ",I26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I54,FIND(" ",I54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J88" s="77">
-        <f>IFERROR(VALUE(LEFT(J28,FIND(" ",J28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J51,FIND(" ",J51&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J52,FIND(" ",J52&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J26,FIND(" ",J26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J54,FIND(" ",J54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K88" s="79" t="inlineStr">
         <is>
-          <t>Jalón neutro bolsillos (X) + Dominada neutra (V) + Remo máq. 30° (V)</t>
+          <t>Jalón ancho plano frontal (X) + Aducción unil. polea alta (V)</t>
         </is>
       </c>
       <c r="L88" s="106" t="inlineStr">
         <is>
-          <t>desglose=jalon-neutro,dominada-neutra-dorsal,remo-maquina-pecho-apoyado-30</t>
+          <t>desglose=jalon-ancho-plano-frontal,aduccion-unil-polea-alta-pull-in</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="52">
       <c r="A89" s="76" t="inlineStr">
         <is>
-          <t>Espalda Alta (Plano Transversal)</t>
+          <t>Dorsal Superior (Plano Sagital)</t>
         </is>
       </c>
       <c r="B89" s="77">
@@ -10191,460 +10200,513 @@
         <v/>
       </c>
       <c r="C89" s="77">
-        <f>IFERROR(VALUE(LEFT(C26,FIND(" ",C26&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C29,FIND(" ",C29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C52,FIND(" ",C52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C53,FIND(" ",C53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D89" s="77">
-        <f>IFERROR(VALUE(LEFT(D26,FIND(" ",D26&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D29,FIND(" ",D29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D52,FIND(" ",D52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D53,FIND(" ",D53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E89" s="77">
-        <f>IFERROR(VALUE(LEFT(E26,FIND(" ",E26&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E29,FIND(" ",E29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E52,FIND(" ",E52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E53,FIND(" ",E53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F89" s="77">
-        <f>IFERROR(VALUE(LEFT(F26,FIND(" ",F26&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F29,FIND(" ",F29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F52,FIND(" ",F52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F53,FIND(" ",F53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G89" s="77">
-        <f>IFERROR(VALUE(LEFT(G26,FIND(" ",G26&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G29,FIND(" ",G29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G52,FIND(" ",G52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G53,FIND(" ",G53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H89" s="77">
-        <f>IFERROR(VALUE(LEFT(H26,FIND(" ",H26&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H29,FIND(" ",H29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H52,FIND(" ",H52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H53,FIND(" ",H53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I89" s="77">
-        <f>IFERROR(VALUE(LEFT(I26,FIND(" ",I26&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I29,FIND(" ",I29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I52,FIND(" ",I52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I53,FIND(" ",I53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J89" s="77">
-        <f>IFERROR(VALUE(LEFT(J26,FIND(" ",J26&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J29,FIND(" ",J29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J52,FIND(" ",J52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J53,FIND(" ",J53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K89" s="79" t="inlineStr">
         <is>
+          <t>Jalón neutro bolsillos (X) + Dominada neutra (V) + Remo máq. 30° (V)</t>
+        </is>
+      </c>
+      <c r="L89" s="106" t="inlineStr">
+        <is>
+          <t>desglose=jalon-neutro,dominada-neutra-dorsal,remo-maquina-pecho-apoyado-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1" s="52">
+      <c r="A90" s="76" t="inlineStr">
+        <is>
+          <t>Espalda Alta (Plano Transversal)</t>
+        </is>
+      </c>
+      <c r="B90" s="77">
+        <f>C90&amp;" → "&amp;J90</f>
+        <v/>
+      </c>
+      <c r="C90" s="77">
+        <f>IFERROR(VALUE(LEFT(C27,FIND(" ",C27&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="D90" s="77">
+        <f>IFERROR(VALUE(LEFT(D27,FIND(" ",D27&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="E90" s="77">
+        <f>IFERROR(VALUE(LEFT(E27,FIND(" ",E27&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="F90" s="77">
+        <f>IFERROR(VALUE(LEFT(F27,FIND(" ",F27&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="G90" s="77">
+        <f>IFERROR(VALUE(LEFT(G27,FIND(" ",G27&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="H90" s="77">
+        <f>IFERROR(VALUE(LEFT(H27,FIND(" ",H27&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="I90" s="77">
+        <f>IFERROR(VALUE(LEFT(I27,FIND(" ",I27&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="J90" s="77">
+        <f>IFERROR(VALUE(LEFT(J27,FIND(" ",J27&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="K90" s="79" t="inlineStr">
+        <is>
           <t>Remo gironda abierto (X)</t>
         </is>
       </c>
-      <c r="L89" s="106" t="inlineStr">
+      <c r="L90" s="106" t="inlineStr">
         <is>
           <t>desglose=remo-gironda-abierto</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="15.75" customHeight="1" s="52">
-      <c r="A90" s="78" t="inlineStr">
+    <row r="91" ht="15.75" customHeight="1" s="52">
+      <c r="A91" s="78" t="inlineStr">
         <is>
           <t>Total Transversal (Espalda Alta + Post.)</t>
         </is>
       </c>
-      <c r="B90" s="75">
-        <f>C90&amp;" → "&amp;J90</f>
-        <v/>
-      </c>
-      <c r="C90" s="75">
-        <f>IFERROR(VALUE(LEFT(C26,FIND(" ",C26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C30,FIND(" ",C30&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="D90" s="75">
-        <f>IFERROR(VALUE(LEFT(D26,FIND(" ",D26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D30,FIND(" ",D30&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="E90" s="75">
-        <f>IFERROR(VALUE(LEFT(E26,FIND(" ",E26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E30,FIND(" ",E30&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="F90" s="75">
-        <f>IFERROR(VALUE(LEFT(F26,FIND(" ",F26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F30,FIND(" ",F30&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="G90" s="75">
-        <f>IFERROR(VALUE(LEFT(G26,FIND(" ",G26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G30,FIND(" ",G30&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="H90" s="75">
-        <f>IFERROR(VALUE(LEFT(H26,FIND(" ",H26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H30,FIND(" ",H30&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="I90" s="75">
-        <f>IFERROR(VALUE(LEFT(I26,FIND(" ",I26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I30,FIND(" ",I30&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="J90" s="75">
-        <f>IFERROR(VALUE(LEFT(J26,FIND(" ",J26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J30,FIND(" ",J30&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="K90" s="80" t="inlineStr">
+      <c r="B91" s="75">
+        <f>C91&amp;" → "&amp;J91</f>
+        <v/>
+      </c>
+      <c r="C91" s="75">
+        <f>IFERROR(VALUE(LEFT(C27,FIND(" ",C27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C31,FIND(" ",C31&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="D91" s="75">
+        <f>IFERROR(VALUE(LEFT(D27,FIND(" ",D27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D31,FIND(" ",D31&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="E91" s="75">
+        <f>IFERROR(VALUE(LEFT(E27,FIND(" ",E27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E31,FIND(" ",E31&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="F91" s="75">
+        <f>IFERROR(VALUE(LEFT(F27,FIND(" ",F27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F31,FIND(" ",F31&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="G91" s="75">
+        <f>IFERROR(VALUE(LEFT(G27,FIND(" ",G27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G31,FIND(" ",G31&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="H91" s="75">
+        <f>IFERROR(VALUE(LEFT(H27,FIND(" ",H27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H31,FIND(" ",H31&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="I91" s="75">
+        <f>IFERROR(VALUE(LEFT(I27,FIND(" ",I27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I31,FIND(" ",I31&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="J91" s="75">
+        <f>IFERROR(VALUE(LEFT(J27,FIND(" ",J27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J31,FIND(" ",J31&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="K91" s="80" t="inlineStr">
         <is>
           <t>Remo gironda abierto (X) + Posterior polea (X)</t>
         </is>
       </c>
-      <c r="L90" s="106" t="inlineStr">
+      <c r="L91" s="106" t="inlineStr">
         <is>
           <t>desglose=remo-gironda-abierto,posterior-polea</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="15.75" customHeight="1" s="52"/>
     <row r="92" ht="15.75" customHeight="1" s="52"/>
-    <row r="93" ht="19.5" customHeight="1" s="52">
-      <c r="A93" s="74" t="inlineStr">
+    <row r="93" ht="15.75" customHeight="1" s="52"/>
+    <row r="94" ht="19.5" customHeight="1" s="52">
+      <c r="A94" s="74" t="inlineStr">
         <is>
           <t>BLOQUE DE CARDIO Y CARRERA (S2-S8)</t>
         </is>
       </c>
-      <c r="B93" s="56" t="n"/>
-      <c r="C93" s="56" t="n"/>
-      <c r="D93" s="56" t="n"/>
-      <c r="E93" s="56" t="n"/>
-      <c r="F93" s="56" t="n"/>
-      <c r="G93" s="56" t="n"/>
-      <c r="H93" s="56" t="n"/>
-      <c r="I93" s="56" t="n"/>
-      <c r="J93" s="56" t="n"/>
-      <c r="K93" s="57" t="n"/>
-      <c r="L93" s="106" t="inlineStr">
+      <c r="B94" s="56" t="n"/>
+      <c r="C94" s="56" t="n"/>
+      <c r="D94" s="56" t="n"/>
+      <c r="E94" s="56" t="n"/>
+      <c r="F94" s="56" t="n"/>
+      <c r="G94" s="56" t="n"/>
+      <c r="H94" s="56" t="n"/>
+      <c r="I94" s="56" t="n"/>
+      <c r="J94" s="56" t="n"/>
+      <c r="K94" s="57" t="n"/>
+      <c r="L94" s="106" t="inlineStr">
         <is>
           <t>cardio</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="15.75" customHeight="1" s="52">
-      <c r="A94" s="75" t="inlineStr">
+    <row r="95" ht="15.75" customHeight="1" s="52">
+      <c r="A95" s="75" t="inlineStr">
         <is>
           <t>Día / Sesión</t>
         </is>
       </c>
-      <c r="B94" s="75" t="inlineStr">
+      <c r="B95" s="75" t="inlineStr">
         <is>
           <t>Tipo / Zona</t>
         </is>
       </c>
-      <c r="C94" s="75" t="inlineStr">
+      <c r="C95" s="75" t="inlineStr">
         <is>
           <t>Sem 1</t>
         </is>
       </c>
-      <c r="D94" s="75" t="inlineStr">
+      <c r="D95" s="75" t="inlineStr">
         <is>
           <t>Sem 2</t>
         </is>
       </c>
-      <c r="E94" s="75" t="inlineStr">
+      <c r="E95" s="75" t="inlineStr">
         <is>
           <t>Sem 3</t>
         </is>
       </c>
-      <c r="F94" s="75" t="inlineStr">
+      <c r="F95" s="75" t="inlineStr">
         <is>
           <t>Sem 4</t>
         </is>
       </c>
-      <c r="G94" s="75" t="inlineStr">
+      <c r="G95" s="75" t="inlineStr">
         <is>
           <t>Sem 5</t>
         </is>
       </c>
-      <c r="H94" s="75" t="inlineStr">
+      <c r="H95" s="75" t="inlineStr">
         <is>
           <t>Sem 6</t>
         </is>
       </c>
-      <c r="I94" s="75" t="inlineStr">
+      <c r="I95" s="75" t="inlineStr">
         <is>
           <t>Sem 7</t>
         </is>
       </c>
-      <c r="J94" s="75" t="inlineStr">
+      <c r="J95" s="75" t="inlineStr">
         <is>
           <t>Sem 8</t>
         </is>
       </c>
-      <c r="K94" s="51" t="inlineStr">
+      <c r="K95" s="51" t="inlineStr">
         <is>
           <t>Pautas Biomecánicas Rodilla &amp; Intensidad</t>
         </is>
       </c>
-      <c r="L94" s="106" t="inlineStr">
+      <c r="L95" s="106" t="inlineStr">
         <is>
           <t>App (no tocar)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="55.5" customHeight="1" s="52">
-      <c r="A95" s="81" t="inlineStr">
+    <row r="96" ht="55.5" customHeight="1" s="52">
+      <c r="A96" s="81" t="inlineStr">
         <is>
           <t>Martes (Post-Push)</t>
         </is>
       </c>
-      <c r="B95" s="82" t="inlineStr">
+      <c r="B96" s="82" t="inlineStr">
         <is>
           <t>Bici Z2 (65–75% FC)</t>
         </is>
       </c>
-      <c r="C95" s="77" t="inlineStr">
+      <c r="C96" s="77" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="D95" s="83" t="inlineStr">
+      <c r="D96" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E95" s="83" t="inlineStr">
+      <c r="E96" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F95" s="83" t="inlineStr">
+      <c r="F96" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G95" s="83" t="inlineStr">
+      <c r="G96" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="H95" s="83" t="inlineStr">
+      <c r="H96" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="I95" s="83" t="inlineStr">
+      <c r="I96" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="J95" s="83" t="inlineStr">
+      <c r="J96" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="K95" s="62" t="inlineStr">
+      <c r="K96" s="62" t="inlineStr">
         <is>
           <t>No se hizo en S1: estímulo NUEVO [LÓGICA]. Entra en S4 (el viernes) solo si S2 y S3 cumplieron la regla; desde S5, martes y viernes. Sin Z3 en este bloque. Lo primero que se quita si hay brote. Sillín alto (rodilla a 20-25° abajo), 85-90 rpm, sentado. 10 min fijos en el bloque; subir a 15 después del viaje, como novedad única.</t>
         </is>
       </c>
-      <c r="L95" s="106" t="inlineStr">
+      <c r="L96" s="106" t="inlineStr">
         <is>
           <t>id=bici-z2-65-75-fc;sesion=M;bici</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="30.75" customHeight="1" s="52">
-      <c r="A96" s="81" t="inlineStr">
+    <row r="97" ht="30.75" customHeight="1" s="52">
+      <c r="A97" s="81" t="inlineStr">
         <is>
           <t>Viernes (Post-Torso)</t>
         </is>
       </c>
-      <c r="B96" s="82" t="inlineStr">
+      <c r="B97" s="82" t="inlineStr">
         <is>
           <t>Bici Z2 (sin Z3 en este bloque)</t>
         </is>
       </c>
-      <c r="C96" s="77" t="inlineStr">
+      <c r="C97" s="77" t="inlineStr">
         <is>
           <t>12 min</t>
         </is>
       </c>
-      <c r="D96" s="83" t="inlineStr">
+      <c r="D97" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E96" s="83" t="inlineStr">
+      <c r="E97" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F96" s="83" t="inlineStr">
+      <c r="F97" s="83" t="inlineStr">
         <is>
           <t>10' Z2
 nov: 1.ª vez</t>
         </is>
       </c>
-      <c r="G96" s="83" t="inlineStr">
+      <c r="G97" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="H96" s="83" t="inlineStr">
+      <c r="H97" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="I96" s="83" t="inlineStr">
+      <c r="I97" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="J96" s="83" t="inlineStr">
+      <c r="J97" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="K96" s="62" t="inlineStr">
+      <c r="K97" s="62" t="inlineStr">
         <is>
           <t>S4: primera vez, solo si esa mañana estás igual o mejor; se valida con las mediciones del sábado y del domingo (el sábado no hay pierna). Ver la nota del martes.</t>
         </is>
       </c>
-      <c r="L96" s="106" t="inlineStr">
+      <c r="L97" s="106" t="inlineStr">
         <is>
           <t>id=bici-z2-sin-z3-en-este-bloque;sesion=V;bici</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="81" customHeight="1" s="52">
-      <c r="A97" s="81" t="inlineStr">
+    <row r="98" ht="81" customHeight="1" s="52">
+      <c r="A98" s="81" t="inlineStr">
         <is>
           <t>Miércoles · Carrera (nivel nuevo)</t>
         </is>
       </c>
-      <c r="B97" s="82" t="inlineStr">
+      <c r="B98" s="82" t="inlineStr">
         <is>
           <t>Andar-correr en llano</t>
         </is>
       </c>
-      <c r="C97" s="83" t="inlineStr">
+      <c r="C98" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D97" s="83" t="inlineStr">
+      <c r="D98" s="83" t="inlineStr">
         <is>
           <t>N1 · 8×(1'/2')</t>
         </is>
       </c>
-      <c r="E97" s="83" t="inlineStr">
+      <c r="E98" s="83" t="inlineStr">
         <is>
           <t>N2 · 6×(2'/1')</t>
         </is>
       </c>
-      <c r="F97" s="83" t="inlineStr">
+      <c r="F98" s="83" t="inlineStr">
         <is>
           <t>N3 · 4×(4'/1')</t>
         </is>
       </c>
-      <c r="G97" s="83" t="inlineStr">
+      <c r="G98" s="83" t="inlineStr">
         <is>
           <t>N4 · 4×(5'/1')</t>
         </is>
       </c>
-      <c r="H97" s="83" t="inlineStr">
+      <c r="H98" s="83" t="inlineStr">
         <is>
           <t>N5 · 3×(8'/1')</t>
         </is>
       </c>
-      <c r="I97" s="83" t="inlineStr">
+      <c r="I98" s="83" t="inlineStr">
         <is>
           <t>N6 · 2×(12'/1')</t>
         </is>
       </c>
-      <c r="J97" s="83" t="inlineStr">
+      <c r="J98" s="83" t="inlineStr">
         <is>
           <t>repite N6</t>
         </is>
       </c>
-      <c r="K97" s="62" t="inlineStr">
+      <c r="K98" s="62" t="inlineStr">
         <is>
           <t>Formato: minutos trotando / minutos andando. Niveles: N1 8×(1'/2') · N2 6×(2'/1') · N3 4×(4'/1') · N4 4×(5'/1') · N5 3×(8'/1') · N6 2×(12'/1'); después del viaje, N7 18' · N8 25' · N9 30' seguidos. Desde N4 el tramo continuo más largo crece como mucho un 50 % por nivel (5 → 8 → 12 → 18 → 25 → 30 min); de N1 a N3 se dobla porque los tramos son muy cortos [LÓGICA]. El calendario marca el máximo de cada semana; el nivel real sale del semáforo: Avanzar = +1, Mantener = el mismo, Retroceder = −1. Nivel nuevo solo si esa mañana estás igual o mejor. 5 min andando antes; llano y firme. Regla de carrera: Retroceder si pasas de 2/10 durante, no vuelves al nivel previo en ≤60 min o la mañana siguiente estás peor; Mantener si cumple pero el peor valor 24-48 h supera la referencia; Avanzar si cumple y el peor 24-48 h ≤ referencia [EVIDENCIA de uso: TREK Education, basada en Esculier; no comparada con otros umbrales]. Cadencia +5-10% opcional [EVIDENCIA mixta: Bramah 2019, serie de 12 corredores con mejora de dolor y función mantenida a 3 meses; Esculier 2018, sin beneficio extra sobre la educación].</t>
         </is>
       </c>
-      <c r="L97" s="106" t="inlineStr">
+      <c r="L98" s="106" t="inlineStr">
         <is>
           <t>id=andar-correr-en-llano;sesion=X;escalera=carrera</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="30.75" customHeight="1" s="52">
-      <c r="A98" s="81" t="inlineStr">
+    <row r="99" ht="30.75" customHeight="1" s="52">
+      <c r="A99" s="81" t="inlineStr">
         <is>
           <t>Domingo · Carrera (repite)</t>
         </is>
       </c>
-      <c r="B98" s="82" t="inlineStr">
+      <c r="B99" s="82" t="inlineStr">
         <is>
           <t>Andar-correr en llano</t>
         </is>
       </c>
-      <c r="C98" s="83" t="inlineStr">
+      <c r="C99" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D98" s="83" t="inlineStr">
+      <c r="D99" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="E98" s="83" t="inlineStr">
+      <c r="E99" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="F98" s="83" t="inlineStr">
+      <c r="F99" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="G98" s="83" t="inlineStr">
+      <c r="G99" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="H98" s="83" t="inlineStr">
+      <c r="H99" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="I98" s="83" t="inlineStr">
+      <c r="I99" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="J98" s="83" t="inlineStr">
+      <c r="J99" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="K98" s="62" t="inlineStr">
+      <c r="K99" s="62" t="inlineStr">
         <is>
           <t>Repite el nivel validado el miércoles. Si el miércoles no se cumplieron los criterios de entrada, esa semana no hay carrera: el domingo no se corre (como mucho, un paseo). Nunca dos días seguidos corriendo [LÓGICA]. El sábado no hay pierna: llegas descansado.</t>
         </is>
       </c>
-      <c r="L98" s="106" t="inlineStr">
+      <c r="L99" s="106" t="inlineStr">
         <is>
           <t>id=andar-correr-en-llano;sesion=D;titulo=Carrera;escalera=carrera:domingo</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="55.5" customHeight="1" s="52">
-      <c r="A99" s="81" t="inlineStr">
+    <row r="100" ht="55.5" customHeight="1" s="52">
+      <c r="A100" s="81" t="inlineStr">
         <is>
           <t>Hitos y avisos</t>
         </is>
       </c>
-      <c r="B99" s="82" t="inlineStr">
+      <c r="B100" s="82" t="inlineStr">
         <is>
           <t>Calendario</t>
         </is>
       </c>
-      <c r="C99" s="83" t="inlineStr">
+      <c r="C100" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D99" s="83" t="inlineStr">
+      <c r="D100" s="83" t="inlineStr">
         <is>
           <t>Mar: paseo 30'
 Mié: TD + saltitos
@@ -10652,79 +10714,57 @@
 Jue: test 1</t>
         </is>
       </c>
-      <c r="E99" s="83" t="inlineStr">
+      <c r="E100" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F99" s="83" t="inlineStr">
+      <c r="F100" s="83" t="inlineStr">
         <is>
           <t>AVISO fisio
 (ver Seguimiento)
 Vie: bici</t>
         </is>
       </c>
-      <c r="G99" s="83" t="inlineStr">
+      <c r="G100" s="83" t="inlineStr">
         <is>
           <t>Lun: x8
 Jue: test 2</t>
         </is>
       </c>
-      <c r="H99" s="83" t="inlineStr">
+      <c r="H100" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I99" s="83" t="inlineStr">
+      <c r="I100" s="83" t="inlineStr">
         <is>
           <t>Jue: test 3</t>
         </is>
       </c>
-      <c r="J99" s="83" t="inlineStr">
+      <c r="J100" s="83" t="inlineStr">
         <is>
           <t>Repite S7
 Jue: test opc.
 rango completo</t>
         </is>
       </c>
-      <c r="K99" s="62" t="inlineStr">
+      <c r="K100" s="62" t="inlineStr">
         <is>
           <t>Entrada a la carrera (S2), con la regla de carrera: martes, paseo de 30 min a paso rápido (≤2/10, nivel previo en ≤60 min y el miércoles por la mañana no peor: el criterio 1 se evalúa solo con esa mañana, sin esperar a las 48 h); miércoles antes de correr, 10 touchdown con cada pierna y 20 saltitos a dos piernas (≤2/10). Si se cumplen los tres, 1.ª carrera ese miércoles (N1). Si no, esa semana no hay carrera (el domingo, como mucho, un paseo) y los criterios se repiten el miércoles siguiente [LÓGICA].</t>
         </is>
       </c>
-      <c r="L99" s="106" t="inlineStr">
+      <c r="L100" s="106" t="inlineStr">
         <is>
           <t>hitos</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="15.75" customHeight="1" s="52"/>
-    <row r="101" ht="19.5" customHeight="1" s="52">
-      <c r="A101" s="74" t="inlineStr">
+    <row r="101" ht="15.75" customHeight="1" s="52"/>
+    <row r="102" ht="19.5" customHeight="1" s="52">
+      <c r="A102" s="74" t="inlineStr">
         <is>
           <t>REGLAS DEL BLOQUE RODILLA (S2-S8)</t>
-        </is>
-      </c>
-      <c r="B101" s="56" t="n"/>
-      <c r="C101" s="56" t="n"/>
-      <c r="D101" s="56" t="n"/>
-      <c r="E101" s="56" t="n"/>
-      <c r="F101" s="56" t="n"/>
-      <c r="G101" s="56" t="n"/>
-      <c r="H101" s="56" t="n"/>
-      <c r="I101" s="56" t="n"/>
-      <c r="J101" s="56" t="n"/>
-      <c r="K101" s="57" t="n"/>
-      <c r="L101" s="106" t="inlineStr">
-        <is>
-          <t>reglas-bloque</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="30.75" customHeight="1" s="52">
-      <c r="A102" s="67" t="inlineStr">
-        <is>
-          <t>Base [EVIDENCIA]: ejercicio combinado de cadera y rodilla (consensos de 2016 y 2018). Rodilla en 2 días, lunes y jueves (72-96 h entre sesiones, dentro de la ventana de 2-3 días de recuperación del tendón que describe el libro), pesado y lento en ambos; sábado sin pierna para llegar descansado a la carrera del domingo [LÓGICA].</t>
         </is>
       </c>
       <c r="B102" s="56" t="n"/>
@@ -10737,11 +10777,16 @@
       <c r="I102" s="56" t="n"/>
       <c r="J102" s="56" t="n"/>
       <c r="K102" s="57" t="n"/>
+      <c r="L102" s="106" t="inlineStr">
+        <is>
+          <t>reglas-bloque</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="30.75" customHeight="1" s="52">
       <c r="A103" s="67" t="inlineStr">
         <is>
-          <t>Mediciones: cada mañana, en casa, con las mismas pruebas: test en declive y 10 subidas con la D al mismo escalón o banco. Vale la peor de las dos (el declive solo no basta: te sale 0 aunque haya molestia). Si falta la medición de la mañana, ese día no se evalúa y la primera medición disponible hace de referencia (en S2, la del martes). Se apuntan en «Seguimiento rodilla».</t>
+          <t>Base [EVIDENCIA]: ejercicio combinado de cadera y rodilla (consensos de 2016 y 2018). Rodilla en 2 días, lunes y jueves (72-96 h entre sesiones, dentro de la ventana de 2-3 días de recuperación del tendón que describe el libro), pesado y lento en ambos; sábado sin pierna para llegar descansado a la carrera del domingo [LÓGICA].</t>
         </is>
       </c>
       <c r="B103" s="56" t="n"/>
@@ -10755,10 +10800,10 @@
       <c r="J103" s="56" t="n"/>
       <c r="K103" s="57" t="n"/>
     </row>
-    <row r="104" ht="18" customHeight="1" s="52">
+    <row r="104" ht="30.75" customHeight="1" s="52">
       <c r="A104" s="67" t="inlineStr">
         <is>
-          <t>Regla de gimnasio [LÓGICA], en semáforo (solo días con carga de rodilla: lunes y jueves): Retroceder si pasas de 3/10 durante o la mañana siguiente estás peor que la de la sesión; Mantener si cumple, pero el peor valor entre 24 y 48 h supera la referencia (no avanzas, pero no has fallado); Avanzar si cumple y el peor valor 24-48 h es igual o mejor que la referencia. Los días sin carga de rodilla no se evalúan («—»).</t>
+          <t>Mediciones: cada mañana, en casa, con las mismas pruebas: test en declive y 10 subidas con la D al mismo escalón o banco. Vale la peor de las dos (el declive solo no basta: te sale 0 aunque haya molestia). Si falta la medición de la mañana, ese día no se evalúa y la primera medición disponible hace de referencia (en S2, la del martes). Se apuntan en «Seguimiento rodilla».</t>
         </is>
       </c>
       <c r="B104" s="56" t="n"/>
@@ -10772,10 +10817,10 @@
       <c r="J104" s="56" t="n"/>
       <c r="K104" s="57" t="n"/>
     </row>
-    <row r="105" ht="30.75" customHeight="1" s="52">
+    <row r="105" ht="18" customHeight="1" s="52">
       <c r="A105" s="67" t="inlineStr">
         <is>
-          <t>Regla de carrera [EVIDENCIA de uso], en semáforo (miércoles y domingo): Retroceder si pasas de 2/10 durante, no vuelves al nivel previo en ≤60 min o la mañana siguiente estás peor; Mantener si cumple, pero el peor valor 24-48 h supera la referencia; Avanzar si cumple y el peor valor 24-48 h ≤ referencia. El paseo de entrada se valida solo con la mañana siguiente. Se aplica también a las fases hacia el fútbol [LÓGICA].</t>
+          <t>Regla de gimnasio [LÓGICA], en semáforo (solo días con carga de rodilla: lunes y jueves): Retroceder si pasas de 3/10 durante o la mañana siguiente estás peor que la de la sesión; Mantener si cumple, pero el peor valor entre 24 y 48 h supera la referencia (no avanzas, pero no has fallado); Avanzar si cumple y el peor valor 24-48 h es igual o mejor que la referencia. Los días sin carga de rodilla no se evalúan («—»).</t>
         </is>
       </c>
       <c r="B105" s="56" t="n"/>
@@ -10792,7 +10837,7 @@
     <row r="106" ht="30.75" customHeight="1" s="52">
       <c r="A106" s="67" t="inlineStr">
         <is>
-          <t>Novedades [LÓGICA]: una por día y validada a las 24 y 48 h antes de repetirla. Lunes: escalón o reps (prensa) · miércoles: nivel de carrera · viernes de S4: bici. Solo si esa mañana estás igual o mejor que la referencia (la mañana del mismo día de la semana anterior; en S3, la primera medición de S2), no que el día anterior: así un empeoramiento lento también salta. El calendario marca el máximo de cada semana; el nivel real sale del semáforo: Avanzar = nivel +1 (sin pasar del calendario), Mantener = el mismo, Retroceder = nivel −1. Lo validado se repite: el jueves usa la profundidad del lunes y el domingo repite el nivel del miércoles.</t>
+          <t>Regla de carrera [EVIDENCIA de uso], en semáforo (miércoles y domingo): Retroceder si pasas de 2/10 durante, no vuelves al nivel previo en ≤60 min o la mañana siguiente estás peor; Mantener si cumple, pero el peor valor 24-48 h supera la referencia; Avanzar si cumple y el peor valor 24-48 h ≤ referencia. El paseo de entrada se valida solo con la mañana siguiente. Se aplica también a las fases hacia el fútbol [LÓGICA].</t>
         </is>
       </c>
       <c r="B106" s="56" t="n"/>
@@ -10806,10 +10851,10 @@
       <c r="J106" s="56" t="n"/>
       <c r="K106" s="57" t="n"/>
     </row>
-    <row r="107" ht="18" customHeight="1" s="52">
+    <row r="107" ht="30.75" customHeight="1" s="52">
       <c r="A107" s="67" t="inlineStr">
         <is>
-          <t>S2 = semana de referencia [LÓGICA]: el paseo del martes no cuenta como novedad (caminas a diario). Si alguna mañana de S2 sale peor que la referencia (la primera medición de S2), en S3 no sube nada y se repite S2 entera, en lugar de intentar atribuir el empeoramiento.</t>
+          <t>Novedades [LÓGICA]: una por día y validada a las 24 y 48 h antes de repetirla. Lunes: escalón o reps (prensa) · miércoles: nivel de carrera · viernes de S4: bici. Solo si esa mañana estás igual o mejor que la referencia (la mañana del mismo día de la semana anterior; en S3, la primera medición de S2), no que el día anterior: así un empeoramiento lento también salta. El calendario marca el máximo de cada semana; el nivel real sale del semáforo: Avanzar = nivel +1 (sin pasar del calendario), Mantener = el mismo, Retroceder = nivel −1. Lo validado se repite: el jueves usa la profundidad del lunes y el domingo repite el nivel del miércoles.</t>
         </is>
       </c>
       <c r="B107" s="56" t="n"/>
@@ -10823,10 +10868,10 @@
       <c r="J107" s="56" t="n"/>
       <c r="K107" s="57" t="n"/>
     </row>
-    <row r="108" ht="43.5" customHeight="1" s="52">
+    <row r="108" ht="18" customHeight="1" s="52">
       <c r="A108" s="67" t="inlineStr">
         <is>
-          <t>Escalones de profundidad de la D [LÓGICA; no hay pautas de rango validadas para la rótula: INCERTIDUMBRE]: escalón 0 = la profundidad que ya usas con la D; escalón 4 = la de la I. Reparte la diferencia en 4 partes iguales (como mucho ~15° cada una; si sale más, se termina después del bloque). Se sube, como mucho, los lunes de S3, S4, S6 y S7 en la prensa (según el semáforo); la touchdown del lunes va a la profundidad ya validada y hace de filtro. Apunta las marcas en «Seguimiento rodilla».</t>
+          <t>S2 = semana de referencia [LÓGICA]: el paseo del martes no cuenta como novedad (caminas a diario). Si alguna mañana de S2 sale peor que la referencia (la primera medición de S2), en S3 no sube nada y se repite S2 entera, en lugar de intentar atribuir el empeoramiento.</t>
         </is>
       </c>
       <c r="B108" s="56" t="n"/>
@@ -10840,10 +10885,10 @@
       <c r="J108" s="56" t="n"/>
       <c r="K108" s="57" t="n"/>
     </row>
-    <row r="109" ht="18" customHeight="1" s="52">
+    <row r="109" ht="43.5" customHeight="1" s="52">
       <c r="A109" s="67" t="inlineStr">
         <is>
-          <t>Chasquido: si no duele, no se quita ni se cambia nada. Si duele, cuenta como dolor.</t>
+          <t>Escalones de profundidad de la D [LÓGICA; no hay pautas de rango validadas para la rótula: INCERTIDUMBRE]: escalón 0 = la profundidad que ya usas con la D; escalón 4 = la de la I. Reparte la diferencia en 4 partes iguales (como mucho ~15° cada una; si sale más, se termina después del bloque). Se sube, como mucho, los lunes de S3, S4, S6 y S7 en la prensa (según el semáforo); la touchdown del lunes va a la profundidad ya validada y hace de filtro. Apunta las marcas en «Seguimiento rodilla».</t>
         </is>
       </c>
       <c r="B109" s="56" t="n"/>
@@ -10860,7 +10905,7 @@
     <row r="110" ht="18" customHeight="1" s="52">
       <c r="A110" s="67" t="inlineStr">
         <is>
-          <t>Retroceso y brote [LÓGICA]: un dolor durante la sesión retrocede la escalera de esa sesión. Si una mañana sale peor, se retrocede la última novedad aún no validada (la que todavía no tiene en verde sus dos mañanas, 24 y 48 h; p. ej., jueves bien y viernes peor → se retrocede la carrera del miércoles y el escalón se mantiene); una novedad ya validada no se culpa. Si tras el retroceso vuelve a fallar, se retrocede la novedad anterior sin validar. Brote = un fallo sin ninguna novedad sin validar, o dos sesiones seguidas en Retroceder: lo primero que se quita es la bici; 48-72 h solo isométricos (sentadilla española 5×45 s diaria) y caminar, sin bici; luego se retoma un escalón por debajo en todo. La bici vuelve al nivel del calendario cuando lleves una semana entera en verde.</t>
+          <t>Chasquido: si no duele, no se quita ni se cambia nada. Si duele, cuenta como dolor.</t>
         </is>
       </c>
       <c r="B110" s="56" t="n"/>
@@ -10877,7 +10922,7 @@
     <row r="111" ht="18" customHeight="1" s="52">
       <c r="A111" s="67" t="inlineStr">
         <is>
-          <t>Alarma: bloqueo real, fallos repetidos de la rodilla o hinchazón visible → se para la progresión y toca valoración clínica.</t>
+          <t>Retroceso y brote [LÓGICA]: un dolor durante la sesión retrocede la escalera de esa sesión. Si una mañana sale peor, se retrocede la última novedad aún no validada (la que todavía no tiene en verde sus dos mañanas, 24 y 48 h; p. ej., jueves bien y viernes peor → se retrocede la carrera del miércoles y el escalón se mantiene); una novedad ya validada no se culpa. Si tras el retroceso vuelve a fallar, se retrocede la novedad anterior sin validar. Brote = un fallo sin ninguna novedad sin validar, o dos sesiones seguidas en Retroceder: lo primero que se quita es la bici; 48-72 h solo isométricos (sentadilla española 5×45 s diaria) y caminar, sin bici; luego se retoma un escalón por debajo en todo. La bici vuelve al nivel del calendario cuando lleves una semana entera en verde.</t>
         </is>
       </c>
       <c r="B111" s="56" t="n"/>
@@ -10891,10 +10936,10 @@
       <c r="J111" s="56" t="n"/>
       <c r="K111" s="57" t="n"/>
     </row>
-    <row r="112" ht="30.75" customHeight="1" s="52">
+    <row r="112" ht="18" customHeight="1" s="52">
       <c r="A112" s="67" t="inlineStr">
         <is>
-          <t>AVISO S4 (fisio deportivo pendiente): se calcula al cerrar S4 (domingo 15/11) si hay al menos 5 mañanas registradas en S2 y en S4. Compara la media de las mañanas: PEOR si la de S4 supera en 0,5 o más a la de S2; MEJOR si queda 0,5 o más por debajo; si no, IGUAL. IGUAL o PEOR, o un chasquido que empieza a doler: la valoración del fisio pasa a ser prioritaria; PEOR además para la progresión [LÓGICA]. «Seguimiento rodilla» lo calcula.</t>
+          <t>Alarma: bloqueo real, fallos repetidos de la rodilla o hinchazón visible → se para la progresión y toca valoración clínica.</t>
         </is>
       </c>
       <c r="B112" s="56" t="n"/>
@@ -10911,7 +10956,7 @@
     <row r="113" ht="30.75" customHeight="1" s="52">
       <c r="A113" s="67" t="inlineStr">
         <is>
-          <t>Fases hacia el fútbol, después del viaje [LÓGICA], siempre con la regla de carrera: cambios de dirección ← 30 min seguidos dos veces sin reacción y rango D = I · pliometría ← 2 semanas de cambios de dirección y 10 saltos a una pierna sin dolor · balón ← cuádriceps D ≥90% de la I en el test y pliometría media sin reacción · equipo ← 2 semanas de balón sin reacción.</t>
+          <t>AVISO S4 (fisio deportivo pendiente): se calcula al cerrar S4 (domingo 15/11) si hay al menos 5 mañanas registradas en S2 y en S4. Compara la media de las mañanas: PEOR si la de S4 supera en 0,5 o más a la de S2; MEJOR si queda 0,5 o más por debajo; si no, IGUAL. IGUAL o PEOR, o un chasquido que empieza a doler: la valoración del fisio pasa a ser prioritaria; PEOR además para la progresión [LÓGICA]. «Seguimiento rodilla» lo calcula.</t>
         </is>
       </c>
       <c r="B113" s="56" t="n"/>
@@ -10925,7 +10970,23 @@
       <c r="J113" s="56" t="n"/>
       <c r="K113" s="57" t="n"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1" s="52"/>
+    <row r="114" ht="30.75" customHeight="1" s="52">
+      <c r="A114" s="67" t="inlineStr">
+        <is>
+          <t>Fases hacia el fútbol, después del viaje [LÓGICA], siempre con la regla de carrera: cambios de dirección ← 30 min seguidos dos veces sin reacción y rango D = I · pliometría ← 2 semanas de cambios de dirección y 10 saltos a una pierna sin dolor · balón ← cuádriceps D ≥90% de la I en el test y pliometría media sin reacción · equipo ← 2 semanas de balón sin reacción.</t>
+        </is>
+      </c>
+      <c r="B114" s="56" t="n"/>
+      <c r="C114" s="56" t="n"/>
+      <c r="D114" s="56" t="n"/>
+      <c r="E114" s="56" t="n"/>
+      <c r="F114" s="56" t="n"/>
+      <c r="G114" s="56" t="n"/>
+      <c r="H114" s="56" t="n"/>
+      <c r="I114" s="56" t="n"/>
+      <c r="J114" s="56" t="n"/>
+      <c r="K114" s="57" t="n"/>
+    </row>
     <row r="115" ht="15.75" customHeight="1" s="52"/>
     <row r="116" ht="15.75" customHeight="1" s="52"/>
     <row r="117" ht="15.75" customHeight="1" s="52"/>
@@ -11820,41 +11881,42 @@
     <row r="1006" ht="15.75" customHeight="1" s="52"/>
     <row r="1007" ht="15.75" customHeight="1" s="52"/>
     <row r="1008" ht="15.75" customHeight="1" s="52"/>
-    <row r="1009" ht="15" customHeight="1" s="52"/>
+    <row r="1009" ht="15.75" customHeight="1" s="52"/>
     <row r="1010" ht="15" customHeight="1" s="52"/>
     <row r="1011" ht="15" customHeight="1" s="52"/>
     <row r="1012" ht="15" customHeight="1" s="52"/>
     <row r="1013" ht="15" customHeight="1" s="52"/>
     <row r="1014" ht="15" customHeight="1" s="52"/>
+    <row r="1015" ht="15" customHeight="1" s="52"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A114:K114"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A24:K24"/>
     <mergeCell ref="A107:K107"/>
+    <mergeCell ref="A94:K94"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A45:K45"/>
     <mergeCell ref="A103:K103"/>
     <mergeCell ref="A110:K110"/>
     <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A65:K65"/>
     <mergeCell ref="A108:K108"/>
-    <mergeCell ref="A66:K66"/>
+    <mergeCell ref="A56:K56"/>
     <mergeCell ref="A105:K105"/>
-    <mergeCell ref="A101:K101"/>
-    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A86:K86"/>
     <mergeCell ref="A104:K104"/>
     <mergeCell ref="A113:K113"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A71:K71"/>
-    <mergeCell ref="A85:K85"/>
     <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A106:K106"/>
     <mergeCell ref="A67:K67"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A109:K109"/>
+    <mergeCell ref="A72:K72"/>
     <mergeCell ref="A112:K112"/>
-    <mergeCell ref="A93:K93"/>
     <mergeCell ref="A68:K68"/>
-    <mergeCell ref="A44:K44"/>
     <mergeCell ref="A102:K102"/>
     <mergeCell ref="A111:K111"/>
   </mergeCells>

--- a/Plan_8sem_vol_definitivo_con_cardio.xlsx
+++ b/Plan_8sem_vol_definitivo_con_cardio.xlsx
@@ -6097,7 +6097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="36.05" customWidth="1" style="51" min="1" max="1"/>
@@ -6117,7 +6117,7 @@
     <row r="2" ht="51.75" customHeight="1" s="52">
       <c r="A2" s="64" t="inlineStr">
         <is>
-          <t>RIR1/0 = todas las series a RIR1 y la ÚLTIMA a RIR0 (si solo hay 1 serie, RIR0).  REHAB RODILLA S2-S8 en 2 días: lunes (touchdown + prensa) y jueves (sentadilla + búlgara), pesado y lento, tempo 3-1-3; D a RIR 2 y en su escalón de profundidad, I a RIR 1-2 y rango completo. Reps: ×12 S1 → ×10 S2-4 → ×8 S5-8 → ×6 tras el viaje. Una novedad por día (lunes profundidad/reps · miércoles carrera), solo si esa mañana estás igual o mejor. El calendario marca el máximo de cada semana: se progresa según el semáforo (Avanzar / Mantener / Retroceder) y la app prescribe con el nivel real. Reglas al final de la hoja; registro diario en «Seguimiento rodilla».</t>
+          <t>RIR1/0 = todas las series a RIR1 y la ÚLTIMA a RIR0 (si solo hay 1 serie, RIR0).  REHAB RODILLA S2-S8 en 2 días: lunes (touchdown + prensa) y viernes (sentadilla + búlgara), pesado y lento, tempo 3-1-3; D a RIR 2 y en su escalón de profundidad, I a RIR 1-2 y rango completo. Reps: ×12 S1 → ×10 S2-4 → ×8 S5-8 → ×6 tras el viaje. Una novedad por día (lunes profundidad/reps · miércoles carrera), solo si esa mañana estás igual o mejor. El calendario marca el máximo de cada semana: se progresa según el semáforo (Avanzar / Mantener / Retroceder) y la app prescribe con el nivel real. Reglas al final de la hoja; registro diario en «Seguimiento rodilla». Desde S3: L pierna 1 + hombro + espalda · M push · X solo carrera · J pull · V pierna 2 · S torso en casa (peso libre) · D carrera.</t>
         </is>
       </c>
       <c r="L2" s="106" t="inlineStr">
@@ -6142,7 +6142,7 @@
     <row r="4" ht="19.5" customHeight="1" s="52">
       <c r="A4" s="68" t="inlineStr">
         <is>
-          <t>(L) Lunes  ·  Rehab + Isquios + Hombro + Gemelo</t>
+          <t>(L) Lunes  ·  Rehab + Isquios + Hombro + Gemelo + Espalda (desde S3)</t>
         </is>
       </c>
       <c r="B4" s="56" t="n"/>
@@ -6246,7 +6246,8 @@
       </c>
       <c r="E6" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>2 @ RIR1/0
+2/11: con goma</t>
         </is>
       </c>
       <c r="F6" s="61" t="inlineStr">
@@ -6310,7 +6311,8 @@
       <c r="E7" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
-@RIR1-2</t>
+@RIR1-2
+2/11: con goma</t>
         </is>
       </c>
       <c r="F7" s="63" t="inlineStr">
@@ -6504,7 +6506,7 @@
       <c r="E10" s="63" t="inlineStr">
         <is>
           <t>2 x10/pierna
-nov: +1 escalón</t>
+2/11: búlgara en casa, escalón 0, sin novedad</t>
         </is>
       </c>
       <c r="F10" s="63" t="inlineStr">
@@ -6534,12 +6536,12 @@
       <c r="J10" s="63" t="inlineStr">
         <is>
           <t>2 x8/pierna
-repite S7</t>
+nov: +1 escalón (4.º) solo si S6-S7 cumplieron; si no, repite S7</t>
         </is>
       </c>
       <c r="K10" s="62" t="inlineStr">
         <is>
-          <t>Pesado y lento para el tendón [EVIDENCIA: Kongsgaard 2009; 1-2 veces/semana para mantenerlo: LÓGICA]. Tempo 3-1-3. D primero: RIR 2 y profundidad de su escalón. I: RIR 1-2, rango completo y mismas reps. Lunes = día de novedad (escalón o reps): solo si esa mañana estás igual o mejor y la touchdown no pasa de 3/10; si no, repite la semana anterior. En la sesión con novedad no cambies nada más (con escalón nuevo, mismo peso).</t>
+          <t>Pesado y lento para el tendón [EVIDENCIA: Kongsgaard 2009; 1-2 veces/semana para mantenerlo: LÓGICA]. Tempo 3-1-3. D primero: RIR 2 y profundidad de su escalón. I: RIR 1-2, rango completo y mismas reps. Lunes = día de novedad (escalón o reps): solo si esa mañana estás igual o mejor y la touchdown no pasa de 3/10; si no, repite la semana anterior. En la sesión con novedad no cambies nada más (con escalón nuevo, mismo peso). S3 (2/11, festivo): búlgara en casa en el escalón 0, sin novedad; mantiene el estímulo pesado y lento sin cambiar dos cosas a la vez [LÓGICA]. Escalones en S4, S6 y S7; el 4.º en S8 solo si S6-S7 cumplieron (si no, después del viaje) [INCERTIDUMBRE: menos días para asentarlo antes del viaje].</t>
         </is>
       </c>
       <c r="L10" s="106" t="inlineStr">
@@ -6571,7 +6573,8 @@
       </c>
       <c r="E11" s="61" t="inlineStr">
         <is>
-          <t>4 @ RIR1/0</t>
+          <t>4 @ RIR1/0
+2/11: de pie, 1 pierna, mancuerna</t>
         </is>
       </c>
       <c r="F11" s="61" t="inlineStr">
@@ -6633,1803 +6636,1818 @@
       </c>
       <c r="E12" s="61" t="inlineStr">
         <is>
+          <t>2 @ RIR1/0
+2/11: PM rumano con barra (RIR 2)</t>
+        </is>
+      </c>
+      <c r="F12" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G12" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H12" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I12" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J12" s="61" t="inlineStr">
+        <is>
+          <t>4 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K12" s="62" t="inlineStr">
+        <is>
+          <t>Extensión de cadera · Rodillas con ligera flexión fija (~10-15°), subir empujando talones sin hiperextender zona lumbar.</t>
+        </is>
+      </c>
+      <c r="L12" s="106" t="inlineStr">
+        <is>
+          <t>id=hiperextensiones</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="52">
+      <c r="A13" s="59" t="inlineStr">
+        <is>
+          <t>Dominada neutra dorsal</t>
+        </is>
+      </c>
+      <c r="B13" s="59" t="inlineStr">
+        <is>
+          <t>Espalda</t>
+        </is>
+      </c>
+      <c r="C13" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="D13" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="E13" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="F13" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="G13" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="H13" s="61" t="inlineStr">
+        <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F12" s="61" t="inlineStr">
+      <c r="I13" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J13" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K13" s="62" t="inlineStr">
+        <is>
+          <t>Desde S3 va el lunes, después de la pierna y el hombro (S1: viernes en el gimnasio; S2: sábado 31/10 en casa con peso libre). Si llegas muy cansado al final del lunes, haz la espalda justo después de la prensa y deja gemelos e hiperextensiones para el final [LÓGICA]. Plano sagital (Dorsal Sup.) · Usar STRAPS obligatoriamente para anular fatiga previa de bíceps y proteger codos.</t>
+        </is>
+      </c>
+      <c r="L13" s="106" t="inlineStr">
+        <is>
+          <t>id=dominada-neutra-dorsal;S1=V;S2=S</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="52">
+      <c r="A14" s="59" t="inlineStr">
+        <is>
+          <t>Remo máquina (pecho apoyado 30°)</t>
+        </is>
+      </c>
+      <c r="B14" s="59" t="inlineStr">
+        <is>
+          <t>Espalda</t>
+        </is>
+      </c>
+      <c r="C14" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D14" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E14" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0
+2/11: mancuerna, pecho apoyado</t>
+        </is>
+      </c>
+      <c r="F14" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G14" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H14" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I14" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J14" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K14" s="62" t="inlineStr">
+        <is>
+          <t>Desde S3 va el lunes, después de la pierna y el hombro (S1: viernes en el gimnasio; S2: sábado 31/10 en casa con peso libre). Plano sagital/híbrido (Dorsal Sup.) · Usar STRAPS, codos a ~30° hasta línea del torso.</t>
+        </is>
+      </c>
+      <c r="L14" s="106" t="inlineStr">
+        <is>
+          <t>id=remo-maquina-pecho-apoyado-30;S1=V;S2=S</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="52">
+      <c r="A15" s="59" t="inlineStr">
+        <is>
+          <t>Aducción unil. polea alta (Pull-in)</t>
+        </is>
+      </c>
+      <c r="B15" s="59" t="inlineStr">
+        <is>
+          <t>Espalda</t>
+        </is>
+      </c>
+      <c r="C15" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D15" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E15" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0
+2/11: con goma en la barra</t>
+        </is>
+      </c>
+      <c r="F15" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G15" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H15" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I15" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J15" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K15" s="62" t="inlineStr">
+        <is>
+          <t>Desde S3 va el lunes, después de la pierna y el hombro (S1: viernes en el gimnasio; S2: sábado 31/10 en casa con peso libre). Prioridad 3 (Dorsal Bajo) · De lado a la polea (con tobillera en muñeca o codo semirrígido) para aislar haz inferior sin usar bíceps ni codo · Sem 1-2 a RIR 1-2.</t>
+        </is>
+      </c>
+      <c r="L15" s="106" t="inlineStr">
+        <is>
+          <t>id=aduccion-unil-polea-alta-pull-in;S1=V;S2=S</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="52"/>
+    <row r="17" ht="19.5" customHeight="1" s="52">
+      <c r="A17" s="65" t="inlineStr">
+        <is>
+          <t>(M) Martes  ·  Push</t>
+        </is>
+      </c>
+      <c r="B17" s="56" t="n"/>
+      <c r="C17" s="56" t="n"/>
+      <c r="D17" s="56" t="n"/>
+      <c r="E17" s="56" t="n"/>
+      <c r="F17" s="56" t="n"/>
+      <c r="G17" s="56" t="n"/>
+      <c r="H17" s="56" t="n"/>
+      <c r="I17" s="56" t="n"/>
+      <c r="J17" s="56" t="n"/>
+      <c r="K17" s="57" t="n"/>
+      <c r="L17" s="106" t="inlineStr">
+        <is>
+          <t>sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1" s="52">
+      <c r="A18" s="66" t="inlineStr">
+        <is>
+          <t>Ejercicio</t>
+        </is>
+      </c>
+      <c r="B18" s="66" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+      <c r="C18" s="66" t="inlineStr">
+        <is>
+          <t>Sem 1 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="D18" s="66" t="inlineStr">
+        <is>
+          <t>Sem 2 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="E18" s="66" t="inlineStr">
+        <is>
+          <t>Sem 3 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="F18" s="66" t="inlineStr">
+        <is>
+          <t>Sem 4 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="G18" s="66" t="inlineStr">
+        <is>
+          <t>Sem 5 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="H18" s="66" t="inlineStr">
+        <is>
+          <t>Sem 6 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="I18" s="66" t="inlineStr">
+        <is>
+          <t>Sem 7 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="J18" s="66" t="inlineStr">
+        <is>
+          <t>Sem 8 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="K18" s="66" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="L18" s="106" t="inlineStr">
+        <is>
+          <t>App (no tocar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="52">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>Press inclinado barra (30–40°)</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Pecho</t>
+        </is>
+      </c>
+      <c r="C19" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D19" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G12" s="61" t="inlineStr">
+      <c r="E19" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H12" s="61" t="inlineStr">
+      <c r="F19" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I12" s="61" t="inlineStr">
+      <c r="G19" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="H19" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I19" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J19" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K12" s="62" t="inlineStr">
-        <is>
-          <t>Extensión de cadera · Rodillas con ligera flexión fija (~10-15°), subir empujando talones sin hiperextender zona lumbar.</t>
-        </is>
-      </c>
-      <c r="L12" s="106" t="inlineStr">
-        <is>
-          <t>id=hiperextensiones</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="52"/>
-    <row r="14" ht="19.5" customHeight="1" s="52">
-      <c r="A14" s="65" t="inlineStr">
-        <is>
-          <t>(M) Martes  ·  Push</t>
-        </is>
-      </c>
-      <c r="B14" s="56" t="n"/>
-      <c r="C14" s="56" t="n"/>
-      <c r="D14" s="56" t="n"/>
-      <c r="E14" s="56" t="n"/>
-      <c r="F14" s="56" t="n"/>
-      <c r="G14" s="56" t="n"/>
-      <c r="H14" s="56" t="n"/>
-      <c r="I14" s="56" t="n"/>
-      <c r="J14" s="56" t="n"/>
-      <c r="K14" s="57" t="n"/>
-      <c r="L14" s="106" t="inlineStr">
-        <is>
-          <t>sesion</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="27" customHeight="1" s="52">
-      <c r="A15" s="66" t="inlineStr">
-        <is>
-          <t>Ejercicio</t>
-        </is>
-      </c>
-      <c r="B15" s="66" t="inlineStr">
-        <is>
-          <t>Objetivo</t>
-        </is>
-      </c>
-      <c r="C15" s="66" t="inlineStr">
-        <is>
-          <t>Sem 1 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="D15" s="66" t="inlineStr">
-        <is>
-          <t>Sem 2 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="E15" s="66" t="inlineStr">
-        <is>
-          <t>Sem 3 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="F15" s="66" t="inlineStr">
-        <is>
-          <t>Sem 4 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="G15" s="66" t="inlineStr">
-        <is>
-          <t>Sem 5 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="H15" s="66" t="inlineStr">
-        <is>
-          <t>Sem 6 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="I15" s="66" t="inlineStr">
-        <is>
-          <t>Sem 7 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="J15" s="66" t="inlineStr">
-        <is>
-          <t>Sem 8 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="K15" s="66" t="inlineStr">
-        <is>
-          <t>Notas</t>
-        </is>
-      </c>
-      <c r="L15" s="106" t="inlineStr">
-        <is>
-          <t>App (no tocar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="52">
-      <c r="A16" s="59" t="inlineStr">
-        <is>
-          <t>Press inclinado barra (30–40°)</t>
-        </is>
-      </c>
-      <c r="B16" s="59" t="inlineStr">
-        <is>
-          <t>Pecho</t>
-        </is>
-      </c>
-      <c r="C16" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D16" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E16" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F16" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G16" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H16" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I16" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J16" s="61" t="inlineStr">
-        <is>
-          <t>4 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K16" s="62" t="inlineStr">
+      <c r="K19" s="62" t="inlineStr">
         <is>
           <t>Prioridad 4 (Haz clavicular) · Agarre ~1.3x ancho hombros y codos a 45–60° (plano escapular) para proteger hombro y codo.</t>
         </is>
       </c>
-      <c r="L16" s="106" t="inlineStr">
+      <c r="L19" s="106" t="inlineStr">
         <is>
           <t>id=press-inclinado-barra-30-40</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" s="52">
-      <c r="A17" s="59" t="inlineStr">
-        <is>
-          <t>Extensión tríceps unil polea</t>
-        </is>
-      </c>
-      <c r="B17" s="59" t="inlineStr">
-        <is>
-          <t>Tríceps</t>
-        </is>
-      </c>
-      <c r="C17" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D17" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E17" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F17" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G17" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H17" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I17" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J17" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K17" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 2 (Tríceps) · Hombro a 0° pegado al costado (máxima palanca de cabeza larga sin estrés articular en codo).</t>
-        </is>
-      </c>
-      <c r="L17" s="106" t="inlineStr">
-        <is>
-          <t>id=extension-triceps-unil-polea</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="52">
-      <c r="A18" s="59" t="inlineStr">
-        <is>
-          <t>Contractora (Pec Deck)</t>
-        </is>
-      </c>
-      <c r="B18" s="59" t="inlineStr">
-        <is>
-          <t>Pecho</t>
-        </is>
-      </c>
-      <c r="C18" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D18" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E18" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F18" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G18" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H18" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I18" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J18" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K18" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 4 (Haz clavicular/esternal) · Asiento medio-bajo (manos altura clavícula/esternón sup.) · NO hiperextender húmeros detrás del torso al abrir para no irritar cápsula anterior del hombro.</t>
-        </is>
-      </c>
-      <c r="L18" s="106" t="inlineStr">
-        <is>
-          <t>id=contractora-pec-deck</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="52">
-      <c r="A19" s="59" t="inlineStr">
-        <is>
-          <t>Triceps tras nuca unil polea</t>
-        </is>
-      </c>
-      <c r="B19" s="59" t="inlineStr">
-        <is>
-          <t>Tríceps</t>
-        </is>
-      </c>
-      <c r="C19" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="D19" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="E19" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F19" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G19" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H19" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I19" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J19" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K19" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 2 (Tríceps en estiramiento) · Dejar que el codo apunte ligeramente hacia fuera (~20-30° plano escapular) para no forzar cápsula del hombro ni tendón olecraniano.</t>
-        </is>
-      </c>
-      <c r="L19" s="106" t="inlineStr">
-        <is>
-          <t>id=triceps-tras-nuca-unil-polea</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="52">
       <c r="A20" s="59" t="inlineStr">
         <is>
-          <t>Abs colgado (retroversión)</t>
+          <t>Extensión tríceps unil polea</t>
         </is>
       </c>
       <c r="B20" s="59" t="inlineStr">
         <is>
-          <t>Abs</t>
+          <t>Tríceps</t>
         </is>
       </c>
       <c r="C20" s="61" t="inlineStr">
         <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D20" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E20" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F20" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G20" s="61" t="inlineStr">
+        <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="D20" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="E20" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="F20" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="G20" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
       <c r="H20" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="I20" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="J20" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="K20" s="62" t="inlineStr">
         <is>
-          <t>Colgado con depresión escapular (activa dorsal) · Enrollar pelvis hacia costillas (retroversión). Usar straps si el agarre molesta al codo.</t>
+          <t>Prioridad 2 (Tríceps) · Hombro a 0° pegado al costado (máxima palanca de cabeza larga sin estrés articular en codo).</t>
         </is>
       </c>
       <c r="L20" s="106" t="inlineStr">
         <is>
-          <t>id=abs-colgado-retroversion</t>
+          <t>id=extension-triceps-unil-polea</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="52">
       <c r="A21" s="59" t="inlineStr">
         <is>
+          <t>Contractora (Pec Deck)</t>
+        </is>
+      </c>
+      <c r="B21" s="59" t="inlineStr">
+        <is>
+          <t>Pecho</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D21" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E21" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F21" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G21" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H21" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I21" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J21" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K21" s="62" t="inlineStr">
+        <is>
+          <t>Prioridad 4 (Haz clavicular/esternal) · Asiento medio-bajo (manos altura clavícula/esternón sup.) · NO hiperextender húmeros detrás del torso al abrir para no irritar cápsula anterior del hombro.</t>
+        </is>
+      </c>
+      <c r="L21" s="106" t="inlineStr">
+        <is>
+          <t>id=contractora-pec-deck</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="52">
+      <c r="A22" s="59" t="inlineStr">
+        <is>
+          <t>Triceps tras nuca unil polea</t>
+        </is>
+      </c>
+      <c r="B22" s="59" t="inlineStr">
+        <is>
+          <t>Tríceps</t>
+        </is>
+      </c>
+      <c r="C22" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="D22" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="E22" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F22" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G22" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H22" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I22" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J22" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K22" s="62" t="inlineStr">
+        <is>
+          <t>Prioridad 2 (Tríceps en estiramiento) · Dejar que el codo apunte ligeramente hacia fuera (~20-30° plano escapular) para no forzar cápsula del hombro ni tendón olecraniano.</t>
+        </is>
+      </c>
+      <c r="L22" s="106" t="inlineStr">
+        <is>
+          <t>id=triceps-tras-nuca-unil-polea</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="52">
+      <c r="A23" s="59" t="inlineStr">
+        <is>
+          <t>Abs colgado (retroversión)</t>
+        </is>
+      </c>
+      <c r="B23" s="59" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D23" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="E23" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="F23" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="G23" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="H23" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="I23" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="J23" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="K23" s="62" t="inlineStr">
+        <is>
+          <t>Colgado con depresión escapular (activa dorsal) · Enrollar pelvis hacia costillas (retroversión). Usar straps si el agarre molesta al codo.</t>
+        </is>
+      </c>
+      <c r="L23" s="106" t="inlineStr">
+        <is>
+          <t>id=abs-colgado-retroversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="52">
+      <c r="A24" s="59" t="inlineStr">
+        <is>
           <t>Abs en máquina (crunch)</t>
         </is>
       </c>
-      <c r="B21" s="59" t="inlineStr">
+      <c r="B24" s="59" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="C21" s="61" t="inlineStr">
+      <c r="C24" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D21" s="61" t="inlineStr">
+      <c r="D24" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="E21" s="61" t="inlineStr">
+      <c r="E24" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F21" s="61" t="inlineStr">
+      <c r="F24" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G21" s="61" t="inlineStr">
+      <c r="G24" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H21" s="61" t="inlineStr">
+      <c r="H24" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I21" s="61" t="inlineStr">
+      <c r="I24" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J21" s="61" t="inlineStr">
+      <c r="J24" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K21" s="62" t="inlineStr">
+      <c r="K24" s="62" t="inlineStr">
         <is>
           <t>Desde S2 recoge las series del colgado (que se queda en 1) · Pies enganchados y cadera fija: enrollar el tronco llevando costillas hacia pelvis, sin tirar con los brazos ni flexionar la cadera. Bajar controlado, 2 s.</t>
         </is>
       </c>
-      <c r="L21" s="106" t="inlineStr">
+      <c r="L24" s="106" t="inlineStr">
         <is>
           <t>id=abs-maquina-crunch</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="52">
-      <c r="A22" s="59" t="n"/>
-      <c r="B22" s="59" t="n"/>
-      <c r="C22" s="61" t="n"/>
-      <c r="D22" s="61" t="n"/>
-      <c r="E22" s="61" t="n"/>
-      <c r="F22" s="61" t="n"/>
-      <c r="G22" s="61" t="n"/>
-      <c r="H22" s="61" t="n"/>
-      <c r="I22" s="61" t="n"/>
-      <c r="J22" s="61" t="n"/>
-      <c r="K22" s="61" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="52">
-      <c r="A23" s="69" t="n"/>
-      <c r="B23" s="69" t="n"/>
-      <c r="C23" s="70" t="n"/>
-      <c r="D23" s="70" t="n"/>
-      <c r="E23" s="70" t="n"/>
-      <c r="F23" s="70" t="n"/>
-      <c r="G23" s="70" t="n"/>
-      <c r="H23" s="70" t="n"/>
-      <c r="I23" s="70" t="n"/>
-      <c r="J23" s="70" t="n"/>
-      <c r="K23" s="70" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="52">
-      <c r="A24" s="65" t="inlineStr">
-        <is>
-          <t>(X) Miércoles  ·  Pull  ·  + carrera (ver bloque de carrera)</t>
-        </is>
-      </c>
-      <c r="B24" s="56" t="n"/>
-      <c r="C24" s="56" t="n"/>
-      <c r="D24" s="56" t="n"/>
-      <c r="E24" s="56" t="n"/>
-      <c r="F24" s="56" t="n"/>
-      <c r="G24" s="56" t="n"/>
-      <c r="H24" s="56" t="n"/>
-      <c r="I24" s="56" t="n"/>
-      <c r="J24" s="56" t="n"/>
-      <c r="K24" s="57" t="n"/>
-      <c r="L24" s="106" t="inlineStr">
+    <row r="25" ht="15.75" customHeight="1" s="52">
+      <c r="A25" s="59" t="n"/>
+      <c r="B25" s="59" t="n"/>
+      <c r="C25" s="61" t="n"/>
+      <c r="D25" s="61" t="n"/>
+      <c r="E25" s="61" t="n"/>
+      <c r="F25" s="61" t="n"/>
+      <c r="G25" s="61" t="n"/>
+      <c r="H25" s="61" t="n"/>
+      <c r="I25" s="61" t="n"/>
+      <c r="J25" s="61" t="n"/>
+      <c r="K25" s="61" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="52">
+      <c r="A26" s="69" t="n"/>
+      <c r="B26" s="69" t="n"/>
+      <c r="C26" s="70" t="n"/>
+      <c r="D26" s="70" t="n"/>
+      <c r="E26" s="70" t="n"/>
+      <c r="F26" s="70" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="52">
+      <c r="A27" s="65" t="inlineStr">
+        <is>
+          <t>(X) Miércoles  ·  sin gimnasio  ·  solo carrera (ver bloque de carrera)</t>
+        </is>
+      </c>
+      <c r="B27" s="56" t="n"/>
+      <c r="C27" s="56" t="n"/>
+      <c r="D27" s="56" t="n"/>
+      <c r="E27" s="56" t="n"/>
+      <c r="F27" s="56" t="n"/>
+      <c r="G27" s="56" t="n"/>
+      <c r="H27" s="56" t="n"/>
+      <c r="I27" s="56" t="n"/>
+      <c r="J27" s="56" t="n"/>
+      <c r="K27" s="57" t="n"/>
+      <c r="L27" s="106" t="inlineStr">
         <is>
           <t>sesion</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="27" customHeight="1" s="52">
-      <c r="A25" s="66" t="inlineStr">
+    <row r="28" ht="15.75" customHeight="1" s="52">
+      <c r="A28" s="69" t="n"/>
+      <c r="B28" s="69" t="n"/>
+      <c r="C28" s="70" t="n"/>
+      <c r="D28" s="70" t="n"/>
+      <c r="E28" s="70" t="n"/>
+      <c r="F28" s="70" t="n"/>
+      <c r="G28" s="70" t="n"/>
+      <c r="H28" s="70" t="n"/>
+      <c r="I28" s="70" t="n"/>
+      <c r="J28" s="70" t="n"/>
+      <c r="K28" s="70" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="52">
+      <c r="A29" s="65" t="inlineStr">
+        <is>
+          <t>(J) Jueves  ·  Pull  (desde S3; S1-S2 se hizo el miércoles)</t>
+        </is>
+      </c>
+      <c r="B29" s="56" t="n"/>
+      <c r="C29" s="56" t="n"/>
+      <c r="D29" s="56" t="n"/>
+      <c r="E29" s="56" t="n"/>
+      <c r="F29" s="56" t="n"/>
+      <c r="G29" s="56" t="n"/>
+      <c r="H29" s="56" t="n"/>
+      <c r="I29" s="56" t="n"/>
+      <c r="J29" s="56" t="n"/>
+      <c r="K29" s="57" t="n"/>
+      <c r="L29" s="106" t="inlineStr">
+        <is>
+          <t>sesion;S1=X;S2=X</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="27" customHeight="1" s="52">
+      <c r="A30" s="66" t="inlineStr">
         <is>
           <t>Ejercicio</t>
         </is>
       </c>
-      <c r="B25" s="66" t="inlineStr">
+      <c r="B30" s="66" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="C25" s="66" t="inlineStr">
+      <c r="C30" s="66" t="inlineStr">
         <is>
           <t>Sem 1 (series@RIR)</t>
         </is>
       </c>
-      <c r="D25" s="66" t="inlineStr">
+      <c r="D30" s="66" t="inlineStr">
         <is>
           <t>Sem 2 (series@RIR)</t>
         </is>
       </c>
-      <c r="E25" s="66" t="inlineStr">
+      <c r="E30" s="66" t="inlineStr">
         <is>
           <t>Sem 3 (series@RIR)</t>
         </is>
       </c>
-      <c r="F25" s="66" t="inlineStr">
+      <c r="F30" s="66" t="inlineStr">
         <is>
           <t>Sem 4 (series@RIR)</t>
         </is>
       </c>
-      <c r="G25" s="66" t="inlineStr">
+      <c r="G30" s="66" t="inlineStr">
         <is>
           <t>Sem 5 (series@RIR)</t>
         </is>
       </c>
-      <c r="H25" s="66" t="inlineStr">
+      <c r="H30" s="66" t="inlineStr">
         <is>
           <t>Sem 6 (series@RIR)</t>
         </is>
       </c>
-      <c r="I25" s="66" t="inlineStr">
+      <c r="I30" s="66" t="inlineStr">
         <is>
           <t>Sem 7 (series@RIR)</t>
         </is>
       </c>
-      <c r="J25" s="66" t="inlineStr">
+      <c r="J30" s="66" t="inlineStr">
         <is>
           <t>Sem 8 (series@RIR)</t>
         </is>
       </c>
-      <c r="K25" s="66" t="inlineStr">
+      <c r="K30" s="66" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="L25" s="106" t="inlineStr">
+      <c r="L30" s="106" t="inlineStr">
         <is>
           <t>App (no tocar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" s="52">
-      <c r="A26" s="59" t="inlineStr">
-        <is>
-          <t>Jalón ancho plano frontal</t>
-        </is>
-      </c>
-      <c r="B26" s="59" t="inlineStr">
-        <is>
-          <t>Espalda</t>
-        </is>
-      </c>
-      <c r="C26" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D26" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E26" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F26" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G26" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H26" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I26" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J26" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K26" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 3 (Dorsal Bajo) · 1º fresco · Torso vertical, codos abiertos en plano frontal hasta ~90° · No encoger hombros.</t>
-        </is>
-      </c>
-      <c r="L26" s="106" t="inlineStr">
-        <is>
-          <t>id=jalon-ancho-plano-frontal</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" s="52">
-      <c r="A27" s="59" t="inlineStr">
-        <is>
-          <t>Remo gironda abierto</t>
-        </is>
-      </c>
-      <c r="B27" s="59" t="inlineStr">
-        <is>
-          <t>Espalda</t>
-        </is>
-      </c>
-      <c r="C27" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D27" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E27" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F27" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G27" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H27" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I27" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J27" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K27" s="62" t="inlineStr">
-        <is>
-          <t>Plano transversal (Espalda Alta) · Codos abiertos y retracción escapular completa.</t>
-        </is>
-      </c>
-      <c r="L27" s="106" t="inlineStr">
-        <is>
-          <t>id=remo-gironda-abierto</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" s="52">
-      <c r="A28" s="59" t="inlineStr">
-        <is>
-          <t>Laterales sentado</t>
-        </is>
-      </c>
-      <c r="B28" s="59" t="inlineStr">
-        <is>
-          <t>Hombro lat.</t>
-        </is>
-      </c>
-      <c r="C28" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="D28" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="E28" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F28" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G28" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H28" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I28" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J28" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K28" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 1 (Hombro Lat.) · Sentado en banco a 75–80°, abducir en plano escapular (~30° adelante) sin rotar internamente el hombro.</t>
-        </is>
-      </c>
-      <c r="L28" s="106" t="inlineStr">
-        <is>
-          <t>id=laterales-sentado</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" s="52">
-      <c r="A29" s="59" t="inlineStr">
-        <is>
-          <t>Jalón neutro</t>
-        </is>
-      </c>
-      <c r="B29" s="59" t="inlineStr">
-        <is>
-          <t>Espalda</t>
-        </is>
-      </c>
-      <c r="C29" s="61" t="inlineStr">
-        <is>
-          <t>1 @ RIR0</t>
-        </is>
-      </c>
-      <c r="D29" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E29" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F29" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G29" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H29" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I29" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J29" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K29" s="62" t="inlineStr">
-        <is>
-          <t>Plano sagital (Dorsal Sup.) · Agarre neutro ancho hombros, llevar codos a los bolsillos cortando a 90° (protege codo/bíceps).</t>
-        </is>
-      </c>
-      <c r="L29" s="106" t="inlineStr">
-        <is>
-          <t>id=jalon-neutro</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" s="52">
-      <c r="A30" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Curl martillo scott </t>
-        </is>
-      </c>
-      <c r="B30" s="59" t="inlineStr">
-        <is>
-          <t>Bíceps</t>
-        </is>
-      </c>
-      <c r="C30" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D30" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E30" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F30" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G30" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H30" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I30" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J30" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K30" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 2 (Bíceps/Braquiorradial) · Agarre neutro (muy amigable para el codo). Bajar en 2-3 s y parar a ~15° de la extensión total para no sobrecargar tendón distal.</t>
-        </is>
-      </c>
-      <c r="L30" s="106" t="inlineStr">
-        <is>
-          <t>id=curl-martillo-scott</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="52">
       <c r="A31" s="59" t="inlineStr">
         <is>
+          <t>Jalón ancho plano frontal</t>
+        </is>
+      </c>
+      <c r="B31" s="59" t="inlineStr">
+        <is>
+          <t>Espalda</t>
+        </is>
+      </c>
+      <c r="C31" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D31" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E31" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F31" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G31" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H31" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I31" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J31" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K31" s="62" t="inlineStr">
+        <is>
+          <t>Prioridad 3 (Dorsal Bajo) · 1º fresco · Torso vertical, codos abiertos en plano frontal hasta ~90° · No encoger hombros.</t>
+        </is>
+      </c>
+      <c r="L31" s="106" t="inlineStr">
+        <is>
+          <t>id=jalon-ancho-plano-frontal</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="52">
+      <c r="A32" s="59" t="inlineStr">
+        <is>
+          <t>Remo gironda abierto</t>
+        </is>
+      </c>
+      <c r="B32" s="59" t="inlineStr">
+        <is>
+          <t>Espalda</t>
+        </is>
+      </c>
+      <c r="C32" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D32" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E32" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F32" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G32" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H32" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I32" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J32" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K32" s="62" t="inlineStr">
+        <is>
+          <t>Plano transversal (Espalda Alta) · Codos abiertos y retracción escapular completa.</t>
+        </is>
+      </c>
+      <c r="L32" s="106" t="inlineStr">
+        <is>
+          <t>id=remo-gironda-abierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" s="52">
+      <c r="A33" s="59" t="inlineStr">
+        <is>
+          <t>Laterales sentado</t>
+        </is>
+      </c>
+      <c r="B33" s="59" t="inlineStr">
+        <is>
+          <t>Hombro lat.</t>
+        </is>
+      </c>
+      <c r="C33" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="D33" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="E33" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F33" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G33" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H33" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I33" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J33" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K33" s="62" t="inlineStr">
+        <is>
+          <t>Prioridad 1 (Hombro Lat.) · Sentado en banco a 75–80°, abducir en plano escapular (~30° adelante) sin rotar internamente el hombro.</t>
+        </is>
+      </c>
+      <c r="L33" s="106" t="inlineStr">
+        <is>
+          <t>id=laterales-sentado</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" s="52">
+      <c r="A34" s="59" t="inlineStr">
+        <is>
+          <t>Jalón neutro</t>
+        </is>
+      </c>
+      <c r="B34" s="59" t="inlineStr">
+        <is>
+          <t>Espalda</t>
+        </is>
+      </c>
+      <c r="C34" s="61" t="inlineStr">
+        <is>
+          <t>1 @ RIR0</t>
+        </is>
+      </c>
+      <c r="D34" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E34" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F34" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G34" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H34" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I34" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J34" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K34" s="62" t="inlineStr">
+        <is>
+          <t>Plano sagital (Dorsal Sup.) · Agarre neutro ancho hombros, llevar codos a los bolsillos cortando a 90° (protege codo/bíceps).</t>
+        </is>
+      </c>
+      <c r="L34" s="106" t="inlineStr">
+        <is>
+          <t>id=jalon-neutro</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="52">
+      <c r="A35" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curl martillo scott </t>
+        </is>
+      </c>
+      <c r="B35" s="59" t="inlineStr">
+        <is>
+          <t>Bíceps</t>
+        </is>
+      </c>
+      <c r="C35" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D35" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E35" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F35" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G35" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H35" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I35" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J35" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K35" s="62" t="inlineStr">
+        <is>
+          <t>Prioridad 2 (Bíceps/Braquiorradial) · Agarre neutro (muy amigable para el codo). Bajar en 2-3 s y parar a ~15° de la extensión total para no sobrecargar tendón distal.</t>
+        </is>
+      </c>
+      <c r="L35" s="106" t="inlineStr">
+        <is>
+          <t>id=curl-martillo-scott</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="52">
+      <c r="A36" s="59" t="inlineStr">
+        <is>
           <t>Posterior polea</t>
         </is>
       </c>
-      <c r="B31" s="59" t="inlineStr">
+      <c r="B36" s="59" t="inlineStr">
         <is>
           <t>Hombro post.</t>
         </is>
       </c>
-      <c r="C31" s="61" t="inlineStr">
+      <c r="C36" s="61" t="inlineStr">
         <is>
           <t>1 @ RIR0</t>
         </is>
       </c>
-      <c r="D31" s="61" t="inlineStr">
+      <c r="D36" s="61" t="inlineStr">
         <is>
           <t>1 @ RIR0</t>
         </is>
       </c>
-      <c r="E31" s="61" t="inlineStr">
+      <c r="E36" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F31" s="61" t="inlineStr">
+      <c r="F36" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G31" s="61" t="inlineStr">
+      <c r="G36" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H31" s="61" t="inlineStr">
+      <c r="H36" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I31" s="61" t="inlineStr">
+      <c r="I36" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J31" s="61" t="inlineStr">
+      <c r="J36" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K31" s="62" t="inlineStr">
+      <c r="K36" s="62" t="inlineStr">
         <is>
           <t>Salud Hombro / Transversal · Clave para centrar cabeza humeral y compensar presses.</t>
         </is>
       </c>
-      <c r="L31" s="106" t="inlineStr">
+      <c r="L36" s="106" t="inlineStr">
         <is>
           <t>id=posterior-polea</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="52">
-      <c r="A32" s="59" t="inlineStr">
+    <row r="37" ht="15" customHeight="1" s="52">
+      <c r="A37" s="59" t="inlineStr">
         <is>
           <t>Curl bayesian</t>
         </is>
       </c>
-      <c r="B32" s="59" t="inlineStr">
+      <c r="B37" s="59" t="inlineStr">
         <is>
           <t>Bíceps</t>
         </is>
       </c>
-      <c r="C32" s="61" t="inlineStr">
+      <c r="C37" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="D32" s="61" t="inlineStr">
+      <c r="D37" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="E32" s="61" t="inlineStr">
+      <c r="E37" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F32" s="61" t="inlineStr">
+      <c r="F37" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G32" s="61" t="inlineStr">
+      <c r="G37" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H32" s="61" t="inlineStr">
+      <c r="H37" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I32" s="61" t="inlineStr">
+      <c r="I37" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J32" s="61" t="inlineStr">
+      <c r="J37" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K32" s="62" t="inlineStr">
+      <c r="K37" s="62" t="inlineStr">
         <is>
           <t>Prioridad 2 (Bíceps en estiramiento) · Hombro en extensión detrás del torso; no dejar que el hombro rote hacia delante al subir.</t>
         </is>
       </c>
-      <c r="L32" s="106" t="inlineStr">
+      <c r="L37" s="106" t="inlineStr">
         <is>
           <t>id=curl-bayesian</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="52"/>
-    <row r="34" ht="19.5" customHeight="1" s="52">
-      <c r="A34" s="65" t="inlineStr">
-        <is>
-          <t>(J) Jueves  ·  Rehab + Isquios + Aductores  ·  test de fuerza S2 / S5 / S7</t>
-        </is>
-      </c>
-      <c r="B34" s="56" t="n"/>
-      <c r="C34" s="56" t="n"/>
-      <c r="D34" s="56" t="n"/>
-      <c r="E34" s="56" t="n"/>
-      <c r="F34" s="56" t="n"/>
-      <c r="G34" s="56" t="n"/>
-      <c r="H34" s="56" t="n"/>
-      <c r="I34" s="56" t="n"/>
-      <c r="J34" s="56" t="n"/>
-      <c r="K34" s="57" t="n"/>
-      <c r="L34" s="106" t="inlineStr">
-        <is>
-          <t>sesion</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="27" customHeight="1" s="52">
-      <c r="A35" s="66" t="inlineStr">
+    <row r="38" ht="15.75" customHeight="1" s="52"/>
+    <row r="39" ht="19.5" customHeight="1" s="52">
+      <c r="A39" s="65" t="inlineStr">
+        <is>
+          <t>(V) Viernes  ·  Rehab + Isquios + Aductores  ·  test de fuerza S3 / S5 / S7 (+ opcional S8)  (desde S3; S1-S2 se hizo el jueves)</t>
+        </is>
+      </c>
+      <c r="B39" s="56" t="n"/>
+      <c r="C39" s="56" t="n"/>
+      <c r="D39" s="56" t="n"/>
+      <c r="E39" s="56" t="n"/>
+      <c r="F39" s="56" t="n"/>
+      <c r="G39" s="56" t="n"/>
+      <c r="H39" s="56" t="n"/>
+      <c r="I39" s="56" t="n"/>
+      <c r="J39" s="56" t="n"/>
+      <c r="K39" s="57" t="n"/>
+      <c r="L39" s="106" t="inlineStr">
+        <is>
+          <t>sesion;S1=J;S2=J</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="27" customHeight="1" s="52">
+      <c r="A40" s="66" t="inlineStr">
         <is>
           <t>Ejercicio</t>
         </is>
       </c>
-      <c r="B35" s="66" t="inlineStr">
+      <c r="B40" s="66" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="C35" s="66" t="inlineStr">
+      <c r="C40" s="66" t="inlineStr">
         <is>
           <t>Sem 1 (series@RIR)</t>
         </is>
       </c>
-      <c r="D35" s="66" t="inlineStr">
+      <c r="D40" s="66" t="inlineStr">
         <is>
           <t>Sem 2 (series@RIR)</t>
         </is>
       </c>
-      <c r="E35" s="66" t="inlineStr">
+      <c r="E40" s="66" t="inlineStr">
         <is>
           <t>Sem 3 (series@RIR)</t>
         </is>
       </c>
-      <c r="F35" s="66" t="inlineStr">
+      <c r="F40" s="66" t="inlineStr">
         <is>
           <t>Sem 4 (series@RIR)</t>
         </is>
       </c>
-      <c r="G35" s="66" t="inlineStr">
+      <c r="G40" s="66" t="inlineStr">
         <is>
           <t>Sem 5 (series@RIR)</t>
         </is>
       </c>
-      <c r="H35" s="66" t="inlineStr">
+      <c r="H40" s="66" t="inlineStr">
         <is>
           <t>Sem 6 (series@RIR)</t>
         </is>
       </c>
-      <c r="I35" s="66" t="inlineStr">
+      <c r="I40" s="66" t="inlineStr">
         <is>
           <t>Sem 7 (series@RIR)</t>
         </is>
       </c>
-      <c r="J35" s="66" t="inlineStr">
+      <c r="J40" s="66" t="inlineStr">
         <is>
           <t>Sem 8 (series@RIR)</t>
         </is>
       </c>
-      <c r="K35" s="66" t="inlineStr">
+      <c r="K40" s="66" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="L35" s="106" t="inlineStr">
+      <c r="L40" s="106" t="inlineStr">
         <is>
           <t>App (no tocar)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="81" customHeight="1" s="52">
-      <c r="A36" s="71" t="inlineStr">
+    <row r="41" ht="81" customHeight="1" s="52">
+      <c r="A41" s="71" t="inlineStr">
         <is>
           <t>TEST fuerza · extensión unilateral en máquina 90→45°</t>
         </is>
       </c>
-      <c r="B36" s="71" t="inlineStr">
+      <c r="B41" s="71" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C36" s="72" t="inlineStr">
+      <c r="C41" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D36" s="72" t="inlineStr">
+      <c r="D41" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="72" t="inlineStr">
         <is>
           <t>2 aprox. +
 1 al fallo
 por pierna</t>
         </is>
       </c>
-      <c r="E36" s="72" t="inlineStr">
+      <c r="F41" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="72" t="inlineStr">
+      <c r="G41" s="72" t="inlineStr">
         <is>
           <t>2 aprox. +
 1 al fallo
 por pierna</t>
         </is>
       </c>
-      <c r="H36" s="72" t="inlineStr">
+      <c r="H41" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I36" s="72" t="inlineStr">
+      <c r="I41" s="72" t="inlineStr">
         <is>
           <t>2 aprox. +
 1 al fallo
 por pierna</t>
         </is>
       </c>
-      <c r="J36" s="72" t="inlineStr">
+      <c r="J41" s="72" t="inlineStr">
         <is>
           <t>Opcional:
 rango completo</t>
         </is>
       </c>
-      <c r="K36" s="71" t="inlineStr">
-        <is>
-          <t>Al empezar la sesión, tras la española 2-3×45 s y 2 series de aproximación. Mismo asiento y SIEMPRE rango fijo 90→45° (si el rango cambia, la comparación entre semanas no vale). Misma carga en las dos piernas (la que la I haga unas 10-15 reps), tempo 2-0-2, D primero, 3 min de descanso y luego la I; para si pasa de 3/10. Apunta carga y reps en «Seguimiento rodilla», que calcula la simetría. Objetivo ≥90% antes del balón [LÓGICA; el 90% viene de la vuelta al deporte tras LCA, no está validado en dolor femoropatelar: INCERTIDUMBRE]. Test en rango completo opcional en S8 y no en S7, para que sea la única novedad de su semana.</t>
-        </is>
-      </c>
-      <c r="L36" s="106" t="inlineStr">
+      <c r="K41" s="71" t="inlineStr">
+        <is>
+          <t>Test 1 → vie 6/11 (S3): en S2 no se hizo (analítica). Al empezar la sesión, tras la española 2-3×45 s y 2 series de aproximación. Mismo asiento y SIEMPRE rango fijo 90→45° (si el rango cambia, la comparación entre semanas no vale). Misma carga en las dos piernas (la que la I haga unas 10-15 reps), tempo 2-0-2, D primero, 3 min de descanso y luego la I; para si pasa de 3/10. Apunta carga y reps en «Seguimiento rodilla», que calcula la simetría. Objetivo ≥90% antes del balón [LÓGICA; el 90% viene de la vuelta al deporte tras LCA, no está validado en dolor femoropatelar: INCERTIDUMBRE]. Test en rango completo opcional en S8 y no en S7, para que sea la única novedad de su semana.</t>
+        </is>
+      </c>
+      <c r="L41" s="106" t="inlineStr">
         <is>
           <t>id=test-fuerza-extension-unilateral-en-maquina-90-45</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="43.5" customHeight="1" s="52">
-      <c r="A37" s="62" t="inlineStr">
+    <row r="42" ht="43.5" customHeight="1" s="52">
+      <c r="A42" s="62" t="inlineStr">
         <is>
           <t>Sentadilla al cajón o desde pines · pesado y lento n.º 2</t>
         </is>
       </c>
-      <c r="B37" s="62" t="inlineStr">
+      <c r="B42" s="62" t="inlineStr">
         <is>
           <t>Rehab</t>
         </is>
       </c>
-      <c r="C37" s="63" t="inlineStr">
+      <c r="C42" s="63" t="inlineStr">
         <is>
           <t>3 x12</t>
         </is>
       </c>
-      <c r="D37" s="63" t="inlineStr">
+      <c r="D42" s="63" t="inlineStr">
         <is>
           <t>3 x10</t>
         </is>
       </c>
-      <c r="E37" s="63" t="inlineStr">
+      <c r="E42" s="63" t="inlineStr">
         <is>
           <t>3 x10
 prof. del lunes</t>
         </is>
       </c>
-      <c r="F37" s="63" t="inlineStr">
+      <c r="F42" s="63" t="inlineStr">
         <is>
           <t>3 x10
 prof. del lunes</t>
         </is>
       </c>
-      <c r="G37" s="63" t="inlineStr">
+      <c r="G42" s="63" t="inlineStr">
         <is>
           <t>3 x8</t>
         </is>
       </c>
-      <c r="H37" s="63" t="inlineStr">
+      <c r="H42" s="63" t="inlineStr">
         <is>
           <t>3 x8
 prof. del lunes</t>
         </is>
       </c>
-      <c r="I37" s="63" t="inlineStr">
+      <c r="I42" s="63" t="inlineStr">
         <is>
           <t>3 x8
 prof. del lunes</t>
         </is>
       </c>
-      <c r="J37" s="63" t="inlineStr">
+      <c r="J42" s="63" t="inlineStr">
         <is>
           <t>3 x8
 repite S7</t>
         </is>
       </c>
-      <c r="K37" s="62" t="inlineStr">
-        <is>
-          <t>Tras el test (S2/S5/S7), carga por RIR. Tempo 3-1-3, RIR 2. Profundidad = la validada el lunes en la prensa. Postura habitual: un chasquido sin dolor no cambia nada; el apoyo ancho solo si te reduce el DOLOR [LÓGICA]. Antes del rehab (si no hay test): sentadilla española 2-3×45 s.</t>
-        </is>
-      </c>
-      <c r="L37" s="106" t="inlineStr">
+      <c r="K42" s="62" t="inlineStr">
+        <is>
+          <t>Tras el test (S3/S5/S7), carga por RIR. Tempo 3-1-3, RIR 2. Profundidad = la validada el lunes en la prensa. Postura habitual: un chasquido sin dolor no cambia nada; el apoyo ancho solo si te reduce el DOLOR [LÓGICA]. Antes del rehab (si no hay test): sentadilla española 2-3×45 s.</t>
+        </is>
+      </c>
+      <c r="L42" s="106" t="inlineStr">
         <is>
           <t>id=sentadilla-al-cajon-o-desde-pines-pesado-y-lento-n-2;escalera=prensa:sigue</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30.75" customHeight="1" s="52">
-      <c r="A38" s="62" t="inlineStr">
+    <row r="43" ht="30.75" customHeight="1" s="52">
+      <c r="A43" s="62" t="inlineStr">
         <is>
           <t>Bulgarian split squat</t>
         </is>
       </c>
-      <c r="B38" s="62" t="inlineStr">
+      <c r="B43" s="62" t="inlineStr">
         <is>
           <t>Rehab</t>
         </is>
       </c>
-      <c r="C38" s="63" t="inlineStr">
+      <c r="C43" s="63" t="inlineStr">
         <is>
           <t>2 x12</t>
         </is>
       </c>
-      <c r="D38" s="63" t="inlineStr">
+      <c r="D43" s="63" t="inlineStr">
         <is>
           <t>2 x10/pierna</t>
         </is>
       </c>
-      <c r="E38" s="63" t="inlineStr">
+      <c r="E43" s="63" t="inlineStr">
         <is>
           <t>2 x10/pierna</t>
         </is>
       </c>
-      <c r="F38" s="63" t="inlineStr">
+      <c r="F43" s="63" t="inlineStr">
         <is>
           <t>2 x10/pierna</t>
         </is>
       </c>
-      <c r="G38" s="63" t="inlineStr">
+      <c r="G43" s="63" t="inlineStr">
         <is>
           <t>2 x8/pierna</t>
         </is>
       </c>
-      <c r="H38" s="63" t="inlineStr">
+      <c r="H43" s="63" t="inlineStr">
         <is>
           <t>2 x8/pierna</t>
         </is>
       </c>
-      <c r="I38" s="63" t="inlineStr">
+      <c r="I43" s="63" t="inlineStr">
         <is>
           <t>2 x8/pierna</t>
         </is>
       </c>
-      <c r="J38" s="63" t="inlineStr">
+      <c r="J43" s="63" t="inlineStr">
         <is>
           <t>2 x8/pierna
 repite S7</t>
         </is>
       </c>
-      <c r="K38" s="62" t="inlineStr">
+      <c r="K43" s="62" t="inlineStr">
         <is>
           <t>D primero: RIR 2 y profundidad validada el lunes. I: RIR 1-2 y rango completo. Tempo 3-1-3. Alterna piernas, 60-90 s entre una y otra.</t>
         </is>
       </c>
-      <c r="L38" s="106" t="inlineStr">
+      <c r="L43" s="106" t="inlineStr">
         <is>
           <t>id=bulgarian-split-squat;escalera=prensa:sigue</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="30.75" customHeight="1" s="52">
-      <c r="A39" s="62" t="inlineStr">
+    <row r="44" ht="30.75" customHeight="1" s="52">
+      <c r="A44" s="62" t="inlineStr">
         <is>
           <t>Abducción de pie unilateral (máquina)</t>
         </is>
       </c>
-      <c r="B39" s="62" t="inlineStr">
+      <c r="B44" s="62" t="inlineStr">
         <is>
           <t>Rehab (cadera)</t>
         </is>
       </c>
-      <c r="C39" s="63" t="inlineStr">
+      <c r="C44" s="63" t="inlineStr">
         <is>
           <t>2 x15–20</t>
         </is>
       </c>
-      <c r="D39" s="63" t="inlineStr">
+      <c r="D44" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="E39" s="63" t="inlineStr">
+      <c r="E44" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="F39" s="63" t="inlineStr">
+      <c r="F44" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="G39" s="63" t="inlineStr">
+      <c r="G44" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="H39" s="63" t="inlineStr">
+      <c r="H44" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="I39" s="63" t="inlineStr">
+      <c r="I44" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="J39" s="63" t="inlineStr">
+      <c r="J44" s="63" t="inlineStr">
         <is>
           <t>3 x10-15/pierna
 @RIR1-2</t>
         </is>
       </c>
-      <c r="K39" s="62" t="inlineStr">
-        <is>
-          <t>Misma máquina que el lunes; empieza por la D. Va DESPUÉS de la búlgara, para no fatigar el glúteo medio antes del trabajo a una pierna [LÓGICA]. Lunes + jueves = 72-96 h entre sesiones de cadera.</t>
-        </is>
-      </c>
-      <c r="L39" s="106" t="inlineStr">
+      <c r="K44" s="62" t="inlineStr">
+        <is>
+          <t>Misma máquina que el lunes; empieza por la D. Va DESPUÉS de la búlgara, para no fatigar el glúteo medio antes del trabajo a una pierna [LÓGICA]. Lunes + viernes = 72-96 h entre sesiones de cadera.</t>
+        </is>
+      </c>
+      <c r="L44" s="106" t="inlineStr">
         <is>
           <t>id=abduccion-de-pie-unilateral-maquina</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1" s="52">
-      <c r="A40" s="62" t="inlineStr">
+    <row r="45" ht="18" customHeight="1" s="52">
+      <c r="A45" s="62" t="inlineStr">
         <is>
           <t>Touchdown squat</t>
         </is>
       </c>
-      <c r="B40" s="62" t="inlineStr">
+      <c r="B45" s="62" t="inlineStr">
         <is>
           <t>Rehab</t>
         </is>
       </c>
-      <c r="C40" s="63" t="inlineStr">
+      <c r="C45" s="63" t="inlineStr">
         <is>
           <t>2 x15–20</t>
         </is>
       </c>
-      <c r="D40" s="63" t="inlineStr">
+      <c r="D45" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="63" t="inlineStr">
+      <c r="E45" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F40" s="63" t="inlineStr">
+      <c r="F45" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G40" s="63" t="inlineStr">
+      <c r="G45" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H40" s="63" t="inlineStr">
+      <c r="H45" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I40" s="63" t="inlineStr">
+      <c r="I45" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J40" s="63" t="inlineStr">
+      <c r="J45" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K40" s="63" t="inlineStr">
-        <is>
-          <t>Sale del jueves desde S2: va el lunes, antes de la prensa [LÓGICA].</t>
-        </is>
-      </c>
-      <c r="L40" s="106" t="inlineStr">
+      <c r="K45" s="63" t="inlineStr">
+        <is>
+          <t>Sale de este día desde S2: va el lunes, antes de la prensa [LÓGICA].</t>
+        </is>
+      </c>
+      <c r="L45" s="106" t="inlineStr">
         <is>
           <t>id=touchdown-squat</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="52">
-      <c r="A41" s="59" t="inlineStr">
+    <row r="46" ht="15.75" customHeight="1" s="52">
+      <c r="A46" s="59" t="inlineStr">
         <is>
           <t>Isquios sentado</t>
         </is>
       </c>
-      <c r="B41" s="59" t="inlineStr">
+      <c r="B46" s="59" t="inlineStr">
         <is>
           <t>Isquios</t>
         </is>
       </c>
-      <c r="C41" s="61" t="inlineStr">
+      <c r="C46" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="D41" s="61" t="inlineStr">
+      <c r="D46" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="E41" s="61" t="inlineStr">
+      <c r="E46" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F41" s="61" t="inlineStr">
+      <c r="F46" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G41" s="61" t="inlineStr">
+      <c r="G46" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H41" s="61" t="inlineStr">
+      <c r="H46" s="61" t="inlineStr">
         <is>
           <t>5 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I41" s="61" t="inlineStr">
+      <c r="I46" s="61" t="inlineStr">
         <is>
           <t>5 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J41" s="61" t="inlineStr">
+      <c r="J46" s="61" t="inlineStr">
         <is>
           <t>5 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K41" s="62" t="inlineStr">
+      <c r="K46" s="62" t="inlineStr">
         <is>
           <t>Isquios en estiramiento máximo (cadera a 90°) · Controlar fase excéntrica.</t>
         </is>
       </c>
-      <c r="L41" s="106" t="inlineStr">
+      <c r="L46" s="106" t="inlineStr">
         <is>
           <t>id=isquios-sentado</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1" s="52">
-      <c r="A42" s="59" t="inlineStr">
-        <is>
-          <t>Aductores</t>
-        </is>
-      </c>
-      <c r="B42" s="59" t="inlineStr">
-        <is>
-          <t>Aductores</t>
-        </is>
-      </c>
-      <c r="C42" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D42" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E42" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F42" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G42" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H42" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I42" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J42" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K42" s="62" t="inlineStr">
-        <is>
-          <t>Plano transversal/frontal · Pausa de 1 s en apertura máxima sin dolor inguinal/rodilla.</t>
-        </is>
-      </c>
-      <c r="L42" s="106" t="inlineStr">
-        <is>
-          <t>id=aductores</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" s="52">
-      <c r="A43" s="59" t="inlineStr">
-        <is>
-          <t>Gemelos prensa</t>
-        </is>
-      </c>
-      <c r="B43" s="59" t="inlineStr">
-        <is>
-          <t>Gemelos</t>
-        </is>
-      </c>
-      <c r="C43" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D43" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E43" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F43" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G43" s="61" t="inlineStr">
-        <is>
-          <t>4 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H43" s="61" t="inlineStr">
-        <is>
-          <t>4 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I43" s="61" t="inlineStr">
-        <is>
-          <t>4 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J43" s="61" t="inlineStr">
-        <is>
-          <t>5 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K43" s="62" t="inlineStr">
-        <is>
-          <t>Prensa con pies abajo · Pausa estricta de 2 s en máximo estiramiento abajo (sin rebote elástico).</t>
-        </is>
-      </c>
-      <c r="L43" s="106" t="inlineStr">
-        <is>
-          <t>id=gemelos-prensa</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" s="52"/>
-    <row r="45" ht="19.5" customHeight="1" s="52">
-      <c r="A45" s="65" t="inlineStr">
-        <is>
-          <t>(V) Viernes  ·  Torso</t>
-        </is>
-      </c>
-      <c r="B45" s="56" t="n"/>
-      <c r="C45" s="56" t="n"/>
-      <c r="D45" s="56" t="n"/>
-      <c r="E45" s="56" t="n"/>
-      <c r="F45" s="56" t="n"/>
-      <c r="G45" s="56" t="n"/>
-      <c r="H45" s="56" t="n"/>
-      <c r="I45" s="56" t="n"/>
-      <c r="J45" s="56" t="n"/>
-      <c r="K45" s="57" t="n"/>
-      <c r="L45" s="106" t="inlineStr">
-        <is>
-          <t>sesion</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="27" customHeight="1" s="52">
-      <c r="A46" s="66" t="inlineStr">
-        <is>
-          <t>Ejercicio</t>
-        </is>
-      </c>
-      <c r="B46" s="66" t="inlineStr">
-        <is>
-          <t>Objetivo</t>
-        </is>
-      </c>
-      <c r="C46" s="66" t="inlineStr">
-        <is>
-          <t>Sem 1 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="D46" s="66" t="inlineStr">
-        <is>
-          <t>Sem 2 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="E46" s="66" t="inlineStr">
-        <is>
-          <t>Sem 3 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="F46" s="66" t="inlineStr">
-        <is>
-          <t>Sem 4 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="G46" s="66" t="inlineStr">
-        <is>
-          <t>Sem 5 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="H46" s="66" t="inlineStr">
-        <is>
-          <t>Sem 6 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="I46" s="66" t="inlineStr">
-        <is>
-          <t>Sem 7 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="J46" s="66" t="inlineStr">
-        <is>
-          <t>Sem 8 (series@RIR)</t>
-        </is>
-      </c>
-      <c r="K46" s="66" t="inlineStr">
-        <is>
-          <t>Notas</t>
-        </is>
-      </c>
-      <c r="L46" s="106" t="inlineStr">
-        <is>
-          <t>App (no tocar)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="52">
       <c r="A47" s="59" t="inlineStr">
         <is>
-          <t>Triceps conc polea (-15°)</t>
+          <t>Aductores</t>
         </is>
       </c>
       <c r="B47" s="59" t="inlineStr">
         <is>
-          <t>Tríceps</t>
+          <t>Aductores</t>
         </is>
       </c>
       <c r="C47" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="D47" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="E47" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="F47" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>2 @ RIR1/0</t>
         </is>
       </c>
       <c r="G47" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="H47" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="I47" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="J47" s="61" t="inlineStr">
         <is>
-          <t>1 @ RIR0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="K47" s="62" t="inlineStr">
         <is>
-          <t>Prioridad 2 + Potenciación de codo · Hombro a -15° (extensión): máximo acortamiento de cabeza larga con torque nulo en flexión máxima de codo (calienta tendón para el francés).</t>
+          <t>Plano transversal/frontal · Pausa de 1 s en apertura máxima sin dolor inguinal/rodilla.</t>
         </is>
       </c>
       <c r="L47" s="106" t="inlineStr">
         <is>
-          <t>id=triceps-conc-polea-15</t>
+          <t>id=aductores</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="52">
       <c r="A48" s="59" t="inlineStr">
         <is>
-          <t>Laterales polea</t>
+          <t>Gemelos prensa</t>
         </is>
       </c>
       <c r="B48" s="59" t="inlineStr">
         <is>
-          <t>Hombro lat.</t>
+          <t>Gemelos</t>
         </is>
       </c>
       <c r="C48" s="61" t="inlineStr">
@@ -8439,245 +8457,144 @@
       </c>
       <c r="D48" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="E48" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="F48" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>3 @ RIR1/0</t>
         </is>
       </c>
       <c r="G48" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>4 @ RIR1/0</t>
         </is>
       </c>
       <c r="H48" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>4 @ RIR1/0</t>
         </is>
       </c>
       <c r="I48" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>4 @ RIR1/0</t>
         </is>
       </c>
       <c r="J48" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>5 @ RIR1/0</t>
         </is>
       </c>
       <c r="K48" s="62" t="inlineStr">
         <is>
-          <t>Prioridad 1 (Hombro Lat.) · Polea a altura de muñeca/muslo, abducción en plano escapular.</t>
+          <t>Prensa con pies abajo · Pausa estricta de 2 s en máximo estiramiento abajo (sin rebote elástico).</t>
         </is>
       </c>
       <c r="L48" s="106" t="inlineStr">
         <is>
-          <t>id=laterales-polea</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" s="52">
-      <c r="A49" s="59" t="inlineStr">
-        <is>
-          <t>Press francés manc (banco plano)</t>
-        </is>
-      </c>
-      <c r="B49" s="59" t="inlineStr">
-        <is>
-          <t>Tríceps</t>
-        </is>
-      </c>
-      <c r="C49" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D49" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E49" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F49" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G49" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H49" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I49" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J49" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K49" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 2 (Tríceps) · Agarre neutro (martillo) y brazos inclinados a ~100° hacia la cabeza: quita cizalla en epitróclea/olécranon y mantiene tensión constante.</t>
-        </is>
-      </c>
-      <c r="L49" s="106" t="inlineStr">
-        <is>
-          <t>id=press-frances-manc-banco-plano</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" s="52">
-      <c r="A50" s="59" t="inlineStr">
-        <is>
-          <t>Curl biceps barra z</t>
-        </is>
-      </c>
-      <c r="B50" s="59" t="inlineStr">
-        <is>
-          <t>Bíceps</t>
-        </is>
-      </c>
-      <c r="C50" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D50" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E50" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F50" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G50" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H50" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I50" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J50" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K50" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 2 (Bíceps rango medio) · Usar el agarre de la barra Z (ancho o estrecho) que resulte 100% libre de molestia en muñeca y codo.</t>
-        </is>
-      </c>
+          <t>id=gemelos-prensa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1" s="52"/>
+    <row r="50" ht="19.5" customHeight="1" s="52">
+      <c r="A50" s="65" t="inlineStr">
+        <is>
+          <t>(S) Sábado  ·  casa, peso libre  ·  Torso (desde S2 = 31/10; S1 se hizo el viernes en el gimnasio)</t>
+        </is>
+      </c>
+      <c r="B50" s="56" t="n"/>
+      <c r="C50" s="56" t="n"/>
+      <c r="D50" s="56" t="n"/>
+      <c r="E50" s="56" t="n"/>
+      <c r="F50" s="56" t="n"/>
+      <c r="G50" s="56" t="n"/>
+      <c r="H50" s="56" t="n"/>
+      <c r="I50" s="56" t="n"/>
+      <c r="J50" s="56" t="n"/>
+      <c r="K50" s="57" t="n"/>
       <c r="L50" s="106" t="inlineStr">
         <is>
-          <t>id=curl-biceps-barra-z</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1" s="52">
-      <c r="A51" s="59" t="inlineStr">
-        <is>
-          <t>Press máquina neutro ascendente</t>
-        </is>
-      </c>
-      <c r="B51" s="59" t="inlineStr">
-        <is>
-          <t>Pecho</t>
-        </is>
-      </c>
-      <c r="C51" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="D51" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="E51" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="F51" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="G51" s="61" t="inlineStr">
-        <is>
-          <t>2 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="H51" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="I51" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="J51" s="61" t="inlineStr">
-        <is>
-          <t>3 @ RIR1/0</t>
-        </is>
-      </c>
-      <c r="K51" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 4 (Haz clavicular) · 10/10 tras brazos: el agarre neutro y la trayectoria convergente ascendente aíslan el haz clavicular sin estrés en hombro ni codo.</t>
+          <t>sesion;S1=V</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="27" customHeight="1" s="52">
+      <c r="A51" s="66" t="inlineStr">
+        <is>
+          <t>Ejercicio</t>
+        </is>
+      </c>
+      <c r="B51" s="66" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+      <c r="C51" s="66" t="inlineStr">
+        <is>
+          <t>Sem 1 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="D51" s="66" t="inlineStr">
+        <is>
+          <t>Sem 2 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="E51" s="66" t="inlineStr">
+        <is>
+          <t>Sem 3 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="F51" s="66" t="inlineStr">
+        <is>
+          <t>Sem 4 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="G51" s="66" t="inlineStr">
+        <is>
+          <t>Sem 5 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="H51" s="66" t="inlineStr">
+        <is>
+          <t>Sem 6 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="I51" s="66" t="inlineStr">
+        <is>
+          <t>Sem 7 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="J51" s="66" t="inlineStr">
+        <is>
+          <t>Sem 8 (series@RIR)</t>
+        </is>
+      </c>
+      <c r="K51" s="66" t="inlineStr">
+        <is>
+          <t>Notas</t>
         </is>
       </c>
       <c r="L51" s="106" t="inlineStr">
         <is>
-          <t>id=press-maquina-neutro-ascendente</t>
+          <t>App (no tocar)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="52">
       <c r="A52" s="59" t="inlineStr">
         <is>
-          <t>Dominada neutra dorsal</t>
+          <t>Patada de tríceps (mancuerna o goma)</t>
         </is>
       </c>
       <c r="B52" s="59" t="inlineStr">
         <is>
-          <t>Espalda</t>
+          <t>Tríceps</t>
         </is>
       </c>
       <c r="C52" s="61" t="inlineStr">
@@ -8707,39 +8624,39 @@
       </c>
       <c r="H52" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>1 @ RIR0</t>
         </is>
       </c>
       <c r="I52" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>1 @ RIR0</t>
         </is>
       </c>
       <c r="J52" s="61" t="inlineStr">
         <is>
-          <t>2 @ RIR1/0</t>
+          <t>1 @ RIR0</t>
         </is>
       </c>
       <c r="K52" s="62" t="inlineStr">
         <is>
-          <t>Plano sagital (Dorsal Sup.) · Usar STRAPS obligatoriamente para anular fatiga previa de bíceps y proteger codos.</t>
+          <t>Primer sábado (31/10): peso libre nuevo → recalibra el peso por RIR; no es comparable con las cargas de máquina [LÓGICA]. S1: tríceps concentrado en polea. Brazo ligeramente por detrás del cuerpo para mantener la cabeza larga estirada [LÓGICA]. Prioridad 2 + Potenciación de codo · Hombro a -15° (extensión): máximo acortamiento de cabeza larga con torque nulo en flexión máxima de codo (calienta tendón para el francés).</t>
         </is>
       </c>
       <c r="L52" s="106" t="inlineStr">
         <is>
-          <t>id=dominada-neutra-dorsal</t>
+          <t>id=triceps-conc-polea-15</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="52">
       <c r="A53" s="59" t="inlineStr">
         <is>
-          <t>Remo máquina (pecho apoyado 30°)</t>
+          <t>Laterales con goma</t>
         </is>
       </c>
       <c r="B53" s="59" t="inlineStr">
         <is>
-          <t>Espalda</t>
+          <t>Hombro lat.</t>
         </is>
       </c>
       <c r="C53" s="61" t="inlineStr">
@@ -8784,24 +8701,24 @@
       </c>
       <c r="K53" s="62" t="inlineStr">
         <is>
-          <t>Plano sagital/híbrido (Dorsal Sup.) · Usar STRAPS, codos a ~30° hasta línea del torso.</t>
+          <t>S1: laterales en polea. La goma imita mejor la curva de resistencia de la polea que la mancuerna [LÓGICA]. Prioridad 1 (Hombro Lat.) · Polea a altura de muñeca/muslo, abducción en plano escapular.</t>
         </is>
       </c>
       <c r="L53" s="106" t="inlineStr">
         <is>
-          <t>id=remo-maquina-pecho-apoyado-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="52">
+          <t>id=laterales-polea</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" s="52">
       <c r="A54" s="59" t="inlineStr">
         <is>
-          <t>Aducción unil. polea alta (Pull-in)</t>
+          <t>Press francés manc (banco plano)</t>
         </is>
       </c>
       <c r="B54" s="59" t="inlineStr">
         <is>
-          <t>Espalda</t>
+          <t>Tríceps</t>
         </is>
       </c>
       <c r="C54" s="61" t="inlineStr">
@@ -8836,588 +8753,689 @@
       </c>
       <c r="I54" s="61" t="inlineStr">
         <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J54" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K54" s="62" t="inlineStr">
+        <is>
+          <t>Prioridad 2 (Tríceps) · Agarre neutro (martillo) y brazos inclinados a ~100° hacia la cabeza: quita cizalla en epitróclea/olécranon y mantiene tensión constante.</t>
+        </is>
+      </c>
+      <c r="L54" s="106" t="inlineStr">
+        <is>
+          <t>id=press-frances-manc-banco-plano</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1" s="52">
+      <c r="A55" s="59" t="inlineStr">
+        <is>
+          <t>Curl con mancuernas</t>
+        </is>
+      </c>
+      <c r="B55" s="59" t="inlineStr">
+        <is>
+          <t>Bíceps</t>
+        </is>
+      </c>
+      <c r="C55" s="61" t="inlineStr">
+        <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J54" s="61" t="inlineStr">
+      <c r="D55" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K54" s="62" t="inlineStr">
-        <is>
-          <t>Prioridad 3 (Dorsal Bajo) · De lado a la polea (con tobillera en muñeca o codo semirrígido) para aislar haz inferior sin usar bíceps ni codo · Sem 1-2 a RIR 1-2.</t>
-        </is>
-      </c>
-      <c r="L54" s="106" t="inlineStr">
-        <is>
-          <t>id=aduccion-unil-polea-alta-pull-in</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1" s="52"/>
-    <row r="56" ht="19.5" customHeight="1" s="52">
-      <c r="A56" s="65" t="inlineStr">
-        <is>
-          <t>(S) Sábado  ·  casa, sin máquinas ni poleas  ·  desde S2, sin pierna (el domingo: carrera)</t>
-        </is>
-      </c>
-      <c r="B56" s="56" t="n"/>
-      <c r="C56" s="56" t="n"/>
-      <c r="D56" s="56" t="n"/>
-      <c r="E56" s="56" t="n"/>
-      <c r="F56" s="56" t="n"/>
-      <c r="G56" s="56" t="n"/>
-      <c r="H56" s="56" t="n"/>
-      <c r="I56" s="56" t="n"/>
-      <c r="J56" s="56" t="n"/>
-      <c r="K56" s="57" t="n"/>
+      <c r="E55" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F55" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G55" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H55" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I55" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J55" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K55" s="62" t="inlineStr">
+        <is>
+          <t>S1: curl con barra Z. Barra recta solo si no molesta en muñeca ni codo. Prioridad 2 (Bíceps rango medio) · Usar el agarre de la barra Z (ancho o estrecho) que resulte 100% libre de molestia en muñeca y codo.</t>
+        </is>
+      </c>
+      <c r="L55" s="106" t="inlineStr">
+        <is>
+          <t>id=curl-biceps-barra-z</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" s="52">
+      <c r="A56" s="59" t="inlineStr">
+        <is>
+          <t>Press inclinado con mancuernas, agarre neutro</t>
+        </is>
+      </c>
+      <c r="B56" s="59" t="inlineStr">
+        <is>
+          <t>Pecho</t>
+        </is>
+      </c>
+      <c r="C56" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="D56" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="E56" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="F56" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="G56" s="61" t="inlineStr">
+        <is>
+          <t>2 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="H56" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="I56" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="J56" s="61" t="inlineStr">
+        <is>
+          <t>3 @ RIR1/0</t>
+        </is>
+      </c>
+      <c r="K56" s="62" t="inlineStr">
+        <is>
+          <t>S1: press en máquina. Prioridad 4 (Haz clavicular) · 10/10 tras brazos: el agarre neutro y la trayectoria convergente ascendente aíslan el haz clavicular sin estrés en hombro ni codo.</t>
+        </is>
+      </c>
       <c r="L56" s="106" t="inlineStr">
         <is>
+          <t>id=press-maquina-neutro-ascendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" s="52"/>
+    <row r="58" ht="19.5" customHeight="1" s="52">
+      <c r="A58" s="65" t="inlineStr">
+        <is>
+          <t>(S) Sábado (cont.)  ·  abdominales + correctivos  ·  sin pierna (el domingo: carrera)</t>
+        </is>
+      </c>
+      <c r="B58" s="56" t="n"/>
+      <c r="C58" s="56" t="n"/>
+      <c r="D58" s="56" t="n"/>
+      <c r="E58" s="56" t="n"/>
+      <c r="F58" s="56" t="n"/>
+      <c r="G58" s="56" t="n"/>
+      <c r="H58" s="56" t="n"/>
+      <c r="I58" s="56" t="n"/>
+      <c r="J58" s="56" t="n"/>
+      <c r="K58" s="57" t="n"/>
+      <c r="L58" s="106" t="inlineStr">
+        <is>
           <t>sesion;nombreS1=Sábado/Domingo</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="27" customHeight="1" s="52">
-      <c r="A57" s="66" t="inlineStr">
+    <row r="59" ht="27" customHeight="1" s="52">
+      <c r="A59" s="66" t="inlineStr">
         <is>
           <t>Ejercicio</t>
         </is>
       </c>
-      <c r="B57" s="66" t="inlineStr">
+      <c r="B59" s="66" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="C57" s="66" t="inlineStr">
+      <c r="C59" s="66" t="inlineStr">
         <is>
           <t>Sem 1 (series@RIR)</t>
         </is>
       </c>
-      <c r="D57" s="66" t="inlineStr">
+      <c r="D59" s="66" t="inlineStr">
         <is>
           <t>Sem 2 (series@RIR)</t>
         </is>
       </c>
-      <c r="E57" s="66" t="inlineStr">
+      <c r="E59" s="66" t="inlineStr">
         <is>
           <t>Sem 3 (series@RIR)</t>
         </is>
       </c>
-      <c r="F57" s="66" t="inlineStr">
+      <c r="F59" s="66" t="inlineStr">
         <is>
           <t>Sem 4 (series@RIR)</t>
         </is>
       </c>
-      <c r="G57" s="66" t="inlineStr">
+      <c r="G59" s="66" t="inlineStr">
         <is>
           <t>Sem 5 (series@RIR)</t>
         </is>
       </c>
-      <c r="H57" s="66" t="inlineStr">
+      <c r="H59" s="66" t="inlineStr">
         <is>
           <t>Sem 6 (series@RIR)</t>
         </is>
       </c>
-      <c r="I57" s="66" t="inlineStr">
+      <c r="I59" s="66" t="inlineStr">
         <is>
           <t>Sem 7 (series@RIR)</t>
         </is>
       </c>
-      <c r="J57" s="66" t="inlineStr">
+      <c r="J59" s="66" t="inlineStr">
         <is>
           <t>Sem 8 (series@RIR)</t>
         </is>
       </c>
-      <c r="K57" s="66" t="inlineStr">
+      <c r="K59" s="66" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="L57" s="106" t="inlineStr">
+      <c r="L59" s="106" t="inlineStr">
         <is>
           <t>App (no tocar)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="30.75" customHeight="1" s="52">
-      <c r="A58" s="62" t="inlineStr">
+    <row r="60" ht="30.75" customHeight="1" s="52">
+      <c r="A60" s="62" t="inlineStr">
         <is>
           <t>Abducción unilateral</t>
         </is>
       </c>
-      <c r="B58" s="62" t="inlineStr">
+      <c r="B60" s="62" t="inlineStr">
         <is>
           <t>Rehab (cadera)</t>
         </is>
       </c>
-      <c r="C58" s="63" t="inlineStr">
+      <c r="C60" s="63" t="inlineStr">
         <is>
           <t>2 x15–20</t>
         </is>
       </c>
-      <c r="D58" s="63" t="inlineStr">
+      <c r="D60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E58" s="63" t="inlineStr">
+      <c r="E60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F58" s="63" t="inlineStr">
+      <c r="F60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G58" s="63" t="inlineStr">
+      <c r="G60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H58" s="63" t="inlineStr">
+      <c r="H60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I58" s="63" t="inlineStr">
+      <c r="I60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J58" s="63" t="inlineStr">
+      <c r="J60" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K58" s="62" t="inlineStr">
-        <is>
-          <t>Sale del sábado desde S2: la abducción va el lunes y el jueves en máquina; la pierna se concentra en 2 días [LÓGICA].</t>
-        </is>
-      </c>
-      <c r="L58" s="106" t="inlineStr">
+      <c r="K60" s="62" t="inlineStr">
+        <is>
+          <t>Sale del sábado desde S2: la abducción va el lunes y el viernes en máquina; la pierna se concentra en 2 días [LÓGICA].</t>
+        </is>
+      </c>
+      <c r="L60" s="106" t="inlineStr">
         <is>
           <t>id=abduccion-unilateral</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1" s="52">
-      <c r="A59" s="62" t="inlineStr">
+    <row r="61" ht="18" customHeight="1" s="52">
+      <c r="A61" s="62" t="inlineStr">
         <is>
           <t>Touchdown squat</t>
         </is>
       </c>
-      <c r="B59" s="62" t="inlineStr">
+      <c r="B61" s="62" t="inlineStr">
         <is>
           <t>Rehab</t>
         </is>
       </c>
-      <c r="C59" s="63" t="inlineStr">
+      <c r="C61" s="63" t="inlineStr">
         <is>
           <t>2 x15–20</t>
         </is>
       </c>
-      <c r="D59" s="63" t="inlineStr">
+      <c r="D61" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E59" s="63" t="inlineStr">
+      <c r="E61" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F59" s="63" t="inlineStr">
+      <c r="F61" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G59" s="63" t="inlineStr">
+      <c r="G61" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H59" s="63" t="inlineStr">
+      <c r="H61" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I59" s="63" t="inlineStr">
+      <c r="I61" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J59" s="63" t="inlineStr">
+      <c r="J61" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K59" s="63" t="inlineStr">
+      <c r="K61" s="63" t="inlineStr">
         <is>
           <t>Sale del sábado desde S2: va el lunes, antes de la prensa [LÓGICA].</t>
         </is>
       </c>
-      <c r="L59" s="106" t="inlineStr">
+      <c r="L61" s="106" t="inlineStr">
         <is>
           <t>id=touchdown-squat</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1" s="52">
-      <c r="A60" s="62" t="inlineStr">
+    <row r="62" ht="18" customHeight="1" s="52">
+      <c r="A62" s="62" t="inlineStr">
         <is>
           <t>Bulgarian split squat</t>
         </is>
       </c>
-      <c r="B60" s="62" t="inlineStr">
+      <c r="B62" s="62" t="inlineStr">
         <is>
           <t>Rehab</t>
         </is>
       </c>
-      <c r="C60" s="63" t="inlineStr">
+      <c r="C62" s="63" t="inlineStr">
         <is>
           <t>2 x12</t>
         </is>
       </c>
-      <c r="D60" s="63" t="inlineStr">
+      <c r="D62" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E60" s="63" t="inlineStr">
+      <c r="E62" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F60" s="63" t="inlineStr">
+      <c r="F62" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G60" s="63" t="inlineStr">
+      <c r="G62" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H60" s="63" t="inlineStr">
+      <c r="H62" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I60" s="63" t="inlineStr">
+      <c r="I62" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J60" s="63" t="inlineStr">
+      <c r="J62" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K60" s="62" t="inlineStr">
-        <is>
-          <t>Sale del sábado desde S2: la pierna se concentra en el lunes y el jueves [LÓGICA].</t>
-        </is>
-      </c>
-      <c r="L60" s="106" t="inlineStr">
+      <c r="K62" s="62" t="inlineStr">
+        <is>
+          <t>Sale del sábado desde S2: la pierna se concentra en el lunes y el viernes [LÓGICA].</t>
+        </is>
+      </c>
+      <c r="L62" s="106" t="inlineStr">
         <is>
           <t>id=bulgarian-split-squat</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1" s="52">
-      <c r="A61" s="59" t="inlineStr">
+    <row r="63" ht="15.75" customHeight="1" s="52">
+      <c r="A63" s="59" t="inlineStr">
         <is>
           <t>Abs wesley banco</t>
         </is>
       </c>
-      <c r="B61" s="59" t="inlineStr">
+      <c r="B63" s="59" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="C61" s="61" t="inlineStr">
+      <c r="C63" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="D61" s="61" t="inlineStr">
+      <c r="D63" s="61" t="inlineStr">
         <is>
           <t>2 @ RIR1/0</t>
         </is>
       </c>
-      <c r="E61" s="61" t="inlineStr">
+      <c r="E63" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="F61" s="61" t="inlineStr">
+      <c r="F63" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="G61" s="61" t="inlineStr">
+      <c r="G63" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="H61" s="61" t="inlineStr">
+      <c r="H63" s="61" t="inlineStr">
         <is>
           <t>3 @ RIR1/0</t>
         </is>
       </c>
-      <c r="I61" s="61" t="inlineStr">
+      <c r="I63" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="J61" s="61" t="inlineStr">
+      <c r="J63" s="61" t="inlineStr">
         <is>
           <t>4 @ RIR1/0</t>
         </is>
       </c>
-      <c r="K61" s="61" t="n"/>
-      <c r="L61" s="106" t="inlineStr">
+      <c r="K63" s="61" t="n"/>
+      <c r="L63" s="106" t="inlineStr">
         <is>
           <t>id=abs-wesley-banco</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="30.75" customHeight="1" s="52">
-      <c r="A62" s="59" t="inlineStr">
+    <row r="64" ht="30.75" customHeight="1" s="52">
+      <c r="A64" s="59" t="inlineStr">
         <is>
           <t>Elevación lateral en prono «T» (mancuernas, banco)</t>
         </is>
       </c>
-      <c r="B62" s="59" t="inlineStr">
+      <c r="B64" s="59" t="inlineStr">
         <is>
           <t>Hombro (correctivo)</t>
         </is>
       </c>
-      <c r="C62" s="61" t="inlineStr">
+      <c r="C64" s="61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D62" s="61" t="inlineStr">
+      <c r="D64" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="E62" s="61" t="inlineStr">
+      <c r="E64" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="F62" s="61" t="inlineStr">
+      <c r="F64" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="G62" s="61" t="inlineStr">
+      <c r="G64" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="H62" s="61" t="inlineStr">
+      <c r="H64" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="I62" s="61" t="inlineStr">
+      <c r="I64" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="J62" s="61" t="inlineStr">
+      <c r="J64" s="61" t="inlineStr">
         <is>
           <t>2-3 x10-15
 5 s arriba</t>
         </is>
       </c>
-      <c r="K62" s="61" t="inlineStr">
+      <c r="K64" s="61" t="inlineStr">
         <is>
           <t>Postura: trapecio medio e inferior y deltoides posterior. Boca abajo en el banco, pulgar arriba, muy poco peso. RIR 3-4; no cuenta como serie de hipertrofia. Libro, p. 290.</t>
         </is>
       </c>
-      <c r="L62" s="106" t="inlineStr">
+      <c r="L64" s="106" t="inlineStr">
         <is>
           <t>id=elevacion-lateral-en-prono-t-mancuernas-banco</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="30.75" customHeight="1" s="52">
-      <c r="A63" s="59" t="inlineStr">
+    <row r="65" ht="30.75" customHeight="1" s="52">
+      <c r="A65" s="59" t="inlineStr">
         <is>
           <t>Rotación externa con banda «W»</t>
         </is>
       </c>
-      <c r="B63" s="59" t="inlineStr">
+      <c r="B65" s="59" t="inlineStr">
         <is>
           <t>Hombro (correctivo)</t>
         </is>
       </c>
-      <c r="C63" s="61" t="inlineStr">
+      <c r="C65" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D63" s="61" t="inlineStr">
+      <c r="D65" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="E63" s="61" t="inlineStr">
+      <c r="E65" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="F63" s="61" t="inlineStr">
+      <c r="F65" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="G63" s="61" t="inlineStr">
+      <c r="G65" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="H63" s="61" t="inlineStr">
+      <c r="H65" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="I63" s="61" t="inlineStr">
+      <c r="I65" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="J63" s="61" t="inlineStr">
+      <c r="J65" s="61" t="inlineStr">
         <is>
           <t>2-3 x15-20
 5-10 s fuera</t>
         </is>
       </c>
-      <c r="K63" s="61" t="inlineStr">
+      <c r="K65" s="61" t="inlineStr">
         <is>
           <t>Codos pegados al cuerpo a 90°. RIR 3-4. Libro, p. 288.</t>
         </is>
       </c>
-      <c r="L63" s="106" t="inlineStr">
+      <c r="L65" s="106" t="inlineStr">
         <is>
           <t>id=rotacion-externa-con-banda-w</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="43.5" customHeight="1" s="52">
-      <c r="A64" s="59" t="inlineStr">
+    <row r="66" ht="43.5" customHeight="1" s="52">
+      <c r="A66" s="59" t="inlineStr">
         <is>
           <t>Curl de muñeca en extensión (mancuerna)</t>
         </is>
       </c>
-      <c r="B64" s="59" t="inlineStr">
+      <c r="B66" s="59" t="inlineStr">
         <is>
           <t>Codo (correctivo)</t>
         </is>
       </c>
-      <c r="C64" s="61" t="inlineStr">
+      <c r="C66" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D64" s="61" t="inlineStr">
+      <c r="D66" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="E64" s="61" t="inlineStr">
+      <c r="E66" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="F64" s="61" t="inlineStr">
+      <c r="F66" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="G64" s="61" t="inlineStr">
+      <c r="G66" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="H64" s="61" t="inlineStr">
+      <c r="H66" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="I64" s="61" t="inlineStr">
+      <c r="I66" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="J64" s="61" t="inlineStr">
+      <c r="J66" s="61" t="inlineStr">
         <is>
           <t>3 x10-15
 3 s / 3 s</t>
         </is>
       </c>
-      <c r="K64" s="61" t="inlineStr">
+      <c r="K66" s="61" t="inlineStr">
         <is>
           <t>Codo (cara externa). Antebrazo apoyado, palma abajo. Si ahora agarrar te duele: isométrico 4-5×30-45 s las 1-2 primeras semanas. Antes, test del nervio radial (libro, p. 323): si es positivo, se cambia por deslizamientos del nervio (p. 338). Dolor ≤3/10 y no peor al día siguiente. Libro, pp. 332-333.</t>
         </is>
       </c>
-      <c r="L64" s="106" t="inlineStr">
+      <c r="L66" s="106" t="inlineStr">
         <is>
           <t>id=curl-de-muneca-en-extension-mancuerna</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1" s="52">
-      <c r="A65" s="67" t="inlineStr">
+    <row r="67" ht="30" customHeight="1" s="52">
+      <c r="A67" s="67" t="inlineStr">
         <is>
           <t>Autorregulación: si un músculo pierde reps 2 sesiones seguidas, esa semana NO le subas series. Si se estancan varios a la vez o la rodilla empeora en el test, repite la semana anterior.</t>
-        </is>
-      </c>
-      <c r="B65" s="56" t="n"/>
-      <c r="C65" s="56" t="n"/>
-      <c r="D65" s="56" t="n"/>
-      <c r="E65" s="56" t="n"/>
-      <c r="F65" s="56" t="n"/>
-      <c r="G65" s="56" t="n"/>
-      <c r="H65" s="56" t="n"/>
-      <c r="I65" s="56" t="n"/>
-      <c r="J65" s="56" t="n"/>
-      <c r="K65" s="57" t="n"/>
-      <c r="L65" s="106" t="inlineStr">
-        <is>
-          <t>regla</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1" s="52"/>
-    <row r="67" ht="19.5" customHeight="1" s="52">
-      <c r="A67" s="65" t="inlineStr">
-        <is>
-          <t>Semana 9 (14-20/12) · Viaje = descarga  ·  Semana 10 · Vuelta progresiva</t>
         </is>
       </c>
       <c r="B67" s="56" t="n"/>
@@ -9432,36 +9450,15 @@
       <c r="K67" s="57" t="n"/>
       <c r="L67" s="106" t="inlineStr">
         <is>
-          <t>nota</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1" s="52">
-      <c r="A68" s="73" t="inlineStr">
-        <is>
-          <t>Hipertrofia: la semana sin entrenar hace de descarga justo después del pico de volumen de la semana 8.</t>
-        </is>
-      </c>
-      <c r="B68" s="56" t="n"/>
-      <c r="C68" s="56" t="n"/>
-      <c r="D68" s="56" t="n"/>
-      <c r="E68" s="56" t="n"/>
-      <c r="F68" s="56" t="n"/>
-      <c r="G68" s="56" t="n"/>
-      <c r="H68" s="56" t="n"/>
-      <c r="I68" s="56" t="n"/>
-      <c r="J68" s="56" t="n"/>
-      <c r="K68" s="57" t="n"/>
-      <c r="L68" s="106" t="inlineStr">
-        <is>
-          <t>nota</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="42" customHeight="1" s="52">
-      <c r="A69" s="73" t="inlineStr">
-        <is>
-          <t>Rodilla en el viaje: nunca reposo total del tendón. Sentadilla española 5×45 s cada día (sin anclaje → wall sit a 1 pierna) y las dos pruebas de la mañana (declive + 10 subidas). Carrera: si puedes, 2 rodajes suaves sin pasar del nivel de S8 y nunca dos días seguidos, con la regla de carrera (≤2/10, nivel previo en ≤60 min, mañana siguiente no peor).</t>
+          <t>regla</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1" s="52"/>
+    <row r="69" ht="19.5" customHeight="1" s="52">
+      <c r="A69" s="65" t="inlineStr">
+        <is>
+          <t>Semana 9 (14-20/12) · Viaje = descarga  ·  Semana 10 · Vuelta progresiva</t>
         </is>
       </c>
       <c r="B69" s="56" t="n"/>
@@ -9480,10 +9477,10 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="42" customHeight="1" s="52">
+    <row r="70" ht="30" customHeight="1" s="52">
       <c r="A70" s="73" t="inlineStr">
         <is>
-          <t>Semana 10 (vuelta): hipertrofia con las series de la sem 3-4 y a RIR2. Rehab ×8 al ~80% del peso de la sem 8; si se cumple la regla de 24-48 h, semana 11 a peso completo y siguiente escalón del libro (×6). Carrera: retomas el nivel de S8, o uno por debajo si no pudiste correr en el viaje.</t>
+          <t>Hipertrofia: la semana sin entrenar hace de descarga justo después del pico de volumen de la semana 8.</t>
         </is>
       </c>
       <c r="B70" s="56" t="n"/>
@@ -9502,11 +9499,32 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="15.75" customHeight="1" s="52"/>
-    <row r="72" ht="19.5" customHeight="1" s="52">
-      <c r="A72" s="74" t="inlineStr">
-        <is>
-          <t>Series semanales por grupo muscular (se recalculan solas al cambiar la tabla)</t>
+    <row r="71" ht="42" customHeight="1" s="52">
+      <c r="A71" s="73" t="inlineStr">
+        <is>
+          <t>Rodilla en el viaje: nunca reposo total del tendón. Sentadilla española 5×45 s cada día (sin anclaje → wall sit a 1 pierna) y las dos pruebas de la mañana (declive + 10 subidas). Carrera: si puedes, 2 rodajes suaves sin pasar del nivel de S8 y nunca dos días seguidos, con la regla de carrera (≤2/10, nivel previo en ≤60 min, mañana siguiente no peor).</t>
+        </is>
+      </c>
+      <c r="B71" s="56" t="n"/>
+      <c r="C71" s="56" t="n"/>
+      <c r="D71" s="56" t="n"/>
+      <c r="E71" s="56" t="n"/>
+      <c r="F71" s="56" t="n"/>
+      <c r="G71" s="56" t="n"/>
+      <c r="H71" s="56" t="n"/>
+      <c r="I71" s="56" t="n"/>
+      <c r="J71" s="56" t="n"/>
+      <c r="K71" s="57" t="n"/>
+      <c r="L71" s="106" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1" s="52">
+      <c r="A72" s="73" t="inlineStr">
+        <is>
+          <t>Semana 10 (vuelta): hipertrofia con las series de la sem 3-4 y a RIR2. Rehab ×8 al ~80% del peso de la sem 8; si se cumple la regla de 24-48 h, semana 11 a peso completo y siguiente escalón del libro (×6). Carrera: retomas el nivel de S8, o uno por debajo si no pudiste correr en el viaje.</t>
         </is>
       </c>
       <c r="B72" s="56" t="n"/>
@@ -9519,156 +9537,91 @@
       <c r="I72" s="56" t="n"/>
       <c r="J72" s="56" t="n"/>
       <c r="K72" s="57" t="n"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1" s="52">
-      <c r="A73" s="75" t="inlineStr">
+      <c r="L72" s="106" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" s="52"/>
+    <row r="74" ht="19.5" customHeight="1" s="52">
+      <c r="A74" s="74" t="inlineStr">
+        <is>
+          <t>Series semanales por grupo muscular (se recalculan solas al cambiar la tabla)</t>
+        </is>
+      </c>
+      <c r="B74" s="56" t="n"/>
+      <c r="C74" s="56" t="n"/>
+      <c r="D74" s="56" t="n"/>
+      <c r="E74" s="56" t="n"/>
+      <c r="F74" s="56" t="n"/>
+      <c r="G74" s="56" t="n"/>
+      <c r="H74" s="56" t="n"/>
+      <c r="I74" s="56" t="n"/>
+      <c r="J74" s="56" t="n"/>
+      <c r="K74" s="57" t="n"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" s="52">
+      <c r="A75" s="75" t="inlineStr">
         <is>
           <t>Grupo muscular</t>
         </is>
       </c>
-      <c r="B73" s="75" t="inlineStr">
+      <c r="B75" s="75" t="inlineStr">
         <is>
           <t>Sem 1 → Sem 8</t>
         </is>
       </c>
-      <c r="C73" s="75" t="inlineStr">
+      <c r="C75" s="75" t="inlineStr">
         <is>
           <t>Sem 1</t>
         </is>
       </c>
-      <c r="D73" s="75" t="inlineStr">
+      <c r="D75" s="75" t="inlineStr">
         <is>
           <t>Sem 2</t>
         </is>
       </c>
-      <c r="E73" s="75" t="inlineStr">
+      <c r="E75" s="75" t="inlineStr">
         <is>
           <t>Sem 3</t>
         </is>
       </c>
-      <c r="F73" s="75" t="inlineStr">
+      <c r="F75" s="75" t="inlineStr">
         <is>
           <t>Sem 4</t>
         </is>
       </c>
-      <c r="G73" s="75" t="inlineStr">
+      <c r="G75" s="75" t="inlineStr">
         <is>
           <t>Sem 5</t>
         </is>
       </c>
-      <c r="H73" s="75" t="inlineStr">
+      <c r="H75" s="75" t="inlineStr">
         <is>
           <t>Sem 6</t>
         </is>
       </c>
-      <c r="I73" s="75" t="inlineStr">
+      <c r="I75" s="75" t="inlineStr">
         <is>
           <t>Sem 7</t>
         </is>
       </c>
-      <c r="J73" s="75" t="inlineStr">
+      <c r="J75" s="75" t="inlineStr">
         <is>
           <t>Sem 8</t>
         </is>
       </c>
-      <c r="L73" s="106" t="inlineStr">
+      <c r="L75" s="106" t="inlineStr">
         <is>
           <t>grupos</t>
         </is>
       </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1" s="52">
-      <c r="A74" s="76" t="inlineStr">
-        <is>
-          <t>Espalda</t>
-        </is>
-      </c>
-      <c r="B74" s="77">
-        <f>C74&amp;" → "&amp;J74</f>
-        <v/>
-      </c>
-      <c r="C74" s="77">
-        <f>IFERROR(VALUE(LEFT(C26,FIND(" ",C26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C27,FIND(" ",C27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C29,FIND(" ",C29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C52,FIND(" ",C52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C53,FIND(" ",C53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C54,FIND(" ",C54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="D74" s="77">
-        <f>IFERROR(VALUE(LEFT(D26,FIND(" ",D26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D27,FIND(" ",D27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D29,FIND(" ",D29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D52,FIND(" ",D52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D53,FIND(" ",D53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D54,FIND(" ",D54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="E74" s="77">
-        <f>IFERROR(VALUE(LEFT(E26,FIND(" ",E26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E27,FIND(" ",E27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E29,FIND(" ",E29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E52,FIND(" ",E52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E53,FIND(" ",E53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E54,FIND(" ",E54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="F74" s="77">
-        <f>IFERROR(VALUE(LEFT(F26,FIND(" ",F26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F27,FIND(" ",F27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F29,FIND(" ",F29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F52,FIND(" ",F52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F53,FIND(" ",F53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F54,FIND(" ",F54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="G74" s="77">
-        <f>IFERROR(VALUE(LEFT(G26,FIND(" ",G26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G27,FIND(" ",G27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G29,FIND(" ",G29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G52,FIND(" ",G52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G53,FIND(" ",G53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G54,FIND(" ",G54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="H74" s="77">
-        <f>IFERROR(VALUE(LEFT(H26,FIND(" ",H26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H27,FIND(" ",H27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H29,FIND(" ",H29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H52,FIND(" ",H52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H53,FIND(" ",H53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H54,FIND(" ",H54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="I74" s="77">
-        <f>IFERROR(VALUE(LEFT(I26,FIND(" ",I26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I27,FIND(" ",I27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I29,FIND(" ",I29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I52,FIND(" ",I52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I53,FIND(" ",I53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I54,FIND(" ",I54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="J74" s="77">
-        <f>IFERROR(VALUE(LEFT(J26,FIND(" ",J26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J27,FIND(" ",J27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J29,FIND(" ",J29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J52,FIND(" ",J52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J53,FIND(" ",J53&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J54,FIND(" ",J54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="K74" s="77" t="n"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1" s="52">
-      <c r="A75" s="76" t="inlineStr">
-        <is>
-          <t>Pecho</t>
-        </is>
-      </c>
-      <c r="B75" s="77">
-        <f>C75&amp;" → "&amp;J75</f>
-        <v/>
-      </c>
-      <c r="C75" s="77">
-        <f>IFERROR(VALUE(LEFT(C16,FIND(" ",C16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C18,FIND(" ",C18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C51,FIND(" ",C51&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="D75" s="77">
-        <f>IFERROR(VALUE(LEFT(D16,FIND(" ",D16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D18,FIND(" ",D18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D51,FIND(" ",D51&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="E75" s="77">
-        <f>IFERROR(VALUE(LEFT(E16,FIND(" ",E16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E18,FIND(" ",E18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E51,FIND(" ",E51&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="F75" s="77">
-        <f>IFERROR(VALUE(LEFT(F16,FIND(" ",F16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F18,FIND(" ",F18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F51,FIND(" ",F51&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="G75" s="77">
-        <f>IFERROR(VALUE(LEFT(G16,FIND(" ",G16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G18,FIND(" ",G18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G51,FIND(" ",G51&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="H75" s="77">
-        <f>IFERROR(VALUE(LEFT(H16,FIND(" ",H16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H18,FIND(" ",H18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H51,FIND(" ",H51&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="I75" s="77">
-        <f>IFERROR(VALUE(LEFT(I16,FIND(" ",I16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I18,FIND(" ",I18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I51,FIND(" ",I51&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="J75" s="77">
-        <f>IFERROR(VALUE(LEFT(J16,FIND(" ",J16&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J18,FIND(" ",J18&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J51,FIND(" ",J51&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="K75" s="77" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="52">
       <c r="A76" s="76" t="inlineStr">
         <is>
-          <t>Hombro lat.</t>
+          <t>Espalda</t>
         </is>
       </c>
       <c r="B76" s="77">
@@ -9676,35 +9629,35 @@
         <v/>
       </c>
       <c r="C76" s="77">
-        <f>IFERROR(VALUE(LEFT(C6,FIND(" ",C6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C8,FIND(" ",C8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C28,FIND(" ",C28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C48,FIND(" ",C48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C13,FIND(" ",C13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C14,FIND(" ",C14&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C15,FIND(" ",C15&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C31,FIND(" ",C31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C32,FIND(" ",C32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C34,FIND(" ",C34&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D76" s="77">
-        <f>IFERROR(VALUE(LEFT(D6,FIND(" ",D6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D8,FIND(" ",D8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D28,FIND(" ",D28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D48,FIND(" ",D48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D13,FIND(" ",D13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D14,FIND(" ",D14&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D15,FIND(" ",D15&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D31,FIND(" ",D31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D32,FIND(" ",D32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D34,FIND(" ",D34&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E76" s="77">
-        <f>IFERROR(VALUE(LEFT(E6,FIND(" ",E6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E8,FIND(" ",E8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E28,FIND(" ",E28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E48,FIND(" ",E48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E13,FIND(" ",E13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E14,FIND(" ",E14&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E15,FIND(" ",E15&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E31,FIND(" ",E31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E32,FIND(" ",E32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E34,FIND(" ",E34&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F76" s="77">
-        <f>IFERROR(VALUE(LEFT(F6,FIND(" ",F6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F8,FIND(" ",F8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F28,FIND(" ",F28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F48,FIND(" ",F48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F13,FIND(" ",F13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F14,FIND(" ",F14&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F15,FIND(" ",F15&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F31,FIND(" ",F31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F32,FIND(" ",F32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F34,FIND(" ",F34&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G76" s="77">
-        <f>IFERROR(VALUE(LEFT(G6,FIND(" ",G6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G8,FIND(" ",G8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G28,FIND(" ",G28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G48,FIND(" ",G48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G13,FIND(" ",G13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G14,FIND(" ",G14&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G15,FIND(" ",G15&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G31,FIND(" ",G31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G32,FIND(" ",G32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G34,FIND(" ",G34&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H76" s="77">
-        <f>IFERROR(VALUE(LEFT(H6,FIND(" ",H6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H8,FIND(" ",H8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H28,FIND(" ",H28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H48,FIND(" ",H48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H13,FIND(" ",H13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H14,FIND(" ",H14&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H15,FIND(" ",H15&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H31,FIND(" ",H31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H32,FIND(" ",H32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H34,FIND(" ",H34&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I76" s="77">
-        <f>IFERROR(VALUE(LEFT(I6,FIND(" ",I6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I8,FIND(" ",I8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I28,FIND(" ",I28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I48,FIND(" ",I48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I13,FIND(" ",I13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I14,FIND(" ",I14&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I15,FIND(" ",I15&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I31,FIND(" ",I31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I32,FIND(" ",I32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I34,FIND(" ",I34&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J76" s="77">
-        <f>IFERROR(VALUE(LEFT(J6,FIND(" ",J6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J8,FIND(" ",J8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J28,FIND(" ",J28&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J48,FIND(" ",J48&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J13,FIND(" ",J13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J14,FIND(" ",J14&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J15,FIND(" ",J15&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J31,FIND(" ",J31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J32,FIND(" ",J32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J34,FIND(" ",J34&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K76" s="77" t="n"/>
@@ -9712,7 +9665,7 @@
     <row r="77" ht="15.75" customHeight="1" s="52">
       <c r="A77" s="76" t="inlineStr">
         <is>
-          <t>Hombro post.</t>
+          <t>Pecho</t>
         </is>
       </c>
       <c r="B77" s="77">
@@ -9720,35 +9673,35 @@
         <v/>
       </c>
       <c r="C77" s="77">
-        <f>IFERROR(VALUE(LEFT(C31,FIND(" ",C31&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C19,FIND(" ",C19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C21,FIND(" ",C21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C56,FIND(" ",C56&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D77" s="77">
-        <f>IFERROR(VALUE(LEFT(D31,FIND(" ",D31&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D19,FIND(" ",D19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D21,FIND(" ",D21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D56,FIND(" ",D56&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E77" s="77">
-        <f>IFERROR(VALUE(LEFT(E31,FIND(" ",E31&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E19,FIND(" ",E19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E21,FIND(" ",E21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E56,FIND(" ",E56&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F77" s="77">
-        <f>IFERROR(VALUE(LEFT(F31,FIND(" ",F31&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F19,FIND(" ",F19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F21,FIND(" ",F21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F56,FIND(" ",F56&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G77" s="77">
-        <f>IFERROR(VALUE(LEFT(G31,FIND(" ",G31&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G19,FIND(" ",G19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G21,FIND(" ",G21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G56,FIND(" ",G56&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H77" s="77">
-        <f>IFERROR(VALUE(LEFT(H31,FIND(" ",H31&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H19,FIND(" ",H19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H21,FIND(" ",H21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H56,FIND(" ",H56&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I77" s="77">
-        <f>IFERROR(VALUE(LEFT(I31,FIND(" ",I31&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I19,FIND(" ",I19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I21,FIND(" ",I21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I56,FIND(" ",I56&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J77" s="77">
-        <f>IFERROR(VALUE(LEFT(J31,FIND(" ",J31&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J19,FIND(" ",J19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J21,FIND(" ",J21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J56,FIND(" ",J56&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K77" s="77" t="n"/>
@@ -9756,7 +9709,7 @@
     <row r="78" ht="15.75" customHeight="1" s="52">
       <c r="A78" s="76" t="inlineStr">
         <is>
-          <t>Bíceps</t>
+          <t>Hombro lat.</t>
         </is>
       </c>
       <c r="B78" s="77">
@@ -9764,35 +9717,35 @@
         <v/>
       </c>
       <c r="C78" s="77">
-        <f>IFERROR(VALUE(LEFT(C30,FIND(" ",C30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C32,FIND(" ",C32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C50,FIND(" ",C50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C6,FIND(" ",C6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C8,FIND(" ",C8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C33,FIND(" ",C33&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C53,FIND(" ",C53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D78" s="77">
-        <f>IFERROR(VALUE(LEFT(D30,FIND(" ",D30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D32,FIND(" ",D32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D50,FIND(" ",D50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D6,FIND(" ",D6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D8,FIND(" ",D8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D33,FIND(" ",D33&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D53,FIND(" ",D53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E78" s="77">
-        <f>IFERROR(VALUE(LEFT(E30,FIND(" ",E30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E32,FIND(" ",E32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E50,FIND(" ",E50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E6,FIND(" ",E6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E8,FIND(" ",E8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E33,FIND(" ",E33&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E53,FIND(" ",E53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F78" s="77">
-        <f>IFERROR(VALUE(LEFT(F30,FIND(" ",F30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F32,FIND(" ",F32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F50,FIND(" ",F50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F6,FIND(" ",F6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F8,FIND(" ",F8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F33,FIND(" ",F33&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F53,FIND(" ",F53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G78" s="77">
-        <f>IFERROR(VALUE(LEFT(G30,FIND(" ",G30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G32,FIND(" ",G32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G50,FIND(" ",G50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G6,FIND(" ",G6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G8,FIND(" ",G8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G33,FIND(" ",G33&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G53,FIND(" ",G53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H78" s="77">
-        <f>IFERROR(VALUE(LEFT(H30,FIND(" ",H30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H32,FIND(" ",H32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H50,FIND(" ",H50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H6,FIND(" ",H6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H8,FIND(" ",H8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H33,FIND(" ",H33&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H53,FIND(" ",H53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I78" s="77">
-        <f>IFERROR(VALUE(LEFT(I30,FIND(" ",I30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I32,FIND(" ",I32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I50,FIND(" ",I50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I6,FIND(" ",I6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I8,FIND(" ",I8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I33,FIND(" ",I33&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I53,FIND(" ",I53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J78" s="77">
-        <f>IFERROR(VALUE(LEFT(J30,FIND(" ",J30&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J32,FIND(" ",J32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J50,FIND(" ",J50&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J6,FIND(" ",J6&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J8,FIND(" ",J8&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J33,FIND(" ",J33&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J53,FIND(" ",J53&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K78" s="77" t="n"/>
@@ -9800,7 +9753,7 @@
     <row r="79" ht="15.75" customHeight="1" s="52">
       <c r="A79" s="76" t="inlineStr">
         <is>
-          <t>Tríceps</t>
+          <t>Hombro post.</t>
         </is>
       </c>
       <c r="B79" s="77">
@@ -9808,35 +9761,35 @@
         <v/>
       </c>
       <c r="C79" s="77">
-        <f>IFERROR(VALUE(LEFT(C17,FIND(" ",C17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C19,FIND(" ",C19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C47,FIND(" ",C47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C49,FIND(" ",C49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C36,FIND(" ",C36&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D79" s="77">
-        <f>IFERROR(VALUE(LEFT(D17,FIND(" ",D17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D19,FIND(" ",D19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D47,FIND(" ",D47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D49,FIND(" ",D49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D36,FIND(" ",D36&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E79" s="77">
-        <f>IFERROR(VALUE(LEFT(E17,FIND(" ",E17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E19,FIND(" ",E19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E47,FIND(" ",E47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E49,FIND(" ",E49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E36,FIND(" ",E36&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F79" s="77">
-        <f>IFERROR(VALUE(LEFT(F17,FIND(" ",F17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F19,FIND(" ",F19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F47,FIND(" ",F47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F49,FIND(" ",F49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F36,FIND(" ",F36&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G79" s="77">
-        <f>IFERROR(VALUE(LEFT(G17,FIND(" ",G17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G19,FIND(" ",G19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G47,FIND(" ",G47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G49,FIND(" ",G49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G36,FIND(" ",G36&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H79" s="77">
-        <f>IFERROR(VALUE(LEFT(H17,FIND(" ",H17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H19,FIND(" ",H19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H47,FIND(" ",H47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H49,FIND(" ",H49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H36,FIND(" ",H36&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I79" s="77">
-        <f>IFERROR(VALUE(LEFT(I17,FIND(" ",I17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I19,FIND(" ",I19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I47,FIND(" ",I47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I49,FIND(" ",I49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I36,FIND(" ",I36&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J79" s="77">
-        <f>IFERROR(VALUE(LEFT(J17,FIND(" ",J17&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J19,FIND(" ",J19&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J47,FIND(" ",J47&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J49,FIND(" ",J49&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J36,FIND(" ",J36&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K79" s="77" t="n"/>
@@ -9844,7 +9797,7 @@
     <row r="80" ht="15.75" customHeight="1" s="52">
       <c r="A80" s="76" t="inlineStr">
         <is>
-          <t>Isquios</t>
+          <t>Bíceps</t>
         </is>
       </c>
       <c r="B80" s="77">
@@ -9852,35 +9805,35 @@
         <v/>
       </c>
       <c r="C80" s="77">
-        <f>IFERROR(VALUE(LEFT(C12,FIND(" ",C12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C41,FIND(" ",C41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C35,FIND(" ",C35&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C37,FIND(" ",C37&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C55,FIND(" ",C55&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D80" s="77">
-        <f>IFERROR(VALUE(LEFT(D12,FIND(" ",D12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D41,FIND(" ",D41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D35,FIND(" ",D35&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D37,FIND(" ",D37&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D55,FIND(" ",D55&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E80" s="77">
-        <f>IFERROR(VALUE(LEFT(E12,FIND(" ",E12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E41,FIND(" ",E41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E35,FIND(" ",E35&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E37,FIND(" ",E37&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E55,FIND(" ",E55&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F80" s="77">
-        <f>IFERROR(VALUE(LEFT(F12,FIND(" ",F12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F41,FIND(" ",F41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F35,FIND(" ",F35&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F37,FIND(" ",F37&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F55,FIND(" ",F55&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G80" s="77">
-        <f>IFERROR(VALUE(LEFT(G12,FIND(" ",G12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G41,FIND(" ",G41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G35,FIND(" ",G35&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G37,FIND(" ",G37&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G55,FIND(" ",G55&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H80" s="77">
-        <f>IFERROR(VALUE(LEFT(H12,FIND(" ",H12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H41,FIND(" ",H41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H35,FIND(" ",H35&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H37,FIND(" ",H37&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H55,FIND(" ",H55&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I80" s="77">
-        <f>IFERROR(VALUE(LEFT(I12,FIND(" ",I12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I41,FIND(" ",I41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I35,FIND(" ",I35&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I37,FIND(" ",I37&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I55,FIND(" ",I55&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J80" s="77">
-        <f>IFERROR(VALUE(LEFT(J12,FIND(" ",J12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J41,FIND(" ",J41&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J35,FIND(" ",J35&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J37,FIND(" ",J37&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J55,FIND(" ",J55&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K80" s="77" t="n"/>
@@ -9888,7 +9841,7 @@
     <row r="81" ht="15.75" customHeight="1" s="52">
       <c r="A81" s="76" t="inlineStr">
         <is>
-          <t>Abs</t>
+          <t>Tríceps</t>
         </is>
       </c>
       <c r="B81" s="77">
@@ -9896,35 +9849,35 @@
         <v/>
       </c>
       <c r="C81" s="77">
-        <f>IFERROR(VALUE(LEFT(C20,FIND(" ",C20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C21,FIND(" ",C21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C61,FIND(" ",C61&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C20,FIND(" ",C20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C22,FIND(" ",C22&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C52,FIND(" ",C52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C54,FIND(" ",C54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D81" s="77">
-        <f>IFERROR(VALUE(LEFT(D20,FIND(" ",D20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D21,FIND(" ",D21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D61,FIND(" ",D61&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D20,FIND(" ",D20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D22,FIND(" ",D22&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D52,FIND(" ",D52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D54,FIND(" ",D54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E81" s="77">
-        <f>IFERROR(VALUE(LEFT(E20,FIND(" ",E20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E21,FIND(" ",E21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E61,FIND(" ",E61&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E20,FIND(" ",E20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E22,FIND(" ",E22&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E52,FIND(" ",E52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E54,FIND(" ",E54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F81" s="77">
-        <f>IFERROR(VALUE(LEFT(F20,FIND(" ",F20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F21,FIND(" ",F21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F61,FIND(" ",F61&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F20,FIND(" ",F20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F22,FIND(" ",F22&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F52,FIND(" ",F52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F54,FIND(" ",F54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G81" s="77">
-        <f>IFERROR(VALUE(LEFT(G20,FIND(" ",G20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G21,FIND(" ",G21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G61,FIND(" ",G61&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G20,FIND(" ",G20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G22,FIND(" ",G22&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G52,FIND(" ",G52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G54,FIND(" ",G54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H81" s="77">
-        <f>IFERROR(VALUE(LEFT(H20,FIND(" ",H20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H21,FIND(" ",H21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H61,FIND(" ",H61&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H20,FIND(" ",H20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H22,FIND(" ",H22&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H52,FIND(" ",H52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H54,FIND(" ",H54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I81" s="77">
-        <f>IFERROR(VALUE(LEFT(I20,FIND(" ",I20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I21,FIND(" ",I21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I61,FIND(" ",I61&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I20,FIND(" ",I20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I22,FIND(" ",I22&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I52,FIND(" ",I52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I54,FIND(" ",I54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J81" s="77">
-        <f>IFERROR(VALUE(LEFT(J20,FIND(" ",J20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J21,FIND(" ",J21&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J61,FIND(" ",J61&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J20,FIND(" ",J20&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J22,FIND(" ",J22&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J52,FIND(" ",J52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J54,FIND(" ",J54&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K81" s="77" t="n"/>
@@ -9932,7 +9885,7 @@
     <row r="82" ht="15.75" customHeight="1" s="52">
       <c r="A82" s="76" t="inlineStr">
         <is>
-          <t>Gemelos</t>
+          <t>Isquios</t>
         </is>
       </c>
       <c r="B82" s="77">
@@ -9940,35 +9893,35 @@
         <v/>
       </c>
       <c r="C82" s="77">
-        <f>IFERROR(VALUE(LEFT(C11,FIND(" ",C11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C43,FIND(" ",C43&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C12,FIND(" ",C12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C46,FIND(" ",C46&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D82" s="77">
-        <f>IFERROR(VALUE(LEFT(D11,FIND(" ",D11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D43,FIND(" ",D43&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D12,FIND(" ",D12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D46,FIND(" ",D46&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E82" s="77">
-        <f>IFERROR(VALUE(LEFT(E11,FIND(" ",E11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E43,FIND(" ",E43&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E12,FIND(" ",E12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E46,FIND(" ",E46&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F82" s="77">
-        <f>IFERROR(VALUE(LEFT(F11,FIND(" ",F11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F43,FIND(" ",F43&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F12,FIND(" ",F12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F46,FIND(" ",F46&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G82" s="77">
-        <f>IFERROR(VALUE(LEFT(G11,FIND(" ",G11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G43,FIND(" ",G43&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G12,FIND(" ",G12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G46,FIND(" ",G46&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H82" s="77">
-        <f>IFERROR(VALUE(LEFT(H11,FIND(" ",H11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H43,FIND(" ",H43&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H12,FIND(" ",H12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H46,FIND(" ",H46&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I82" s="77">
-        <f>IFERROR(VALUE(LEFT(I11,FIND(" ",I11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I43,FIND(" ",I43&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I12,FIND(" ",I12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I46,FIND(" ",I46&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J82" s="77">
-        <f>IFERROR(VALUE(LEFT(J11,FIND(" ",J11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J43,FIND(" ",J43&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J12,FIND(" ",J12&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J46,FIND(" ",J46&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K82" s="77" t="n"/>
@@ -9976,7 +9929,7 @@
     <row r="83" ht="15.75" customHeight="1" s="52">
       <c r="A83" s="76" t="inlineStr">
         <is>
-          <t>Aductores</t>
+          <t>Abs</t>
         </is>
       </c>
       <c r="B83" s="77">
@@ -9984,268 +9937,250 @@
         <v/>
       </c>
       <c r="C83" s="77">
-        <f>IFERROR(VALUE(LEFT(C42,FIND(" ",C42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C23,FIND(" ",C23&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C24,FIND(" ",C24&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C63,FIND(" ",C63&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D83" s="77">
-        <f>IFERROR(VALUE(LEFT(D42,FIND(" ",D42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D23,FIND(" ",D23&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D24,FIND(" ",D24&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D63,FIND(" ",D63&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E83" s="77">
-        <f>IFERROR(VALUE(LEFT(E42,FIND(" ",E42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E23,FIND(" ",E23&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E24,FIND(" ",E24&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E63,FIND(" ",E63&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F83" s="77">
-        <f>IFERROR(VALUE(LEFT(F42,FIND(" ",F42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F23,FIND(" ",F23&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F24,FIND(" ",F24&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F63,FIND(" ",F63&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G83" s="77">
-        <f>IFERROR(VALUE(LEFT(G42,FIND(" ",G42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G23,FIND(" ",G23&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G24,FIND(" ",G24&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G63,FIND(" ",G63&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H83" s="77">
-        <f>IFERROR(VALUE(LEFT(H42,FIND(" ",H42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H23,FIND(" ",H23&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H24,FIND(" ",H24&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H63,FIND(" ",H63&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I83" s="77">
-        <f>IFERROR(VALUE(LEFT(I42,FIND(" ",I42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I23,FIND(" ",I23&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I24,FIND(" ",I24&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I63,FIND(" ",I63&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J83" s="77">
-        <f>IFERROR(VALUE(LEFT(J42,FIND(" ",J42&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J23,FIND(" ",J23&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J24,FIND(" ",J24&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J63,FIND(" ",J63&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K83" s="77" t="n"/>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="52">
-      <c r="A84" s="78" t="inlineStr">
+      <c r="A84" s="76" t="inlineStr">
+        <is>
+          <t>Gemelos</t>
+        </is>
+      </c>
+      <c r="B84" s="77">
+        <f>C84&amp;" → "&amp;J84</f>
+        <v/>
+      </c>
+      <c r="C84" s="77">
+        <f>IFERROR(VALUE(LEFT(C11,FIND(" ",C11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C48,FIND(" ",C48&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="D84" s="77">
+        <f>IFERROR(VALUE(LEFT(D11,FIND(" ",D11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D48,FIND(" ",D48&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="E84" s="77">
+        <f>IFERROR(VALUE(LEFT(E11,FIND(" ",E11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E48,FIND(" ",E48&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="F84" s="77">
+        <f>IFERROR(VALUE(LEFT(F11,FIND(" ",F11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F48,FIND(" ",F48&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="G84" s="77">
+        <f>IFERROR(VALUE(LEFT(G11,FIND(" ",G11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G48,FIND(" ",G48&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="H84" s="77">
+        <f>IFERROR(VALUE(LEFT(H11,FIND(" ",H11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H48,FIND(" ",H48&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="I84" s="77">
+        <f>IFERROR(VALUE(LEFT(I11,FIND(" ",I11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I48,FIND(" ",I48&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="J84" s="77">
+        <f>IFERROR(VALUE(LEFT(J11,FIND(" ",J11&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J48,FIND(" ",J48&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="K84" s="77" t="n"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" s="52">
+      <c r="A85" s="76" t="inlineStr">
+        <is>
+          <t>Aductores</t>
+        </is>
+      </c>
+      <c r="B85" s="77">
+        <f>C85&amp;" → "&amp;J85</f>
+        <v/>
+      </c>
+      <c r="C85" s="77">
+        <f>IFERROR(VALUE(LEFT(C47,FIND(" ",C47&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="D85" s="77">
+        <f>IFERROR(VALUE(LEFT(D47,FIND(" ",D47&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="E85" s="77">
+        <f>IFERROR(VALUE(LEFT(E47,FIND(" ",E47&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="F85" s="77">
+        <f>IFERROR(VALUE(LEFT(F47,FIND(" ",F47&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="G85" s="77">
+        <f>IFERROR(VALUE(LEFT(G47,FIND(" ",G47&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="H85" s="77">
+        <f>IFERROR(VALUE(LEFT(H47,FIND(" ",H47&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="I85" s="77">
+        <f>IFERROR(VALUE(LEFT(I47,FIND(" ",I47&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="J85" s="77">
+        <f>IFERROR(VALUE(LEFT(J47,FIND(" ",J47&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="K85" s="77" t="n"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1" s="52">
+      <c r="A86" s="78" t="inlineStr">
         <is>
           <t>TOTAL hipertrofia</t>
         </is>
       </c>
-      <c r="B84" s="75">
-        <f>C84&amp;" → "&amp;J84</f>
-        <v/>
-      </c>
-      <c r="C84" s="75">
-        <f>SUM(C74:C83)</f>
-        <v/>
-      </c>
-      <c r="D84" s="75">
-        <f>SUM(D74:D83)</f>
-        <v/>
-      </c>
-      <c r="E84" s="75">
-        <f>SUM(E74:E83)</f>
-        <v/>
-      </c>
-      <c r="F84" s="75">
-        <f>SUM(F74:F83)</f>
-        <v/>
-      </c>
-      <c r="G84" s="75">
-        <f>SUM(G74:G83)</f>
-        <v/>
-      </c>
-      <c r="H84" s="75">
-        <f>SUM(H74:H83)</f>
-        <v/>
-      </c>
-      <c r="I84" s="75">
-        <f>SUM(I74:I83)</f>
-        <v/>
-      </c>
-      <c r="J84" s="75">
-        <f>SUM(J74:J83)</f>
-        <v/>
-      </c>
-      <c r="K84" s="75" t="n"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1" s="52"/>
-    <row r="86" ht="19.5" customHeight="1" s="52">
-      <c r="A86" s="74" t="inlineStr">
+      <c r="B86" s="75">
+        <f>C86&amp;" → "&amp;J86</f>
+        <v/>
+      </c>
+      <c r="C86" s="75">
+        <f>SUM(C76:C85)</f>
+        <v/>
+      </c>
+      <c r="D86" s="75">
+        <f>SUM(D76:D85)</f>
+        <v/>
+      </c>
+      <c r="E86" s="75">
+        <f>SUM(E76:E85)</f>
+        <v/>
+      </c>
+      <c r="F86" s="75">
+        <f>SUM(F76:F85)</f>
+        <v/>
+      </c>
+      <c r="G86" s="75">
+        <f>SUM(G76:G85)</f>
+        <v/>
+      </c>
+      <c r="H86" s="75">
+        <f>SUM(H76:H85)</f>
+        <v/>
+      </c>
+      <c r="I86" s="75">
+        <f>SUM(I76:I85)</f>
+        <v/>
+      </c>
+      <c r="J86" s="75">
+        <f>SUM(J76:J85)</f>
+        <v/>
+      </c>
+      <c r="K86" s="75" t="n"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1" s="52"/>
+    <row r="88" ht="19.5" customHeight="1" s="52">
+      <c r="A88" s="74" t="inlineStr">
         <is>
           <t>Desglose biomecánico de Espalda por planos (se recalcula solo al cambiar la tabla)</t>
         </is>
       </c>
-      <c r="B86" s="56" t="n"/>
-      <c r="C86" s="56" t="n"/>
-      <c r="D86" s="56" t="n"/>
-      <c r="E86" s="56" t="n"/>
-      <c r="F86" s="56" t="n"/>
-      <c r="G86" s="56" t="n"/>
-      <c r="H86" s="56" t="n"/>
-      <c r="I86" s="56" t="n"/>
-      <c r="J86" s="56" t="n"/>
-      <c r="K86" s="57" t="n"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" s="52">
-      <c r="A87" s="75" t="inlineStr">
+      <c r="B88" s="56" t="n"/>
+      <c r="C88" s="56" t="n"/>
+      <c r="D88" s="56" t="n"/>
+      <c r="E88" s="56" t="n"/>
+      <c r="F88" s="56" t="n"/>
+      <c r="G88" s="56" t="n"/>
+      <c r="H88" s="56" t="n"/>
+      <c r="I88" s="56" t="n"/>
+      <c r="J88" s="56" t="n"/>
+      <c r="K88" s="57" t="n"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1" s="52">
+      <c r="A89" s="75" t="inlineStr">
         <is>
           <t>Plano / Región de Espalda</t>
         </is>
       </c>
-      <c r="B87" s="75" t="inlineStr">
+      <c r="B89" s="75" t="inlineStr">
         <is>
           <t>Sem 1 → Sem 8</t>
         </is>
       </c>
-      <c r="C87" s="75" t="inlineStr">
+      <c r="C89" s="75" t="inlineStr">
         <is>
           <t>Sem 1</t>
         </is>
       </c>
-      <c r="D87" s="75" t="inlineStr">
+      <c r="D89" s="75" t="inlineStr">
         <is>
           <t>Sem 2</t>
         </is>
       </c>
-      <c r="E87" s="75" t="inlineStr">
+      <c r="E89" s="75" t="inlineStr">
         <is>
           <t>Sem 3</t>
         </is>
       </c>
-      <c r="F87" s="75" t="inlineStr">
+      <c r="F89" s="75" t="inlineStr">
         <is>
           <t>Sem 4</t>
         </is>
       </c>
-      <c r="G87" s="75" t="inlineStr">
+      <c r="G89" s="75" t="inlineStr">
         <is>
           <t>Sem 5</t>
         </is>
       </c>
-      <c r="H87" s="75" t="inlineStr">
+      <c r="H89" s="75" t="inlineStr">
         <is>
           <t>Sem 6</t>
         </is>
       </c>
-      <c r="I87" s="75" t="inlineStr">
+      <c r="I89" s="75" t="inlineStr">
         <is>
           <t>Sem 7</t>
         </is>
       </c>
-      <c r="J87" s="75" t="inlineStr">
+      <c r="J89" s="75" t="inlineStr">
         <is>
           <t>Sem 8</t>
         </is>
       </c>
-      <c r="K87" s="51" t="inlineStr">
+      <c r="K89" s="51" t="inlineStr">
         <is>
           <t>Ejercicios incluidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1" s="52">
-      <c r="A88" s="76" t="inlineStr">
-        <is>
-          <t>Dorsal Bajo (Plano Frontal)</t>
-        </is>
-      </c>
-      <c r="B88" s="77">
-        <f>C88&amp;" → "&amp;J88</f>
-        <v/>
-      </c>
-      <c r="C88" s="77">
-        <f>IFERROR(VALUE(LEFT(C26,FIND(" ",C26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C54,FIND(" ",C54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="D88" s="77">
-        <f>IFERROR(VALUE(LEFT(D26,FIND(" ",D26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D54,FIND(" ",D54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="E88" s="77">
-        <f>IFERROR(VALUE(LEFT(E26,FIND(" ",E26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E54,FIND(" ",E54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="F88" s="77">
-        <f>IFERROR(VALUE(LEFT(F26,FIND(" ",F26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F54,FIND(" ",F54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="G88" s="77">
-        <f>IFERROR(VALUE(LEFT(G26,FIND(" ",G26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G54,FIND(" ",G54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="H88" s="77">
-        <f>IFERROR(VALUE(LEFT(H26,FIND(" ",H26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H54,FIND(" ",H54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="I88" s="77">
-        <f>IFERROR(VALUE(LEFT(I26,FIND(" ",I26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I54,FIND(" ",I54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="J88" s="77">
-        <f>IFERROR(VALUE(LEFT(J26,FIND(" ",J26&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J54,FIND(" ",J54&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="K88" s="79" t="inlineStr">
-        <is>
-          <t>Jalón ancho plano frontal (X) + Aducción unil. polea alta (V)</t>
-        </is>
-      </c>
-      <c r="L88" s="106" t="inlineStr">
-        <is>
-          <t>desglose=jalon-ancho-plano-frontal,aduccion-unil-polea-alta-pull-in</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1" s="52">
-      <c r="A89" s="76" t="inlineStr">
-        <is>
-          <t>Dorsal Superior (Plano Sagital)</t>
-        </is>
-      </c>
-      <c r="B89" s="77">
-        <f>C89&amp;" → "&amp;J89</f>
-        <v/>
-      </c>
-      <c r="C89" s="77">
-        <f>IFERROR(VALUE(LEFT(C29,FIND(" ",C29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C52,FIND(" ",C52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C53,FIND(" ",C53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="D89" s="77">
-        <f>IFERROR(VALUE(LEFT(D29,FIND(" ",D29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D52,FIND(" ",D52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D53,FIND(" ",D53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="E89" s="77">
-        <f>IFERROR(VALUE(LEFT(E29,FIND(" ",E29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E52,FIND(" ",E52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E53,FIND(" ",E53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="F89" s="77">
-        <f>IFERROR(VALUE(LEFT(F29,FIND(" ",F29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F52,FIND(" ",F52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F53,FIND(" ",F53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="G89" s="77">
-        <f>IFERROR(VALUE(LEFT(G29,FIND(" ",G29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G52,FIND(" ",G52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G53,FIND(" ",G53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="H89" s="77">
-        <f>IFERROR(VALUE(LEFT(H29,FIND(" ",H29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H52,FIND(" ",H52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H53,FIND(" ",H53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="I89" s="77">
-        <f>IFERROR(VALUE(LEFT(I29,FIND(" ",I29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I52,FIND(" ",I52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I53,FIND(" ",I53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="J89" s="77">
-        <f>IFERROR(VALUE(LEFT(J29,FIND(" ",J29&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J52,FIND(" ",J52&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J53,FIND(" ",J53&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="K89" s="79" t="inlineStr">
-        <is>
-          <t>Jalón neutro bolsillos (X) + Dominada neutra (V) + Remo máq. 30° (V)</t>
-        </is>
-      </c>
-      <c r="L89" s="106" t="inlineStr">
-        <is>
-          <t>desglose=jalon-neutro,dominada-neutra-dorsal,remo-maquina-pecho-apoyado-30</t>
         </is>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="52">
       <c r="A90" s="76" t="inlineStr">
         <is>
-          <t>Espalda Alta (Plano Transversal)</t>
+          <t>Dorsal Bajo (Plano Frontal)</t>
         </is>
       </c>
       <c r="B90" s="77">
@@ -10253,557 +10188,624 @@
         <v/>
       </c>
       <c r="C90" s="77">
-        <f>IFERROR(VALUE(LEFT(C27,FIND(" ",C27&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(C31,FIND(" ",C31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C15,FIND(" ",C15&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="D90" s="77">
-        <f>IFERROR(VALUE(LEFT(D27,FIND(" ",D27&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(D31,FIND(" ",D31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D15,FIND(" ",D15&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="E90" s="77">
-        <f>IFERROR(VALUE(LEFT(E27,FIND(" ",E27&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(E31,FIND(" ",E31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E15,FIND(" ",E15&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="F90" s="77">
-        <f>IFERROR(VALUE(LEFT(F27,FIND(" ",F27&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(F31,FIND(" ",F31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F15,FIND(" ",F15&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="G90" s="77">
-        <f>IFERROR(VALUE(LEFT(G27,FIND(" ",G27&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(G31,FIND(" ",G31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G15,FIND(" ",G15&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="H90" s="77">
-        <f>IFERROR(VALUE(LEFT(H27,FIND(" ",H27&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(H31,FIND(" ",H31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H15,FIND(" ",H15&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="I90" s="77">
-        <f>IFERROR(VALUE(LEFT(I27,FIND(" ",I27&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(I31,FIND(" ",I31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I15,FIND(" ",I15&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="J90" s="77">
-        <f>IFERROR(VALUE(LEFT(J27,FIND(" ",J27&amp;" ")-1)),0)</f>
+        <f>IFERROR(VALUE(LEFT(J31,FIND(" ",J31&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J15,FIND(" ",J15&amp;" ")-1)),0)</f>
         <v/>
       </c>
       <c r="K90" s="79" t="inlineStr">
         <is>
-          <t>Remo gironda abierto (X)</t>
+          <t>Jalón ancho plano frontal (J) + Aducción unil. polea alta (L)</t>
         </is>
       </c>
       <c r="L90" s="106" t="inlineStr">
         <is>
+          <t>desglose=jalon-ancho-plano-frontal,aduccion-unil-polea-alta-pull-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1" s="52">
+      <c r="A91" s="76" t="inlineStr">
+        <is>
+          <t>Dorsal Superior (Plano Sagital)</t>
+        </is>
+      </c>
+      <c r="B91" s="77">
+        <f>C91&amp;" → "&amp;J91</f>
+        <v/>
+      </c>
+      <c r="C91" s="77">
+        <f>IFERROR(VALUE(LEFT(C34,FIND(" ",C34&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C13,FIND(" ",C13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C14,FIND(" ",C14&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="D91" s="77">
+        <f>IFERROR(VALUE(LEFT(D34,FIND(" ",D34&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D13,FIND(" ",D13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D14,FIND(" ",D14&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="E91" s="77">
+        <f>IFERROR(VALUE(LEFT(E34,FIND(" ",E34&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E13,FIND(" ",E13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E14,FIND(" ",E14&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="F91" s="77">
+        <f>IFERROR(VALUE(LEFT(F34,FIND(" ",F34&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F13,FIND(" ",F13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F14,FIND(" ",F14&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="G91" s="77">
+        <f>IFERROR(VALUE(LEFT(G34,FIND(" ",G34&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G13,FIND(" ",G13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G14,FIND(" ",G14&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="H91" s="77">
+        <f>IFERROR(VALUE(LEFT(H34,FIND(" ",H34&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H13,FIND(" ",H13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H14,FIND(" ",H14&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="I91" s="77">
+        <f>IFERROR(VALUE(LEFT(I34,FIND(" ",I34&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I13,FIND(" ",I13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I14,FIND(" ",I14&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="J91" s="77">
+        <f>IFERROR(VALUE(LEFT(J34,FIND(" ",J34&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J13,FIND(" ",J13&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J14,FIND(" ",J14&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="K91" s="79" t="inlineStr">
+        <is>
+          <t>Jalón neutro bolsillos (J) + Dominada neutra (L) + Remo máq. 30° (L)</t>
+        </is>
+      </c>
+      <c r="L91" s="106" t="inlineStr">
+        <is>
+          <t>desglose=jalon-neutro,dominada-neutra-dorsal,remo-maquina-pecho-apoyado-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1" s="52">
+      <c r="A92" s="76" t="inlineStr">
+        <is>
+          <t>Espalda Alta (Plano Transversal)</t>
+        </is>
+      </c>
+      <c r="B92" s="77">
+        <f>C92&amp;" → "&amp;J92</f>
+        <v/>
+      </c>
+      <c r="C92" s="77">
+        <f>IFERROR(VALUE(LEFT(C32,FIND(" ",C32&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="D92" s="77">
+        <f>IFERROR(VALUE(LEFT(D32,FIND(" ",D32&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="E92" s="77">
+        <f>IFERROR(VALUE(LEFT(E32,FIND(" ",E32&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="F92" s="77">
+        <f>IFERROR(VALUE(LEFT(F32,FIND(" ",F32&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="G92" s="77">
+        <f>IFERROR(VALUE(LEFT(G32,FIND(" ",G32&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="H92" s="77">
+        <f>IFERROR(VALUE(LEFT(H32,FIND(" ",H32&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="I92" s="77">
+        <f>IFERROR(VALUE(LEFT(I32,FIND(" ",I32&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="J92" s="77">
+        <f>IFERROR(VALUE(LEFT(J32,FIND(" ",J32&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="K92" s="79" t="inlineStr">
+        <is>
+          <t>Remo gironda abierto (J)</t>
+        </is>
+      </c>
+      <c r="L92" s="106" t="inlineStr">
+        <is>
           <t>desglose=remo-gironda-abierto</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="15.75" customHeight="1" s="52">
-      <c r="A91" s="78" t="inlineStr">
+    <row r="93" ht="15.75" customHeight="1" s="52">
+      <c r="A93" s="78" t="inlineStr">
         <is>
           <t>Total Transversal (Espalda Alta + Post.)</t>
         </is>
       </c>
-      <c r="B91" s="75">
-        <f>C91&amp;" → "&amp;J91</f>
-        <v/>
-      </c>
-      <c r="C91" s="75">
-        <f>IFERROR(VALUE(LEFT(C27,FIND(" ",C27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C31,FIND(" ",C31&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="D91" s="75">
-        <f>IFERROR(VALUE(LEFT(D27,FIND(" ",D27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D31,FIND(" ",D31&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="E91" s="75">
-        <f>IFERROR(VALUE(LEFT(E27,FIND(" ",E27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E31,FIND(" ",E31&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="F91" s="75">
-        <f>IFERROR(VALUE(LEFT(F27,FIND(" ",F27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F31,FIND(" ",F31&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="G91" s="75">
-        <f>IFERROR(VALUE(LEFT(G27,FIND(" ",G27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G31,FIND(" ",G31&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="H91" s="75">
-        <f>IFERROR(VALUE(LEFT(H27,FIND(" ",H27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H31,FIND(" ",H31&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="I91" s="75">
-        <f>IFERROR(VALUE(LEFT(I27,FIND(" ",I27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I31,FIND(" ",I31&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="J91" s="75">
-        <f>IFERROR(VALUE(LEFT(J27,FIND(" ",J27&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J31,FIND(" ",J31&amp;" ")-1)),0)</f>
-        <v/>
-      </c>
-      <c r="K91" s="80" t="inlineStr">
-        <is>
-          <t>Remo gironda abierto (X) + Posterior polea (X)</t>
-        </is>
-      </c>
-      <c r="L91" s="106" t="inlineStr">
+      <c r="B93" s="75">
+        <f>C93&amp;" → "&amp;J93</f>
+        <v/>
+      </c>
+      <c r="C93" s="75">
+        <f>IFERROR(VALUE(LEFT(C32,FIND(" ",C32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(C36,FIND(" ",C36&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="D93" s="75">
+        <f>IFERROR(VALUE(LEFT(D32,FIND(" ",D32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(D36,FIND(" ",D36&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="E93" s="75">
+        <f>IFERROR(VALUE(LEFT(E32,FIND(" ",E32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(E36,FIND(" ",E36&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="F93" s="75">
+        <f>IFERROR(VALUE(LEFT(F32,FIND(" ",F32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(F36,FIND(" ",F36&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="G93" s="75">
+        <f>IFERROR(VALUE(LEFT(G32,FIND(" ",G32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(G36,FIND(" ",G36&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="H93" s="75">
+        <f>IFERROR(VALUE(LEFT(H32,FIND(" ",H32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(H36,FIND(" ",H36&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="I93" s="75">
+        <f>IFERROR(VALUE(LEFT(I32,FIND(" ",I32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(I36,FIND(" ",I36&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="J93" s="75">
+        <f>IFERROR(VALUE(LEFT(J32,FIND(" ",J32&amp;" ")-1)),0)+IFERROR(VALUE(LEFT(J36,FIND(" ",J36&amp;" ")-1)),0)</f>
+        <v/>
+      </c>
+      <c r="K93" s="80" t="inlineStr">
+        <is>
+          <t>Remo gironda abierto (J) + Posterior polea (J)</t>
+        </is>
+      </c>
+      <c r="L93" s="106" t="inlineStr">
         <is>
           <t>desglose=remo-gironda-abierto,posterior-polea</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="15.75" customHeight="1" s="52"/>
-    <row r="93" ht="15.75" customHeight="1" s="52"/>
-    <row r="94" ht="19.5" customHeight="1" s="52">
-      <c r="A94" s="74" t="inlineStr">
+    <row r="94" ht="15.75" customHeight="1" s="52"/>
+    <row r="95" ht="15.75" customHeight="1" s="52"/>
+    <row r="96" ht="19.5" customHeight="1" s="52">
+      <c r="A96" s="74" t="inlineStr">
         <is>
           <t>BLOQUE DE CARDIO Y CARRERA (S2-S8)</t>
         </is>
       </c>
-      <c r="B94" s="56" t="n"/>
-      <c r="C94" s="56" t="n"/>
-      <c r="D94" s="56" t="n"/>
-      <c r="E94" s="56" t="n"/>
-      <c r="F94" s="56" t="n"/>
-      <c r="G94" s="56" t="n"/>
-      <c r="H94" s="56" t="n"/>
-      <c r="I94" s="56" t="n"/>
-      <c r="J94" s="56" t="n"/>
-      <c r="K94" s="57" t="n"/>
-      <c r="L94" s="106" t="inlineStr">
+      <c r="B96" s="56" t="n"/>
+      <c r="C96" s="56" t="n"/>
+      <c r="D96" s="56" t="n"/>
+      <c r="E96" s="56" t="n"/>
+      <c r="F96" s="56" t="n"/>
+      <c r="G96" s="56" t="n"/>
+      <c r="H96" s="56" t="n"/>
+      <c r="I96" s="56" t="n"/>
+      <c r="J96" s="56" t="n"/>
+      <c r="K96" s="57" t="n"/>
+      <c r="L96" s="106" t="inlineStr">
         <is>
           <t>cardio</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="15.75" customHeight="1" s="52">
-      <c r="A95" s="75" t="inlineStr">
+    <row r="97" ht="15.75" customHeight="1" s="52">
+      <c r="A97" s="75" t="inlineStr">
         <is>
           <t>Día / Sesión</t>
         </is>
       </c>
-      <c r="B95" s="75" t="inlineStr">
+      <c r="B97" s="75" t="inlineStr">
         <is>
           <t>Tipo / Zona</t>
         </is>
       </c>
-      <c r="C95" s="75" t="inlineStr">
+      <c r="C97" s="75" t="inlineStr">
         <is>
           <t>Sem 1</t>
         </is>
       </c>
-      <c r="D95" s="75" t="inlineStr">
+      <c r="D97" s="75" t="inlineStr">
         <is>
           <t>Sem 2</t>
         </is>
       </c>
-      <c r="E95" s="75" t="inlineStr">
+      <c r="E97" s="75" t="inlineStr">
         <is>
           <t>Sem 3</t>
         </is>
       </c>
-      <c r="F95" s="75" t="inlineStr">
+      <c r="F97" s="75" t="inlineStr">
         <is>
           <t>Sem 4</t>
         </is>
       </c>
-      <c r="G95" s="75" t="inlineStr">
+      <c r="G97" s="75" t="inlineStr">
         <is>
           <t>Sem 5</t>
         </is>
       </c>
-      <c r="H95" s="75" t="inlineStr">
+      <c r="H97" s="75" t="inlineStr">
         <is>
           <t>Sem 6</t>
         </is>
       </c>
-      <c r="I95" s="75" t="inlineStr">
+      <c r="I97" s="75" t="inlineStr">
         <is>
           <t>Sem 7</t>
         </is>
       </c>
-      <c r="J95" s="75" t="inlineStr">
+      <c r="J97" s="75" t="inlineStr">
         <is>
           <t>Sem 8</t>
         </is>
       </c>
-      <c r="K95" s="51" t="inlineStr">
+      <c r="K97" s="51" t="inlineStr">
         <is>
           <t>Pautas Biomecánicas Rodilla &amp; Intensidad</t>
         </is>
       </c>
-      <c r="L95" s="106" t="inlineStr">
+      <c r="L97" s="106" t="inlineStr">
         <is>
           <t>App (no tocar)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="55.5" customHeight="1" s="52">
-      <c r="A96" s="81" t="inlineStr">
+    <row r="98" ht="55.5" customHeight="1" s="52">
+      <c r="A98" s="81" t="inlineStr">
         <is>
           <t>Martes (Post-Push)</t>
         </is>
       </c>
-      <c r="B96" s="82" t="inlineStr">
+      <c r="B98" s="82" t="inlineStr">
         <is>
           <t>Bici Z2 (65–75% FC)</t>
         </is>
       </c>
-      <c r="C96" s="77" t="inlineStr">
+      <c r="C98" s="77" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="D96" s="83" t="inlineStr">
+      <c r="D98" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E96" s="83" t="inlineStr">
+      <c r="E98" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F96" s="83" t="inlineStr">
+      <c r="F98" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G96" s="83" t="inlineStr">
+      <c r="G98" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="H96" s="83" t="inlineStr">
+      <c r="H98" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="I96" s="83" t="inlineStr">
+      <c r="I98" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="J96" s="83" t="inlineStr">
+      <c r="J98" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="K96" s="62" t="inlineStr">
+      <c r="K98" s="62" t="inlineStr">
         <is>
           <t>No se hizo en S1: estímulo NUEVO [LÓGICA]. Entra en S4 (el viernes) solo si S2 y S3 cumplieron la regla; desde S5, martes y viernes. Sin Z3 en este bloque. Lo primero que se quita si hay brote. Sillín alto (rodilla a 20-25° abajo), 85-90 rpm, sentado. 10 min fijos en el bloque; subir a 15 después del viaje, como novedad única.</t>
         </is>
       </c>
-      <c r="L96" s="106" t="inlineStr">
+      <c r="L98" s="106" t="inlineStr">
         <is>
           <t>id=bici-z2-65-75-fc;sesion=M;bici</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="30.75" customHeight="1" s="52">
-      <c r="A97" s="81" t="inlineStr">
-        <is>
-          <t>Viernes (Post-Torso)</t>
-        </is>
-      </c>
-      <c r="B97" s="82" t="inlineStr">
+    <row r="99" ht="30.75" customHeight="1" s="52">
+      <c r="A99" s="81" t="inlineStr">
+        <is>
+          <t>Viernes (tras pierna 2)</t>
+        </is>
+      </c>
+      <c r="B99" s="82" t="inlineStr">
         <is>
           <t>Bici Z2 (sin Z3 en este bloque)</t>
         </is>
       </c>
-      <c r="C97" s="77" t="inlineStr">
+      <c r="C99" s="77" t="inlineStr">
         <is>
           <t>12 min</t>
         </is>
       </c>
-      <c r="D97" s="83" t="inlineStr">
+      <c r="D99" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E97" s="83" t="inlineStr">
+      <c r="E99" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F97" s="83" t="inlineStr">
+      <c r="F99" s="83" t="inlineStr">
         <is>
           <t>10' Z2
 nov: 1.ª vez</t>
         </is>
       </c>
-      <c r="G97" s="83" t="inlineStr">
+      <c r="G99" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="H97" s="83" t="inlineStr">
+      <c r="H99" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="I97" s="83" t="inlineStr">
+      <c r="I99" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="J97" s="83" t="inlineStr">
+      <c r="J99" s="83" t="inlineStr">
         <is>
           <t>10' Z2</t>
         </is>
       </c>
-      <c r="K97" s="62" t="inlineStr">
-        <is>
-          <t>S4: primera vez, solo si esa mañana estás igual o mejor; se valida con las mediciones del sábado y del domingo (el sábado no hay pierna). Ver la nota del martes.</t>
-        </is>
-      </c>
-      <c r="L97" s="106" t="inlineStr">
+      <c r="K99" s="62" t="inlineStr">
+        <is>
+          <t>S4: primera vez, solo si esa mañana estás igual o mejor. Va después de la pierna 2, que repite la profundidad ya validada, así que la bici es la única novedad del día. Se valida con las mediciones del sábado y del domingo (el sábado no hay pierna) [LÓGICA]. Ver la nota del martes.</t>
+        </is>
+      </c>
+      <c r="L99" s="106" t="inlineStr">
         <is>
           <t>id=bici-z2-sin-z3-en-este-bloque;sesion=V;bici</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="81" customHeight="1" s="52">
-      <c r="A98" s="81" t="inlineStr">
-        <is>
-          <t>Miércoles · Carrera (nivel nuevo)</t>
-        </is>
-      </c>
-      <c r="B98" s="82" t="inlineStr">
+    <row r="100" ht="81" customHeight="1" s="52">
+      <c r="A100" s="81" t="inlineStr">
+        <is>
+          <t>Miércoles · Carrera, sin gimnasio (nivel nuevo)</t>
+        </is>
+      </c>
+      <c r="B100" s="82" t="inlineStr">
         <is>
           <t>Andar-correr en llano</t>
         </is>
       </c>
-      <c r="C98" s="83" t="inlineStr">
+      <c r="C100" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D98" s="83" t="inlineStr">
+      <c r="D100" s="83" t="inlineStr">
         <is>
           <t>N1 · 8×(1'/2')</t>
         </is>
       </c>
-      <c r="E98" s="83" t="inlineStr">
+      <c r="E100" s="83" t="inlineStr">
         <is>
           <t>N2 · 6×(2'/1')</t>
         </is>
       </c>
-      <c r="F98" s="83" t="inlineStr">
+      <c r="F100" s="83" t="inlineStr">
         <is>
           <t>N3 · 4×(4'/1')</t>
         </is>
       </c>
-      <c r="G98" s="83" t="inlineStr">
+      <c r="G100" s="83" t="inlineStr">
         <is>
           <t>N4 · 4×(5'/1')</t>
         </is>
       </c>
-      <c r="H98" s="83" t="inlineStr">
+      <c r="H100" s="83" t="inlineStr">
         <is>
           <t>N5 · 3×(8'/1')</t>
         </is>
       </c>
-      <c r="I98" s="83" t="inlineStr">
+      <c r="I100" s="83" t="inlineStr">
         <is>
           <t>N6 · 2×(12'/1')</t>
         </is>
       </c>
-      <c r="J98" s="83" t="inlineStr">
+      <c r="J100" s="83" t="inlineStr">
         <is>
           <t>repite N6</t>
         </is>
       </c>
-      <c r="K98" s="62" t="inlineStr">
+      <c r="K100" s="62" t="inlineStr">
         <is>
           <t>Formato: minutos trotando / minutos andando. Niveles: N1 8×(1'/2') · N2 6×(2'/1') · N3 4×(4'/1') · N4 4×(5'/1') · N5 3×(8'/1') · N6 2×(12'/1'); después del viaje, N7 18' · N8 25' · N9 30' seguidos. Desde N4 el tramo continuo más largo crece como mucho un 50 % por nivel (5 → 8 → 12 → 18 → 25 → 30 min); de N1 a N3 se dobla porque los tramos son muy cortos [LÓGICA]. El calendario marca el máximo de cada semana; el nivel real sale del semáforo: Avanzar = +1, Mantener = el mismo, Retroceder = −1. Nivel nuevo solo si esa mañana estás igual o mejor. 5 min andando antes; llano y firme. Regla de carrera: Retroceder si pasas de 2/10 durante, no vuelves al nivel previo en ≤60 min o la mañana siguiente estás peor; Mantener si cumple pero el peor valor 24-48 h supera la referencia; Avanzar si cumple y el peor 24-48 h ≤ referencia [EVIDENCIA de uso: TREK Education, basada en Esculier; no comparada con otros umbrales]. Cadencia +5-10% opcional [EVIDENCIA mixta: Bramah 2019, serie de 12 corredores con mejora de dolor y función mantenida a 3 meses; Esculier 2018, sin beneficio extra sobre la educación].</t>
         </is>
       </c>
-      <c r="L98" s="106" t="inlineStr">
+      <c r="L100" s="106" t="inlineStr">
         <is>
           <t>id=andar-correr-en-llano;sesion=X;escalera=carrera</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="30.75" customHeight="1" s="52">
-      <c r="A99" s="81" t="inlineStr">
+    <row r="101" ht="30.75" customHeight="1" s="52">
+      <c r="A101" s="81" t="inlineStr">
         <is>
           <t>Domingo · Carrera (repite)</t>
         </is>
       </c>
-      <c r="B99" s="82" t="inlineStr">
+      <c r="B101" s="82" t="inlineStr">
         <is>
           <t>Andar-correr en llano</t>
         </is>
       </c>
-      <c r="C99" s="83" t="inlineStr">
+      <c r="C101" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D99" s="83" t="inlineStr">
+      <c r="D101" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="E99" s="83" t="inlineStr">
+      <c r="E101" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="F99" s="83" t="inlineStr">
+      <c r="F101" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="G99" s="83" t="inlineStr">
+      <c r="G101" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="H99" s="83" t="inlineStr">
+      <c r="H101" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="I99" s="83" t="inlineStr">
+      <c r="I101" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="J99" s="83" t="inlineStr">
+      <c r="J101" s="83" t="inlineStr">
         <is>
           <t>repite el
 miércoles</t>
         </is>
       </c>
-      <c r="K99" s="62" t="inlineStr">
+      <c r="K101" s="62" t="inlineStr">
         <is>
           <t>Repite el nivel validado el miércoles. Si el miércoles no se cumplieron los criterios de entrada, esa semana no hay carrera: el domingo no se corre (como mucho, un paseo). Nunca dos días seguidos corriendo [LÓGICA]. El sábado no hay pierna: llegas descansado.</t>
         </is>
       </c>
-      <c r="L99" s="106" t="inlineStr">
+      <c r="L101" s="106" t="inlineStr">
         <is>
           <t>id=andar-correr-en-llano;sesion=D;titulo=Carrera;escalera=carrera:domingo</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="55.5" customHeight="1" s="52">
-      <c r="A100" s="81" t="inlineStr">
+    <row r="102" ht="55.5" customHeight="1" s="52">
+      <c r="A102" s="81" t="inlineStr">
         <is>
           <t>Hitos y avisos</t>
         </is>
       </c>
-      <c r="B100" s="82" t="inlineStr">
+      <c r="B102" s="82" t="inlineStr">
         <is>
           <t>Calendario</t>
         </is>
       </c>
-      <c r="C100" s="83" t="inlineStr">
+      <c r="C102" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D100" s="83" t="inlineStr">
+      <c r="D102" s="83" t="inlineStr">
         <is>
           <t>Mar: paseo 30'
 Mié: TD + saltitos
-→ 1.ª carrera
-Jue: test 1</t>
-        </is>
-      </c>
-      <c r="E100" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F100" s="83" t="inlineStr">
+→ 1.ª carrera</t>
+        </is>
+      </c>
+      <c r="E102" s="83" t="inlineStr">
+        <is>
+          <t>Lun 2/11 festivo: en casa, sin escalón
+Vie 6/11: test 1</t>
+        </is>
+      </c>
+      <c r="F102" s="83" t="inlineStr">
         <is>
           <t>AVISO fisio
 (ver Seguimiento)
 Vie: bici</t>
         </is>
       </c>
-      <c r="G100" s="83" t="inlineStr">
+      <c r="G102" s="83" t="inlineStr">
         <is>
           <t>Lun: x8
-Jue: test 2</t>
-        </is>
-      </c>
-      <c r="H100" s="83" t="inlineStr">
+Vie: test 2</t>
+        </is>
+      </c>
+      <c r="H102" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I100" s="83" t="inlineStr">
-        <is>
-          <t>Jue: test 3</t>
-        </is>
-      </c>
-      <c r="J100" s="83" t="inlineStr">
-        <is>
-          <t>Repite S7
-Jue: test opc.
+      <c r="I102" s="83" t="inlineStr">
+        <is>
+          <t>Vie: test 3</t>
+        </is>
+      </c>
+      <c r="J102" s="83" t="inlineStr">
+        <is>
+          <t>Lun: 4.º escalón solo si S6-S7 OK
+Vie: test opc.
 rango completo</t>
         </is>
       </c>
-      <c r="K100" s="62" t="inlineStr">
+      <c r="K102" s="62" t="inlineStr">
         <is>
           <t>Entrada a la carrera (S2), con la regla de carrera: martes, paseo de 30 min a paso rápido (≤2/10, nivel previo en ≤60 min y el miércoles por la mañana no peor: el criterio 1 se evalúa solo con esa mañana, sin esperar a las 48 h); miércoles antes de correr, 10 touchdown con cada pierna y 20 saltitos a dos piernas (≤2/10). Si se cumplen los tres, 1.ª carrera ese miércoles (N1). Si no, esa semana no hay carrera (el domingo, como mucho, un paseo) y los criterios se repiten el miércoles siguiente [LÓGICA].</t>
         </is>
       </c>
-      <c r="L100" s="106" t="inlineStr">
+      <c r="L102" s="106" t="inlineStr">
         <is>
           <t>hitos</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="15.75" customHeight="1" s="52"/>
-    <row r="102" ht="19.5" customHeight="1" s="52">
-      <c r="A102" s="74" t="inlineStr">
+    <row r="103" ht="15.75" customHeight="1" s="52"/>
+    <row r="104" ht="19.5" customHeight="1" s="52">
+      <c r="A104" s="74" t="inlineStr">
         <is>
           <t>REGLAS DEL BLOQUE RODILLA (S2-S8)</t>
-        </is>
-      </c>
-      <c r="B102" s="56" t="n"/>
-      <c r="C102" s="56" t="n"/>
-      <c r="D102" s="56" t="n"/>
-      <c r="E102" s="56" t="n"/>
-      <c r="F102" s="56" t="n"/>
-      <c r="G102" s="56" t="n"/>
-      <c r="H102" s="56" t="n"/>
-      <c r="I102" s="56" t="n"/>
-      <c r="J102" s="56" t="n"/>
-      <c r="K102" s="57" t="n"/>
-      <c r="L102" s="106" t="inlineStr">
-        <is>
-          <t>reglas-bloque</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="30.75" customHeight="1" s="52">
-      <c r="A103" s="67" t="inlineStr">
-        <is>
-          <t>Base [EVIDENCIA]: ejercicio combinado de cadera y rodilla (consensos de 2016 y 2018). Rodilla en 2 días, lunes y jueves (72-96 h entre sesiones, dentro de la ventana de 2-3 días de recuperación del tendón que describe el libro), pesado y lento en ambos; sábado sin pierna para llegar descansado a la carrera del domingo [LÓGICA].</t>
-        </is>
-      </c>
-      <c r="B103" s="56" t="n"/>
-      <c r="C103" s="56" t="n"/>
-      <c r="D103" s="56" t="n"/>
-      <c r="E103" s="56" t="n"/>
-      <c r="F103" s="56" t="n"/>
-      <c r="G103" s="56" t="n"/>
-      <c r="H103" s="56" t="n"/>
-      <c r="I103" s="56" t="n"/>
-      <c r="J103" s="56" t="n"/>
-      <c r="K103" s="57" t="n"/>
-    </row>
-    <row r="104" ht="30.75" customHeight="1" s="52">
-      <c r="A104" s="67" t="inlineStr">
-        <is>
-          <t>Mediciones: cada mañana, en casa, con las mismas pruebas: test en declive y 10 subidas con la D al mismo escalón o banco. Vale la peor de las dos (el declive solo no basta: te sale 0 aunque haya molestia). Si falta la medición de la mañana, ese día no se evalúa y la primera medición disponible hace de referencia (en S2, la del martes). Se apuntan en «Seguimiento rodilla».</t>
         </is>
       </c>
       <c r="B104" s="56" t="n"/>
@@ -10816,11 +10818,16 @@
       <c r="I104" s="56" t="n"/>
       <c r="J104" s="56" t="n"/>
       <c r="K104" s="57" t="n"/>
-    </row>
-    <row r="105" ht="18" customHeight="1" s="52">
+      <c r="L104" s="106" t="inlineStr">
+        <is>
+          <t>reglas-bloque</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30.75" customHeight="1" s="52">
       <c r="A105" s="67" t="inlineStr">
         <is>
-          <t>Regla de gimnasio [LÓGICA], en semáforo (solo días con carga de rodilla: lunes y jueves): Retroceder si pasas de 3/10 durante o la mañana siguiente estás peor que la de la sesión; Mantener si cumple, pero el peor valor entre 24 y 48 h supera la referencia (no avanzas, pero no has fallado); Avanzar si cumple y el peor valor 24-48 h es igual o mejor que la referencia. Los días sin carga de rodilla no se evalúan («—»).</t>
+          <t>Base [EVIDENCIA]: ejercicio combinado de cadera y rodilla (consensos de 2016 y 2018). Rodilla en 2 días, lunes y viernes (72-96 h entre sesiones, dentro de la ventana de 2-3 días de recuperación del tendón que describe el libro), pesado y lento en ambos; sábado sin pierna para llegar descansado a la carrera del domingo [LÓGICA].</t>
         </is>
       </c>
       <c r="B105" s="56" t="n"/>
@@ -10837,7 +10844,7 @@
     <row r="106" ht="30.75" customHeight="1" s="52">
       <c r="A106" s="67" t="inlineStr">
         <is>
-          <t>Regla de carrera [EVIDENCIA de uso], en semáforo (miércoles y domingo): Retroceder si pasas de 2/10 durante, no vuelves al nivel previo en ≤60 min o la mañana siguiente estás peor; Mantener si cumple, pero el peor valor 24-48 h supera la referencia; Avanzar si cumple y el peor valor 24-48 h ≤ referencia. El paseo de entrada se valida solo con la mañana siguiente. Se aplica también a las fases hacia el fútbol [LÓGICA].</t>
+          <t>Mediciones: cada mañana, en casa, con las mismas pruebas: test en declive y 10 subidas con la D al mismo escalón o banco. Vale la peor de las dos (el declive solo no basta: te sale 0 aunque haya molestia). Si falta la medición de la mañana, ese día no se evalúa y la primera medición disponible hace de referencia (en S2, la del martes). Se apuntan en «Seguimiento rodilla».</t>
         </is>
       </c>
       <c r="B106" s="56" t="n"/>
@@ -10851,10 +10858,10 @@
       <c r="J106" s="56" t="n"/>
       <c r="K106" s="57" t="n"/>
     </row>
-    <row r="107" ht="30.75" customHeight="1" s="52">
+    <row r="107" ht="18" customHeight="1" s="52">
       <c r="A107" s="67" t="inlineStr">
         <is>
-          <t>Novedades [LÓGICA]: una por día y validada a las 24 y 48 h antes de repetirla. Lunes: escalón o reps (prensa) · miércoles: nivel de carrera · viernes de S4: bici. Solo si esa mañana estás igual o mejor que la referencia (la mañana del mismo día de la semana anterior; en S3, la primera medición de S2), no que el día anterior: así un empeoramiento lento también salta. El calendario marca el máximo de cada semana; el nivel real sale del semáforo: Avanzar = nivel +1 (sin pasar del calendario), Mantener = el mismo, Retroceder = nivel −1. Lo validado se repite: el jueves usa la profundidad del lunes y el domingo repite el nivel del miércoles.</t>
+          <t>Regla de gimnasio [LÓGICA], en semáforo (solo días con carga de rodilla: lunes y viernes): Retroceder si pasas de 3/10 durante o la mañana siguiente estás peor que la de la sesión; Mantener si cumple, pero el peor valor entre 24 y 48 h supera la referencia (no avanzas, pero no has fallado); Avanzar si cumple y el peor valor 24-48 h es igual o mejor que la referencia. Los días sin carga de rodilla no se evalúan («—»).</t>
         </is>
       </c>
       <c r="B107" s="56" t="n"/>
@@ -10868,10 +10875,10 @@
       <c r="J107" s="56" t="n"/>
       <c r="K107" s="57" t="n"/>
     </row>
-    <row r="108" ht="18" customHeight="1" s="52">
+    <row r="108" ht="30.75" customHeight="1" s="52">
       <c r="A108" s="67" t="inlineStr">
         <is>
-          <t>S2 = semana de referencia [LÓGICA]: el paseo del martes no cuenta como novedad (caminas a diario). Si alguna mañana de S2 sale peor que la referencia (la primera medición de S2), en S3 no sube nada y se repite S2 entera, en lugar de intentar atribuir el empeoramiento.</t>
+          <t>Regla de carrera [EVIDENCIA de uso], en semáforo (miércoles y domingo): Retroceder si pasas de 2/10 durante, no vuelves al nivel previo en ≤60 min o la mañana siguiente estás peor; Mantener si cumple, pero el peor valor 24-48 h supera la referencia; Avanzar si cumple y el peor valor 24-48 h ≤ referencia. El paseo de entrada se valida solo con la mañana siguiente. Se aplica también a las fases hacia el fútbol [LÓGICA].</t>
         </is>
       </c>
       <c r="B108" s="56" t="n"/>
@@ -10885,10 +10892,10 @@
       <c r="J108" s="56" t="n"/>
       <c r="K108" s="57" t="n"/>
     </row>
-    <row r="109" ht="43.5" customHeight="1" s="52">
+    <row r="109" ht="30.75" customHeight="1" s="52">
       <c r="A109" s="67" t="inlineStr">
         <is>
-          <t>Escalones de profundidad de la D [LÓGICA; no hay pautas de rango validadas para la rótula: INCERTIDUMBRE]: escalón 0 = la profundidad que ya usas con la D; escalón 4 = la de la I. Reparte la diferencia en 4 partes iguales (como mucho ~15° cada una; si sale más, se termina después del bloque). Se sube, como mucho, los lunes de S3, S4, S6 y S7 en la prensa (según el semáforo); la touchdown del lunes va a la profundidad ya validada y hace de filtro. Apunta las marcas en «Seguimiento rodilla».</t>
+          <t>Novedades [LÓGICA]: una por día y validada a las 24 y 48 h antes de repetirla. Lunes: escalón o reps (prensa) · miércoles: nivel de carrera · viernes de S4: bici. Solo si esa mañana estás igual o mejor que la referencia (la mañana del mismo día de la semana anterior; en S3, la primera medición de S2), no que el día anterior: así un empeoramiento lento también salta. El calendario marca el máximo de cada semana; el nivel real sale del semáforo: Avanzar = nivel +1 (sin pasar del calendario), Mantener = el mismo, Retroceder = nivel −1. Lo validado se repite: el viernes usa la profundidad del lunes y el domingo repite el nivel del miércoles.</t>
         </is>
       </c>
       <c r="B109" s="56" t="n"/>
@@ -10905,7 +10912,7 @@
     <row r="110" ht="18" customHeight="1" s="52">
       <c r="A110" s="67" t="inlineStr">
         <is>
-          <t>Chasquido: si no duele, no se quita ni se cambia nada. Si duele, cuenta como dolor.</t>
+          <t>S2: la pierna 2 y la prueba del test pasaron al viernes 30/10 (el jueves 29 fue libre), dentro de las 48 h de la 1.ª carrera. Si la mañana del sábado 31/10 sale peor, cuenta para las dos: el domingo repites N1 y el miércoles de S3 no subes de nivel [LÓGICA].</t>
         </is>
       </c>
       <c r="B110" s="56" t="n"/>
@@ -10919,10 +10926,10 @@
       <c r="J110" s="56" t="n"/>
       <c r="K110" s="57" t="n"/>
     </row>
-    <row r="111" ht="18" customHeight="1" s="52">
+    <row r="111" ht="43.5" customHeight="1" s="52">
       <c r="A111" s="67" t="inlineStr">
         <is>
-          <t>Retroceso y brote [LÓGICA]: un dolor durante la sesión retrocede la escalera de esa sesión. Si una mañana sale peor, se retrocede la última novedad aún no validada (la que todavía no tiene en verde sus dos mañanas, 24 y 48 h; p. ej., jueves bien y viernes peor → se retrocede la carrera del miércoles y el escalón se mantiene); una novedad ya validada no se culpa. Si tras el retroceso vuelve a fallar, se retrocede la novedad anterior sin validar. Brote = un fallo sin ninguna novedad sin validar, o dos sesiones seguidas en Retroceder: lo primero que se quita es la bici; 48-72 h solo isométricos (sentadilla española 5×45 s diaria) y caminar, sin bici; luego se retoma un escalón por debajo en todo. La bici vuelve al nivel del calendario cuando lleves una semana entera en verde.</t>
+          <t>Escalones de profundidad de la D [LÓGICA; no hay pautas de rango validadas para la rótula: INCERTIDUMBRE]: escalón 0 = la profundidad que ya usas con la D; escalón 4 = la de la I. Reparte la diferencia en 4 partes iguales (como mucho ~15° cada una; si sale más, se termina después del bloque). Se sube, como mucho, los lunes de S4, S6 y S7 en la prensa (según el semáforo), y el 4.º escalón el lunes de S8 solo si S6 y S7 cumplieron la regla (si no, después del viaje); el lunes de S3 fue festivo y no hubo escalón; la touchdown del lunes va a la profundidad ya validada y hace de filtro. Apunta las marcas en «Seguimiento rodilla».</t>
         </is>
       </c>
       <c r="B111" s="56" t="n"/>
@@ -10939,7 +10946,7 @@
     <row r="112" ht="18" customHeight="1" s="52">
       <c r="A112" s="67" t="inlineStr">
         <is>
-          <t>Alarma: bloqueo real, fallos repetidos de la rodilla o hinchazón visible → se para la progresión y toca valoración clínica.</t>
+          <t>Chasquido: si no duele, no se quita ni se cambia nada. Si duele, cuenta como dolor.</t>
         </is>
       </c>
       <c r="B112" s="56" t="n"/>
@@ -10953,10 +10960,10 @@
       <c r="J112" s="56" t="n"/>
       <c r="K112" s="57" t="n"/>
     </row>
-    <row r="113" ht="30.75" customHeight="1" s="52">
+    <row r="113" ht="18" customHeight="1" s="52">
       <c r="A113" s="67" t="inlineStr">
         <is>
-          <t>AVISO S4 (fisio deportivo pendiente): se calcula al cerrar S4 (domingo 15/11) si hay al menos 5 mañanas registradas en S2 y en S4. Compara la media de las mañanas: PEOR si la de S4 supera en 0,5 o más a la de S2; MEJOR si queda 0,5 o más por debajo; si no, IGUAL. IGUAL o PEOR, o un chasquido que empieza a doler: la valoración del fisio pasa a ser prioritaria; PEOR además para la progresión [LÓGICA]. «Seguimiento rodilla» lo calcula.</t>
+          <t>Retroceso y brote [LÓGICA]: un dolor durante la sesión retrocede la escalera de esa sesión. Si una mañana sale peor, se retrocede la última novedad aún no validada (la que todavía no tiene en verde sus dos mañanas, 24 y 48 h; p. ej., en S4, sábado peor tras el viernes → se quita la bici, la novedad de ese viernes, y el escalón del lunes, ya validado, se mantiene); una novedad ya validada no se culpa. Si tras el retroceso vuelve a fallar, se retrocede la novedad anterior sin validar. Brote = un fallo sin ninguna novedad sin validar, o dos sesiones seguidas en Retroceder: lo primero que se quita es la bici; 48-72 h solo isométricos (sentadilla española 5×45 s diaria) y caminar, sin bici; luego se retoma un escalón por debajo en todo. La bici vuelve al nivel del calendario cuando lleves una semana entera en verde.</t>
         </is>
       </c>
       <c r="B113" s="56" t="n"/>
@@ -10970,10 +10977,10 @@
       <c r="J113" s="56" t="n"/>
       <c r="K113" s="57" t="n"/>
     </row>
-    <row r="114" ht="30.75" customHeight="1" s="52">
+    <row r="114" ht="18" customHeight="1" s="52">
       <c r="A114" s="67" t="inlineStr">
         <is>
-          <t>Fases hacia el fútbol, después del viaje [LÓGICA], siempre con la regla de carrera: cambios de dirección ← 30 min seguidos dos veces sin reacción y rango D = I · pliometría ← 2 semanas de cambios de dirección y 10 saltos a una pierna sin dolor · balón ← cuádriceps D ≥90% de la I en el test y pliometría media sin reacción · equipo ← 2 semanas de balón sin reacción.</t>
+          <t>Alarma: bloqueo real, fallos repetidos de la rodilla o hinchazón visible → se para la progresión y toca valoración clínica.</t>
         </is>
       </c>
       <c r="B114" s="56" t="n"/>
@@ -10987,8 +10994,40 @@
       <c r="J114" s="56" t="n"/>
       <c r="K114" s="57" t="n"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1" s="52"/>
-    <row r="116" ht="15.75" customHeight="1" s="52"/>
+    <row r="115" ht="30.75" customHeight="1" s="52">
+      <c r="A115" s="67" t="inlineStr">
+        <is>
+          <t>AVISO S4 (fisio deportivo pendiente): se calcula al cerrar S4 (domingo 15/11) si hay al menos 5 mañanas registradas en S2 y en S4. Compara la media de las mañanas: PEOR si la de S4 supera en 0,5 o más a la de S2; MEJOR si queda 0,5 o más por debajo; si no, IGUAL. IGUAL o PEOR, o un chasquido que empieza a doler: la valoración del fisio pasa a ser prioritaria; PEOR además para la progresión [LÓGICA]. «Seguimiento rodilla» lo calcula.</t>
+        </is>
+      </c>
+      <c r="B115" s="56" t="n"/>
+      <c r="C115" s="56" t="n"/>
+      <c r="D115" s="56" t="n"/>
+      <c r="E115" s="56" t="n"/>
+      <c r="F115" s="56" t="n"/>
+      <c r="G115" s="56" t="n"/>
+      <c r="H115" s="56" t="n"/>
+      <c r="I115" s="56" t="n"/>
+      <c r="J115" s="56" t="n"/>
+      <c r="K115" s="57" t="n"/>
+    </row>
+    <row r="116" ht="30.75" customHeight="1" s="52">
+      <c r="A116" s="67" t="inlineStr">
+        <is>
+          <t>Fases hacia el fútbol, después del viaje [LÓGICA], siempre con la regla de carrera: cambios de dirección ← 30 min seguidos dos veces sin reacción y rango D = I · pliometría ← 2 semanas de cambios de dirección y 10 saltos a una pierna sin dolor · balón ← cuádriceps D ≥90% de la I en el test y pliometría media sin reacción · equipo ← 2 semanas de balón sin reacción.</t>
+        </is>
+      </c>
+      <c r="B116" s="56" t="n"/>
+      <c r="C116" s="56" t="n"/>
+      <c r="D116" s="56" t="n"/>
+      <c r="E116" s="56" t="n"/>
+      <c r="F116" s="56" t="n"/>
+      <c r="G116" s="56" t="n"/>
+      <c r="H116" s="56" t="n"/>
+      <c r="I116" s="56" t="n"/>
+      <c r="J116" s="56" t="n"/>
+      <c r="K116" s="57" t="n"/>
+    </row>
     <row r="117" ht="15.75" customHeight="1" s="52"/>
     <row r="118" ht="15.75" customHeight="1" s="52"/>
     <row r="119" ht="15.75" customHeight="1" s="52"/>
@@ -11882,42 +11921,46 @@
     <row r="1007" ht="15.75" customHeight="1" s="52"/>
     <row r="1008" ht="15.75" customHeight="1" s="52"/>
     <row r="1009" ht="15.75" customHeight="1" s="52"/>
-    <row r="1010" ht="15" customHeight="1" s="52"/>
-    <row r="1011" ht="15" customHeight="1" s="52"/>
+    <row r="1010" ht="15.75" customHeight="1" s="52"/>
+    <row r="1011" ht="15.75" customHeight="1" s="52"/>
     <row r="1012" ht="15" customHeight="1" s="52"/>
     <row r="1013" ht="15" customHeight="1" s="52"/>
     <row r="1014" ht="15" customHeight="1" s="52"/>
     <row r="1015" ht="15" customHeight="1" s="52"/>
+    <row r="1016" ht="15" customHeight="1" s="52"/>
+    <row r="1017" ht="15" customHeight="1" s="52"/>
+    <row r="1018" s="52"/>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
+    <mergeCell ref="A58:K58"/>
     <mergeCell ref="A114:K114"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A39:K39"/>
     <mergeCell ref="A107:K107"/>
-    <mergeCell ref="A94:K94"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A70:K70"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A103:K103"/>
     <mergeCell ref="A110:K110"/>
+    <mergeCell ref="A88:K88"/>
     <mergeCell ref="A69:K69"/>
-    <mergeCell ref="A65:K65"/>
     <mergeCell ref="A108:K108"/>
-    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A27:K27"/>
     <mergeCell ref="A105:K105"/>
-    <mergeCell ref="A86:K86"/>
+    <mergeCell ref="A74:K74"/>
+    <mergeCell ref="A50:K50"/>
     <mergeCell ref="A104:K104"/>
     <mergeCell ref="A113:K113"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="A116:K116"/>
+    <mergeCell ref="A17:K17"/>
     <mergeCell ref="A106:K106"/>
     <mergeCell ref="A67:K67"/>
     <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A96:K96"/>
+    <mergeCell ref="A72:K72"/>
     <mergeCell ref="A109:K109"/>
-    <mergeCell ref="A72:K72"/>
+    <mergeCell ref="A29:K29"/>
     <mergeCell ref="A112:K112"/>
-    <mergeCell ref="A68:K68"/>
-    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="A115:K115"/>
     <mergeCell ref="A111:K111"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -12298,17 +12341,17 @@
       </c>
       <c r="D8" s="88" t="inlineStr">
         <is>
-          <t>Test + rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo</t>
+          <t>Libre (la sesión pasó al viernes)</t>
         </is>
       </c>
       <c r="E8" s="89" t="inlineStr">
         <is>
-          <t>Gimnasio (≤3/10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="90" t="inlineStr">
         <is>
-          <t>Test de fuerza 1 (nuevo)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="91" t="n"/>
@@ -12354,17 +12397,17 @@
       </c>
       <c r="D9" s="88" t="inlineStr">
         <is>
-          <t>Torso</t>
+          <t>Prueba del test + rehab: sentadilla (con goma en las rodillas) + búlgara (pesado) + abducción · isquio/aductor/gemelo</t>
         </is>
       </c>
       <c r="E9" s="89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gimnasio (≤3/10)</t>
         </is>
       </c>
       <c r="F9" s="90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Prueba del test de fuerza + sentadilla con goma</t>
         </is>
       </c>
       <c r="G9" s="91" t="n"/>
@@ -12410,7 +12453,7 @@
       </c>
       <c r="D10" s="88" t="inlineStr">
         <is>
-          <t>Hombro/codo + abdominales (sin pierna)</t>
+          <t>Torso del viernes en casa (peso libre) + hombro/codo + abdominales (sin pierna)</t>
         </is>
       </c>
       <c r="E10" s="89" t="inlineStr">
@@ -12522,7 +12565,7 @@
       </c>
       <c r="D12" s="98" t="inlineStr">
         <is>
-          <t>Rehab: touchdown + prensa (pesado) + abducción · laterales/gemelo/isquio</t>
+          <t>En casa (festivo): touchdown + búlgara (pesado, escalón 0) + abducción con goma · laterales/gemelo/PM rumano · espalda</t>
         </is>
       </c>
       <c r="E12" s="99" t="inlineStr">
@@ -12532,7 +12575,7 @@
       </c>
       <c r="F12" s="100" t="inlineStr">
         <is>
-          <t>Escalón +1 (prensa)</t>
+          <t>ninguna (festivo, en casa)</t>
         </is>
       </c>
       <c r="G12" s="91" t="n"/>
@@ -12634,7 +12677,7 @@
       </c>
       <c r="D14" s="98" t="inlineStr">
         <is>
-          <t>Pull + carrera</t>
+          <t>Carrera (sin gimnasio)</t>
         </is>
       </c>
       <c r="E14" s="99" t="inlineStr">
@@ -12690,12 +12733,12 @@
       </c>
       <c r="D15" s="98" t="inlineStr">
         <is>
-          <t>rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo</t>
+          <t>Pull</t>
         </is>
       </c>
       <c r="E15" s="99" t="inlineStr">
         <is>
-          <t>Gimnasio (≤3/10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="100" t="inlineStr">
@@ -12746,17 +12789,17 @@
       </c>
       <c r="D16" s="98" t="inlineStr">
         <is>
-          <t>Torso</t>
+          <t>Test + rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo</t>
         </is>
       </c>
       <c r="E16" s="99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gimnasio (≤3/10)</t>
         </is>
       </c>
       <c r="F16" s="100" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Test de fuerza 1</t>
         </is>
       </c>
       <c r="G16" s="91" t="n"/>
@@ -12802,7 +12845,7 @@
       </c>
       <c r="D17" s="98" t="inlineStr">
         <is>
-          <t>Hombro/codo + abdominales (sin pierna)</t>
+          <t>Torso en casa (peso libre) + hombro/codo + abdominales (sin pierna)</t>
         </is>
       </c>
       <c r="E17" s="99" t="inlineStr">
@@ -12914,7 +12957,7 @@
       </c>
       <c r="D19" s="88" t="inlineStr">
         <is>
-          <t>Rehab: touchdown + prensa (pesado) + abducción · laterales/gemelo/isquio</t>
+          <t>Rehab: touchdown + prensa (pesado) + abducción · laterales/gemelo/isquio · espalda</t>
         </is>
       </c>
       <c r="E19" s="89" t="inlineStr">
@@ -13026,7 +13069,7 @@
       </c>
       <c r="D21" s="88" t="inlineStr">
         <is>
-          <t>Pull + carrera</t>
+          <t>Carrera (sin gimnasio)</t>
         </is>
       </c>
       <c r="E21" s="89" t="inlineStr">
@@ -13082,12 +13125,12 @@
       </c>
       <c r="D22" s="88" t="inlineStr">
         <is>
-          <t>rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo</t>
+          <t>Pull</t>
         </is>
       </c>
       <c r="E22" s="89" t="inlineStr">
         <is>
-          <t>Gimnasio (≤3/10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="90" t="inlineStr">
@@ -13138,12 +13181,12 @@
       </c>
       <c r="D23" s="88" t="inlineStr">
         <is>
-          <t>Torso + bici 10' Z2 (1.ª vez)</t>
+          <t>rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo + bici 10' Z2 (1.ª vez)</t>
         </is>
       </c>
       <c r="E23" s="89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gimnasio (≤3/10)</t>
         </is>
       </c>
       <c r="F23" s="90" t="inlineStr">
@@ -13194,7 +13237,7 @@
       </c>
       <c r="D24" s="88" t="inlineStr">
         <is>
-          <t>Hombro/codo + abdominales (sin pierna)</t>
+          <t>Torso en casa (peso libre) + hombro/codo + abdominales (sin pierna)</t>
         </is>
       </c>
       <c r="E24" s="89" t="inlineStr">
@@ -13306,7 +13349,7 @@
       </c>
       <c r="D26" s="98" t="inlineStr">
         <is>
-          <t>Rehab: touchdown + prensa (pesado) + abducción · laterales/gemelo/isquio</t>
+          <t>Rehab: touchdown + prensa (pesado) + abducción · laterales/gemelo/isquio · espalda</t>
         </is>
       </c>
       <c r="E26" s="99" t="inlineStr">
@@ -13418,7 +13461,7 @@
       </c>
       <c r="D28" s="98" t="inlineStr">
         <is>
-          <t>Pull + carrera</t>
+          <t>Carrera (sin gimnasio)</t>
         </is>
       </c>
       <c r="E28" s="99" t="inlineStr">
@@ -13474,17 +13517,17 @@
       </c>
       <c r="D29" s="98" t="inlineStr">
         <is>
-          <t>Test + rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo</t>
+          <t>Pull</t>
         </is>
       </c>
       <c r="E29" s="99" t="inlineStr">
         <is>
-          <t>Gimnasio (≤3/10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="100" t="inlineStr">
         <is>
-          <t>— (test 2, repetido)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="91" t="n"/>
@@ -13530,17 +13573,17 @@
       </c>
       <c r="D30" s="98" t="inlineStr">
         <is>
-          <t>Torso + bici 10' Z2</t>
+          <t>Test + rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo + bici 10' Z2</t>
         </is>
       </c>
       <c r="E30" s="99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gimnasio (≤3/10)</t>
         </is>
       </c>
       <c r="F30" s="100" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>— (test 2, repetido)</t>
         </is>
       </c>
       <c r="G30" s="91" t="n"/>
@@ -13586,7 +13629,7 @@
       </c>
       <c r="D31" s="98" t="inlineStr">
         <is>
-          <t>Hombro/codo + abdominales (sin pierna)</t>
+          <t>Torso en casa (peso libre) + hombro/codo + abdominales (sin pierna)</t>
         </is>
       </c>
       <c r="E31" s="99" t="inlineStr">
@@ -13698,7 +13741,7 @@
       </c>
       <c r="D33" s="88" t="inlineStr">
         <is>
-          <t>Rehab: touchdown + prensa (pesado) + abducción · laterales/gemelo/isquio</t>
+          <t>Rehab: touchdown + prensa (pesado) + abducción · laterales/gemelo/isquio · espalda</t>
         </is>
       </c>
       <c r="E33" s="89" t="inlineStr">
@@ -13810,7 +13853,7 @@
       </c>
       <c r="D35" s="88" t="inlineStr">
         <is>
-          <t>Pull + carrera</t>
+          <t>Carrera (sin gimnasio)</t>
         </is>
       </c>
       <c r="E35" s="89" t="inlineStr">
@@ -13866,12 +13909,12 @@
       </c>
       <c r="D36" s="88" t="inlineStr">
         <is>
-          <t>rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo</t>
+          <t>Pull</t>
         </is>
       </c>
       <c r="E36" s="89" t="inlineStr">
         <is>
-          <t>Gimnasio (≤3/10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="90" t="inlineStr">
@@ -13922,12 +13965,12 @@
       </c>
       <c r="D37" s="88" t="inlineStr">
         <is>
-          <t>Torso + bici 10' Z2</t>
+          <t>rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo + bici 10' Z2</t>
         </is>
       </c>
       <c r="E37" s="89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gimnasio (≤3/10)</t>
         </is>
       </c>
       <c r="F37" s="90" t="inlineStr">
@@ -13978,7 +14021,7 @@
       </c>
       <c r="D38" s="88" t="inlineStr">
         <is>
-          <t>Hombro/codo + abdominales (sin pierna)</t>
+          <t>Torso en casa (peso libre) + hombro/codo + abdominales (sin pierna)</t>
         </is>
       </c>
       <c r="E38" s="89" t="inlineStr">
@@ -14090,7 +14133,7 @@
       </c>
       <c r="D40" s="98" t="inlineStr">
         <is>
-          <t>Rehab: touchdown + prensa (pesado) + abducción · laterales/gemelo/isquio</t>
+          <t>Rehab: touchdown + prensa (pesado) + abducción · laterales/gemelo/isquio · espalda</t>
         </is>
       </c>
       <c r="E40" s="99" t="inlineStr">
@@ -14202,7 +14245,7 @@
       </c>
       <c r="D42" s="98" t="inlineStr">
         <is>
-          <t>Pull + carrera</t>
+          <t>Carrera (sin gimnasio)</t>
         </is>
       </c>
       <c r="E42" s="99" t="inlineStr">
@@ -14258,17 +14301,17 @@
       </c>
       <c r="D43" s="98" t="inlineStr">
         <is>
-          <t>Test + rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo</t>
+          <t>Pull</t>
         </is>
       </c>
       <c r="E43" s="99" t="inlineStr">
         <is>
-          <t>Gimnasio (≤3/10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="100" t="inlineStr">
         <is>
-          <t>— (test 3, repetido)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="91" t="n"/>
@@ -14314,17 +14357,17 @@
       </c>
       <c r="D44" s="98" t="inlineStr">
         <is>
-          <t>Torso + bici 10' Z2</t>
+          <t>Test + rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo + bici 10' Z2</t>
         </is>
       </c>
       <c r="E44" s="99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gimnasio (≤3/10)</t>
         </is>
       </c>
       <c r="F44" s="100" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>— (test 3, repetido)</t>
         </is>
       </c>
       <c r="G44" s="91" t="n"/>
@@ -14370,7 +14413,7 @@
       </c>
       <c r="D45" s="98" t="inlineStr">
         <is>
-          <t>Hombro/codo + abdominales (sin pierna)</t>
+          <t>Torso en casa (peso libre) + hombro/codo + abdominales (sin pierna)</t>
         </is>
       </c>
       <c r="E45" s="99" t="inlineStr">
@@ -14482,7 +14525,7 @@
       </c>
       <c r="D47" s="88" t="inlineStr">
         <is>
-          <t>Rehab: touchdown + prensa (pesado) + abducción · laterales/gemelo/isquio</t>
+          <t>Rehab: touchdown + prensa (pesado) + abducción · laterales/gemelo/isquio · espalda</t>
         </is>
       </c>
       <c r="E47" s="89" t="inlineStr">
@@ -14492,7 +14535,7 @@
       </c>
       <c r="F47" s="90" t="inlineStr">
         <is>
-          <t>ninguna (repite S7)</t>
+          <t>Escalón +1 (4.º) solo si S6-S7 cumplieron; si no, ninguna</t>
         </is>
       </c>
       <c r="G47" s="91" t="n"/>
@@ -14594,7 +14637,7 @@
       </c>
       <c r="D49" s="88" t="inlineStr">
         <is>
-          <t>Pull + carrera</t>
+          <t>Carrera (sin gimnasio)</t>
         </is>
       </c>
       <c r="E49" s="89" t="inlineStr">
@@ -14650,17 +14693,17 @@
       </c>
       <c r="D50" s="88" t="inlineStr">
         <is>
-          <t>rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo</t>
+          <t>Pull</t>
         </is>
       </c>
       <c r="E50" s="89" t="inlineStr">
         <is>
-          <t>Gimnasio (≤3/10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="90" t="inlineStr">
         <is>
-          <t>Test opcional rango completo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G50" s="91" t="n"/>
@@ -14706,17 +14749,17 @@
       </c>
       <c r="D51" s="88" t="inlineStr">
         <is>
-          <t>Torso + bici 10' Z2</t>
+          <t>rehab: sentadilla + búlgara (pesado) + abducción · isquio/aductor/gemelo + bici 10' Z2</t>
         </is>
       </c>
       <c r="E51" s="89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gimnasio (≤3/10)</t>
         </is>
       </c>
       <c r="F51" s="90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Test opcional rango completo</t>
         </is>
       </c>
       <c r="G51" s="91" t="n"/>
@@ -14762,7 +14805,7 @@
       </c>
       <c r="D52" s="88" t="inlineStr">
         <is>
-          <t>Hombro/codo + abdominales (sin pierna)</t>
+          <t>Torso en casa (peso libre) + hombro/codo + abdominales (sin pierna)</t>
         </is>
       </c>
       <c r="E52" s="89" t="inlineStr">
@@ -15266,7 +15309,7 @@
       </c>
       <c r="D61" s="88" t="inlineStr">
         <is>
-          <t>Vuelta: touchdown + prensa x8 al ~80% del peso de S8</t>
+          <t>Vuelta: touchdown + prensa x8 al ~80% del peso de S8 · espalda</t>
         </is>
       </c>
       <c r="E61" s="89" t="inlineStr">
@@ -15378,7 +15421,7 @@
       </c>
       <c r="D63" s="88" t="inlineStr">
         <is>
-          <t>Pull + carrera (nivel S8 o uno menos)</t>
+          <t>Carrera (nivel S8 o uno menos), sin gimnasio</t>
         </is>
       </c>
       <c r="E63" s="89" t="inlineStr">
@@ -15434,12 +15477,12 @@
       </c>
       <c r="D64" s="88" t="inlineStr">
         <is>
-          <t>Vuelta: sentadilla/búlgara x8 al ~80% + abducción</t>
+          <t>Pull</t>
         </is>
       </c>
       <c r="E64" s="89" t="inlineStr">
         <is>
-          <t>Gimnasio (≤3/10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F64" s="90" t="inlineStr">
@@ -15490,12 +15533,12 @@
       </c>
       <c r="D65" s="88" t="inlineStr">
         <is>
-          <t>Torso + bici 10' Z2</t>
+          <t>Vuelta: sentadilla/búlgara x8 al ~80% + abducción + bici 10' Z2</t>
         </is>
       </c>
       <c r="E65" s="89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gimnasio (≤3/10)</t>
         </is>
       </c>
       <c r="F65" s="90" t="inlineStr">
@@ -15546,7 +15589,7 @@
       </c>
       <c r="D66" s="88" t="inlineStr">
         <is>
-          <t>Hombro/codo + abdominales (sin pierna)</t>
+          <t>Torso en casa (peso libre) + hombro/codo + abdominales (sin pierna)</t>
         </is>
       </c>
       <c r="E66" s="89" t="inlineStr">
@@ -16392,7 +16435,7 @@
     <row r="95" ht="19.5" customHeight="1" s="52">
       <c r="A95" s="65" t="inlineStr">
         <is>
-          <t>Test de fuerza · extensión unilateral en máquina, rango fijo 90→45° (jueves, al empezar la sesión)</t>
+          <t>Test de fuerza · extensión unilateral en máquina, rango fijo 90→45° (viernes, al empezar la sesión)</t>
         </is>
       </c>
       <c r="B95" s="56" t="n"/>
@@ -16483,13 +16526,13 @@
     <row r="97" ht="15" customHeight="1" s="52">
       <c r="A97" s="101" t="inlineStr">
         <is>
-          <t>Test 1 (S2)</t>
+          <t>Test 1 (S3)</t>
         </is>
       </c>
       <c r="B97" s="56" t="n"/>
       <c r="C97" s="57" t="n"/>
       <c r="D97" s="85" t="n">
-        <v>46324</v>
+        <v>46332</v>
       </c>
       <c r="E97" s="87" t="inlineStr">
         <is>
@@ -16515,7 +16558,11 @@
         <f>IF(K97="","",IF(K97&gt;=0.9,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="M97" s="91" t="n"/>
+      <c r="M97" s="91" t="inlineStr">
+        <is>
+          <t>Test 1 real: vie 6/11 (en S2 no se hizo: analítica)</t>
+        </is>
+      </c>
       <c r="N97" s="56" t="n"/>
       <c r="O97" s="56" t="n"/>
       <c r="P97" s="56" t="n"/>
@@ -16535,7 +16582,7 @@
       <c r="B98" s="56" t="n"/>
       <c r="C98" s="57" t="n"/>
       <c r="D98" s="85" t="n">
-        <v>46345</v>
+        <v>46346</v>
       </c>
       <c r="E98" s="87" t="inlineStr">
         <is>
@@ -16581,7 +16628,7 @@
       <c r="B99" s="56" t="n"/>
       <c r="C99" s="57" t="n"/>
       <c r="D99" s="85" t="n">
-        <v>46359</v>
+        <v>46360</v>
       </c>
       <c r="E99" s="87" t="inlineStr">
         <is>
@@ -16627,7 +16674,7 @@
       <c r="B100" s="56" t="n"/>
       <c r="C100" s="57" t="n"/>
       <c r="D100" s="85" t="n">
-        <v>46366</v>
+        <v>46367</v>
       </c>
       <c r="E100" s="87" t="inlineStr">
         <is>
@@ -16915,7 +16962,7 @@
     <row r="110" ht="39.75" customHeight="1" s="52">
       <c r="A110" s="73" t="inlineStr">
         <is>
-          <t>Reparte la diferencia entre la D y la I en 4 partes iguales (como mucho ~15° cada una; si sale más, se termina después del bloque). El ángulo se puede medir con una app de goniómetro. Se sube solo los lunes de S3, S4, S6 y S7, en la prensa y si esa mañana estás igual o mejor [LÓGICA]. La touchdown del lunes va a la profundidad ya validada (la de la semana anterior) y hace de filtro; el jueves usa la profundidad nueva validada el lunes.</t>
+          <t>Reparte la diferencia entre la D y la I en 4 partes iguales (como mucho ~15° cada una; si sale más, se termina después del bloque). El ángulo se puede medir con una app de goniómetro. Se sube solo los lunes de S4, S6 y S7 (el 4.º escalón, el lunes de S8 si S6-S7 cumplieron; si no, después del viaje), en la prensa y si esa mañana estás igual o mejor [LÓGICA]. La touchdown del lunes va a la profundidad ya validada (la de la semana anterior) y hace de filtro; el viernes usa la profundidad nueva validada el lunes.</t>
         </is>
       </c>
       <c r="B110" s="56" t="n"/>

--- a/Plan_8sem_vol_definitivo_con_cardio.xlsx
+++ b/Plan_8sem_vol_definitivo_con_cardio.xlsx
@@ -7904,7 +7904,7 @@
     <row r="39" ht="19.5" customHeight="1" s="52">
       <c r="A39" s="65" t="inlineStr">
         <is>
-          <t>(V) Viernes  ·  Rehab + Isquios + Aductores  ·  test de fuerza S3 / S5 / S7 (+ opcional S8)  (desde S3; S1-S2 se hizo el jueves)</t>
+          <t>(V) Viernes  ·  Rehab + Isquios + Aductores  ·  test de fuerza S3 / S5 / S7 (+ opcional S8)  (desde S2; S1 se hizo el jueves; en S2, el viernes 30/10)</t>
         </is>
       </c>
       <c r="B39" s="56" t="n"/>
@@ -7919,7 +7919,7 @@
       <c r="K39" s="57" t="n"/>
       <c r="L39" s="106" t="inlineStr">
         <is>
-          <t>sesion;S1=J;S2=J</t>
+          <t>sesion;S1=J</t>
         </is>
       </c>
     </row>
